--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5937B94C-DF71-485F-AA68-22D953DB36C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA89746-7FDA-4655-8BA9-E9CCA8B3EC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$649</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$767</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="114">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>Cycles: 3</t>
   </si>
   <si>
+    <t>Store as Address.</t>
+  </si>
+  <si>
     <t>ORA (05)</t>
   </si>
   <si>
@@ -116,6 +119,12 @@
     <t>Cycles: 4</t>
   </si>
   <si>
+    <t>Store as Address.L.</t>
+  </si>
+  <si>
+    <t>Absolute (Read/Modify/Write)</t>
+  </si>
+  <si>
     <t>Store as Pointer.</t>
   </si>
   <si>
@@ -2114,6 +2123,180 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> based off Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>PHD (0B)</t>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>TSB (0C)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read Address:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read Address + 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to Address + 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to Address:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
     </r>
   </si>
 </sst>
@@ -2138,7 +2321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2166,6 +2349,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2286,7 +2481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2330,6 +2525,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2339,19 +2535,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2686,7 +2883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="B1:E602"/>
+  <dimension ref="B1:E731"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4.7109375" customWidth="1"/>
@@ -2722,18 +2919,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2742,7 +2939,7 @@
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2750,7 +2947,7 @@
         <v>1.2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>10</v>
@@ -2762,7 +2959,7 @@
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2770,10 +2967,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2788,10 +2985,10 @@
         <v>3.2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2806,10 +3003,10 @@
         <v>4.2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2818,35 +3015,35 @@
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
       <c r="E14" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="8"/>
       <c r="D16" s="9"/>
       <c r="E16" s="15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="8"/>
       <c r="D17" s="9"/>
       <c r="E17" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2854,10 +3051,10 @@
         <v>5.2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2866,7 +3063,7 @@
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2874,7 +3071,7 @@
         <v>6.2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>12</v>
@@ -2886,7 +3083,7 @@
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2894,7 +3091,7 @@
         <v>7.2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>13</v>
@@ -2905,86 +3102,86 @@
         <v>8.1</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="20" t="s">
-        <v>64</v>
+      <c r="E23" s="21" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="11"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="8">
         <v>8.1999999999999993</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="24"/>
+      <c r="C26" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
     </row>
     <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
     </row>
     <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
     </row>
     <row r="30" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
     </row>
     <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
     </row>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
     </row>
     <row r="33" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
     </row>
     <row r="34" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
+      <c r="B34" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
     </row>
     <row r="35" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
+      <c r="B35" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
     </row>
     <row r="60" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="1" t="s">
@@ -3000,7 +3197,7 @@
     <row r="61" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="4"/>
       <c r="D61" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E61" s="6"/>
     </row>
@@ -3012,15 +3209,15 @@
         <v>4</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>9</v>
@@ -3032,7 +3229,7 @@
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3040,10 +3237,10 @@
         <v>1.2</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3052,7 +3249,7 @@
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3061,7 +3258,7 @@
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3069,8 +3266,8 @@
         <v>3.1</v>
       </c>
       <c r="D68" s="17"/>
-      <c r="E68" s="26" t="s">
-        <v>35</v>
+      <c r="E68" s="27" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3078,7 +3275,7 @@
         <v>3.2</v>
       </c>
       <c r="D69" s="17"/>
-      <c r="E69" s="26"/>
+      <c r="E69" s="27"/>
     </row>
     <row r="70" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="8">
@@ -3095,7 +3292,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3110,10 +3307,10 @@
         <v>5.2</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3124,14 +3321,14 @@
       <c r="E74" s="15"/>
     </row>
     <row r="75" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="8">
+      <c r="C75" s="19">
         <v>6.2</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3142,14 +3339,14 @@
       <c r="E76" s="18"/>
     </row>
     <row r="77" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C77" s="16">
+      <c r="C77" s="28">
         <v>7.2</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3157,41 +3354,41 @@
         <v>8.1</v>
       </c>
       <c r="D78" s="9"/>
-      <c r="E78" s="20" t="s">
-        <v>95</v>
+      <c r="E78" s="21" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="8"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="20"/>
+      <c r="E79" s="21"/>
     </row>
     <row r="80" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="8"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="20"/>
+      <c r="E80" s="21"/>
     </row>
     <row r="81" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="8">
         <v>8.1999999999999993</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E81" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C82" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D82" s="23"/>
-      <c r="E82" s="25"/>
+      <c r="C82" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D82" s="24"/>
+      <c r="E82" s="26"/>
     </row>
     <row r="119" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>15</v>
@@ -3215,15 +3412,15 @@
         <v>4</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E122" s="12" t="s">
         <v>9</v>
@@ -3235,7 +3432,7 @@
       </c>
       <c r="D123" s="9"/>
       <c r="E123" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="124" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3243,7 +3440,7 @@
         <v>1.2</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>10</v>
@@ -3255,7 +3452,7 @@
       </c>
       <c r="D125" s="9"/>
       <c r="E125" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="126" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3263,10 +3460,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3275,7 +3472,7 @@
       </c>
       <c r="D127" s="9"/>
       <c r="E127" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="128" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3283,10 +3480,10 @@
         <v>3.2</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3301,10 +3498,10 @@
         <v>4.2</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3313,7 +3510,7 @@
       </c>
       <c r="D131" s="9"/>
       <c r="E131" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3321,10 +3518,10 @@
         <v>5.2</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3333,7 +3530,7 @@
       </c>
       <c r="D133" s="9"/>
       <c r="E133" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3341,7 +3538,7 @@
         <v>6.2</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E134" s="15" t="s">
         <v>12</v>
@@ -3353,15 +3550,15 @@
       </c>
       <c r="D135" s="9"/>
       <c r="E135" s="15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="8">
+      <c r="C136" s="19">
         <v>7.2</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E136" s="15" t="s">
         <v>13</v>
@@ -3372,85 +3569,85 @@
         <v>8.1</v>
       </c>
       <c r="D137" s="9"/>
-      <c r="E137" s="20" t="s">
-        <v>64</v>
+      <c r="E137" s="21" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="138" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="8"/>
       <c r="D138" s="9"/>
-      <c r="E138" s="20"/>
+      <c r="E138" s="21"/>
     </row>
     <row r="139" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C139" s="8">
         <v>8.1999999999999993</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E139" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="140" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C140" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D140" s="23"/>
-      <c r="E140" s="25"/>
+      <c r="C140" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D140" s="24"/>
+      <c r="E140" s="26"/>
     </row>
     <row r="142" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="21" t="s">
+      <c r="B142" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C142" s="21"/>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
+      <c r="C142" s="22"/>
+      <c r="D142" s="22"/>
+      <c r="E142" s="22"/>
     </row>
     <row r="143" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="21"/>
-      <c r="C143" s="21"/>
-      <c r="D143" s="21"/>
-      <c r="E143" s="21"/>
+      <c r="B143" s="22"/>
+      <c r="C143" s="22"/>
+      <c r="D143" s="22"/>
+      <c r="E143" s="22"/>
     </row>
     <row r="144" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="21"/>
-      <c r="C144" s="21"/>
-      <c r="D144" s="21"/>
-      <c r="E144" s="21"/>
+      <c r="B144" s="22"/>
+      <c r="C144" s="22"/>
+      <c r="D144" s="22"/>
+      <c r="E144" s="22"/>
     </row>
     <row r="145" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="21"/>
-      <c r="C145" s="21"/>
-      <c r="D145" s="21"/>
-      <c r="E145" s="21"/>
+      <c r="B145" s="22"/>
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
     </row>
     <row r="146" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="21"/>
-      <c r="C146" s="21"/>
-      <c r="D146" s="21"/>
-      <c r="E146" s="21"/>
+      <c r="B146" s="22"/>
+      <c r="C146" s="22"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="22"/>
     </row>
     <row r="147" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="21"/>
-      <c r="C147" s="21"/>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
+      <c r="B147" s="22"/>
+      <c r="C147" s="22"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="22"/>
     </row>
     <row r="148" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C148" s="21"/>
-      <c r="D148" s="21"/>
-      <c r="E148" s="21"/>
+      <c r="B148" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C148" s="22"/>
+      <c r="D148" s="22"/>
+      <c r="E148" s="22"/>
     </row>
     <row r="178" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C178" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>8</v>
@@ -3459,7 +3656,7 @@
     <row r="179" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C179" s="4"/>
       <c r="D179" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E179" s="6"/>
     </row>
@@ -3471,15 +3668,15 @@
         <v>4</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="181" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C181" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E181" s="12" t="s">
         <v>9</v>
@@ -3491,7 +3688,7 @@
       </c>
       <c r="D182" s="9"/>
       <c r="E182" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="183" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3499,10 +3696,10 @@
         <v>1.2</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="184" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3511,7 +3708,7 @@
       </c>
       <c r="D184" s="9"/>
       <c r="E184" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="185" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3529,14 +3726,14 @@
       <c r="E186" s="10"/>
     </row>
     <row r="187" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C187" s="8">
+      <c r="C187" s="19">
         <v>3.2</v>
       </c>
       <c r="D187" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3547,14 +3744,14 @@
       <c r="E188" s="18"/>
     </row>
     <row r="189" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C189" s="16">
+      <c r="C189" s="28">
         <v>4.2</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E189" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3562,44 +3759,44 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D190" s="9"/>
-      <c r="E190" s="20" t="s">
-        <v>95</v>
+      <c r="E190" s="21" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="191" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C191" s="8"/>
       <c r="D191" s="9"/>
-      <c r="E191" s="20"/>
+      <c r="E191" s="21"/>
     </row>
     <row r="192" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C192" s="8"/>
       <c r="D192" s="9"/>
-      <c r="E192" s="20"/>
+      <c r="E192" s="21"/>
     </row>
     <row r="193" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C193" s="8">
         <v>5.2</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E193" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="194" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C194" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D194" s="23"/>
-      <c r="E194" s="25"/>
+      <c r="C194" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D194" s="24"/>
+      <c r="E194" s="26"/>
     </row>
     <row r="237" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C237" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>8</v>
@@ -3608,7 +3805,7 @@
     <row r="238" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C238" s="4"/>
       <c r="D238" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E238" s="6"/>
     </row>
@@ -3620,15 +3817,15 @@
         <v>4</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="240" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C240" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E240" s="12" t="s">
         <v>9</v>
@@ -3640,7 +3837,7 @@
       </c>
       <c r="D241" s="9"/>
       <c r="E241" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="242" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3648,10 +3845,10 @@
         <v>1.2</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E242" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="243" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3659,8 +3856,8 @@
         <v>2.1</v>
       </c>
       <c r="D243" s="17"/>
-      <c r="E243" s="26" t="s">
-        <v>60</v>
+      <c r="E243" s="27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="244" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3668,21 +3865,21 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D244" s="17"/>
-      <c r="E244" s="26"/>
+      <c r="E244" s="27"/>
     </row>
     <row r="245" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C245" s="8">
         <v>3.1</v>
       </c>
       <c r="D245" s="9"/>
-      <c r="E245" s="20" t="s">
-        <v>82</v>
+      <c r="E245" s="21" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="246" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C246" s="8"/>
       <c r="D246" s="9"/>
-      <c r="E246" s="20"/>
+      <c r="E246" s="21"/>
     </row>
     <row r="247" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C247" s="8">
@@ -3692,7 +3889,7 @@
         <v>11</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="248" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3707,10 +3904,10 @@
         <v>4.2</v>
       </c>
       <c r="D249" s="17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E249" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="250" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3718,19 +3915,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D250" s="9"/>
-      <c r="E250" s="20" t="s">
-        <v>96</v>
+      <c r="E250" s="21" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="251" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C251" s="8"/>
       <c r="D251" s="9"/>
-      <c r="E251" s="20"/>
+      <c r="E251" s="21"/>
     </row>
     <row r="252" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C252" s="8"/>
       <c r="D252" s="9"/>
-      <c r="E252" s="20"/>
+      <c r="E252" s="21"/>
     </row>
     <row r="253" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C253" s="8">
@@ -3738,7 +3935,7 @@
       </c>
       <c r="D253" s="9"/>
       <c r="E253" s="15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="254" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3753,10 +3950,10 @@
         <v>6.2</v>
       </c>
       <c r="D255" s="17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E255" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="256" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3767,14 +3964,14 @@
       <c r="E256" s="15"/>
     </row>
     <row r="257" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C257" s="8">
+      <c r="C257" s="19">
         <v>7.2</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E257" s="15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="258" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3789,22 +3986,22 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E259" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="260" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C260" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D260" s="23"/>
-      <c r="E260" s="25"/>
+      <c r="C260" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D260" s="24"/>
+      <c r="E260" s="26"/>
     </row>
     <row r="296" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C296" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>16</v>
@@ -3816,7 +4013,7 @@
     <row r="297" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C297" s="4"/>
       <c r="D297" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E297" s="6"/>
     </row>
@@ -3828,15 +4025,15 @@
         <v>4</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="299" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C299" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D299" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E299" s="12" t="s">
         <v>9</v>
@@ -3848,7 +4045,7 @@
       </c>
       <c r="D300" s="9"/>
       <c r="E300" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="301" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,10 +4053,10 @@
         <v>1.2</v>
       </c>
       <c r="D301" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="302" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3867,8 +4064,8 @@
         <v>2.1</v>
       </c>
       <c r="D302" s="17"/>
-      <c r="E302" s="26" t="s">
-        <v>60</v>
+      <c r="E302" s="27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="303" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3876,31 +4073,31 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D303" s="17"/>
-      <c r="E303" s="26"/>
+      <c r="E303" s="27"/>
     </row>
     <row r="304" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C304" s="8">
         <v>3.1</v>
       </c>
       <c r="D304" s="9"/>
-      <c r="E304" s="20" t="s">
-        <v>82</v>
+      <c r="E304" s="21" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="305" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C305" s="8"/>
       <c r="D305" s="9"/>
-      <c r="E305" s="20"/>
+      <c r="E305" s="21"/>
     </row>
     <row r="306" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C306" s="8">
+      <c r="C306" s="19">
         <v>3.2</v>
       </c>
       <c r="D306" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E306" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="307" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3908,17 +4105,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="D307" s="17"/>
-      <c r="E307" s="26"/>
+      <c r="E307" s="27"/>
     </row>
     <row r="308" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C308" s="16">
+      <c r="C308" s="28">
         <v>4.2</v>
       </c>
       <c r="D308" s="17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E308" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="309" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3926,44 +4123,44 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D309" s="9"/>
-      <c r="E309" s="20" t="s">
-        <v>95</v>
+      <c r="E309" s="21" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="310" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C310" s="8"/>
       <c r="D310" s="9"/>
-      <c r="E310" s="20"/>
+      <c r="E310" s="21"/>
     </row>
     <row r="311" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C311" s="8"/>
       <c r="D311" s="9"/>
-      <c r="E311" s="20"/>
+      <c r="E311" s="21"/>
     </row>
     <row r="312" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C312" s="8">
         <v>5.2</v>
       </c>
       <c r="D312" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E312" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="313" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C313" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D313" s="23"/>
-      <c r="E313" s="25"/>
+      <c r="C313" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D313" s="24"/>
+      <c r="E313" s="26"/>
     </row>
     <row r="355" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C355" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>8</v>
@@ -3972,7 +4169,7 @@
     <row r="356" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C356" s="4"/>
       <c r="D356" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E356" s="6"/>
     </row>
@@ -3984,15 +4181,15 @@
         <v>4</v>
       </c>
       <c r="E357" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="358" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C358" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E358" s="12" t="s">
         <v>9</v>
@@ -4004,7 +4201,7 @@
       </c>
       <c r="D359" s="9"/>
       <c r="E359" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="360" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4012,10 +4209,10 @@
         <v>1.2</v>
       </c>
       <c r="D360" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E360" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="361" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4023,8 +4220,8 @@
         <v>2.1</v>
       </c>
       <c r="D361" s="17"/>
-      <c r="E361" s="26" t="s">
-        <v>60</v>
+      <c r="E361" s="27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="362" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4032,21 +4229,21 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D362" s="17"/>
-      <c r="E362" s="26"/>
+      <c r="E362" s="27"/>
     </row>
     <row r="363" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C363" s="8">
         <v>3.1</v>
       </c>
       <c r="D363" s="9"/>
-      <c r="E363" s="20" t="s">
-        <v>82</v>
+      <c r="E363" s="21" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="364" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C364" s="8"/>
       <c r="D364" s="9"/>
-      <c r="E364" s="20"/>
+      <c r="E364" s="21"/>
     </row>
     <row r="365" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C365" s="8">
@@ -4056,7 +4253,7 @@
         <v>11</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="366" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4064,17 +4261,17 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="D366" s="17"/>
-      <c r="E366" s="26"/>
+      <c r="E366" s="27"/>
     </row>
     <row r="367" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C367" s="16">
         <v>4.2</v>
       </c>
       <c r="D367" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E367" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="E367" s="27" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="368" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4082,29 +4279,29 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D368" s="9"/>
-      <c r="E368" s="20" t="s">
-        <v>100</v>
+      <c r="E368" s="21" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="369" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C369" s="8"/>
       <c r="D369" s="9"/>
-      <c r="E369" s="20"/>
+      <c r="E369" s="21"/>
     </row>
     <row r="370" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C370" s="8"/>
       <c r="D370" s="9"/>
-      <c r="E370" s="20"/>
+      <c r="E370" s="21"/>
     </row>
     <row r="371" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C371" s="8"/>
       <c r="D371" s="9"/>
-      <c r="E371" s="20"/>
+      <c r="E371" s="21"/>
     </row>
     <row r="372" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C372" s="8"/>
       <c r="D372" s="9"/>
-      <c r="E372" s="20"/>
+      <c r="E372" s="21"/>
     </row>
     <row r="373" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C373" s="8">
@@ -4112,7 +4309,7 @@
       </c>
       <c r="D373" s="9"/>
       <c r="E373" s="15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="374" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4120,17 +4317,17 @@
         <v>6.1</v>
       </c>
       <c r="D374" s="17"/>
-      <c r="E374" s="26"/>
+      <c r="E374" s="27"/>
     </row>
     <row r="375" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C375" s="16">
         <v>6.2</v>
       </c>
       <c r="D375" s="17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E375" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="376" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4141,14 +4338,14 @@
       <c r="E376" s="10"/>
     </row>
     <row r="377" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C377" s="8">
+      <c r="C377" s="19">
         <v>7.2</v>
       </c>
       <c r="D377" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="378" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4163,22 +4360,22 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="D379" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E379" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="380" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C380" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D380" s="23"/>
-      <c r="E380" s="25"/>
+      <c r="C380" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D380" s="24"/>
+      <c r="E380" s="26"/>
     </row>
     <row r="414" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C414" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>7</v>
@@ -4190,7 +4387,7 @@
     <row r="415" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C415" s="4"/>
       <c r="D415" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E415" s="6"/>
     </row>
@@ -4202,15 +4399,15 @@
         <v>4</v>
       </c>
       <c r="E416" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="417" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C417" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D417" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E417" s="12" t="s">
         <v>9</v>
@@ -4222,7 +4419,7 @@
       </c>
       <c r="D418" s="9"/>
       <c r="E418" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="419" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4230,10 +4427,10 @@
         <v>1.2</v>
       </c>
       <c r="D419" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="420" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4241,8 +4438,8 @@
         <v>2.1</v>
       </c>
       <c r="D420" s="17"/>
-      <c r="E420" s="26" t="s">
-        <v>60</v>
+      <c r="E420" s="27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="421" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4250,21 +4447,21 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D421" s="17"/>
-      <c r="E421" s="26"/>
+      <c r="E421" s="27"/>
     </row>
     <row r="422" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C422" s="8">
         <v>3.1</v>
       </c>
       <c r="D422" s="9"/>
-      <c r="E422" s="20" t="s">
-        <v>82</v>
+      <c r="E422" s="21" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="423" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C423" s="8"/>
       <c r="D423" s="9"/>
-      <c r="E423" s="20"/>
+      <c r="E423" s="21"/>
     </row>
     <row r="424" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C424" s="8">
@@ -4274,7 +4471,7 @@
         <v>11</v>
       </c>
       <c r="E424" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="425" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4289,10 +4486,10 @@
         <v>4.2</v>
       </c>
       <c r="D426" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E426" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="427" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4307,10 +4504,10 @@
         <v>5.2</v>
       </c>
       <c r="D428" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E428" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="429" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4321,14 +4518,14 @@
       <c r="E429" s="15"/>
     </row>
     <row r="430" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C430" s="8">
+      <c r="C430" s="19">
         <v>6.2</v>
       </c>
       <c r="D430" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E430" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="431" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4339,14 +4536,14 @@
       <c r="E431" s="18"/>
     </row>
     <row r="432" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C432" s="16">
+      <c r="C432" s="28">
         <v>7.2</v>
       </c>
       <c r="D432" s="17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E432" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="433" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4354,41 +4551,41 @@
         <v>8.1</v>
       </c>
       <c r="D433" s="9"/>
-      <c r="E433" s="20" t="s">
-        <v>95</v>
+      <c r="E433" s="21" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="434" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C434" s="8"/>
       <c r="D434" s="9"/>
-      <c r="E434" s="20"/>
+      <c r="E434" s="21"/>
     </row>
     <row r="435" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C435" s="8"/>
       <c r="D435" s="9"/>
-      <c r="E435" s="20"/>
+      <c r="E435" s="21"/>
     </row>
     <row r="436" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C436" s="8">
         <v>8.1999999999999993</v>
       </c>
       <c r="D436" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E436" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="437" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C437" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D437" s="23"/>
-      <c r="E437" s="24"/>
+      <c r="C437" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D437" s="24"/>
+      <c r="E437" s="25"/>
     </row>
     <row r="473" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C473" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>16</v>
@@ -4412,15 +4609,15 @@
         <v>4</v>
       </c>
       <c r="E475" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="476" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C476" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D476" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E476" s="12" t="s">
         <v>9</v>
@@ -4432,7 +4629,7 @@
       </c>
       <c r="D477" s="9"/>
       <c r="E477" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="478" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4448,18 +4645,18 @@
       </c>
       <c r="D479" s="9"/>
       <c r="E479" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="480" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C480" s="8">
+      <c r="C480" s="19">
         <v>2.2000000000000002</v>
       </c>
       <c r="D480" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="481" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4474,34 +4671,34 @@
         <v>3.2</v>
       </c>
       <c r="D482" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E482" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="483" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C483" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D483" s="23"/>
-      <c r="E483" s="25"/>
+      <c r="C483" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D483" s="24"/>
+      <c r="E483" s="26"/>
     </row>
     <row r="532" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C532" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E532" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="533" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C533" s="4"/>
       <c r="D533" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E533" s="6"/>
     </row>
@@ -4513,15 +4710,15 @@
         <v>4</v>
       </c>
       <c r="E534" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="535" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C535" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D535" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E535" s="12" t="s">
         <v>9</v>
@@ -4533,18 +4730,18 @@
       </c>
       <c r="D536" s="9"/>
       <c r="E536" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="537" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C537" s="8">
+      <c r="C537" s="19">
         <v>1.2</v>
       </c>
       <c r="D537" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E537" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="538" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4552,19 +4749,19 @@
         <v>2.1</v>
       </c>
       <c r="D538" s="17"/>
-      <c r="E538" s="26" t="s">
-        <v>60</v>
+      <c r="E538" s="27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="539" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C539" s="16">
+      <c r="C539" s="28">
         <v>2.2000000000000002</v>
       </c>
       <c r="D539" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E539" s="26" t="s">
-        <v>39</v>
+        <v>97</v>
+      </c>
+      <c r="E539" s="27" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="540" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4572,44 +4769,44 @@
         <v>3.1</v>
       </c>
       <c r="D540" s="9"/>
-      <c r="E540" s="20" t="s">
-        <v>97</v>
+      <c r="E540" s="21" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="541" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C541" s="8"/>
       <c r="D541" s="9"/>
-      <c r="E541" s="20"/>
+      <c r="E541" s="21"/>
     </row>
     <row r="542" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C542" s="8"/>
       <c r="D542" s="9"/>
-      <c r="E542" s="20"/>
+      <c r="E542" s="21"/>
     </row>
     <row r="543" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C543" s="8">
         <v>3.2</v>
       </c>
       <c r="D543" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E543" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="544" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C544" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D544" s="23"/>
-      <c r="E544" s="25"/>
+      <c r="C544" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D544" s="24"/>
+      <c r="E544" s="26"/>
     </row>
     <row r="591" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D591" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D591" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E591" s="3" t="s">
         <v>14</v>
@@ -4630,15 +4827,15 @@
         <v>4</v>
       </c>
       <c r="E593" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="594" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C594" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D594" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E594" s="12" t="s">
         <v>9</v>
@@ -4650,18 +4847,18 @@
       </c>
       <c r="D595" s="9"/>
       <c r="E595" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="596" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C596" s="8">
+      <c r="C596" s="19">
         <v>1.2</v>
       </c>
       <c r="D596" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E596" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="597" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4669,46 +4866,371 @@
         <v>2.1</v>
       </c>
       <c r="D597" s="9"/>
-      <c r="E597" s="20" t="s">
-        <v>99</v>
+      <c r="E597" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="598" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C598" s="8"/>
       <c r="D598" s="9"/>
-      <c r="E598" s="20"/>
+      <c r="E598" s="21"/>
     </row>
     <row r="599" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C599" s="8"/>
       <c r="D599" s="9"/>
-      <c r="E599" s="20"/>
+      <c r="E599" s="21"/>
     </row>
     <row r="600" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C600" s="8"/>
       <c r="D600" s="9"/>
-      <c r="E600" s="20"/>
+      <c r="E600" s="21"/>
     </row>
     <row r="601" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C601" s="8">
         <v>2.2000000000000002</v>
       </c>
       <c r="D601" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E601" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="602" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C602" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D602" s="23"/>
-      <c r="E602" s="25"/>
+      <c r="C602" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D602" s="24"/>
+      <c r="E602" s="26"/>
+    </row>
+    <row r="650" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C650" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D650" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E650" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="651" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C651" s="4"/>
+      <c r="D651" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E651" s="6"/>
+    </row>
+    <row r="652" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C652" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D652" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E652" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="653" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C653" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D653" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E653" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="654" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C654" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D654" s="9"/>
+      <c r="E654" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="655" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C655" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D655" s="9"/>
+      <c r="E655" s="10"/>
+    </row>
+    <row r="656" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C656" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="D656" s="9"/>
+      <c r="E656" s="10"/>
+    </row>
+    <row r="657" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C657" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D657" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E657" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="658" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C658" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="D658" s="9"/>
+      <c r="E658" s="10"/>
+    </row>
+    <row r="659" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C659" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="D659" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E659" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="660" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C660" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D660" s="9"/>
+      <c r="E660" s="15"/>
+    </row>
+    <row r="661" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C661" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="D661" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E661" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="662" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C662" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D662" s="24"/>
+      <c r="E662" s="26"/>
+    </row>
+    <row r="709" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C709" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D709" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E709" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="710" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C710" s="4"/>
+      <c r="D710" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E710" s="6"/>
+    </row>
+    <row r="711" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C711" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D711" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E711" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="712" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C712" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D712" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E712" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="713" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C713" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D713" s="9"/>
+      <c r="E713" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="714" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C714" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D714" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E714" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="715" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C715" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="D715" s="9"/>
+      <c r="E715" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="716" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C716" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D716" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E716" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="717" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C717" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="D717" s="9"/>
+      <c r="E717" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="718" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C718" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="D718" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E718" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="719" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C719" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D719" s="17"/>
+      <c r="E719" s="18"/>
+    </row>
+    <row r="720" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C720" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="D720" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E720" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="721" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C721" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D721" s="9"/>
+      <c r="E721" s="21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="722" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C722" s="8"/>
+      <c r="D722" s="9"/>
+      <c r="E722" s="21"/>
+    </row>
+    <row r="723" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C723" s="8"/>
+      <c r="D723" s="9"/>
+      <c r="E723" s="21"/>
+    </row>
+    <row r="724" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C724" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="D724" s="9"/>
+      <c r="E724" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="725" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C725" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="D725" s="17"/>
+      <c r="E725" s="18"/>
+    </row>
+    <row r="726" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C726" s="28">
+        <v>6.2</v>
+      </c>
+      <c r="D726" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E726" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="727" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C727" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="D727" s="9"/>
+      <c r="E727" s="15"/>
+    </row>
+    <row r="728" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C728" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="D728" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E728" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="729" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C729" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="D729" s="9"/>
+      <c r="E729" s="10"/>
+    </row>
+    <row r="730" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C730" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D730" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E730" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="731" spans="3:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C731" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D731" s="24"/>
+      <c r="E731" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="E597:E600"/>
+    <mergeCell ref="E721:E723"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="E137:E138"/>
     <mergeCell ref="E190:E192"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1CC2BF-6A0B-430E-BE97-9AB3660BE115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08A4A0D-695D-4359-AE48-4F2A75F6213C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$1357</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$1534</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="159">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -3016,6 +3016,102 @@
   </si>
   <si>
     <t>Direct Indexed Indirect (d,x) (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>ORA (17)</t>
+  </si>
+  <si>
+    <t>Direct Indirect Indexed Long [d],y (Read)</t>
+  </si>
+  <si>
+    <t>CLC (18)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>ORA (19)</t>
+  </si>
+  <si>
+    <t>Absolute, Y (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Perform Orig = Pointer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Tmp = ui32(Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>Bank += (Tmp &gt;&gt; 16).</t>
   </si>
 </sst>
 </file>
@@ -3616,7 +3712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:D1323"/>
+  <dimension ref="A1:D1497"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -7703,9 +7799,508 @@
       <c r="C1323" s="21"/>
       <c r="D1323" s="23"/>
     </row>
+    <row r="1358" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1358" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1358" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1358" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1359" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1359" s="4"/>
+      <c r="C1359" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1359" s="31"/>
+    </row>
+    <row r="1360" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1360" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1360" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1360" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1361" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1361" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1361" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1361" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1362" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1362" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1362" s="9"/>
+      <c r="D1362" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1363" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1363" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1363" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1363" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1364" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1364" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="C1364" s="17"/>
+      <c r="D1364" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1365" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1365" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1365" s="17"/>
+      <c r="D1365" s="24"/>
+    </row>
+    <row r="1366" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1366" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1366" s="9"/>
+      <c r="D1366" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1367" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1367" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C1367" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1367" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1368" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1368" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1368" s="9"/>
+      <c r="D1368" s="15"/>
+    </row>
+    <row r="1369" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1369" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C1369" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1369" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1370" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1370" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1370" s="9"/>
+      <c r="D1370" s="10"/>
+    </row>
+    <row r="1371" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1371" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C1371" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1371" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1372" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1372" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1372" s="9"/>
+      <c r="D1372" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1373" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1373" s="8"/>
+      <c r="C1373" s="9"/>
+      <c r="D1373" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1374" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1374" s="8"/>
+      <c r="C1374" s="9"/>
+      <c r="D1374" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1375" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1375" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="C1375" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1375" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1376" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1376" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="C1376" s="17"/>
+      <c r="D1376" s="18"/>
+    </row>
+    <row r="1377" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1377" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="C1377" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1377" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1378" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1378" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C1378" s="9"/>
+      <c r="D1378" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1379" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1379" s="8"/>
+      <c r="C1379" s="9"/>
+      <c r="D1379" s="29"/>
+    </row>
+    <row r="1380" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1380" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C1380" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1380" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1381" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1381" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1381" s="21"/>
+      <c r="D1381" s="23"/>
+    </row>
+    <row r="1417" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1417" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1417" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1417" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1418" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1418" s="4"/>
+      <c r="C1418" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1418" s="27"/>
+    </row>
+    <row r="1419" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1419" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1419" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1419" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1420" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1420" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1420" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1420" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1421" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1421" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1421" s="9"/>
+      <c r="D1421" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1422" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1422" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="C1422" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1422" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1423" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1423" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1423" s="9"/>
+      <c r="D1423" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="1424" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1424" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1424" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1424" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1425" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1425" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1425" s="21"/>
+      <c r="D1425" s="23"/>
+    </row>
+    <row r="1476" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1476" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1476" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1476" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1477" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1477" s="4"/>
+      <c r="C1477" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1477" s="31"/>
+    </row>
+    <row r="1478" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1478" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1478" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1478" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1479" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1479" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1479" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1479" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1480" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1480" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1480" s="9"/>
+      <c r="D1480" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1481" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1481" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1481" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1481" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1482" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1482" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1482" s="9"/>
+      <c r="D1482" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1483" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1483" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1483" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1483" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1484" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1484" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1484" s="9"/>
+      <c r="D1484" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1485" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1485" s="8"/>
+      <c r="C1485" s="9"/>
+      <c r="D1485" s="15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1486" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1486" s="8"/>
+      <c r="C1486" s="9"/>
+      <c r="D1486" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1487" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1487" s="8"/>
+      <c r="C1487" s="9"/>
+      <c r="D1487" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1488" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1488" s="8"/>
+      <c r="C1488" s="9"/>
+      <c r="D1488" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1489" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1489" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="C1489" s="17"/>
+      <c r="D1489" s="24"/>
+    </row>
+    <row r="1490" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1490" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1490" s="17"/>
+      <c r="D1490" s="18"/>
+    </row>
+    <row r="1491" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1491" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="C1491" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1491" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1492" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1492" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1492" s="17"/>
+      <c r="D1492" s="24"/>
+    </row>
+    <row r="1493" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1493" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="C1493" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1493" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1494" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1494" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1494" s="9"/>
+      <c r="D1494" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1495" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1495" s="8"/>
+      <c r="C1495" s="9"/>
+      <c r="D1495" s="29"/>
+    </row>
+    <row r="1496" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1496" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="C1496" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1496" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1497" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1497" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1497" s="21"/>
+      <c r="D1497" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="33">
+    <mergeCell ref="C1477:D1477"/>
+    <mergeCell ref="D1494:D1495"/>
     <mergeCell ref="D1313:D1315"/>
+    <mergeCell ref="C1359:D1359"/>
+    <mergeCell ref="D1378:D1379"/>
     <mergeCell ref="D597:D599"/>
     <mergeCell ref="D721:D722"/>
     <mergeCell ref="C1300:D1300"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08A4A0D-695D-4359-AE48-4F2A75F6213C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DB7F92-D5D9-4ED5-8638-5F18291E6BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$1534</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$2220</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="191">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -3112,6 +3112,1073 @@
   </si>
   <si>
     <t>Bank += (Tmp &gt;&gt; 16).</t>
+  </si>
+  <si>
+    <t>INC (1A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>TSC (1B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>TRB (1C)</t>
+  </si>
+  <si>
+    <t>ORA (1D)</t>
+  </si>
+  <si>
+    <t>Absolute, X (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tmp = ui32(Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>ASL (1E)</t>
+  </si>
+  <si>
+    <t>Absolute, X (Read/Modiy/Write)</t>
+  </si>
+  <si>
+    <t>Write to Pointer + 1:Bank</t>
+  </si>
+  <si>
+    <t>Write to Pointer:Bank</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Tmp = ui32(Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>ORA (1F)</t>
+  </si>
+  <si>
+    <t>Absolute Long, X (Read)</t>
+  </si>
+  <si>
+    <t>JSR (20)</t>
+  </si>
+  <si>
+    <t>Absolute</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 2. Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Address.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Discard, then schedule </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (21)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>JSL (22)</t>
+  </si>
+  <si>
+    <t>Absolute Long</t>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3.  Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Copy Bank to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (23)</t>
+  </si>
+  <si>
+    <t>BIT (24)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $40), otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Operand), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $40).</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (25)</t>
   </si>
 </sst>
 </file>
@@ -3295,7 +4362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3377,6 +4444,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3712,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:D1497"/>
+  <dimension ref="A1:D2199"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -8294,8 +9364,2030 @@
       <c r="C1497" s="21"/>
       <c r="D1497" s="23"/>
     </row>
+    <row r="1535" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1535" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1535" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1535" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1536" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1536" s="4"/>
+      <c r="C1536" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1536" s="27"/>
+    </row>
+    <row r="1537" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1537" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1537" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1537" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1538" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1538" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1538" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1538" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1539" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1539" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1539" s="9"/>
+      <c r="D1539" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1540" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1540" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1540" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1540" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1541" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1541" s="19">
+        <v>2.1</v>
+      </c>
+      <c r="C1541" s="9"/>
+      <c r="D1541" s="29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1542" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1542" s="8"/>
+      <c r="C1542" s="9"/>
+      <c r="D1542" s="29"/>
+    </row>
+    <row r="1543" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1543" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1543" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1543" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1544" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1544" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1544" s="21"/>
+      <c r="D1544" s="23"/>
+    </row>
+    <row r="1594" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1594" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1594" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1594" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1595" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1595" s="4"/>
+      <c r="C1595" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1595" s="27"/>
+    </row>
+    <row r="1596" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1596" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1596" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1596" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1597" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1597" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1597" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1597" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1598" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1598" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1598" s="9"/>
+      <c r="D1598" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1599" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1599" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="C1599" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1599" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1600" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1600" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1600" s="9"/>
+      <c r="D1600" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="1601" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1601" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1601" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1601" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1602" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1602" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1602" s="21"/>
+      <c r="D1602" s="23"/>
+    </row>
+    <row r="1653" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1653" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1653" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1653" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1654" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1654" s="4"/>
+      <c r="C1654" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1654" s="31"/>
+    </row>
+    <row r="1655" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1655" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1655" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1655" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1656" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1656" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1656" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1656" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1657" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1657" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1657" s="9"/>
+      <c r="D1657" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1658" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1658" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1658" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1658" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1659" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1659" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1659" s="9"/>
+      <c r="D1659" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1660" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1660" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1660" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1660" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1661" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1661" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1661" s="9"/>
+      <c r="D1661" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1662" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1662" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C1662" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1662" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1663" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1663" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1663" s="17"/>
+      <c r="D1663" s="24"/>
+    </row>
+    <row r="1664" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1664" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="C1664" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1664" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1665" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1665" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1665" s="9"/>
+      <c r="D1665" s="29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1666" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1666" s="8"/>
+      <c r="C1666" s="9"/>
+      <c r="D1666" s="29"/>
+    </row>
+    <row r="1667" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1667" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C1667" s="9"/>
+      <c r="D1667" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1668" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1668" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="C1668" s="17"/>
+      <c r="D1668" s="18"/>
+    </row>
+    <row r="1669" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1669" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="C1669" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1669" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1670" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1670" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="C1670" s="9"/>
+      <c r="D1670" s="10"/>
+    </row>
+    <row r="1671" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1671" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="C1671" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1671" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1672" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1672" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C1672" s="9"/>
+      <c r="D1672" s="10"/>
+    </row>
+    <row r="1673" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1673" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C1673" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1673" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1674" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1674" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1674" s="21"/>
+      <c r="D1674" s="23"/>
+    </row>
+    <row r="1712" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1712" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1712" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1712" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1713" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1713" s="4"/>
+      <c r="C1713" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1713" s="27"/>
+    </row>
+    <row r="1714" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1714" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1714" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1714" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1715" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1715" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1715" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1715" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1716" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1716" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1716" s="9"/>
+      <c r="D1716" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1717" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1717" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1717" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1717" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1718" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1718" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1718" s="9"/>
+      <c r="D1718" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1719" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1719" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1719" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1719" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1720" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1720" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1720" s="9"/>
+      <c r="D1720" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1721" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1721" s="8"/>
+      <c r="C1721" s="9"/>
+      <c r="D1721" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1722" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1722" s="8"/>
+      <c r="C1722" s="9"/>
+      <c r="D1722" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1723" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1723" s="8"/>
+      <c r="C1723" s="9"/>
+      <c r="D1723" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1724" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1724" s="8"/>
+      <c r="C1724" s="9"/>
+      <c r="D1724" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1725" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1725" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="C1725" s="17"/>
+      <c r="D1725" s="18"/>
+    </row>
+    <row r="1726" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1726" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1726" s="17"/>
+      <c r="D1726" s="24"/>
+    </row>
+    <row r="1727" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1727" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="C1727" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1727" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1728" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1728" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1728" s="17"/>
+      <c r="D1728" s="24"/>
+    </row>
+    <row r="1729" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1729" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="C1729" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1729" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1730" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1730" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1730" s="9"/>
+      <c r="D1730" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1731" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1731" s="8"/>
+      <c r="C1731" s="9"/>
+      <c r="D1731" s="29"/>
+    </row>
+    <row r="1732" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1732" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="C1732" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1732" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1733" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1733" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1733" s="21"/>
+      <c r="D1733" s="23"/>
+    </row>
+    <row r="1771" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1771" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1771" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1771" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1772" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1772" s="4"/>
+      <c r="C1772" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1772" s="31"/>
+    </row>
+    <row r="1773" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1773" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1773" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1773" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1774" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1774" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1774" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1774" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1775" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1775" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1775" s="9"/>
+      <c r="D1775" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1776" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1776" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1776" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1776" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1777" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1777" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1777" s="9"/>
+      <c r="D1777" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1778" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1778" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1778" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1778" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1779" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1779" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1779" s="9"/>
+      <c r="D1779" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1780" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1780" s="8"/>
+      <c r="C1780" s="9"/>
+      <c r="D1780" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1781" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1781" s="8"/>
+      <c r="C1781" s="9"/>
+      <c r="D1781" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1782" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1782" s="8"/>
+      <c r="C1782" s="9"/>
+      <c r="D1782" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1783" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1783" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C1783" s="9"/>
+      <c r="D1783" s="10"/>
+    </row>
+    <row r="1784" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1784" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1784" s="9"/>
+      <c r="D1784" s="10"/>
+    </row>
+    <row r="1785" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1785" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C1785" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1785" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1786" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1786" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1786" s="17"/>
+      <c r="D1786" s="24"/>
+    </row>
+    <row r="1787" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1787" s="16">
+        <v>5.2</v>
+      </c>
+      <c r="C1787" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1787" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1788" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1788" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1788" s="9"/>
+      <c r="D1788" s="29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1789" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1789" s="8"/>
+      <c r="C1789" s="9"/>
+      <c r="D1789" s="29"/>
+    </row>
+    <row r="1790" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1790" s="8"/>
+      <c r="C1790" s="9"/>
+      <c r="D1790" s="29"/>
+    </row>
+    <row r="1791" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1791" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="C1791" s="9"/>
+      <c r="D1791" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1792" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1792" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="C1792" s="17"/>
+      <c r="D1792" s="24"/>
+    </row>
+    <row r="1793" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1793" s="16">
+        <v>7.2</v>
+      </c>
+      <c r="C1793" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1793" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1794" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1794" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C1794" s="9"/>
+      <c r="D1794" s="10"/>
+    </row>
+    <row r="1795" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1795" s="19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C1795" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1795" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1796" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1796" s="8">
+        <v>9.1</v>
+      </c>
+      <c r="C1796" s="9"/>
+      <c r="D1796" s="10"/>
+    </row>
+    <row r="1797" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1797" s="8">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="C1797" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1797" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1798" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1798" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1798" s="21"/>
+      <c r="D1798" s="23"/>
+    </row>
+    <row r="1830" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1830" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1830" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1830" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1831" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1831" s="4"/>
+      <c r="C1831" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1831" s="27"/>
+    </row>
+    <row r="1832" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1832" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1832" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1832" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1833" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1833" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1833" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1833" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1834" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1834" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1834" s="9"/>
+      <c r="D1834" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1835" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1835" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1835" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1835" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1836" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1836" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1836" s="9"/>
+      <c r="D1836" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1837" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1837" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1837" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1837" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1838" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1838" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1838" s="9"/>
+      <c r="D1838" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1839" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1839" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C1839" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1839" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1840" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1840" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1840" s="9"/>
+      <c r="D1840" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1841" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1841" s="8"/>
+      <c r="C1841" s="9"/>
+      <c r="D1841" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1842" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1842" s="8"/>
+      <c r="C1842" s="9"/>
+      <c r="D1842" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1843" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1843" s="8"/>
+      <c r="C1843" s="9"/>
+      <c r="D1843" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1844" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1844" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="C1844" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1844" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1845" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1845" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1845" s="17"/>
+      <c r="D1845" s="24"/>
+    </row>
+    <row r="1846" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1846" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="C1846" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1846" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1847" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1847" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1847" s="9"/>
+      <c r="D1847" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1848" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1848" s="8"/>
+      <c r="C1848" s="9"/>
+      <c r="D1848" s="29"/>
+    </row>
+    <row r="1849" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1849" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="C1849" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1849" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1850" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1850" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1850" s="21"/>
+      <c r="D1850" s="23"/>
+    </row>
+    <row r="1889" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1889" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1889" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1889" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1890" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1890" s="4"/>
+      <c r="C1890" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1890" s="27"/>
+    </row>
+    <row r="1891" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1891" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1891" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1891" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1892" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1892" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1892" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1892" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1893" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1893" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1893" s="9"/>
+      <c r="D1893" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1894" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1894" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1894" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1894" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1895" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1895" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1895" s="9"/>
+      <c r="D1895" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1896" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1896" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1896" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1896" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1897" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1897" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C1897" s="9"/>
+      <c r="D1897" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1898" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1898" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C1898" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1898" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="1899" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1899" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1899" s="9"/>
+      <c r="D1899" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1900" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1900" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C1900" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1900" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1901" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1901" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1901" s="9"/>
+      <c r="D1901" s="10"/>
+    </row>
+    <row r="1902" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1902" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="C1902" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1902" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1903" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1903" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1903" s="9"/>
+      <c r="D1903" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1904" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1904" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="C1904" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1904" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1905" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1905" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1905" s="21"/>
+      <c r="D1905" s="23"/>
+    </row>
+    <row r="1948" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1948" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1948" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1948" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1949" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1949" s="4"/>
+      <c r="C1949" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1949" s="31"/>
+    </row>
+    <row r="1950" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1950" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1950" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1950" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1951" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1951" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1951" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1951" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1952" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1952" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1952" s="9"/>
+      <c r="D1952" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1953" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1953" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C1953" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1953" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1954" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1954" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C1954" s="9"/>
+      <c r="D1954" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1955" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1955" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1955" s="9"/>
+      <c r="D1955" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1956" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1956" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="C1956" s="17"/>
+      <c r="D1956" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1957" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1957" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="C1957" s="17"/>
+      <c r="D1957" s="24"/>
+    </row>
+    <row r="1958" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1958" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C1958" s="9"/>
+      <c r="D1958" s="15"/>
+    </row>
+    <row r="1959" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1959" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C1959" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1959" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1960" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1960" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1960" s="9"/>
+      <c r="D1960" s="15"/>
+    </row>
+    <row r="1961" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1961" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C1961" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1961" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1962" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1962" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C1962" s="9"/>
+      <c r="D1962" s="15"/>
+    </row>
+    <row r="1963" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1963" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="C1963" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1963" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1964" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1964" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="C1964" s="17"/>
+      <c r="D1964" s="18"/>
+    </row>
+    <row r="1965" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1965" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="C1965" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1965" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1966" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1966" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C1966" s="9"/>
+      <c r="D1966" s="29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1967" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1967" s="8"/>
+      <c r="C1967" s="9"/>
+      <c r="D1967" s="29"/>
+    </row>
+    <row r="1968" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1968" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C1968" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1968" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1969" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1969" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1969" s="21"/>
+      <c r="D1969" s="23"/>
+    </row>
+    <row r="2007" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2007" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2007" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2007" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2008" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2008" s="4"/>
+      <c r="C2008" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2008" s="31"/>
+    </row>
+    <row r="2009" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2009" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2009" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2009" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2010" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2010" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2010" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2010" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2011" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2011" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2011" s="9"/>
+      <c r="D2011" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2012" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2012" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C2012" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2012" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2013" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2013" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C2013" s="9"/>
+      <c r="D2013" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2014" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2014" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2014" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2014" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2015" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2015" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C2015" s="9"/>
+      <c r="D2015" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2016" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2016" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C2016" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2016" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2017" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2017" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C2017" s="9"/>
+      <c r="D2017" s="15"/>
+    </row>
+    <row r="2018" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2018" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C2018" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2018" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2019" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2019" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C2019" s="9"/>
+      <c r="D2019" s="15"/>
+    </row>
+    <row r="2020" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2020" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C2020" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2020" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2021" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2021" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C2021" s="9"/>
+      <c r="D2021" s="15"/>
+    </row>
+    <row r="2022" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2022" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="C2022" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2022" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2023" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2023" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="C2023" s="9"/>
+      <c r="D2023" s="15"/>
+    </row>
+    <row r="2024" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2024" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="C2024" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2024" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2025" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2025" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C2025" s="9"/>
+      <c r="D2025" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2026" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2026" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C2026" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2026" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2027" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2027" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2027" s="21"/>
+      <c r="D2027" s="23"/>
+    </row>
+    <row r="2066" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2066" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2066" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2066" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2067" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2067" s="4"/>
+      <c r="C2067" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2067" s="27"/>
+    </row>
+    <row r="2068" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2068" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2068" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2068" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2069" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2069" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2069" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2069" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2070" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2070" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2070" s="9"/>
+      <c r="D2070" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2071" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2071" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C2071" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2071" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2072" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2072" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="C2072" s="9"/>
+      <c r="D2072" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2073" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2073" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2073" s="9"/>
+      <c r="D2073" s="10"/>
+    </row>
+    <row r="2074" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2074" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C2074" s="9"/>
+      <c r="D2074" s="10"/>
+    </row>
+    <row r="2075" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2075" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C2075" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2075" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2076" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2076" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C2076" s="9"/>
+      <c r="D2076" s="15"/>
+    </row>
+    <row r="2077" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2077" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C2077" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2077" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2078" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2078" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C2078" s="9"/>
+      <c r="D2078" s="29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2079" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2079" s="8"/>
+      <c r="C2079" s="9"/>
+      <c r="D2079" s="29"/>
+    </row>
+    <row r="2080" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2080" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C2080" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2080" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2081" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2081" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2081" s="21"/>
+      <c r="D2081" s="23"/>
+    </row>
+    <row r="2125" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2125" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2125" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2125" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2126" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2126" s="4"/>
+      <c r="C2126" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2126" s="6"/>
+    </row>
+    <row r="2127" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2127" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2127" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2127" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2128" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2128" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2128" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2128" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2129" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2129" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2129" s="9"/>
+      <c r="D2129" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2130" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2130" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C2130" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2130" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2131" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2131" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="C2131" s="17"/>
+      <c r="D2131" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2132" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2132" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2132" s="17"/>
+      <c r="D2132" s="24"/>
+    </row>
+    <row r="2133" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2133" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C2133" s="9"/>
+      <c r="D2133" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2134" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2134" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="C2134" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2134" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2135" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2135" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C2135" s="17"/>
+      <c r="D2135" s="18"/>
+    </row>
+    <row r="2136" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2136" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="C2136" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2136" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2137" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2137" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C2137" s="9"/>
+      <c r="D2137" s="29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2138" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2138" s="8"/>
+      <c r="C2138" s="9"/>
+      <c r="D2138" s="29"/>
+    </row>
+    <row r="2139" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2139" s="8"/>
+      <c r="C2139" s="9"/>
+      <c r="D2139" s="29"/>
+    </row>
+    <row r="2140" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2140" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C2140" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2140" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2141" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2141" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2141" s="21"/>
+      <c r="D2141" s="23"/>
+    </row>
+    <row r="2184" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2184" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2184" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2184" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2185" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2185" s="4"/>
+      <c r="C2185" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2185" s="6"/>
+    </row>
+    <row r="2186" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2186" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2186" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2186" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2187" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2187" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2187" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2187" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2188" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2188" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2188" s="9"/>
+      <c r="D2188" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2189" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2189" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C2189" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2189" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2190" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2190" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="C2190" s="17"/>
+      <c r="D2190" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2191" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2191" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2191" s="17"/>
+      <c r="D2191" s="24"/>
+    </row>
+    <row r="2192" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2192" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C2192" s="9"/>
+      <c r="D2192" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2193" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2193" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="C2193" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2193" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2194" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2194" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C2194" s="17"/>
+      <c r="D2194" s="18"/>
+    </row>
+    <row r="2195" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2195" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="C2195" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2195" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2196" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2196" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C2196" s="9"/>
+      <c r="D2196" s="29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2197" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2197" s="8"/>
+      <c r="C2197" s="9"/>
+      <c r="D2197" s="29"/>
+    </row>
+    <row r="2198" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2198" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C2198" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2198" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2199" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2199" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2199" s="21"/>
+      <c r="D2199" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="46">
+    <mergeCell ref="D2137:D2139"/>
+    <mergeCell ref="D2196:D2197"/>
+    <mergeCell ref="D1966:D1967"/>
+    <mergeCell ref="C2008:D2008"/>
+    <mergeCell ref="D2078:D2079"/>
+    <mergeCell ref="D1847:D1848"/>
+    <mergeCell ref="C1949:D1949"/>
+    <mergeCell ref="D1730:D1731"/>
+    <mergeCell ref="D1788:D1790"/>
+    <mergeCell ref="C1772:D1772"/>
+    <mergeCell ref="D1541:D1542"/>
+    <mergeCell ref="C1654:D1654"/>
+    <mergeCell ref="D1665:D1666"/>
     <mergeCell ref="C1477:D1477"/>
     <mergeCell ref="D1494:D1495"/>
     <mergeCell ref="D1313:D1315"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DB7F92-D5D9-4ED5-8638-5F18291E6BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C062E5-22EC-4D06-9456-31DC11DB0E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$2220</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$2360</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="193">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -3587,8 +3587,284 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Discard, then schedule </t>
+    <t>AND (21)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>JSL (22)</t>
+  </si>
+  <si>
+    <t>Absolute Long</t>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
     </r>
     <r>
       <rPr>
@@ -3609,15 +3885,123 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> -= 1.</t>
-    </r>
-  </si>
-  <si>
-    <t>AND (21)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
+      <t xml:space="preserve">. Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3.  Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Copy Bank to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (23)</t>
+  </si>
+  <si>
+    <t>BIT (24)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
     </r>
     <r>
       <rPr>
@@ -3638,7 +4022,144 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> &amp;= Operand. If </t>
+      <t xml:space="preserve">.L &amp; Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $40), otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Operand), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $40).</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (25)</t>
+  </si>
+  <si>
+    <t>ROL (26)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
     </r>
     <r>
       <rPr>
@@ -3670,6 +4191,48 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), perform Operand.L = (Operand.L &lt;&lt; 1) | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>N</t>
     </r>
     <r>
@@ -3680,28 +4243,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
     </r>
     <r>
       <rPr>
@@ -3722,28 +4264,49 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L, otherwise set </t>
+      <t xml:space="preserve"> based off Operand.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $80), perform Operand = (Operand &lt;&lt; 1) | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and set </t>
     </r>
     <r>
       <rPr>
@@ -3764,28 +4327,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80) and </t>
+      <t xml:space="preserve"> based off (Operand.H &amp; $80) and </t>
     </r>
     <r>
       <rPr>
@@ -3806,379 +4348,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>JSL (22)</t>
-  </si>
-  <si>
-    <t>Absolute Long</t>
-  </si>
-  <si>
-    <r>
-      <t>Read (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-2)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 3.  Copy Address to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Copy Bank to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>AND (23)</t>
-  </si>
-  <si>
-    <t>BIT (24)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag is set, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; Operand.L), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $40), otherwise set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; Operand), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.H &amp; $80), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.H &amp; $40).</t>
-    </r>
-  </si>
-  <si>
-    <t>AND (25)</t>
+      <t xml:space="preserve"> based off Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (27)</t>
   </si>
 </sst>
 </file>
@@ -4782,7 +4956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:D2199"/>
+  <dimension ref="A1:D2323"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -10467,7 +10641,7 @@
         <v>93</v>
       </c>
       <c r="D1898" s="10" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1899" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10537,7 +10711,7 @@
     </row>
     <row r="1948" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1948" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C1948" s="2" t="s">
         <v>6</v>
@@ -10707,7 +10881,7 @@
       </c>
       <c r="C1966" s="9"/>
       <c r="D1966" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1967" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10735,7 +10909,7 @@
     </row>
     <row r="2007" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2007" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2007" s="2" t="s">
         <v>14</v>
@@ -10747,7 +10921,7 @@
     <row r="2008" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2008" s="4"/>
       <c r="C2008" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D2008" s="31"/>
     </row>
@@ -10845,7 +11019,7 @@
         <v>4.2</v>
       </c>
       <c r="C2018" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D2018" s="15" t="s">
         <v>97</v>
@@ -10899,7 +11073,7 @@
         <v>7.2</v>
       </c>
       <c r="C2024" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D2024" s="15" t="s">
         <v>36</v>
@@ -10911,7 +11085,7 @@
       </c>
       <c r="C2025" s="9"/>
       <c r="D2025" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2026" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10934,7 +11108,7 @@
     </row>
     <row r="2066" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2066" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C2066" s="2" t="s">
         <v>24</v>
@@ -11016,7 +11190,7 @@
       <c r="D2074" s="10"/>
     </row>
     <row r="2075" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2075" s="8">
+      <c r="B2075" s="19">
         <v>3.2</v>
       </c>
       <c r="C2075" s="9" t="s">
@@ -11027,20 +11201,20 @@
       </c>
     </row>
     <row r="2076" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2076" s="8">
+      <c r="B2076" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C2076" s="9"/>
-      <c r="D2076" s="15"/>
+      <c r="C2076" s="17"/>
+      <c r="D2076" s="18"/>
     </row>
     <row r="2077" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2077" s="8">
+      <c r="B2077" s="25">
         <v>4.2</v>
       </c>
-      <c r="C2077" s="9" t="s">
+      <c r="C2077" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D2077" s="15" t="s">
+      <c r="D2077" s="18" t="s">
         <v>45</v>
       </c>
     </row>
@@ -11050,7 +11224,7 @@
       </c>
       <c r="C2078" s="9"/>
       <c r="D2078" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2079" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11078,7 +11252,7 @@
     </row>
     <row r="2125" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2125" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2125" s="2" t="s">
         <v>15</v>
@@ -11196,7 +11370,7 @@
       </c>
       <c r="C2137" s="9"/>
       <c r="D2137" s="29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2138" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11229,7 +11403,7 @@
     </row>
     <row r="2184" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2184" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2184" s="2" t="s">
         <v>15</v>
@@ -11347,7 +11521,7 @@
       </c>
       <c r="C2196" s="9"/>
       <c r="D2196" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2197" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11373,10 +11547,416 @@
       <c r="C2199" s="21"/>
       <c r="D2199" s="23"/>
     </row>
+    <row r="2243" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2243" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2243" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2243" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2244" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2244" s="4"/>
+      <c r="C2244" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2244" s="31"/>
+    </row>
+    <row r="2245" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2245" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2245" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2245" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2246" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2246" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2246" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2246" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2247" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2247" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2247" s="9"/>
+      <c r="D2247" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2248" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2248" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C2248" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2248" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2249" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2249" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="C2249" s="17"/>
+      <c r="D2249" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2250" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2250" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2250" s="17"/>
+      <c r="D2250" s="24"/>
+    </row>
+    <row r="2251" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2251" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C2251" s="9"/>
+      <c r="D2251" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2252" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2252" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C2252" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2252" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2253" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2253" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C2253" s="17"/>
+      <c r="D2253" s="18"/>
+    </row>
+    <row r="2254" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2254" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="C2254" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2254" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2255" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2255" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C2255" s="9"/>
+      <c r="D2255" s="29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2256" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2256" s="8"/>
+      <c r="C2256" s="9"/>
+      <c r="D2256" s="29"/>
+    </row>
+    <row r="2257" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2257" s="8"/>
+      <c r="C2257" s="9"/>
+      <c r="D2257" s="29"/>
+    </row>
+    <row r="2258" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2258" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C2258" s="9"/>
+      <c r="D2258" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2259" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2259" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="C2259" s="17"/>
+      <c r="D2259" s="18"/>
+    </row>
+    <row r="2260" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2260" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="C2260" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2260" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2261" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2261" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="C2261" s="9"/>
+      <c r="D2261" s="15"/>
+    </row>
+    <row r="2262" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2262" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="C2262" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2262" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2263" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2263" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C2263" s="9"/>
+      <c r="D2263" s="10"/>
+    </row>
+    <row r="2264" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2264" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C2264" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2264" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2265" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2265" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2265" s="21"/>
+      <c r="D2265" s="23"/>
+    </row>
+    <row r="2302" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2302" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2302" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2302" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2303" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2303" s="4"/>
+      <c r="C2303" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2303" s="27"/>
+    </row>
+    <row r="2304" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2304" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2304" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2304" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2305" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2305" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2305" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2305" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2306" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2306" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2306" s="9"/>
+      <c r="D2306" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2307" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2307" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="C2307" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2307" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2308" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2308" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="C2308" s="17"/>
+      <c r="D2308" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2309" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2309" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C2309" s="17"/>
+      <c r="D2309" s="24"/>
+    </row>
+    <row r="2310" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2310" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C2310" s="9"/>
+      <c r="D2310" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2311" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2311" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="C2311" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2311" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2312" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2312" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C2312" s="9"/>
+      <c r="D2312" s="15"/>
+    </row>
+    <row r="2313" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2313" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="C2313" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2313" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2314" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2314" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C2314" s="9"/>
+      <c r="D2314" s="10"/>
+    </row>
+    <row r="2315" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2315" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="C2315" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2315" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2316" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2316" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="C2316" s="9"/>
+      <c r="D2316" s="10"/>
+    </row>
+    <row r="2317" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2317" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="C2317" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2317" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2318" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2318" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="C2318" s="17"/>
+      <c r="D2318" s="18"/>
+    </row>
+    <row r="2319" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2319" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="C2319" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2319" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2320" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2320" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="C2320" s="9"/>
+      <c r="D2320" s="29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2321" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2321" s="8"/>
+      <c r="C2321" s="9"/>
+      <c r="D2321" s="29"/>
+    </row>
+    <row r="2322" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2322" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C2322" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2322" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2323" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2323" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2323" s="21"/>
+      <c r="D2323" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="49">
+    <mergeCell ref="D2320:D2321"/>
+    <mergeCell ref="D2255:D2257"/>
     <mergeCell ref="D2137:D2139"/>
     <mergeCell ref="D2196:D2197"/>
+    <mergeCell ref="C2244:D2244"/>
     <mergeCell ref="D1966:D1967"/>
     <mergeCell ref="C2008:D2008"/>
     <mergeCell ref="D2078:D2079"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F1A26A-AFCD-4C0A-B359-3E10435ED757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DCFD44-5E45-4EB3-96CB-AC7581C4D15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$3776</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$4012</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="243">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -6197,6 +6197,487 @@
   </si>
   <si>
     <t>AND (3F)</t>
+  </si>
+  <si>
+    <t>Direct, X (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>RTI (40)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (41)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^= Operand. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>WDM (42)</t>
+  </si>
+  <si>
+    <t>EOR (43)</t>
   </si>
 </sst>
 </file>
@@ -6801,7 +7282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C3737"/>
+  <dimension ref="A1:C3969"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -10656,7 +11137,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
       <c r="B1300" s="31" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="C1300" s="32"/>
     </row>
@@ -17647,8 +18128,614 @@
       <c r="B3737" s="21"/>
       <c r="C3737" s="23"/>
     </row>
+    <row r="3777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3777" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3777" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3777" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3778" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3778" s="4"/>
+      <c r="B3778" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3778" s="27"/>
+    </row>
+    <row r="3779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3779" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3779" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3779" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3780" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3780" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3780" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3781" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3781" s="9"/>
+      <c r="C3781" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3782" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B3782" s="9"/>
+      <c r="C3782" s="10"/>
+    </row>
+    <row r="3783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3783" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3783" s="9"/>
+      <c r="C3783" s="10"/>
+    </row>
+    <row r="3784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3784" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3784" s="9"/>
+      <c r="C3784" s="10"/>
+    </row>
+    <row r="3785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3785" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B3785" s="9"/>
+      <c r="C3785" s="15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3786" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B3786" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3786" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3787" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3787" s="9"/>
+      <c r="C3787" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3788" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B3788" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3788" s="15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3789" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3789" s="9"/>
+      <c r="C3789" s="10"/>
+    </row>
+    <row r="3790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3790" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B3790" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3790" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3791" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B3791" s="9"/>
+      <c r="C3791" s="10"/>
+    </row>
+    <row r="3792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3792" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B3792" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3792" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3793" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B3793" s="9"/>
+      <c r="C3793" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3794" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B3794" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3794" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3795" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3795" s="21"/>
+      <c r="C3795" s="23"/>
+    </row>
+    <row r="3836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3836" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3836" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3836" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3837" s="4"/>
+      <c r="B3837" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3837" s="32"/>
+    </row>
+    <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3838" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3838" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3838" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3839" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3839" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3839" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3840" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3840" s="9"/>
+      <c r="C3840" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3841" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B3841" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3841" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3842" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3842" s="9"/>
+      <c r="C3842" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3843" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3843" s="9"/>
+      <c r="C3843" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3844" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="B3844" s="17"/>
+      <c r="C3844" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3845" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B3845" s="17"/>
+      <c r="C3845" s="24"/>
+    </row>
+    <row r="3846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3846" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3846" s="9"/>
+      <c r="C3846" s="15"/>
+    </row>
+    <row r="3847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3847" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B3847" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3847" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3848" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3848" s="9"/>
+      <c r="C3848" s="15"/>
+    </row>
+    <row r="3849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3849" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B3849" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3849" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3850" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B3850" s="9"/>
+      <c r="C3850" s="10"/>
+    </row>
+    <row r="3851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3851" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B3851" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3851" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3852" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B3852" s="17"/>
+      <c r="C3852" s="24"/>
+    </row>
+    <row r="3853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3853" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B3853" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3853" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3854" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B3854" s="9"/>
+      <c r="C3854" s="30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3855" s="8"/>
+      <c r="B3855" s="9"/>
+      <c r="C3855" s="30"/>
+    </row>
+    <row r="3856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3856" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B3856" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3856" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3857" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3857" s="21"/>
+      <c r="C3857" s="23"/>
+    </row>
+    <row r="3895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3895" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3895" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3895" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3896" s="4"/>
+      <c r="B3896" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3896" s="27"/>
+    </row>
+    <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3897" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3897" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3897" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3898" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3898" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3898" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3899" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3899" s="9"/>
+      <c r="C3899" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3900" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B3900" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3900" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3901" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3901" s="9"/>
+      <c r="C3901" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3902" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3902" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3902" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3903" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3903" s="21"/>
+      <c r="C3903" s="23"/>
+    </row>
+    <row r="3954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3954" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3954" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3954" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3955" s="4"/>
+      <c r="B3955" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3955" s="32"/>
+    </row>
+    <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3956" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3956" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3956" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3957" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3957" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3957" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3958" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3958" s="9"/>
+      <c r="C3958" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3959" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B3959" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3959" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3960" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3960" s="9"/>
+      <c r="C3960" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3961" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3961" s="9"/>
+      <c r="C3961" s="10"/>
+    </row>
+    <row r="3962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3962" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B3962" s="9"/>
+      <c r="C3962" s="15"/>
+    </row>
+    <row r="3963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3963" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B3963" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3963" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3964" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3964" s="17"/>
+      <c r="C3964" s="18"/>
+    </row>
+    <row r="3965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3965" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B3965" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3965" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3966" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3966" s="9"/>
+      <c r="C3966" s="30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3967" s="8"/>
+      <c r="B3967" s="9"/>
+      <c r="C3967" s="30"/>
+    </row>
+    <row r="3968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3968" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B3968" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3968" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3969" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3969" s="21"/>
+      <c r="C3969" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="82">
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="C3966:C3967"/>
+    <mergeCell ref="C3854:C3855"/>
+    <mergeCell ref="B3837:C3837"/>
     <mergeCell ref="B3719:C3719"/>
     <mergeCell ref="C3734:C3735"/>
     <mergeCell ref="C3559:C3561"/>
@@ -17730,6 +18817,9 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="3776" max="2" man="1"/>
+  </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="4" max="1048575" man="1"/>
   </colBreaks>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DCFD44-5E45-4EB3-96CB-AC7581C4D15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6793A4DF-CFA4-4E55-BCE0-2A6CEAD47A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$4012</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$5605</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="291">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -6678,6 +6678,1667 @@
   </si>
   <si>
     <t>EOR (43)</t>
+  </si>
+  <si>
+    <t>MVP (44)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L -= 1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L -= 1, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is not $FFFF, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 3.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Read </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:Bank</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (45)</t>
+  </si>
+  <si>
+    <t>LSR (46)</t>
+  </si>
+  <si>
+    <t>EOR (47)</t>
+  </si>
+  <si>
+    <t>PHA (48)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (49)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^= Operand. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LSR (4A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01), perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &gt;&gt;= 1, and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A.L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $01), perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt;= 1, and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A.H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $01), perform Operand.L &gt;&gt;= 1, and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $01), perform Operand &gt;&gt;= 1, and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>PHK (4B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (4C)</t>
+  </si>
+  <si>
+    <t>EOR (4D)</t>
+  </si>
+  <si>
+    <t>LSR (4E)</t>
+  </si>
+  <si>
+    <t>EOR (4F)</t>
+  </si>
+  <si>
+    <t>BVC (50)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>Block Move (Positive)</t>
+  </si>
+  <si>
+    <t>EOR (51)</t>
+  </si>
+  <si>
+    <t>EOR (52)</t>
+  </si>
+  <si>
+    <t>EOR (53)</t>
+  </si>
+  <si>
+    <t>MVN (54)</t>
+  </si>
+  <si>
+    <t>Block Move (Negative)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is not $FFFF, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 3.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (55)</t>
+  </si>
+  <si>
+    <t>LSR (56)</t>
+  </si>
+  <si>
+    <t>CLI (58)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (59)</t>
+  </si>
+  <si>
+    <t>PHY (5A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCD (5B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>JML (5C)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Copy Bank to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Store as Address.H.</t>
+  </si>
+  <si>
+    <t>EOR (5D)</t>
+  </si>
+  <si>
+    <t>LSR (5E)</t>
+  </si>
+  <si>
+    <t>EOR (5F)</t>
   </si>
 </sst>
 </file>
@@ -6932,22 +8593,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7282,7 +8943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C3969"/>
+  <dimension ref="A1:C5566"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -7545,11 +9206,11 @@
       <c r="C30" s="34"/>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+      <c r="A31" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
@@ -7729,14 +9390,14 @@
         <v>8.1</v>
       </c>
       <c r="B78" s="9"/>
-      <c r="C78" s="30" t="s">
+      <c r="C78" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
-      <c r="C79" s="30"/>
+      <c r="C79" s="33"/>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
@@ -8113,14 +9774,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B190" s="9"/>
-      <c r="C190" s="30" t="s">
+      <c r="C190" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
-      <c r="C191" s="30"/>
+      <c r="C191" s="33"/>
     </row>
     <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
@@ -8259,14 +9920,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B249" s="9"/>
-      <c r="C249" s="30" t="s">
+      <c r="C249" s="33" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8"/>
       <c r="B250" s="9"/>
-      <c r="C250" s="30"/>
+      <c r="C250" s="33"/>
     </row>
     <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8">
@@ -8457,14 +10118,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B308" s="9"/>
-      <c r="C308" s="30" t="s">
+      <c r="C308" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="8"/>
       <c r="B309" s="9"/>
-      <c r="C309" s="30"/>
+      <c r="C309" s="33"/>
     </row>
     <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8">
@@ -8603,19 +10264,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="9"/>
-      <c r="C367" s="30" t="s">
+      <c r="C367" s="33" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
-      <c r="C368" s="30"/>
+      <c r="C368" s="33"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="8"/>
       <c r="B369" s="9"/>
-      <c r="C369" s="30"/>
+      <c r="C369" s="33"/>
     </row>
     <row r="370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8">
@@ -8860,14 +10521,14 @@
         <v>8.1</v>
       </c>
       <c r="B432" s="9"/>
-      <c r="C432" s="30" t="s">
+      <c r="C432" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="8"/>
       <c r="B433" s="9"/>
-      <c r="C433" s="30"/>
+      <c r="C433" s="33"/>
     </row>
     <row r="434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8">
@@ -9075,14 +10736,14 @@
         <v>3.1</v>
       </c>
       <c r="B540" s="9"/>
-      <c r="C540" s="30" t="s">
+      <c r="C540" s="33" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="8"/>
       <c r="B541" s="9"/>
-      <c r="C541" s="30"/>
+      <c r="C541" s="33"/>
     </row>
     <row r="542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="8">
@@ -9167,14 +10828,14 @@
         <v>2.1</v>
       </c>
       <c r="B597" s="9"/>
-      <c r="C597" s="30" t="s">
+      <c r="C597" s="33" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="8"/>
       <c r="B598" s="9"/>
-      <c r="C598" s="30"/>
+      <c r="C598" s="33"/>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="8">
@@ -9631,14 +11292,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B780" s="9"/>
-      <c r="C780" s="30" t="s">
+      <c r="C780" s="33" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="8"/>
       <c r="B781" s="9"/>
-      <c r="C781" s="30"/>
+      <c r="C781" s="33"/>
     </row>
     <row r="782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="8">
@@ -9781,19 +11442,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B839" s="9"/>
-      <c r="C839" s="30" t="s">
+      <c r="C839" s="33" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
-      <c r="C840" s="30"/>
+      <c r="C840" s="33"/>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="8"/>
       <c r="B841" s="9"/>
-      <c r="C841" s="30"/>
+      <c r="C841" s="33"/>
     </row>
     <row r="842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="8">
@@ -10008,14 +11669,14 @@
         <v>6.1</v>
       </c>
       <c r="B900" s="9"/>
-      <c r="C900" s="30" t="s">
+      <c r="C900" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="8"/>
       <c r="B901" s="9"/>
-      <c r="C901" s="30"/>
+      <c r="C901" s="33"/>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="8">
@@ -10339,14 +12000,14 @@
         <v>8.1</v>
       </c>
       <c r="B1026" s="9"/>
-      <c r="C1026" s="30" t="s">
+      <c r="C1026" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="8"/>
       <c r="B1027" s="9"/>
-      <c r="C1027" s="30"/>
+      <c r="C1027" s="33"/>
     </row>
     <row r="1028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="8">
@@ -10521,14 +12182,14 @@
         <v>7.1</v>
       </c>
       <c r="B1079" s="9"/>
-      <c r="C1079" s="30" t="s">
+      <c r="C1079" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="8"/>
       <c r="B1080" s="9"/>
-      <c r="C1080" s="30"/>
+      <c r="C1080" s="33"/>
     </row>
     <row r="1081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="8">
@@ -10738,14 +12399,14 @@
         <v>8.1</v>
       </c>
       <c r="B1143" s="9"/>
-      <c r="C1143" s="30" t="s">
+      <c r="C1143" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1144" s="8"/>
       <c r="B1144" s="9"/>
-      <c r="C1144" s="30"/>
+      <c r="C1144" s="33"/>
     </row>
     <row r="1145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="8">
@@ -10884,14 +12545,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1193" s="9"/>
-      <c r="C1193" s="30" t="s">
+      <c r="C1193" s="33" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="1194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1194" s="8"/>
       <c r="B1194" s="9"/>
-      <c r="C1194" s="30"/>
+      <c r="C1194" s="33"/>
     </row>
     <row r="1195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1195" s="8">
@@ -11096,14 +12757,14 @@
         <v>6.1</v>
       </c>
       <c r="B1254" s="9"/>
-      <c r="C1254" s="30" t="s">
+      <c r="C1254" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1255" s="8"/>
       <c r="B1255" s="9"/>
-      <c r="C1255" s="30"/>
+      <c r="C1255" s="33"/>
     </row>
     <row r="1256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1256" s="8">
@@ -11256,19 +12917,19 @@
         <v>6.1</v>
       </c>
       <c r="B1313" s="9"/>
-      <c r="C1313" s="30" t="s">
+      <c r="C1313" s="33" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="1314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="8"/>
       <c r="B1314" s="9"/>
-      <c r="C1314" s="30"/>
+      <c r="C1314" s="33"/>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
-      <c r="C1315" s="30"/>
+      <c r="C1315" s="33"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="8">
@@ -11529,14 +13190,14 @@
         <v>8.1</v>
       </c>
       <c r="B1378" s="9"/>
-      <c r="C1378" s="30" t="s">
+      <c r="C1378" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1379" s="8"/>
       <c r="B1379" s="9"/>
-      <c r="C1379" s="30"/>
+      <c r="C1379" s="33"/>
     </row>
     <row r="1380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="8">
@@ -11808,14 +13469,14 @@
         <v>6.1</v>
       </c>
       <c r="B1494" s="9"/>
-      <c r="C1494" s="30" t="s">
+      <c r="C1494" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1495" s="8"/>
       <c r="B1495" s="9"/>
-      <c r="C1495" s="30"/>
+      <c r="C1495" s="33"/>
     </row>
     <row r="1496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1496" s="8">
@@ -11900,14 +13561,14 @@
         <v>2.1</v>
       </c>
       <c r="B1541" s="9"/>
-      <c r="C1541" s="30" t="s">
+      <c r="C1541" s="33" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1542" s="8"/>
       <c r="B1542" s="9"/>
-      <c r="C1542" s="30"/>
+      <c r="C1542" s="33"/>
     </row>
     <row r="1543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1543" s="8">
@@ -12137,14 +13798,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1665" s="9"/>
-      <c r="C1665" s="30" t="s">
+      <c r="C1665" s="33" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="1666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1666" s="8"/>
       <c r="B1666" s="9"/>
-      <c r="C1666" s="30"/>
+      <c r="C1666" s="33"/>
     </row>
     <row r="1667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1667" s="8">
@@ -12381,14 +14042,14 @@
         <v>6.1</v>
       </c>
       <c r="B1730" s="9"/>
-      <c r="C1730" s="30" t="s">
+      <c r="C1730" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1731" s="8"/>
       <c r="B1731" s="9"/>
-      <c r="C1731" s="30"/>
+      <c r="C1731" s="33"/>
     </row>
     <row r="1732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1732" s="8">
@@ -12566,19 +14227,19 @@
         <v>6.1</v>
       </c>
       <c r="B1788" s="9"/>
-      <c r="C1788" s="30" t="s">
+      <c r="C1788" s="33" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1789" s="8"/>
       <c r="B1789" s="9"/>
-      <c r="C1789" s="30"/>
+      <c r="C1789" s="33"/>
     </row>
     <row r="1790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1790" s="8"/>
       <c r="B1790" s="9"/>
-      <c r="C1790" s="30"/>
+      <c r="C1790" s="33"/>
     </row>
     <row r="1791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1791" s="8">
@@ -12814,14 +14475,14 @@
         <v>6.1</v>
       </c>
       <c r="B1847" s="9"/>
-      <c r="C1847" s="30" t="s">
+      <c r="C1847" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1848" s="8"/>
       <c r="B1848" s="9"/>
-      <c r="C1848" s="30"/>
+      <c r="C1848" s="33"/>
     </row>
     <row r="1849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1849" s="8">
@@ -13177,14 +14838,14 @@
         <v>8.1</v>
       </c>
       <c r="B1966" s="9"/>
-      <c r="C1966" s="30" t="s">
+      <c r="C1966" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="1967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1967" s="8"/>
       <c r="B1967" s="9"/>
-      <c r="C1967" s="30"/>
+      <c r="C1967" s="33"/>
     </row>
     <row r="1968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1968" s="8">
@@ -13520,14 +15181,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2078" s="9"/>
-      <c r="C2078" s="30" t="s">
+      <c r="C2078" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2079" s="8"/>
       <c r="B2079" s="9"/>
-      <c r="C2079" s="30"/>
+      <c r="C2079" s="33"/>
     </row>
     <row r="2080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2080" s="8">
@@ -13666,19 +15327,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2137" s="9"/>
-      <c r="C2137" s="30" t="s">
+      <c r="C2137" s="33" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="2138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2138" s="8"/>
       <c r="B2138" s="9"/>
-      <c r="C2138" s="30"/>
+      <c r="C2138" s="33"/>
     </row>
     <row r="2139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2139" s="8"/>
       <c r="B2139" s="9"/>
-      <c r="C2139" s="30"/>
+      <c r="C2139" s="33"/>
     </row>
     <row r="2140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2140" s="8">
@@ -13817,14 +15478,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2196" s="9"/>
-      <c r="C2196" s="30" t="s">
+      <c r="C2196" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2197" s="8"/>
       <c r="B2197" s="9"/>
-      <c r="C2197" s="30"/>
+      <c r="C2197" s="33"/>
     </row>
     <row r="2198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2198" s="8">
@@ -13963,19 +15624,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="9"/>
-      <c r="C2255" s="30" t="s">
+      <c r="C2255" s="33" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="8"/>
       <c r="B2256" s="9"/>
-      <c r="C2256" s="30"/>
+      <c r="C2256" s="33"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="8"/>
       <c r="B2257" s="9"/>
-      <c r="C2257" s="30"/>
+      <c r="C2257" s="33"/>
     </row>
     <row r="2258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2258" s="8">
@@ -14220,14 +15881,14 @@
         <v>8.1</v>
       </c>
       <c r="B2320" s="9"/>
-      <c r="C2320" s="30" t="s">
+      <c r="C2320" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2321" s="8"/>
       <c r="B2321" s="9"/>
-      <c r="C2321" s="30"/>
+      <c r="C2321" s="33"/>
     </row>
     <row r="2322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2322" s="8">
@@ -14449,14 +16110,14 @@
         <v>3.1</v>
       </c>
       <c r="B2428" s="9"/>
-      <c r="C2428" s="30" t="s">
+      <c r="C2428" s="33" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="2429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2429" s="8"/>
       <c r="B2429" s="9"/>
-      <c r="C2429" s="30"/>
+      <c r="C2429" s="33"/>
     </row>
     <row r="2430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2430" s="8">
@@ -14541,19 +16202,19 @@
         <v>2.1</v>
       </c>
       <c r="B2485" s="9"/>
-      <c r="C2485" s="30" t="s">
+      <c r="C2485" s="33" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2486" s="8"/>
       <c r="B2486" s="9"/>
-      <c r="C2486" s="30"/>
+      <c r="C2486" s="33"/>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2487" s="8"/>
       <c r="B2487" s="9"/>
-      <c r="C2487" s="30"/>
+      <c r="C2487" s="33"/>
     </row>
     <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2488" s="8">
@@ -14829,19 +16490,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2609" s="9"/>
-      <c r="C2609" s="30" t="s">
+      <c r="C2609" s="33" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2610" s="8"/>
       <c r="B2610" s="9"/>
-      <c r="C2610" s="30"/>
+      <c r="C2610" s="33"/>
     </row>
     <row r="2611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2611" s="8"/>
       <c r="B2611" s="9"/>
-      <c r="C2611" s="30"/>
+      <c r="C2611" s="33"/>
     </row>
     <row r="2612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2612" s="8">
@@ -14984,14 +16645,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2668" s="9"/>
-      <c r="C2668" s="30" t="s">
+      <c r="C2668" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2669" s="8"/>
       <c r="B2669" s="9"/>
-      <c r="C2669" s="30"/>
+      <c r="C2669" s="33"/>
     </row>
     <row r="2670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2670" s="8">
@@ -15134,19 +16795,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2727" s="9"/>
-      <c r="C2727" s="30" t="s">
+      <c r="C2727" s="33" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2728" s="8"/>
       <c r="B2728" s="9"/>
-      <c r="C2728" s="30"/>
+      <c r="C2728" s="33"/>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="8"/>
       <c r="B2729" s="9"/>
-      <c r="C2729" s="30"/>
+      <c r="C2729" s="33"/>
     </row>
     <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2730" s="8">
@@ -15361,14 +17022,14 @@
         <v>6.1</v>
       </c>
       <c r="B2788" s="9"/>
-      <c r="C2788" s="30" t="s">
+      <c r="C2788" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2789" s="8"/>
       <c r="B2789" s="9"/>
-      <c r="C2789" s="30"/>
+      <c r="C2789" s="33"/>
     </row>
     <row r="2790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2790" s="8">
@@ -15692,14 +17353,14 @@
         <v>8.1</v>
       </c>
       <c r="B2914" s="9"/>
-      <c r="C2914" s="30" t="s">
+      <c r="C2914" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2915" s="8"/>
       <c r="B2915" s="9"/>
-      <c r="C2915" s="30"/>
+      <c r="C2915" s="33"/>
     </row>
     <row r="2916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2916" s="8">
@@ -15874,14 +17535,14 @@
         <v>7.1</v>
       </c>
       <c r="B2967" s="9"/>
-      <c r="C2967" s="30" t="s">
+      <c r="C2967" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2968" s="8"/>
       <c r="B2968" s="9"/>
-      <c r="C2968" s="30"/>
+      <c r="C2968" s="33"/>
     </row>
     <row r="2969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2969" s="8">
@@ -16084,14 +17745,14 @@
         <v>8.1</v>
       </c>
       <c r="B3030" s="9"/>
-      <c r="C3030" s="30" t="s">
+      <c r="C3030" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3031" s="8"/>
       <c r="B3031" s="9"/>
-      <c r="C3031" s="30"/>
+      <c r="C3031" s="33"/>
     </row>
     <row r="3032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3032" s="8">
@@ -16244,19 +17905,19 @@
         <v>6.1</v>
       </c>
       <c r="B3083" s="9"/>
-      <c r="C3083" s="30" t="s">
+      <c r="C3083" s="33" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="3084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3084" s="8"/>
       <c r="B3084" s="9"/>
-      <c r="C3084" s="30"/>
+      <c r="C3084" s="33"/>
     </row>
     <row r="3085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3085" s="8"/>
       <c r="B3085" s="9"/>
-      <c r="C3085" s="30"/>
+      <c r="C3085" s="33"/>
     </row>
     <row r="3086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3086" s="8">
@@ -16409,14 +18070,14 @@
         <v>6.1</v>
       </c>
       <c r="B3142" s="9"/>
-      <c r="C3142" s="30" t="s">
+      <c r="C3142" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3143" s="8"/>
       <c r="B3143" s="9"/>
-      <c r="C3143" s="30"/>
+      <c r="C3143" s="33"/>
     </row>
     <row r="3144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3144" s="8">
@@ -16569,19 +18230,19 @@
         <v>6.1</v>
       </c>
       <c r="B3201" s="9"/>
-      <c r="C3201" s="30" t="s">
+      <c r="C3201" s="33" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="3202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3202" s="8"/>
       <c r="B3202" s="9"/>
-      <c r="C3202" s="30"/>
+      <c r="C3202" s="33"/>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="8"/>
       <c r="B3203" s="9"/>
-      <c r="C3203" s="30"/>
+      <c r="C3203" s="33"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="8">
@@ -16819,14 +18480,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3264" spans="1:3" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3264" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3264" s="16">
         <v>7.1</v>
       </c>
       <c r="B3264" s="17"/>
       <c r="C3264" s="24"/>
     </row>
-    <row r="3265" spans="1:3" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3265" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3265" s="25">
         <v>7.2</v>
       </c>
@@ -16842,14 +18503,14 @@
         <v>8.1</v>
       </c>
       <c r="B3266" s="9"/>
-      <c r="C3266" s="30" t="s">
+      <c r="C3266" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3267" s="8"/>
       <c r="B3267" s="9"/>
-      <c r="C3267" s="30"/>
+      <c r="C3267" s="33"/>
     </row>
     <row r="3268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3268" s="8">
@@ -17073,14 +18734,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3377" spans="1:3" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3377" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3377" s="16">
         <v>3.2</v>
       </c>
       <c r="B3377" s="17"/>
       <c r="C3377" s="24"/>
     </row>
-    <row r="3378" spans="1:3" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3378" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3378" s="16">
         <v>4.0999999999999996</v>
       </c>
@@ -17121,14 +18782,14 @@
         <v>6.1</v>
       </c>
       <c r="B3382" s="9"/>
-      <c r="C3382" s="30" t="s">
+      <c r="C3382" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3383" s="8"/>
       <c r="B3383" s="9"/>
-      <c r="C3383" s="30"/>
+      <c r="C3383" s="33"/>
     </row>
     <row r="3384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3384" s="8">
@@ -17213,14 +18874,14 @@
         <v>2.1</v>
       </c>
       <c r="B3429" s="9"/>
-      <c r="C3429" s="30" t="s">
+      <c r="C3429" s="33" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3430" s="8"/>
       <c r="B3430" s="9"/>
-      <c r="C3430" s="30"/>
+      <c r="C3430" s="33"/>
     </row>
     <row r="3431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3431" s="8">
@@ -17444,14 +19105,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3554" spans="1:3" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3554" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3554" s="16">
         <v>3.2</v>
       </c>
       <c r="B3554" s="17"/>
       <c r="C3554" s="24"/>
     </row>
-    <row r="3555" spans="1:3" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3555" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3555" s="16">
         <v>4.0999999999999996</v>
       </c>
@@ -17492,19 +19153,19 @@
         <v>6.1</v>
       </c>
       <c r="B3559" s="9"/>
-      <c r="C3559" s="30" t="s">
+      <c r="C3559" s="33" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="3560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3560" s="8"/>
       <c r="B3560" s="9"/>
-      <c r="C3560" s="30"/>
+      <c r="C3560" s="33"/>
     </row>
     <row r="3561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3561" s="8"/>
       <c r="B3561" s="9"/>
-      <c r="C3561" s="30"/>
+      <c r="C3561" s="33"/>
     </row>
     <row r="3562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3562" s="8">
@@ -17682,14 +19343,14 @@
         <v>6.1</v>
       </c>
       <c r="B3617" s="9"/>
-      <c r="C3617" s="30" t="s">
+      <c r="C3617" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3618" s="8"/>
       <c r="B3618" s="9"/>
-      <c r="C3618" s="30"/>
+      <c r="C3618" s="33"/>
     </row>
     <row r="3619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3619" s="8">
@@ -17860,19 +19521,19 @@
         <v>6.1</v>
       </c>
       <c r="B3675" s="9"/>
-      <c r="C3675" s="30" t="s">
+      <c r="C3675" s="33" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3676" s="8"/>
       <c r="B3676" s="9"/>
-      <c r="C3676" s="30"/>
+      <c r="C3676" s="33"/>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="8"/>
       <c r="B3677" s="9"/>
-      <c r="C3677" s="30"/>
+      <c r="C3677" s="33"/>
     </row>
     <row r="3678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3678" s="8">
@@ -18101,14 +19762,14 @@
         <v>6.1</v>
       </c>
       <c r="B3734" s="9"/>
-      <c r="C3734" s="30" t="s">
+      <c r="C3734" s="33" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3735" s="8"/>
       <c r="B3735" s="9"/>
-      <c r="C3735" s="30"/>
+      <c r="C3735" s="33"/>
     </row>
     <row r="3736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3736" s="8">
@@ -18472,14 +20133,14 @@
         <v>8.1</v>
       </c>
       <c r="B3854" s="9"/>
-      <c r="C3854" s="30" t="s">
+      <c r="C3854" s="33" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="3855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3855" s="8"/>
       <c r="B3855" s="9"/>
-      <c r="C3855" s="30"/>
+      <c r="C3855" s="33"/>
     </row>
     <row r="3856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3856" s="8">
@@ -18703,14 +20364,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B3966" s="9"/>
-      <c r="C3966" s="30" t="s">
+      <c r="C3966" s="33" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3967" s="8"/>
       <c r="B3967" s="9"/>
-      <c r="C3967" s="30"/>
+      <c r="C3967" s="33"/>
     </row>
     <row r="3968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3968" s="8">
@@ -18730,47 +20391,4359 @@
       <c r="B3969" s="21"/>
       <c r="C3969" s="23"/>
     </row>
+    <row r="4013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4013" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4013" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4013" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4014" s="4"/>
+      <c r="B4014" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4014" s="32"/>
+    </row>
+    <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4015" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4015" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4015" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4016" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4016" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4016" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4017" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4017" s="9"/>
+      <c r="C4017" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4018" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4018" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4018" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4019" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4019" s="9"/>
+      <c r="C4019" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4020" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4020" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4020" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4021" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4021" s="9"/>
+      <c r="C4021" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4022" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4022" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4022" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4023" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4023" s="9"/>
+      <c r="C4023" s="10"/>
+    </row>
+    <row r="4024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4024" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4024" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4024" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4025" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4025" s="9"/>
+      <c r="C4025" s="33" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4026" s="8"/>
+      <c r="B4026" s="9"/>
+      <c r="C4026" s="33"/>
+    </row>
+    <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4027" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4027" s="9"/>
+      <c r="C4027" s="10"/>
+    </row>
+    <row r="4028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4028" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B4028" s="9"/>
+      <c r="C4028" s="15"/>
+    </row>
+    <row r="4029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4029" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B4029" s="9"/>
+      <c r="C4029" s="15"/>
+    </row>
+    <row r="4030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4030" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B4030" s="9"/>
+      <c r="C4030" s="10"/>
+    </row>
+    <row r="4031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4031" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B4031" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4031" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4032" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4032" s="21"/>
+      <c r="C4032" s="23"/>
+    </row>
+    <row r="4072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4072" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4072" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4072" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4073" s="4"/>
+      <c r="B4073" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4073" s="32"/>
+    </row>
+    <row r="4074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4074" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4074" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4074" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4075" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4075" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4075" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4076" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4076" s="9"/>
+      <c r="C4076" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4077" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4077" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4077" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4078" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4078" s="17"/>
+      <c r="C4078" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4079" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4079" s="17"/>
+      <c r="C4079" s="24"/>
+    </row>
+    <row r="4080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4080" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4080" s="9"/>
+      <c r="C4080" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4081" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B4081" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4081" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4082" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4082" s="17"/>
+      <c r="C4082" s="24"/>
+    </row>
+    <row r="4083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4083" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B4083" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4083" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4084" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4084" s="9"/>
+      <c r="C4084" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4085" s="8"/>
+      <c r="B4085" s="9"/>
+      <c r="C4085" s="33"/>
+    </row>
+    <row r="4086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4086" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4086" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4086" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4087" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4087" s="21"/>
+      <c r="C4087" s="23"/>
+    </row>
+    <row r="4131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4131" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4131" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4131" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4132" s="4"/>
+      <c r="B4132" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4132" s="32"/>
+    </row>
+    <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4133" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4133" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4133" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4134" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4134" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4134" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4135" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4135" s="9"/>
+      <c r="C4135" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4136" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4136" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4136" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4137" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4137" s="17"/>
+      <c r="C4137" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4138" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4138" s="17"/>
+      <c r="C4138" s="24"/>
+    </row>
+    <row r="4139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4139" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4139" s="9"/>
+      <c r="C4139" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4140" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4140" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4140" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4141" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4141" s="17"/>
+      <c r="C4141" s="24"/>
+    </row>
+    <row r="4142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4142" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="B4142" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4142" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4143" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4143" s="9"/>
+      <c r="C4143" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4144" s="8"/>
+      <c r="B4144" s="9"/>
+      <c r="C4144" s="33"/>
+    </row>
+    <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4145" s="8"/>
+      <c r="B4145" s="9"/>
+      <c r="C4145" s="33"/>
+    </row>
+    <row r="4146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4146" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4146" s="9"/>
+      <c r="C4146" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4147" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B4147" s="17"/>
+      <c r="C4147" s="24"/>
+    </row>
+    <row r="4148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4148" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="B4148" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4148" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4149" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B4149" s="9"/>
+      <c r="C4149" s="10"/>
+    </row>
+    <row r="4150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4150" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="B4150" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4150" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4151" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B4151" s="9"/>
+      <c r="C4151" s="10"/>
+    </row>
+    <row r="4152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4152" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B4152" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4152" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4153" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4153" s="21"/>
+      <c r="C4153" s="23"/>
+    </row>
+    <row r="4190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4190" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4190" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4190" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4191" s="4"/>
+      <c r="B4191" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4191" s="32"/>
+    </row>
+    <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4192" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4192" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4192" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4193" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4193" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4193" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4194" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4194" s="9"/>
+      <c r="C4194" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4195" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4195" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4195" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4196" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4196" s="17"/>
+      <c r="C4196" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4197" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4197" s="17"/>
+      <c r="C4197" s="24"/>
+    </row>
+    <row r="4198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4198" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4198" s="9"/>
+      <c r="C4198" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4199" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4199" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4199" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4200" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4200" s="9"/>
+      <c r="C4200" s="10"/>
+    </row>
+    <row r="4201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4201" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4201" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4201" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4202" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4202" s="9"/>
+      <c r="C4202" s="10"/>
+    </row>
+    <row r="4203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4203" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4203" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4203" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4204" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B4204" s="9"/>
+      <c r="C4204" s="10"/>
+    </row>
+    <row r="4205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4205" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B4205" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4205" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4206" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B4206" s="17"/>
+      <c r="C4206" s="24"/>
+    </row>
+    <row r="4207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4207" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B4207" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4207" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4208" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B4208" s="9"/>
+      <c r="C4208" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4209" s="8"/>
+      <c r="B4209" s="9"/>
+      <c r="C4209" s="33"/>
+    </row>
+    <row r="4210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4210" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B4210" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4210" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4211" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4211" s="21"/>
+      <c r="C4211" s="23"/>
+    </row>
+    <row r="4249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4249" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4249" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4249" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4250" s="4"/>
+      <c r="B4250" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4250" s="27"/>
+    </row>
+    <row r="4251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4251" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4251" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4251" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4252" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4252" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4252" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4253" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4253" s="9"/>
+      <c r="C4253" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4254" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4254" s="9"/>
+      <c r="C4254" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4255" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4255" s="17"/>
+      <c r="C4255" s="24"/>
+    </row>
+    <row r="4256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4256" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4256" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4256" s="24" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4257" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4257" s="9"/>
+      <c r="C4257" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4258" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4258" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4258" s="10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4259" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4259" s="9"/>
+      <c r="C4259" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4260" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4260" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4260" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4261" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4261" s="21"/>
+      <c r="C4261" s="23"/>
+    </row>
+    <row r="4308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4308" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4308" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4308" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4309" s="4"/>
+      <c r="B4309" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4309" s="27"/>
+    </row>
+    <row r="4310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4310" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4310" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4310" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4311" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4311" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4311" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4312" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4312" s="9"/>
+      <c r="C4312" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4313" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B4313" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4313" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4314" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4314" s="17"/>
+      <c r="C4314" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4315" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4315" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4315" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4316" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4316" s="9"/>
+      <c r="C4316" s="33" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4317" s="8"/>
+      <c r="B4317" s="9"/>
+      <c r="C4317" s="33"/>
+    </row>
+    <row r="4318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4318" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4318" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4318" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4319" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4319" s="21"/>
+      <c r="C4319" s="23"/>
+    </row>
+    <row r="4367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4367" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4367" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4367" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4368" s="4"/>
+      <c r="B4368" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4368" s="27"/>
+    </row>
+    <row r="4369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4369" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4369" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4369" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4370" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4370" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4370" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4371" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4371" s="9"/>
+      <c r="C4371" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4372" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B4372" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4372" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4373" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4373" s="9"/>
+      <c r="C4373" s="33" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4374" s="8"/>
+      <c r="B4374" s="9"/>
+      <c r="C4374" s="33"/>
+    </row>
+    <row r="4375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4375" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4375" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4375" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4376" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4376" s="21"/>
+      <c r="C4376" s="23"/>
+    </row>
+    <row r="4426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4426" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4426" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4426" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4427" s="4"/>
+      <c r="B4427" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4427" s="27"/>
+    </row>
+    <row r="4428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4428" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4428" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4428" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4429" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4429" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4429" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4430" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4430" s="9"/>
+      <c r="C4430" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4431" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4431" s="9"/>
+      <c r="C4431" s="10"/>
+    </row>
+    <row r="4432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4432" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4432" s="9"/>
+      <c r="C4432" s="10"/>
+    </row>
+    <row r="4433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4433" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4433" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4433" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4434" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4434" s="9"/>
+      <c r="C4434" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4435" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4435" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4435" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4436" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4436" s="21"/>
+      <c r="C4436" s="23"/>
+    </row>
+    <row r="4485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4485" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4485" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4485" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4486" s="4"/>
+      <c r="B4486" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4486" s="27"/>
+    </row>
+    <row r="4487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4487" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4487" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4487" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4488" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4488" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4488" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4489" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4489" s="9"/>
+      <c r="C4489" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4490" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4490" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4490" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4491" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4491" s="9"/>
+      <c r="C4491" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4492" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4492" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4492" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4493" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4493" s="9"/>
+      <c r="C4493" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4494" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4494" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4494" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4495" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4495" s="21"/>
+      <c r="C4495" s="23"/>
+    </row>
+    <row r="4544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4544" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4544" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4544" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4545" s="4"/>
+      <c r="B4545" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4545" s="27"/>
+    </row>
+    <row r="4546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4546" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4546" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4546" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4547" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4547" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4547" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4548" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4548" s="9"/>
+      <c r="C4548" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4549" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4549" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4549" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4550" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4550" s="9"/>
+      <c r="C4550" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4551" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4551" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4551" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4552" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4552" s="9"/>
+      <c r="C4552" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4553" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B4553" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4553" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4554" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4554" s="17"/>
+      <c r="C4554" s="24"/>
+    </row>
+    <row r="4555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4555" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B4555" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4555" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4556" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4556" s="9"/>
+      <c r="C4556" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4557" s="8"/>
+      <c r="B4557" s="9"/>
+      <c r="C4557" s="33"/>
+    </row>
+    <row r="4558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4558" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4558" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4558" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4559" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4559" s="21"/>
+      <c r="C4559" s="23"/>
+    </row>
+    <row r="4603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4603" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4603" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4603" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4604" s="4"/>
+      <c r="B4604" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4604" s="32"/>
+    </row>
+    <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4605" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4605" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4605" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4606" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4606" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4606" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4607" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4607" s="9"/>
+      <c r="C4607" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4608" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4608" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4608" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4609" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4609" s="9"/>
+      <c r="C4609" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4610" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4610" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4610" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4611" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4611" s="9"/>
+      <c r="C4611" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4612" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4612" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4612" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4613" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4613" s="17"/>
+      <c r="C4613" s="24"/>
+    </row>
+    <row r="4614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4614" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="B4614" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4614" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4615" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4615" s="9"/>
+      <c r="C4615" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4616" s="8"/>
+      <c r="B4616" s="9"/>
+      <c r="C4616" s="33"/>
+    </row>
+    <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4617" s="8"/>
+      <c r="B4617" s="9"/>
+      <c r="C4617" s="33"/>
+    </row>
+    <row r="4618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4618" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4618" s="9"/>
+      <c r="C4618" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4619" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B4619" s="17"/>
+      <c r="C4619" s="24"/>
+    </row>
+    <row r="4620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4620" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="B4620" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4620" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4621" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B4621" s="9"/>
+      <c r="C4621" s="10"/>
+    </row>
+    <row r="4622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4622" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="B4622" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4622" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4623" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B4623" s="9"/>
+      <c r="C4623" s="10"/>
+    </row>
+    <row r="4624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4624" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B4624" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4624" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4625" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4625" s="21"/>
+      <c r="C4625" s="23"/>
+    </row>
+    <row r="4662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4662" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4662" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4662" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4663" s="4"/>
+      <c r="B4663" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4663" s="32"/>
+    </row>
+    <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4664" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4664" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4664" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4665" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4665" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4665" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4666" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4666" s="9"/>
+      <c r="C4666" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4667" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4667" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4667" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4668" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4668" s="9"/>
+      <c r="C4668" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4669" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4669" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4669" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4670" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4670" s="9"/>
+      <c r="C4670" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4671" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4671" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4671" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4672" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4672" s="9"/>
+      <c r="C4672" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4673" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B4673" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4673" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4674" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4674" s="17"/>
+      <c r="C4674" s="24"/>
+    </row>
+    <row r="4675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4675" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B4675" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4675" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4676" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B4676" s="9"/>
+      <c r="C4676" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4677" s="8"/>
+      <c r="B4677" s="9"/>
+      <c r="C4677" s="33"/>
+    </row>
+    <row r="4678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4678" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B4678" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4678" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4679" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4679" s="21"/>
+      <c r="C4679" s="23"/>
+    </row>
+    <row r="4721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4721" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4721" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4721" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4722" s="4"/>
+      <c r="B4722" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4722" s="6"/>
+    </row>
+    <row r="4723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4723" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4723" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4723" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4724" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4724" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4724" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4725" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4725" s="9"/>
+      <c r="C4725" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4726" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B4726" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4726" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4727" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4727" s="9"/>
+      <c r="C4727" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4728" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4728" s="9"/>
+      <c r="C4728" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4729" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4729" s="9"/>
+      <c r="C4729" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4730" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4730" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4730" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4731" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4731" s="21"/>
+      <c r="C4731" s="22"/>
+    </row>
+    <row r="4780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4780" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4780" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4780" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4781" s="4"/>
+      <c r="B4781" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4781" s="32"/>
+    </row>
+    <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4782" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4782" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4782" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4783" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4783" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4783" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4784" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4784" s="9"/>
+      <c r="C4784" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4785" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4785" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4785" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4786" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4786" s="17"/>
+      <c r="C4786" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4787" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4787" s="17"/>
+      <c r="C4787" s="24"/>
+    </row>
+    <row r="4788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4788" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4788" s="9"/>
+      <c r="C4788" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4789" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4789" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4789" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4790" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4790" s="9"/>
+      <c r="C4790" s="10"/>
+    </row>
+    <row r="4791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4791" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4791" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4791" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4792" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4792" s="9"/>
+      <c r="C4792" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4793" s="8"/>
+      <c r="B4793" s="9"/>
+      <c r="C4793" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4794" s="8"/>
+      <c r="B4794" s="9"/>
+      <c r="C4794" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4795" s="8"/>
+      <c r="B4795" s="9"/>
+      <c r="C4795" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4796" s="8"/>
+      <c r="B4796" s="9"/>
+      <c r="C4796" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4797" s="16">
+        <v>5.2</v>
+      </c>
+      <c r="B4797" s="17"/>
+      <c r="C4797" s="24"/>
+    </row>
+    <row r="4798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4798" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B4798" s="17"/>
+      <c r="C4798" s="24"/>
+    </row>
+    <row r="4799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4799" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B4799" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4799" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4800" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B4800" s="17"/>
+      <c r="C4800" s="24"/>
+    </row>
+    <row r="4801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4801" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="B4801" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4801" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4802" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B4802" s="9"/>
+      <c r="C4802" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4803" s="8"/>
+      <c r="B4803" s="9"/>
+      <c r="C4803" s="33"/>
+    </row>
+    <row r="4804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4804" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B4804" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4804" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4805" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4805" s="21"/>
+      <c r="C4805" s="23"/>
+    </row>
+    <row r="4839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4839" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4839" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4839" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4840" s="4"/>
+      <c r="B4840" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4840" s="27"/>
+    </row>
+    <row r="4841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4841" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4841" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4841" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4842" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4842" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4842" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4843" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4843" s="9"/>
+      <c r="C4843" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4844" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4844" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4844" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4845" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B4845" s="17"/>
+      <c r="C4845" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4846" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4846" s="17"/>
+      <c r="C4846" s="24"/>
+    </row>
+    <row r="4847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4847" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4847" s="9"/>
+      <c r="C4847" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4848" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4848" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4848" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4849" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4849" s="9"/>
+      <c r="C4849" s="10"/>
+    </row>
+    <row r="4850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4850" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4850" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4850" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4851" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4851" s="9"/>
+      <c r="C4851" s="10"/>
+    </row>
+    <row r="4852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4852" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="B4852" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4852" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4853" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B4853" s="17"/>
+      <c r="C4853" s="24"/>
+    </row>
+    <row r="4854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4854" s="25">
+        <v>6.2</v>
+      </c>
+      <c r="B4854" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4854" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4855" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B4855" s="9"/>
+      <c r="C4855" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4856" s="8"/>
+      <c r="B4856" s="9"/>
+      <c r="C4856" s="33"/>
+    </row>
+    <row r="4857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4857" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B4857" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4857" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4858" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4858" s="21"/>
+      <c r="C4858" s="23"/>
+    </row>
+    <row r="4898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4898" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4898" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4898" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4899" s="4"/>
+      <c r="B4899" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4899" s="32"/>
+    </row>
+    <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4900" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4900" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4900" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4901" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4901" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4901" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4902" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4902" s="9"/>
+      <c r="C4902" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4903" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4903" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4903" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4904" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4904" s="9"/>
+      <c r="C4904" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4905" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4905" s="9"/>
+      <c r="C4905" s="10"/>
+    </row>
+    <row r="4906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4906" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4906" s="9"/>
+      <c r="C4906" s="10"/>
+    </row>
+    <row r="4907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4907" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4907" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4907" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4908" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4908" s="9"/>
+      <c r="C4908" s="10"/>
+    </row>
+    <row r="4909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4909" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4909" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4909" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4910" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4910" s="9"/>
+      <c r="C4910" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4911" s="8"/>
+      <c r="B4911" s="9"/>
+      <c r="C4911" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4912" s="8"/>
+      <c r="B4912" s="9"/>
+      <c r="C4912" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4913" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4913" s="9"/>
+      <c r="C4913" s="10"/>
+    </row>
+    <row r="4914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4914" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B4914" s="9"/>
+      <c r="C4914" s="10"/>
+    </row>
+    <row r="4915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4915" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B4915" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4915" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4916" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B4916" s="17"/>
+      <c r="C4916" s="24"/>
+    </row>
+    <row r="4917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4917" s="16">
+        <v>7.2</v>
+      </c>
+      <c r="B4917" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4917" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4918" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B4918" s="9"/>
+      <c r="C4918" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4919" s="8"/>
+      <c r="B4919" s="9"/>
+      <c r="C4919" s="33"/>
+    </row>
+    <row r="4920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4920" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B4920" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4920" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4921" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4921" s="21"/>
+      <c r="C4921" s="23"/>
+    </row>
+    <row r="4957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4957" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4957" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4957" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4958" s="4"/>
+      <c r="B4958" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4958" s="32"/>
+    </row>
+    <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4959" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4959" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4959" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4960" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4960" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4960" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4961" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4961" s="9"/>
+      <c r="C4961" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4962" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4962" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4962" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4963" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4963" s="9"/>
+      <c r="C4963" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4964" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4964" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4964" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4965" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4965" s="9"/>
+      <c r="C4965" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4966" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B4966" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4966" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4967" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4967" s="9"/>
+      <c r="C4967" s="10"/>
+    </row>
+    <row r="4968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4968" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4968" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4968" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4969" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4969" s="9"/>
+      <c r="C4969" s="33" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4970" s="8"/>
+      <c r="B4970" s="9"/>
+      <c r="C4970" s="33"/>
+    </row>
+    <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4971" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B4971" s="9"/>
+      <c r="C4971" s="10"/>
+    </row>
+    <row r="4972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4972" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B4972" s="9"/>
+      <c r="C4972" s="15"/>
+    </row>
+    <row r="4973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4973" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B4973" s="9"/>
+      <c r="C4973" s="15"/>
+    </row>
+    <row r="4974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4974" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B4974" s="9"/>
+      <c r="C4974" s="10"/>
+    </row>
+    <row r="4975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4975" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B4975" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4975" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4976" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4976" s="21"/>
+      <c r="C4976" s="23"/>
+    </row>
+    <row r="5016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5016" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5016" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5016" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5017" s="4"/>
+      <c r="B5017" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5017" s="27"/>
+    </row>
+    <row r="5018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5018" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5018" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5018" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5019" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5019" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5019" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5020" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5020" s="9"/>
+      <c r="C5020" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5021" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5021" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5021" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5022" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5022" s="9"/>
+      <c r="C5022" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5023" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5023" s="9"/>
+      <c r="C5023" s="10"/>
+    </row>
+    <row r="5024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5024" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5024" s="9"/>
+      <c r="C5024" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5025" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B5025" s="17"/>
+      <c r="C5025" s="24"/>
+    </row>
+    <row r="5026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5026" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5026" s="17"/>
+      <c r="C5026" s="24"/>
+    </row>
+    <row r="5027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5027" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B5027" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5027" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5028" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5028" s="17"/>
+      <c r="C5028" s="18"/>
+    </row>
+    <row r="5029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5029" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B5029" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5029" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5030" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5030" s="9"/>
+      <c r="C5030" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5031" s="8"/>
+      <c r="B5031" s="9"/>
+      <c r="C5031" s="33"/>
+    </row>
+    <row r="5032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5032" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5032" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5032" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5033" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5033" s="21"/>
+      <c r="C5033" s="23"/>
+    </row>
+    <row r="5075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5075" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5075" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5075" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5076" s="4"/>
+      <c r="B5076" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5076" s="32"/>
+    </row>
+    <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5077" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5077" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5077" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5078" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5078" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5078" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5079" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5079" s="9"/>
+      <c r="C5079" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5080" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5080" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5080" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5081" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5081" s="9"/>
+      <c r="C5081" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5082" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5082" s="9"/>
+      <c r="C5082" s="10"/>
+    </row>
+    <row r="5083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5083" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5083" s="9"/>
+      <c r="C5083" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5084" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B5084" s="17"/>
+      <c r="C5084" s="24"/>
+    </row>
+    <row r="5085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5085" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5085" s="17"/>
+      <c r="C5085" s="24"/>
+    </row>
+    <row r="5086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5086" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5086" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5086" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5087" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5087" s="17"/>
+      <c r="C5087" s="24"/>
+    </row>
+    <row r="5088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5088" s="16">
+        <v>5.2</v>
+      </c>
+      <c r="B5088" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5088" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5089" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5089" s="9"/>
+      <c r="C5089" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5090" s="8"/>
+      <c r="B5090" s="9"/>
+      <c r="C5090" s="33"/>
+    </row>
+    <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5091" s="8"/>
+      <c r="B5091" s="9"/>
+      <c r="C5091" s="33"/>
+    </row>
+    <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5092" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5092" s="9"/>
+      <c r="C5092" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5093" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B5093" s="17"/>
+      <c r="C5093" s="24"/>
+    </row>
+    <row r="5094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5094" s="16">
+        <v>7.2</v>
+      </c>
+      <c r="B5094" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5094" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5095" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B5095" s="9"/>
+      <c r="C5095" s="15"/>
+    </row>
+    <row r="5096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5096" s="19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B5096" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5096" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5097" s="8">
+        <v>9.1</v>
+      </c>
+      <c r="B5097" s="9"/>
+      <c r="C5097" s="15"/>
+    </row>
+    <row r="5098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5098" s="8">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="B5098" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5098" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5099" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5099" s="21"/>
+      <c r="C5099" s="23"/>
+    </row>
+    <row r="5134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5134" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5134" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5134" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5135" s="4"/>
+      <c r="B5135" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5135" s="27"/>
+    </row>
+    <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5136" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5136" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5136" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5137" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5137" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5137" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5138" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5138" s="9"/>
+      <c r="C5138" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5139" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B5139" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5139" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5140" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5140" s="9"/>
+      <c r="C5140" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5141" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5141" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5141" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5142" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5142" s="21"/>
+      <c r="C5142" s="23"/>
+    </row>
+    <row r="5193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5193" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5193" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5193" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5194" s="4"/>
+      <c r="B5194" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5194" s="27"/>
+    </row>
+    <row r="5195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5195" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5195" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5195" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5196" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5196" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5196" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5197" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5197" s="9"/>
+      <c r="C5197" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5198" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5198" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5198" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5199" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5199" s="9"/>
+      <c r="C5199" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5200" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5200" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5200" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5201" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5201" s="9"/>
+      <c r="C5201" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5202" s="8"/>
+      <c r="B5202" s="9"/>
+      <c r="C5202" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5203" s="8"/>
+      <c r="B5203" s="9"/>
+      <c r="C5203" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5204" s="8"/>
+      <c r="B5204" s="9"/>
+      <c r="C5204" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5205" s="8"/>
+      <c r="B5205" s="9"/>
+      <c r="C5205" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5206" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B5206" s="17"/>
+      <c r="C5206" s="24"/>
+    </row>
+    <row r="5207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5207" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5207" s="17"/>
+      <c r="C5207" s="24"/>
+    </row>
+    <row r="5208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5208" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B5208" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5208" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5209" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5209" s="17"/>
+      <c r="C5209" s="24"/>
+    </row>
+    <row r="5210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5210" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B5210" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5210" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5211" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5211" s="9"/>
+      <c r="C5211" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5212" s="8"/>
+      <c r="B5212" s="9"/>
+      <c r="C5212" s="33"/>
+    </row>
+    <row r="5213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5213" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5213" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5213" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5214" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5214" s="21"/>
+      <c r="C5214" s="23"/>
+    </row>
+    <row r="5252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5252" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5252" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5252" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5253" s="4"/>
+      <c r="B5253" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5253" s="27"/>
+    </row>
+    <row r="5254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5254" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5254" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5254" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5255" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5255" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5255" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5256" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5256" s="9"/>
+      <c r="C5256" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5257" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5257" s="9"/>
+      <c r="C5257" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5258" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B5258" s="17"/>
+      <c r="C5258" s="24"/>
+    </row>
+    <row r="5259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5259" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5259" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5259" s="24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5260" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5260" s="9"/>
+      <c r="C5260" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5261" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B5261" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5261" s="10" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5262" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5262" s="9"/>
+      <c r="C5262" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5263" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5263" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5263" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5264" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5264" s="21"/>
+      <c r="C5264" s="23"/>
+    </row>
+    <row r="5311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5311" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5311" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5311" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5312" s="4"/>
+      <c r="B5312" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5312" s="27"/>
+    </row>
+    <row r="5313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5313" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5313" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5313" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5314" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5314" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5314" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5315" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5315" s="9"/>
+      <c r="C5315" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5316" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B5316" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5316" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5317" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5317" s="9"/>
+      <c r="C5317" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5318" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5318" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5318" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5319" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5319" s="21"/>
+      <c r="C5319" s="23"/>
+    </row>
+    <row r="5370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5370" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5370" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5370" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5371" s="4"/>
+      <c r="B5371" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5371" s="32"/>
+    </row>
+    <row r="5372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5372" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5372" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5372" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5373" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5373" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5373" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5374" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5374" s="9"/>
+      <c r="C5374" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5375" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5375" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5375" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5376" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5376" s="9"/>
+      <c r="C5376" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5377" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5377" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5377" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5378" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5378" s="9"/>
+      <c r="C5378" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5379" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B5379" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5379" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5380" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5380" s="9"/>
+      <c r="C5380" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5381" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5381" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5381" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5382" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5382" s="21"/>
+      <c r="C5382" s="23"/>
+    </row>
+    <row r="5429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5429" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5429" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5429" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5430" s="4"/>
+      <c r="B5430" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5430" s="27"/>
+    </row>
+    <row r="5431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5431" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5431" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5431" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5432" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5432" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5432" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5433" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5433" s="9"/>
+      <c r="C5433" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5434" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5434" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5434" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5435" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5435" s="9"/>
+      <c r="C5435" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5436" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5436" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5436" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5437" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5437" s="9"/>
+      <c r="C5437" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5438" s="8"/>
+      <c r="B5438" s="9"/>
+      <c r="C5438" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5439" s="8"/>
+      <c r="B5439" s="9"/>
+      <c r="C5439" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5440" s="8"/>
+      <c r="B5440" s="9"/>
+      <c r="C5440" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5441" s="8"/>
+      <c r="B5441" s="9"/>
+      <c r="C5441" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5442" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B5442" s="17"/>
+      <c r="C5442" s="24"/>
+    </row>
+    <row r="5443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5443" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5443" s="17"/>
+      <c r="C5443" s="24"/>
+    </row>
+    <row r="5444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5444" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B5444" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5444" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5445" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5445" s="17"/>
+      <c r="C5445" s="24"/>
+    </row>
+    <row r="5446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5446" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B5446" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5446" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5447" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5447" s="9"/>
+      <c r="C5447" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5448" s="8"/>
+      <c r="B5448" s="9"/>
+      <c r="C5448" s="33"/>
+    </row>
+    <row r="5449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5449" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5449" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5449" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5450" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5450" s="21"/>
+      <c r="C5450" s="23"/>
+    </row>
+    <row r="5488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5488" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5488" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5488" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5489" s="4"/>
+      <c r="B5489" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5489" s="32"/>
+    </row>
+    <row r="5490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5490" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5490" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5490" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5491" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5491" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5491" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5492" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5492" s="9"/>
+      <c r="C5492" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5493" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5493" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5493" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5494" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5494" s="9"/>
+      <c r="C5494" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5495" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5495" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5495" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5496" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5496" s="9"/>
+      <c r="C5496" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5497" s="8"/>
+      <c r="B5497" s="9"/>
+      <c r="C5497" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5498" s="8"/>
+      <c r="B5498" s="9"/>
+      <c r="C5498" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5499" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B5499" s="9"/>
+      <c r="C5499" s="10"/>
+    </row>
+    <row r="5500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5500" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5500" s="9"/>
+      <c r="C5500" s="10"/>
+    </row>
+    <row r="5501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5501" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5501" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5501" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5502" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5502" s="17"/>
+      <c r="C5502" s="24"/>
+    </row>
+    <row r="5503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5503" s="16">
+        <v>5.2</v>
+      </c>
+      <c r="B5503" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5503" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5504" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5504" s="9"/>
+      <c r="C5504" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5505" s="8"/>
+      <c r="B5505" s="9"/>
+      <c r="C5505" s="33"/>
+    </row>
+    <row r="5506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5506" s="8"/>
+      <c r="B5506" s="9"/>
+      <c r="C5506" s="33"/>
+    </row>
+    <row r="5507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5507" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5507" s="9"/>
+      <c r="C5507" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5508" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B5508" s="17"/>
+      <c r="C5508" s="24"/>
+    </row>
+    <row r="5509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5509" s="16">
+        <v>7.2</v>
+      </c>
+      <c r="B5509" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5509" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5510" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B5510" s="9"/>
+      <c r="C5510" s="10"/>
+    </row>
+    <row r="5511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5511" s="19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B5511" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5511" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5512" s="8">
+        <v>9.1</v>
+      </c>
+      <c r="B5512" s="9"/>
+      <c r="C5512" s="15"/>
+    </row>
+    <row r="5513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5513" s="8">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="B5513" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5513" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5514" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5514" s="21"/>
+      <c r="C5514" s="23"/>
+    </row>
+    <row r="5547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5547" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5547" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5547" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5548" s="4"/>
+      <c r="B5548" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5548" s="32"/>
+    </row>
+    <row r="5549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5549" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5549" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5549" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5550" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5550" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5550" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5551" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5551" s="9"/>
+      <c r="C5551" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5552" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5552" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5552" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5553" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5553" s="9"/>
+      <c r="C5553" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5554" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5554" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5554" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5555" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5555" s="9"/>
+      <c r="C5555" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5556" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B5556" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5556" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5557" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5557" s="9"/>
+      <c r="C5557" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5558" s="8"/>
+      <c r="B5558" s="9"/>
+      <c r="C5558" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5559" s="8"/>
+      <c r="B5559" s="9"/>
+      <c r="C5559" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5560" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B5560" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5560" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5561" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5561" s="17"/>
+      <c r="C5561" s="24"/>
+    </row>
+    <row r="5562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5562" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B5562" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5562" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5563" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5563" s="9"/>
+      <c r="C5563" s="33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5564" s="8"/>
+      <c r="B5564" s="9"/>
+      <c r="C5564" s="33"/>
+    </row>
+    <row r="5565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5565" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5565" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5565" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5566" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5566" s="21"/>
+      <c r="C5566" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="B3955:C3955"/>
-    <mergeCell ref="C3966:C3967"/>
-    <mergeCell ref="C3854:C3855"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3719:C3719"/>
-    <mergeCell ref="C3734:C3735"/>
-    <mergeCell ref="C3559:C3561"/>
-    <mergeCell ref="C3617:C3618"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="C3675:C3677"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3382:C3383"/>
-    <mergeCell ref="C3429:C3430"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="C3266:C3267"/>
-    <mergeCell ref="C3142:C3143"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3201:C3203"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="C3030:C3031"/>
-    <mergeCell ref="C3083:C3085"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="C2914:C2915"/>
-    <mergeCell ref="B2952:C2952"/>
-    <mergeCell ref="C2967:C2968"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2727:C2729"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2788:C2789"/>
-    <mergeCell ref="B2539:C2539"/>
-    <mergeCell ref="C2609:C2611"/>
-    <mergeCell ref="C2668:C2669"/>
-    <mergeCell ref="C2428:C2429"/>
-    <mergeCell ref="C597:C598"/>
-    <mergeCell ref="C2485:C2487"/>
-    <mergeCell ref="C308:C309"/>
-    <mergeCell ref="C367:C369"/>
-    <mergeCell ref="C432:C433"/>
-    <mergeCell ref="C540:C541"/>
+  <mergeCells count="114">
+    <mergeCell ref="C5504:C5506"/>
+    <mergeCell ref="B5548:C5548"/>
+    <mergeCell ref="C5563:C5564"/>
+    <mergeCell ref="B5371:C5371"/>
+    <mergeCell ref="C5447:C5448"/>
+    <mergeCell ref="B5489:C5489"/>
+    <mergeCell ref="C5211:C5212"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5089:C5091"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="C5030:C5031"/>
+    <mergeCell ref="C4855:C4856"/>
+    <mergeCell ref="C4918:C4919"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4676:C4677"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="C4802:C4803"/>
+    <mergeCell ref="C4556:C4557"/>
+    <mergeCell ref="C4615:C4617"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4316:C4317"/>
+    <mergeCell ref="C4373:C4374"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="C4208:C4209"/>
+    <mergeCell ref="C4084:C4085"/>
+    <mergeCell ref="B4073:C4073"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="C4143:C4145"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="C2320:C2321"/>
+    <mergeCell ref="C2255:C2257"/>
+    <mergeCell ref="C2137:C2139"/>
+    <mergeCell ref="C2196:C2197"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B2303:C2303"/>
+    <mergeCell ref="C1966:C1967"/>
+    <mergeCell ref="B2008:C2008"/>
+    <mergeCell ref="C2078:C2079"/>
+    <mergeCell ref="C1847:C1848"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="C1730:C1731"/>
+    <mergeCell ref="C1788:C1790"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="C1541:C1542"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="C1665:C1666"/>
+    <mergeCell ref="C839:C841"/>
+    <mergeCell ref="C900:C901"/>
+    <mergeCell ref="C780:C781"/>
+    <mergeCell ref="B1477:C1477"/>
+    <mergeCell ref="C1494:C1495"/>
+    <mergeCell ref="C1313:C1315"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="C1378:C1379"/>
     <mergeCell ref="A27:C30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
@@ -18780,6 +24753,13 @@
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="C190:C191"/>
     <mergeCell ref="B61:C61"/>
+    <mergeCell ref="C2428:C2429"/>
+    <mergeCell ref="C597:C598"/>
+    <mergeCell ref="C2485:C2487"/>
+    <mergeCell ref="C308:C309"/>
+    <mergeCell ref="C367:C369"/>
+    <mergeCell ref="C432:C433"/>
+    <mergeCell ref="C540:C541"/>
     <mergeCell ref="B1300:C1300"/>
     <mergeCell ref="C1254:C1255"/>
     <mergeCell ref="C1143:C1144"/>
@@ -18789,36 +24769,44 @@
     <mergeCell ref="C1026:C1027"/>
     <mergeCell ref="B1005:C1005"/>
     <mergeCell ref="C1079:C1080"/>
-    <mergeCell ref="C839:C841"/>
-    <mergeCell ref="C900:C901"/>
-    <mergeCell ref="C780:C781"/>
-    <mergeCell ref="B1477:C1477"/>
-    <mergeCell ref="C1494:C1495"/>
-    <mergeCell ref="C1313:C1315"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="C1378:C1379"/>
-    <mergeCell ref="C1730:C1731"/>
-    <mergeCell ref="C1788:C1790"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="C1541:C1542"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="C1665:C1666"/>
-    <mergeCell ref="C1966:C1967"/>
-    <mergeCell ref="B2008:C2008"/>
-    <mergeCell ref="C2078:C2079"/>
-    <mergeCell ref="C1847:C1848"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="C2320:C2321"/>
-    <mergeCell ref="C2255:C2257"/>
-    <mergeCell ref="C2137:C2139"/>
-    <mergeCell ref="C2196:C2197"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B2303:C2303"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2727:C2729"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2788:C2789"/>
+    <mergeCell ref="B2539:C2539"/>
+    <mergeCell ref="C2609:C2611"/>
+    <mergeCell ref="C2668:C2669"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="C3030:C3031"/>
+    <mergeCell ref="C3083:C3085"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="C2914:C2915"/>
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="C2967:C2968"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="C3266:C3267"/>
+    <mergeCell ref="C3142:C3143"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3201:C3203"/>
+    <mergeCell ref="C3559:C3561"/>
+    <mergeCell ref="C3617:C3618"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="C3675:C3677"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3382:C3383"/>
+    <mergeCell ref="C3429:C3430"/>
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="C3966:C3967"/>
+    <mergeCell ref="C3854:C3855"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3719:C3719"/>
+    <mergeCell ref="C3734:C3735"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
+  <rowBreaks count="2" manualBreakCount="2">
     <brk id="3776" max="2" man="1"/>
+    <brk id="5192" max="2" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="4" max="1048575" man="1"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6793A4DF-CFA4-4E55-BCE0-2A6CEAD47A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2386F49-DE09-4AE8-8C9D-9B68A2A9006E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -21204,7 +21204,7 @@
       </c>
     </row>
     <row r="4258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4258" s="8">
+      <c r="A4258" s="19">
         <v>3.2</v>
       </c>
       <c r="B4258" s="9" t="s">
@@ -22843,7 +22843,7 @@
       <c r="C4914" s="10"/>
     </row>
     <row r="4915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4915" s="8">
+      <c r="A4915" s="19">
         <v>6.2</v>
       </c>
       <c r="B4915" s="9" t="s">
@@ -22861,7 +22861,7 @@
       <c r="C4916" s="24"/>
     </row>
     <row r="4917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4917" s="16">
+      <c r="A4917" s="25">
         <v>7.2</v>
       </c>
       <c r="B4917" s="17" t="s">

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F6205A-1089-416A-9DD1-CFF890011D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A6314D-3B29-412A-BC8B-F1A5F35C1A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$5957</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$6608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="353">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -8300,6 +8300,9 @@
     <t>RTS (60)</t>
   </si>
   <si>
+    <t xml:space="preserve">Inc. S by 1. </t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Inc. </t>
     </r>
@@ -9374,6 +9377,1102 @@
       </rPr>
       <t xml:space="preserve"> flag is set, skip the next cycle.</t>
     </r>
+  </si>
+  <si>
+    <t>ADC (65)</t>
+  </si>
+  <si>
+    <t>ROR (66)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $01), perform Operand.L = (Operand.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $01), perform Operand = (Operand &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 15), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (67)</t>
+  </si>
+  <si>
+    <t>PLA (68)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as Operand.L. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (69)</t>
+  </si>
+  <si>
+    <t>ROR (6A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01), perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01), perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 15), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RTL (6B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (6C)</t>
+  </si>
+  <si>
+    <t>Absolute Indirect</t>
+  </si>
+  <si>
+    <t>Read Pointer</t>
+  </si>
+  <si>
+    <t>Read Pointer + 1</t>
+  </si>
+  <si>
+    <t>ADC (6D)</t>
+  </si>
+  <si>
+    <t>ROR (6E)</t>
+  </si>
+  <si>
+    <t>ADC (6F)</t>
   </si>
 </sst>
 </file>
@@ -9978,7 +11077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C5915"/>
+  <dimension ref="A1:C6597"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -26064,7 +27163,7 @@
       </c>
       <c r="B5679" s="9"/>
       <c r="C5679" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26087,7 +27186,7 @@
     </row>
     <row r="5724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5724" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B5724" s="2" t="s">
         <v>6</v>
@@ -26257,224 +27356,224 @@
       </c>
       <c r="B5742" s="9"/>
       <c r="C5742" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5743" s="8"/>
       <c r="B5743" s="9"/>
       <c r="C5743" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5744" s="8"/>
       <c r="B5744" s="9"/>
       <c r="C5744" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5745" s="8"/>
       <c r="B5745" s="9"/>
       <c r="C5745" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5746" s="8"/>
       <c r="B5746" s="9"/>
       <c r="C5746" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5747" s="8"/>
       <c r="B5747" s="9"/>
       <c r="C5747" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5748" s="8"/>
       <c r="B5748" s="9"/>
       <c r="C5748" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5749" s="8"/>
       <c r="B5749" s="9"/>
       <c r="C5749" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5750" s="8"/>
       <c r="B5750" s="9"/>
       <c r="C5750" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5751" s="8"/>
       <c r="B5751" s="9"/>
       <c r="C5751" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5752" s="8"/>
       <c r="B5752" s="9"/>
       <c r="C5752" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5753" s="8"/>
       <c r="B5753" s="9"/>
       <c r="C5753" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5754" s="8"/>
       <c r="B5754" s="9"/>
       <c r="C5754" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5755" s="8"/>
       <c r="B5755" s="9"/>
       <c r="C5755" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5756" s="8"/>
       <c r="B5756" s="9"/>
       <c r="C5756" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5757" s="8"/>
       <c r="B5757" s="9"/>
       <c r="C5757" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5758" s="8"/>
       <c r="B5758" s="9"/>
       <c r="C5758" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5759" s="8"/>
       <c r="B5759" s="9"/>
       <c r="C5759" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5760" s="8"/>
       <c r="B5760" s="9"/>
       <c r="C5760" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5761" s="8"/>
       <c r="B5761" s="9"/>
       <c r="C5761" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5762" s="8"/>
       <c r="B5762" s="9"/>
       <c r="C5762" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5763" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5763" s="8"/>
       <c r="B5763" s="9"/>
       <c r="C5763" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5764" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5764" s="8"/>
       <c r="B5764" s="9"/>
       <c r="C5764" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5765" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5765" s="8"/>
       <c r="B5765" s="9"/>
       <c r="C5765" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5766" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5766" s="8"/>
       <c r="B5766" s="9"/>
       <c r="C5766" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5767" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5767" s="8"/>
       <c r="B5767" s="9"/>
       <c r="C5767" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5768" s="8"/>
       <c r="B5768" s="9"/>
       <c r="C5768" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5769" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5769" s="8"/>
       <c r="B5769" s="9"/>
       <c r="C5769" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5770" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5770" s="8"/>
       <c r="B5770" s="9"/>
       <c r="C5770" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5771" s="8"/>
       <c r="B5771" s="9"/>
       <c r="C5771" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5772" s="8"/>
       <c r="B5772" s="9"/>
       <c r="C5772" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5773" s="8"/>
       <c r="B5773" s="9"/>
       <c r="C5773" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26497,7 +27596,7 @@
     </row>
     <row r="5783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5783" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B5783" s="2" t="s">
         <v>6</v>
@@ -26581,7 +27680,7 @@
       </c>
       <c r="B5791" s="9"/>
       <c r="C5791" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26606,7 +27705,7 @@
         <v>88</v>
       </c>
       <c r="C5794" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26633,7 +27732,7 @@
       </c>
       <c r="B5797" s="9"/>
       <c r="C5797" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26656,7 +27755,7 @@
     </row>
     <row r="5842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5842" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B5842" s="2" t="s">
         <v>24</v>
@@ -26772,224 +27871,224 @@
       </c>
       <c r="B5854" s="9"/>
       <c r="C5854" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5855" s="8"/>
       <c r="B5855" s="9"/>
       <c r="C5855" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5856" s="8"/>
       <c r="B5856" s="9"/>
       <c r="C5856" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5857" s="8"/>
       <c r="B5857" s="9"/>
       <c r="C5857" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5858" s="8"/>
       <c r="B5858" s="9"/>
       <c r="C5858" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5859" s="8"/>
       <c r="B5859" s="9"/>
       <c r="C5859" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5860" s="8"/>
       <c r="B5860" s="9"/>
       <c r="C5860" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5861" s="8"/>
       <c r="B5861" s="9"/>
       <c r="C5861" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5862" s="8"/>
       <c r="B5862" s="9"/>
       <c r="C5862" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5863" s="8"/>
       <c r="B5863" s="9"/>
       <c r="C5863" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5864" s="8"/>
       <c r="B5864" s="9"/>
       <c r="C5864" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5865" s="8"/>
       <c r="B5865" s="9"/>
       <c r="C5865" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5866" s="8"/>
       <c r="B5866" s="9"/>
       <c r="C5866" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5867" s="8"/>
       <c r="B5867" s="9"/>
       <c r="C5867" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5868" s="8"/>
       <c r="B5868" s="9"/>
       <c r="C5868" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5869" s="8"/>
       <c r="B5869" s="9"/>
       <c r="C5869" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5870" s="8"/>
       <c r="B5870" s="9"/>
       <c r="C5870" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5871" s="8"/>
       <c r="B5871" s="9"/>
       <c r="C5871" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5872" s="8"/>
       <c r="B5872" s="9"/>
       <c r="C5872" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5873" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5873" s="8"/>
       <c r="B5873" s="9"/>
       <c r="C5873" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5874" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5874" s="8"/>
       <c r="B5874" s="9"/>
       <c r="C5874" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5875" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5875" s="8"/>
       <c r="B5875" s="9"/>
       <c r="C5875" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5876" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5876" s="8"/>
       <c r="B5876" s="9"/>
       <c r="C5876" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5877" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5877" s="8"/>
       <c r="B5877" s="9"/>
       <c r="C5877" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5878" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5878" s="8"/>
       <c r="B5878" s="9"/>
       <c r="C5878" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5879" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5879" s="8"/>
       <c r="B5879" s="9"/>
       <c r="C5879" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5880" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5880" s="8"/>
       <c r="B5880" s="9"/>
       <c r="C5880" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5881" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5881" s="8"/>
       <c r="B5881" s="9"/>
       <c r="C5881" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5882" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5882" s="8"/>
       <c r="B5882" s="9"/>
       <c r="C5882" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5883" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5883" s="8"/>
       <c r="B5883" s="9"/>
       <c r="C5883" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5884" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5884" s="8"/>
       <c r="B5884" s="9"/>
       <c r="C5884" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5885" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5885" s="8"/>
       <c r="B5885" s="9"/>
       <c r="C5885" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27012,7 +28111,7 @@
     </row>
     <row r="5901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5901" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B5901" s="2" t="s">
         <v>15</v>
@@ -27024,7 +28123,7 @@
     <row r="5902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5902" s="4"/>
       <c r="B5902" s="26" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5902" s="27"/>
     </row>
@@ -27103,7 +28202,7 @@
         <v>48</v>
       </c>
       <c r="C5910" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27121,7 +28220,7 @@
         <v>46</v>
       </c>
       <c r="C5912" s="24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27149,8 +28248,2802 @@
       <c r="B5915" s="21"/>
       <c r="C5915" s="22"/>
     </row>
+    <row r="5960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5960" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5960" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5960" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5961" s="4"/>
+      <c r="B5961" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5961" s="27"/>
+    </row>
+    <row r="5962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5962" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5962" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5962" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5963" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5963" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5963" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5964" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5964" s="9"/>
+      <c r="C5964" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5965" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5965" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5965" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5966" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B5966" s="17"/>
+      <c r="C5966" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5967" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5967" s="17"/>
+      <c r="C5967" s="24"/>
+    </row>
+    <row r="5968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5968" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5968" s="9"/>
+      <c r="C5968" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5969" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B5969" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5969" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5970" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5970" s="17"/>
+      <c r="C5970" s="24"/>
+    </row>
+    <row r="5971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5971" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B5971" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5971" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5972" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5972" s="9"/>
+      <c r="C5972" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5973" s="8"/>
+      <c r="B5973" s="9"/>
+      <c r="C5973" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5974" s="8"/>
+      <c r="B5974" s="9"/>
+      <c r="C5974" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5975" s="8"/>
+      <c r="B5975" s="9"/>
+      <c r="C5975" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5976" s="8"/>
+      <c r="B5976" s="9"/>
+      <c r="C5976" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5977" s="8"/>
+      <c r="B5977" s="9"/>
+      <c r="C5977" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5978" s="8"/>
+      <c r="B5978" s="9"/>
+      <c r="C5978" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5979" s="8"/>
+      <c r="B5979" s="9"/>
+      <c r="C5979" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5980" s="8"/>
+      <c r="B5980" s="9"/>
+      <c r="C5980" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5981" s="8"/>
+      <c r="B5981" s="9"/>
+      <c r="C5981" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5982" s="8"/>
+      <c r="B5982" s="9"/>
+      <c r="C5982" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5983" s="8"/>
+      <c r="B5983" s="9"/>
+      <c r="C5983" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5984" s="8"/>
+      <c r="B5984" s="9"/>
+      <c r="C5984" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5985" s="8"/>
+      <c r="B5985" s="9"/>
+      <c r="C5985" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5986" s="8"/>
+      <c r="B5986" s="9"/>
+      <c r="C5986" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5987" s="8"/>
+      <c r="B5987" s="9"/>
+      <c r="C5987" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5988" s="8"/>
+      <c r="B5988" s="9"/>
+      <c r="C5988" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5989" s="8"/>
+      <c r="B5989" s="9"/>
+      <c r="C5989" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5990" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5990" s="8"/>
+      <c r="B5990" s="9"/>
+      <c r="C5990" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5991" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5991" s="8"/>
+      <c r="B5991" s="9"/>
+      <c r="C5991" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5992" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5992" s="8"/>
+      <c r="B5992" s="9"/>
+      <c r="C5992" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5993" s="8"/>
+      <c r="B5993" s="9"/>
+      <c r="C5993" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5994" s="8"/>
+      <c r="B5994" s="9"/>
+      <c r="C5994" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5995" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5995" s="8"/>
+      <c r="B5995" s="9"/>
+      <c r="C5995" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5996" s="8"/>
+      <c r="B5996" s="9"/>
+      <c r="C5996" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5997" s="8"/>
+      <c r="B5997" s="9"/>
+      <c r="C5997" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5998" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5998" s="8"/>
+      <c r="B5998" s="9"/>
+      <c r="C5998" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5999" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5999" s="8"/>
+      <c r="B5999" s="9"/>
+      <c r="C5999" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6000" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6000" s="8"/>
+      <c r="B6000" s="9"/>
+      <c r="C6000" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6001" s="8"/>
+      <c r="B6001" s="9"/>
+      <c r="C6001" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6002" s="8"/>
+      <c r="B6002" s="9"/>
+      <c r="C6002" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6003" s="8"/>
+      <c r="B6003" s="9"/>
+      <c r="C6003" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6004" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6004" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6004" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6005" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6005" s="21"/>
+      <c r="C6005" s="22"/>
+    </row>
+    <row r="6019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6019" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6019" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6019" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6020" s="4"/>
+      <c r="B6020" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6020" s="27"/>
+    </row>
+    <row r="6021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6021" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6021" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6021" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6022" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6022" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6022" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6023" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6023" s="9"/>
+      <c r="C6023" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6024" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6024" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6024" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6025" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B6025" s="17"/>
+      <c r="C6025" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6026" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6026" s="17"/>
+      <c r="C6026" s="24"/>
+    </row>
+    <row r="6027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6027" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6027" s="9"/>
+      <c r="C6027" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6028" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6028" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6028" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6029" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6029" s="17"/>
+      <c r="C6029" s="24"/>
+    </row>
+    <row r="6030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6030" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="B6030" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6030" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6031" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6031" s="9"/>
+      <c r="C6031" s="33" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6032" s="8"/>
+      <c r="B6032" s="9"/>
+      <c r="C6032" s="33"/>
+    </row>
+    <row r="6033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6033" s="8"/>
+      <c r="B6033" s="9"/>
+      <c r="C6033" s="33"/>
+    </row>
+    <row r="6034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6034" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6034" s="9"/>
+      <c r="C6034" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6035" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B6035" s="17"/>
+      <c r="C6035" s="18"/>
+    </row>
+    <row r="6036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6036" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="B6036" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6036" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6037" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B6037" s="9"/>
+      <c r="C6037" s="15"/>
+    </row>
+    <row r="6038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6038" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="B6038" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6038" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6039" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B6039" s="9"/>
+      <c r="C6039" s="15"/>
+    </row>
+    <row r="6040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6040" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B6040" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6040" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6041" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6041" s="21"/>
+      <c r="C6041" s="22"/>
+    </row>
+    <row r="6078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6078" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6078" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6078" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6079" s="4"/>
+      <c r="B6079" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6079" s="32"/>
+    </row>
+    <row r="6080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6080" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6080" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6080" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6081" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6081" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6081" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6082" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6082" s="9"/>
+      <c r="C6082" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6083" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6083" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6083" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6084" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B6084" s="17"/>
+      <c r="C6084" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6085" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6085" s="17"/>
+      <c r="C6085" s="24"/>
+    </row>
+    <row r="6086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6086" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6086" s="9"/>
+      <c r="C6086" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6087" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6087" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6087" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6088" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6088" s="9"/>
+      <c r="C6088" s="10"/>
+    </row>
+    <row r="6089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6089" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6089" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6089" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6090" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6090" s="9"/>
+      <c r="C6090" s="10"/>
+    </row>
+    <row r="6091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6091" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6091" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6091" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6092" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6092" s="9"/>
+      <c r="C6092" s="10"/>
+    </row>
+    <row r="6093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6093" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B6093" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6093" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6094" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B6094" s="17"/>
+      <c r="C6094" s="24"/>
+    </row>
+    <row r="6095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6095" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B6095" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6095" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6096" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B6096" s="9"/>
+      <c r="C6096" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6097" s="8"/>
+      <c r="B6097" s="9"/>
+      <c r="C6097" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6098" s="8"/>
+      <c r="B6098" s="9"/>
+      <c r="C6098" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6099" s="8"/>
+      <c r="B6099" s="9"/>
+      <c r="C6099" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6100" s="8"/>
+      <c r="B6100" s="9"/>
+      <c r="C6100" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6101" s="8"/>
+      <c r="B6101" s="9"/>
+      <c r="C6101" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6102" s="8"/>
+      <c r="B6102" s="9"/>
+      <c r="C6102" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6103" s="8"/>
+      <c r="B6103" s="9"/>
+      <c r="C6103" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6104" s="8"/>
+      <c r="B6104" s="9"/>
+      <c r="C6104" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6105" s="8"/>
+      <c r="B6105" s="9"/>
+      <c r="C6105" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6106" s="8"/>
+      <c r="B6106" s="9"/>
+      <c r="C6106" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6107" s="8"/>
+      <c r="B6107" s="9"/>
+      <c r="C6107" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6108" s="8"/>
+      <c r="B6108" s="9"/>
+      <c r="C6108" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6109" s="8"/>
+      <c r="B6109" s="9"/>
+      <c r="C6109" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6110" s="8"/>
+      <c r="B6110" s="9"/>
+      <c r="C6110" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6111" s="8"/>
+      <c r="B6111" s="9"/>
+      <c r="C6111" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6112" s="8"/>
+      <c r="B6112" s="9"/>
+      <c r="C6112" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6113" s="8"/>
+      <c r="B6113" s="9"/>
+      <c r="C6113" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6114" s="8"/>
+      <c r="B6114" s="9"/>
+      <c r="C6114" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6115" s="8"/>
+      <c r="B6115" s="9"/>
+      <c r="C6115" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6116" s="8"/>
+      <c r="B6116" s="9"/>
+      <c r="C6116" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6117" s="8"/>
+      <c r="B6117" s="9"/>
+      <c r="C6117" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6118" s="8"/>
+      <c r="B6118" s="9"/>
+      <c r="C6118" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6119" s="8"/>
+      <c r="B6119" s="9"/>
+      <c r="C6119" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6120" s="8"/>
+      <c r="B6120" s="9"/>
+      <c r="C6120" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6121" s="8"/>
+      <c r="B6121" s="9"/>
+      <c r="C6121" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6122" s="8"/>
+      <c r="B6122" s="9"/>
+      <c r="C6122" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6123" s="8"/>
+      <c r="B6123" s="9"/>
+      <c r="C6123" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6124" s="8"/>
+      <c r="B6124" s="9"/>
+      <c r="C6124" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6125" s="8"/>
+      <c r="B6125" s="9"/>
+      <c r="C6125" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6126" s="8"/>
+      <c r="B6126" s="9"/>
+      <c r="C6126" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6127" s="8"/>
+      <c r="B6127" s="9"/>
+      <c r="C6127" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6128" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B6128" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6128" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6129" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6129" s="21"/>
+      <c r="C6129" s="22"/>
+    </row>
+    <row r="6137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6137" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B6137" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6137" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6138" s="4"/>
+      <c r="B6138" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6138" s="27"/>
+    </row>
+    <row r="6139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6139" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6139" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6139" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6140" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6140" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6140" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6141" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6141" s="9"/>
+      <c r="C6141" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6142" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6142" s="9"/>
+      <c r="C6142" s="10"/>
+    </row>
+    <row r="6143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6143" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6143" s="9"/>
+      <c r="C6143" s="10"/>
+    </row>
+    <row r="6144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6144" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6144" s="9"/>
+      <c r="C6144" s="10"/>
+    </row>
+    <row r="6145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6145" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6145" s="9"/>
+      <c r="C6145" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6146" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B6146" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6146" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6147" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6147" s="17"/>
+      <c r="C6147" s="24"/>
+    </row>
+    <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6148" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B6148" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6148" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6149" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6149" s="9"/>
+      <c r="C6149" s="33" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6150" s="8"/>
+      <c r="B6150" s="9"/>
+      <c r="C6150" s="33"/>
+    </row>
+    <row r="6151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6151" s="8"/>
+      <c r="B6151" s="9"/>
+      <c r="C6151" s="33"/>
+    </row>
+    <row r="6152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6152" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6152" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6152" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6153" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6153" s="21"/>
+      <c r="C6153" s="22"/>
+    </row>
+    <row r="6196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6196" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B6196" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6196" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6197" s="4"/>
+      <c r="B6197" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6197" s="27"/>
+    </row>
+    <row r="6198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6198" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6198" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6198" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6199" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6199" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6199" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6200" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6200" s="9"/>
+      <c r="C6200" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6201" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B6201" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6201" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6202" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B6202" s="17"/>
+      <c r="C6202" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6203" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6203" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6203" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6204" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6204" s="9"/>
+      <c r="C6204" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6205" s="8"/>
+      <c r="B6205" s="9"/>
+      <c r="C6205" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6206" s="8"/>
+      <c r="B6206" s="9"/>
+      <c r="C6206" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6207" s="8"/>
+      <c r="B6207" s="9"/>
+      <c r="C6207" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6208" s="8"/>
+      <c r="B6208" s="9"/>
+      <c r="C6208" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6209" s="8"/>
+      <c r="B6209" s="9"/>
+      <c r="C6209" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6210" s="8"/>
+      <c r="B6210" s="9"/>
+      <c r="C6210" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6211" s="8"/>
+      <c r="B6211" s="9"/>
+      <c r="C6211" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6212" s="8"/>
+      <c r="B6212" s="9"/>
+      <c r="C6212" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6213" s="8"/>
+      <c r="B6213" s="9"/>
+      <c r="C6213" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6214" s="8"/>
+      <c r="B6214" s="9"/>
+      <c r="C6214" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6215" s="8"/>
+      <c r="B6215" s="9"/>
+      <c r="C6215" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6216" s="8"/>
+      <c r="B6216" s="9"/>
+      <c r="C6216" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6217" s="8"/>
+      <c r="B6217" s="9"/>
+      <c r="C6217" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6218" s="8"/>
+      <c r="B6218" s="9"/>
+      <c r="C6218" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6219" s="8"/>
+      <c r="B6219" s="9"/>
+      <c r="C6219" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6220" s="8"/>
+      <c r="B6220" s="9"/>
+      <c r="C6220" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6221" s="8"/>
+      <c r="B6221" s="9"/>
+      <c r="C6221" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6222" s="8"/>
+      <c r="B6222" s="9"/>
+      <c r="C6222" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6223" s="8"/>
+      <c r="B6223" s="9"/>
+      <c r="C6223" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6224" s="8"/>
+      <c r="B6224" s="9"/>
+      <c r="C6224" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6225" s="8"/>
+      <c r="B6225" s="9"/>
+      <c r="C6225" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6226" s="8"/>
+      <c r="B6226" s="9"/>
+      <c r="C6226" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6227" s="8"/>
+      <c r="B6227" s="9"/>
+      <c r="C6227" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6228" s="8"/>
+      <c r="B6228" s="9"/>
+      <c r="C6228" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6229" s="8"/>
+      <c r="B6229" s="9"/>
+      <c r="C6229" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6230" s="8"/>
+      <c r="B6230" s="9"/>
+      <c r="C6230" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6231" s="8"/>
+      <c r="B6231" s="9"/>
+      <c r="C6231" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6232" s="8"/>
+      <c r="B6232" s="9"/>
+      <c r="C6232" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6233" s="8"/>
+      <c r="B6233" s="9"/>
+      <c r="C6233" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6234" s="8"/>
+      <c r="B6234" s="9"/>
+      <c r="C6234" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6235" s="8"/>
+      <c r="B6235" s="9"/>
+      <c r="C6235" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6236" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6236" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6236" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6237" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6237" s="21"/>
+      <c r="C6237" s="22"/>
+    </row>
+    <row r="6255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6255" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6255" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6255" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6256" s="4"/>
+      <c r="B6256" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6256" s="27"/>
+    </row>
+    <row r="6257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6257" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6257" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6257" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6258" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6258" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6258" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6259" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6259" s="9"/>
+      <c r="C6259" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6260" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B6260" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6260" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6261" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6261" s="9"/>
+      <c r="C6261" s="33" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6262" s="8"/>
+      <c r="B6262" s="9"/>
+      <c r="C6262" s="33"/>
+    </row>
+    <row r="6263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6263" s="8"/>
+      <c r="B6263" s="9"/>
+      <c r="C6263" s="33"/>
+    </row>
+    <row r="6264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6264" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6264" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6264" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6265" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6265" s="21"/>
+      <c r="C6265" s="22"/>
+    </row>
+    <row r="6314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6314" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6314" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6314" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6315" s="4"/>
+      <c r="B6315" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6315" s="27"/>
+    </row>
+    <row r="6316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6316" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6316" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6316" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6317" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6317" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6317" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6318" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6318" s="9"/>
+      <c r="C6318" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6319" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6319" s="9"/>
+      <c r="C6319" s="10"/>
+    </row>
+    <row r="6320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6320" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6320" s="9"/>
+      <c r="C6320" s="10"/>
+    </row>
+    <row r="6321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6321" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6321" s="9"/>
+      <c r="C6321" s="10"/>
+    </row>
+    <row r="6322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6322" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6322" s="9"/>
+      <c r="C6322" s="10"/>
+    </row>
+    <row r="6323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6323" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6323" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6323" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6324" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6324" s="9"/>
+      <c r="C6324" s="15"/>
+    </row>
+    <row r="6325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6325" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6325" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6325" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6326" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6326" s="9"/>
+      <c r="C6326" s="15"/>
+    </row>
+    <row r="6327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6327" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="B6327" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6327" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6328" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6328" s="9"/>
+      <c r="C6328" s="15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6329" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B6329" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6329" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6330" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6330" s="21"/>
+      <c r="C6330" s="22"/>
+    </row>
+    <row r="6373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6373" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6373" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6373" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6374" s="4"/>
+      <c r="B6374" s="31" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6374" s="32"/>
+    </row>
+    <row r="6375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6375" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6375" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6375" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6376" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6376" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6376" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6377" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6377" s="9"/>
+      <c r="C6377" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6378" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6378" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6378" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6379" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6379" s="9"/>
+      <c r="C6379" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6380" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6380" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6380" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6381" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6381" s="9"/>
+      <c r="C6381" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6382" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6382" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6382" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6383" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6383" s="9"/>
+      <c r="C6383" s="15"/>
+    </row>
+    <row r="6384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6384" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B6384" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6384" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6385" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6385" s="9"/>
+      <c r="C6385" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6386" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6386" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6386" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6387" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6387" s="21"/>
+      <c r="C6387" s="22"/>
+    </row>
+    <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6432" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6432" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6432" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6433" s="4"/>
+      <c r="B6433" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6433" s="27"/>
+    </row>
+    <row r="6434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6434" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6434" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6434" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6435" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6435" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6435" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6436" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6436" s="9"/>
+      <c r="C6436" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6437" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6437" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6437" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6438" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6438" s="9"/>
+      <c r="C6438" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6439" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6439" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6439" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6440" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6440" s="9"/>
+      <c r="C6440" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6441" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6441" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6441" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6442" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6442" s="9"/>
+      <c r="C6442" s="10"/>
+    </row>
+    <row r="6443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6443" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6443" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6443" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6444" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6444" s="9"/>
+      <c r="C6444" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6445" s="8"/>
+      <c r="B6445" s="9"/>
+      <c r="C6445" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6446" s="8"/>
+      <c r="B6446" s="9"/>
+      <c r="C6446" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6447" s="8"/>
+      <c r="B6447" s="9"/>
+      <c r="C6447" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6448" s="8"/>
+      <c r="B6448" s="9"/>
+      <c r="C6448" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6449" s="8"/>
+      <c r="B6449" s="9"/>
+      <c r="C6449" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6450" s="8"/>
+      <c r="B6450" s="9"/>
+      <c r="C6450" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6451" s="8"/>
+      <c r="B6451" s="9"/>
+      <c r="C6451" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6452" s="8"/>
+      <c r="B6452" s="9"/>
+      <c r="C6452" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6453" s="8"/>
+      <c r="B6453" s="9"/>
+      <c r="C6453" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6454" s="8"/>
+      <c r="B6454" s="9"/>
+      <c r="C6454" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6455" s="8"/>
+      <c r="B6455" s="9"/>
+      <c r="C6455" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6456" s="8"/>
+      <c r="B6456" s="9"/>
+      <c r="C6456" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6457" s="8"/>
+      <c r="B6457" s="9"/>
+      <c r="C6457" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6458" s="8"/>
+      <c r="B6458" s="9"/>
+      <c r="C6458" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6459" s="8"/>
+      <c r="B6459" s="9"/>
+      <c r="C6459" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6460" s="8"/>
+      <c r="B6460" s="9"/>
+      <c r="C6460" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6461" s="8"/>
+      <c r="B6461" s="9"/>
+      <c r="C6461" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6462" s="8"/>
+      <c r="B6462" s="9"/>
+      <c r="C6462" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6463" s="8"/>
+      <c r="B6463" s="9"/>
+      <c r="C6463" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6464" s="8"/>
+      <c r="B6464" s="9"/>
+      <c r="C6464" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6465" s="8"/>
+      <c r="B6465" s="9"/>
+      <c r="C6465" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6466" s="8"/>
+      <c r="B6466" s="9"/>
+      <c r="C6466" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6467" s="8"/>
+      <c r="B6467" s="9"/>
+      <c r="C6467" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6468" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6468" s="8"/>
+      <c r="B6468" s="9"/>
+      <c r="C6468" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6469" s="8"/>
+      <c r="B6469" s="9"/>
+      <c r="C6469" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6470" s="8"/>
+      <c r="B6470" s="9"/>
+      <c r="C6470" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6471" s="8"/>
+      <c r="B6471" s="9"/>
+      <c r="C6471" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6472" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6472" s="8"/>
+      <c r="B6472" s="9"/>
+      <c r="C6472" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6473" s="8"/>
+      <c r="B6473" s="9"/>
+      <c r="C6473" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6474" s="8"/>
+      <c r="B6474" s="9"/>
+      <c r="C6474" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6475" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6475" s="8"/>
+      <c r="B6475" s="9"/>
+      <c r="C6475" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6476" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6476" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6476" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6477" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6477" s="21"/>
+      <c r="C6477" s="22"/>
+    </row>
+    <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6491" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6491" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6491" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6492" s="4"/>
+      <c r="B6492" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6492" s="32"/>
+    </row>
+    <row r="6493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6493" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6493" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6493" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6494" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6494" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6494" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6495" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6495" s="9"/>
+      <c r="C6495" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6496" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6496" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6496" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6497" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6497" s="9"/>
+      <c r="C6497" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6498" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6498" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6498" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6499" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6499" s="9"/>
+      <c r="C6499" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6500" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6500" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6500" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6501" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6501" s="17"/>
+      <c r="C6501" s="24"/>
+    </row>
+    <row r="6502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6502" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="B6502" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6502" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6503" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6503" s="9"/>
+      <c r="C6503" s="33" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6504" s="8"/>
+      <c r="B6504" s="9"/>
+      <c r="C6504" s="33"/>
+    </row>
+    <row r="6505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6505" s="8"/>
+      <c r="B6505" s="9"/>
+      <c r="C6505" s="33"/>
+    </row>
+    <row r="6506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6506" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6506" s="9"/>
+      <c r="C6506" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6507" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B6507" s="17"/>
+      <c r="C6507" s="18"/>
+    </row>
+    <row r="6508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6508" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="B6508" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6508" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6509" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B6509" s="9"/>
+      <c r="C6509" s="15"/>
+    </row>
+    <row r="6510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6510" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="B6510" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6510" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6511" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B6511" s="9"/>
+      <c r="C6511" s="15"/>
+    </row>
+    <row r="6512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6512" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B6512" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6512" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6513" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6513" s="21"/>
+      <c r="C6513" s="22"/>
+    </row>
+    <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6550" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6550" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6550" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6551" s="4"/>
+      <c r="B6551" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6551" s="32"/>
+    </row>
+    <row r="6552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6552" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6552" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6552" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6553" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6553" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6553" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6554" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6554" s="9"/>
+      <c r="C6554" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6555" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6555" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6555" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6556" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6556" s="9"/>
+      <c r="C6556" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6557" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6557" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6557" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6558" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6558" s="9"/>
+      <c r="C6558" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6559" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6559" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6559" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6560" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6560" s="9"/>
+      <c r="C6560" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6561" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B6561" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6561" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6562" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6562" s="17"/>
+      <c r="C6562" s="24"/>
+    </row>
+    <row r="6563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6563" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B6563" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6563" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6564" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6564" s="9"/>
+      <c r="C6564" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6565" s="8"/>
+      <c r="B6565" s="9"/>
+      <c r="C6565" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6566" s="8"/>
+      <c r="B6566" s="9"/>
+      <c r="C6566" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6567" s="8"/>
+      <c r="B6567" s="9"/>
+      <c r="C6567" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6568" s="8"/>
+      <c r="B6568" s="9"/>
+      <c r="C6568" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6569" s="8"/>
+      <c r="B6569" s="9"/>
+      <c r="C6569" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6570" s="8"/>
+      <c r="B6570" s="9"/>
+      <c r="C6570" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6571" s="8"/>
+      <c r="B6571" s="9"/>
+      <c r="C6571" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6572" s="8"/>
+      <c r="B6572" s="9"/>
+      <c r="C6572" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6573" s="8"/>
+      <c r="B6573" s="9"/>
+      <c r="C6573" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6574" s="8"/>
+      <c r="B6574" s="9"/>
+      <c r="C6574" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6575" s="8"/>
+      <c r="B6575" s="9"/>
+      <c r="C6575" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6576" s="8"/>
+      <c r="B6576" s="9"/>
+      <c r="C6576" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6577" s="8"/>
+      <c r="B6577" s="9"/>
+      <c r="C6577" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6578" s="8"/>
+      <c r="B6578" s="9"/>
+      <c r="C6578" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6579" s="8"/>
+      <c r="B6579" s="9"/>
+      <c r="C6579" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6580" s="8"/>
+      <c r="B6580" s="9"/>
+      <c r="C6580" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6581" s="8"/>
+      <c r="B6581" s="9"/>
+      <c r="C6581" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6582" s="8"/>
+      <c r="B6582" s="9"/>
+      <c r="C6582" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6583" s="8"/>
+      <c r="B6583" s="9"/>
+      <c r="C6583" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6584" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6584" s="8"/>
+      <c r="B6584" s="9"/>
+      <c r="C6584" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6585" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6585" s="8"/>
+      <c r="B6585" s="9"/>
+      <c r="C6585" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6586" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6586" s="8"/>
+      <c r="B6586" s="9"/>
+      <c r="C6586" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6587" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6587" s="8"/>
+      <c r="B6587" s="9"/>
+      <c r="C6587" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6588" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6588" s="8"/>
+      <c r="B6588" s="9"/>
+      <c r="C6588" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6589" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6589" s="8"/>
+      <c r="B6589" s="9"/>
+      <c r="C6589" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6590" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6590" s="8"/>
+      <c r="B6590" s="9"/>
+      <c r="C6590" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6591" s="8"/>
+      <c r="B6591" s="9"/>
+      <c r="C6591" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6592" s="8"/>
+      <c r="B6592" s="9"/>
+      <c r="C6592" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6593" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6593" s="8"/>
+      <c r="B6593" s="9"/>
+      <c r="C6593" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6594" s="8"/>
+      <c r="B6594" s="9"/>
+      <c r="C6594" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6595" s="8"/>
+      <c r="B6595" s="9"/>
+      <c r="C6595" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6596" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B6596" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6596" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6597" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6597" s="21"/>
+      <c r="C6597" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="125">
+    <mergeCell ref="C6503:C6505"/>
+    <mergeCell ref="B6551:C6551"/>
+    <mergeCell ref="C6261:C6263"/>
+    <mergeCell ref="B6374:C6374"/>
+    <mergeCell ref="B6492:C6492"/>
+    <mergeCell ref="C6031:C6033"/>
+    <mergeCell ref="B6079:C6079"/>
+    <mergeCell ref="C6149:C6151"/>
     <mergeCell ref="B5725:C5725"/>
     <mergeCell ref="C5563:C5565"/>
     <mergeCell ref="B5607:C5607"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A6314D-3B29-412A-BC8B-F1A5F35C1A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D38BF9-F4DD-4766-84A4-DC552F49A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -9611,6 +9611,419 @@
     </r>
   </si>
   <si>
+    <t>ADC (69)</t>
+  </si>
+  <si>
+    <t>ROR (6A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01), perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01), perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 15), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RTL (6B)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Inc. </t>
     </r>
@@ -9633,6 +10046,95 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve"> by 3. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (6C)</t>
+  </si>
+  <si>
+    <t>Absolute Indirect</t>
+  </si>
+  <si>
+    <t>Read Pointer</t>
+  </si>
+  <si>
+    <t>Read Pointer + 1</t>
+  </si>
+  <si>
+    <t>ADC (6D)</t>
+  </si>
+  <si>
+    <t>ROR (6E)</t>
+  </si>
+  <si>
+    <t>ADC (6F)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> by 1. If </t>
     </r>
     <r>
@@ -9864,615 +10366,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <t>ADC (69)</t>
-  </si>
-  <si>
-    <t>ROR (6A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag is set, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $01), perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 1) | (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;&lt; 7), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L, otherwise set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $01), perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &gt;&gt; 1) | (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;&lt; 15), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>RTL (6B)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 3. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (Operand + 1). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Bank.</t>
-    </r>
-  </si>
-  <si>
-    <t>JMP (6C)</t>
-  </si>
-  <si>
-    <t>Absolute Indirect</t>
-  </si>
-  <si>
-    <t>Read Pointer</t>
-  </si>
-  <si>
-    <t>Read Pointer + 1</t>
-  </si>
-  <si>
-    <t>ADC (6D)</t>
-  </si>
-  <si>
-    <t>ROR (6E)</t>
-  </si>
-  <si>
-    <t>ADC (6F)</t>
   </si>
 </sst>
 </file>
@@ -29335,7 +29230,7 @@
       </c>
       <c r="B6149" s="9"/>
       <c r="C6149" s="33" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29344,31 +29239,26 @@
       <c r="C6150" s="33"/>
     </row>
     <row r="6151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6151" s="8"/>
-      <c r="B6151" s="9"/>
-      <c r="C6151" s="33"/>
+      <c r="A6151" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6151" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6151" s="10" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="6152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6152" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="B6152" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6152" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6153" s="20" t="s">
+      <c r="A6152" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B6153" s="21"/>
-      <c r="C6153" s="22"/>
+      <c r="B6152" s="21"/>
+      <c r="C6152" s="22"/>
     </row>
     <row r="6196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6196" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B6196" s="2" t="s">
         <v>22</v>
@@ -29692,7 +29582,7 @@
     </row>
     <row r="6255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6255" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B6255" s="2" t="s">
         <v>22</v>
@@ -29756,7 +29646,7 @@
       </c>
       <c r="B6261" s="9"/>
       <c r="C6261" s="33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29789,7 +29679,7 @@
     </row>
     <row r="6314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6314" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B6314" s="2" t="s">
         <v>6</v>
@@ -29917,7 +29807,7 @@
       </c>
       <c r="B6328" s="9"/>
       <c r="C6328" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29940,7 +29830,7 @@
     </row>
     <row r="6373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6373" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B6373" s="2" t="s">
         <v>19</v>
@@ -29952,7 +29842,7 @@
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="4"/>
       <c r="B6374" s="31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C6374" s="32"/>
     </row>
@@ -30032,7 +29922,7 @@
         <v>3.2</v>
       </c>
       <c r="B6382" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C6382" s="10" t="s">
         <v>16</v>
@@ -30050,7 +29940,7 @@
         <v>4.2</v>
       </c>
       <c r="B6384" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C6384" s="15" t="s">
         <v>287</v>
@@ -30085,7 +29975,7 @@
     </row>
     <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6432" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B6432" s="2" t="s">
         <v>24</v>
@@ -30447,7 +30337,7 @@
     </row>
     <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6491" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B6491" s="2" t="s">
         <v>6</v>
@@ -30654,7 +30544,7 @@
     </row>
     <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6550" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B6550" s="2" t="s">
         <v>19</v>
@@ -31043,7 +30933,7 @@
     <mergeCell ref="B6492:C6492"/>
     <mergeCell ref="C6031:C6033"/>
     <mergeCell ref="B6079:C6079"/>
-    <mergeCell ref="C6149:C6151"/>
+    <mergeCell ref="C6149:C6150"/>
     <mergeCell ref="B5725:C5725"/>
     <mergeCell ref="C5563:C5565"/>
     <mergeCell ref="B5607:C5607"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A906E32-7B6C-402B-B8DB-59E7544C3A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D92F5B9-8149-48A7-BC2E-51477D280EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$7579</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$8493</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3712" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4049" uniqueCount="424">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -10211,9 +10211,6 @@
     <t>ADC (77)</t>
   </si>
   <si>
-    <t>CLI (78)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Sets the </t>
     </r>
@@ -10988,6 +10985,1316 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>Program Counter Relative Long</t>
+  </si>
+  <si>
+    <t>SEI (78)</t>
+  </si>
+  <si>
+    <t>STA (81)</t>
+  </si>
+  <si>
+    <t>Direct Indexed Indirect (d,x) (Write)</t>
+  </si>
+  <si>
+    <t>Address = Pointer.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Pointer to Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to Pointer + 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to Pointer:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write Operand.L. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>BRL (82)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (83)</t>
+  </si>
+  <si>
+    <t>Stack Relative (Write)</t>
+  </si>
+  <si>
+    <t>STY (84)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (85)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <t>STX (86)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (87)</t>
+  </si>
+  <si>
+    <t>Direct Indirect Long (Write)</t>
+  </si>
+  <si>
+    <t>DEY (88)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L -= 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>BIT (89)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; Operand.L), otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Operand).</t>
+    </r>
+  </si>
+  <si>
+    <t>TXA (8A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>PHB (8B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>STY (8C)</t>
+  </si>
+  <si>
+    <t>Absolute (Write)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write Operand.L. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (8D)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STX (8E)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (8F)</t>
+  </si>
+  <si>
+    <t>Absolute Long (Write)</t>
+  </si>
+  <si>
+    <t>Write to Address:Bank</t>
+  </si>
+  <si>
+    <t>Write to Address + 1:Bank (With Carry)</t>
   </si>
 </sst>
 </file>
@@ -11243,6 +12550,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -11257,15 +12573,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11601,7 +12908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C7560"/>
+  <dimension ref="A1:C8451"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -11842,40 +13149,40 @@
       <c r="C25" s="22"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
+      <c r="A32" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -11890,10 +13197,10 @@
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="32"/>
+      <c r="C61" s="35"/>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
@@ -12048,14 +13355,14 @@
         <v>8.1</v>
       </c>
       <c r="B78" s="9"/>
-      <c r="C78" s="33" t="s">
+      <c r="C78" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
-      <c r="C79" s="33"/>
+      <c r="C79" s="36"/>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
@@ -12281,39 +13588,39 @@
       <c r="C139" s="23"/>
     </row>
     <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="34"/>
-      <c r="B141" s="34"/>
-      <c r="C141" s="34"/>
+      <c r="A141" s="37"/>
+      <c r="B141" s="37"/>
+      <c r="C141" s="37"/>
     </row>
     <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="34"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="34"/>
+      <c r="A142" s="37"/>
+      <c r="B142" s="37"/>
+      <c r="C142" s="37"/>
     </row>
     <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="34"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="34"/>
+      <c r="A143" s="37"/>
+      <c r="B143" s="37"/>
+      <c r="C143" s="37"/>
     </row>
     <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="34"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="34"/>
+      <c r="A144" s="37"/>
+      <c r="B144" s="37"/>
+      <c r="C144" s="37"/>
     </row>
     <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="34"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="34"/>
+      <c r="A145" s="37"/>
+      <c r="B145" s="37"/>
+      <c r="C145" s="37"/>
     </row>
     <row r="146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="34"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="34"/>
+      <c r="A146" s="37"/>
+      <c r="B146" s="37"/>
+      <c r="C146" s="37"/>
     </row>
     <row r="147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="34"/>
-      <c r="B147" s="34"/>
-      <c r="C147" s="34"/>
+      <c r="A147" s="37"/>
+      <c r="B147" s="37"/>
+      <c r="C147" s="37"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
@@ -12432,14 +13739,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B190" s="9"/>
-      <c r="C190" s="33" t="s">
+      <c r="C190" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
-      <c r="C191" s="33"/>
+      <c r="C191" s="36"/>
     </row>
     <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
@@ -12578,14 +13885,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B249" s="9"/>
-      <c r="C249" s="33" t="s">
+      <c r="C249" s="36" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8"/>
       <c r="B250" s="9"/>
-      <c r="C250" s="33"/>
+      <c r="C250" s="36"/>
     </row>
     <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8">
@@ -12776,14 +14083,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B308" s="9"/>
-      <c r="C308" s="33" t="s">
+      <c r="C308" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="8"/>
       <c r="B309" s="9"/>
-      <c r="C309" s="33"/>
+      <c r="C309" s="36"/>
     </row>
     <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8">
@@ -12922,19 +14229,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="9"/>
-      <c r="C367" s="33" t="s">
+      <c r="C367" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
-      <c r="C368" s="33"/>
+      <c r="C368" s="36"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="8"/>
       <c r="B369" s="9"/>
-      <c r="C369" s="33"/>
+      <c r="C369" s="36"/>
     </row>
     <row r="370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8">
@@ -13167,7 +14474,7 @@
       <c r="A431" s="25">
         <v>7.2</v>
       </c>
-      <c r="B431" s="36" t="s">
+      <c r="B431" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C431" s="18" t="s">
@@ -13176,7 +14483,7 @@
     </row>
     <row r="432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="25"/>
-      <c r="B432" s="36"/>
+      <c r="B432" s="33"/>
       <c r="C432" s="18"/>
     </row>
     <row r="433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13184,14 +14491,14 @@
         <v>8.1</v>
       </c>
       <c r="B433" s="9"/>
-      <c r="C433" s="33" t="s">
+      <c r="C433" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8"/>
       <c r="B434" s="9"/>
-      <c r="C434" s="33"/>
+      <c r="C434" s="36"/>
     </row>
     <row r="435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="8">
@@ -13399,14 +14706,14 @@
         <v>3.1</v>
       </c>
       <c r="B540" s="9"/>
-      <c r="C540" s="33" t="s">
+      <c r="C540" s="36" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="8"/>
       <c r="B541" s="9"/>
-      <c r="C541" s="33"/>
+      <c r="C541" s="36"/>
     </row>
     <row r="542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="8">
@@ -13491,14 +14798,14 @@
         <v>2.1</v>
       </c>
       <c r="B597" s="9"/>
-      <c r="C597" s="33" t="s">
+      <c r="C597" s="36" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="8"/>
       <c r="B598" s="9"/>
-      <c r="C598" s="33"/>
+      <c r="C598" s="36"/>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="8">
@@ -13955,14 +15262,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B780" s="9"/>
-      <c r="C780" s="33" t="s">
+      <c r="C780" s="36" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="8"/>
       <c r="B781" s="9"/>
-      <c r="C781" s="33"/>
+      <c r="C781" s="36"/>
     </row>
     <row r="782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="8">
@@ -14105,19 +15412,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B839" s="9"/>
-      <c r="C839" s="33" t="s">
+      <c r="C839" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
-      <c r="C840" s="33"/>
+      <c r="C840" s="36"/>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="8"/>
       <c r="B841" s="9"/>
-      <c r="C841" s="33"/>
+      <c r="C841" s="36"/>
     </row>
     <row r="842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="8">
@@ -14320,7 +15627,7 @@
       <c r="A899" s="25">
         <v>5.2</v>
       </c>
-      <c r="B899" s="36" t="s">
+      <c r="B899" s="33" t="s">
         <v>351</v>
       </c>
       <c r="C899" s="18" t="s">
@@ -14329,7 +15636,7 @@
     </row>
     <row r="900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="25"/>
-      <c r="B900" s="36"/>
+      <c r="B900" s="33"/>
       <c r="C900" s="18"/>
     </row>
     <row r="901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14337,14 +15644,14 @@
         <v>6.1</v>
       </c>
       <c r="B901" s="9"/>
-      <c r="C901" s="33" t="s">
+      <c r="C901" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="8"/>
       <c r="B902" s="9"/>
-      <c r="C902" s="33"/>
+      <c r="C902" s="36"/>
     </row>
     <row r="903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="8">
@@ -14482,10 +15789,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="4"/>
-      <c r="B1005" s="31" t="s">
+      <c r="B1005" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C1005" s="32"/>
+      <c r="C1005" s="35"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="13" t="s">
@@ -14656,7 +15963,7 @@
       <c r="A1025" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1025" s="36" t="s">
+      <c r="B1025" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1025" s="18" t="s">
@@ -14665,7 +15972,7 @@
     </row>
     <row r="1026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="25"/>
-      <c r="B1026" s="36"/>
+      <c r="B1026" s="33"/>
       <c r="C1026" s="18"/>
     </row>
     <row r="1027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14673,14 +15980,14 @@
         <v>8.1</v>
       </c>
       <c r="B1027" s="9"/>
-      <c r="C1027" s="33" t="s">
+      <c r="C1027" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="8"/>
       <c r="B1028" s="9"/>
-      <c r="C1028" s="33"/>
+      <c r="C1028" s="36"/>
     </row>
     <row r="1029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="8">
@@ -14855,14 +16162,14 @@
         <v>7.1</v>
       </c>
       <c r="B1079" s="9"/>
-      <c r="C1079" s="33" t="s">
+      <c r="C1079" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="8"/>
       <c r="B1080" s="9"/>
-      <c r="C1080" s="33"/>
+      <c r="C1080" s="36"/>
     </row>
     <row r="1081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="8">
@@ -14895,10 +16202,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="4"/>
-      <c r="B1123" s="31" t="s">
+      <c r="B1123" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C1123" s="32"/>
+      <c r="C1123" s="35"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="13" t="s">
@@ -15060,7 +16367,7 @@
       <c r="A1142" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1142" s="36" t="s">
+      <c r="B1142" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1142" s="24" t="s">
@@ -15069,7 +16376,7 @@
     </row>
     <row r="1143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1143" s="25"/>
-      <c r="B1143" s="36"/>
+      <c r="B1143" s="33"/>
       <c r="C1143" s="24"/>
     </row>
     <row r="1144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15077,14 +16384,14 @@
         <v>8.1</v>
       </c>
       <c r="B1144" s="9"/>
-      <c r="C1144" s="33" t="s">
+      <c r="C1144" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="8"/>
       <c r="B1145" s="9"/>
-      <c r="C1145" s="33"/>
+      <c r="C1145" s="36"/>
     </row>
     <row r="1146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1146" s="8">
@@ -15117,10 +16424,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="4"/>
-      <c r="B1182" s="31" t="s">
+      <c r="B1182" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C1182" s="32"/>
+      <c r="C1182" s="35"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="13" t="s">
@@ -15223,14 +16530,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1193" s="9"/>
-      <c r="C1193" s="33" t="s">
+      <c r="C1193" s="36" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="1194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1194" s="8"/>
       <c r="B1194" s="9"/>
-      <c r="C1194" s="33"/>
+      <c r="C1194" s="36"/>
     </row>
     <row r="1195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1195" s="8">
@@ -15435,14 +16742,14 @@
         <v>6.1</v>
       </c>
       <c r="B1254" s="9"/>
-      <c r="C1254" s="33" t="s">
+      <c r="C1254" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1255" s="8"/>
       <c r="B1255" s="9"/>
-      <c r="C1255" s="33"/>
+      <c r="C1255" s="36"/>
     </row>
     <row r="1256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1256" s="8">
@@ -15475,10 +16782,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
-      <c r="B1300" s="31" t="s">
+      <c r="B1300" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="C1300" s="32"/>
+      <c r="C1300" s="35"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="13" t="s">
@@ -15595,19 +16902,19 @@
         <v>6.1</v>
       </c>
       <c r="B1313" s="9"/>
-      <c r="C1313" s="33" t="s">
+      <c r="C1313" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="1314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="8"/>
       <c r="B1314" s="9"/>
-      <c r="C1314" s="33"/>
+      <c r="C1314" s="36"/>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
-      <c r="C1315" s="33"/>
+      <c r="C1315" s="36"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="8">
@@ -15692,10 +16999,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="4"/>
-      <c r="B1359" s="31" t="s">
+      <c r="B1359" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C1359" s="32"/>
+      <c r="C1359" s="35"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="13" t="s">
@@ -15856,7 +17163,7 @@
       <c r="A1377" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1377" s="36" t="s">
+      <c r="B1377" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1377" s="18" t="s">
@@ -15865,7 +17172,7 @@
     </row>
     <row r="1378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1378" s="25"/>
-      <c r="B1378" s="36"/>
+      <c r="B1378" s="33"/>
       <c r="C1378" s="18"/>
     </row>
     <row r="1379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15873,14 +17180,14 @@
         <v>8.1</v>
       </c>
       <c r="B1379" s="9"/>
-      <c r="C1379" s="33" t="s">
+      <c r="C1379" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="8"/>
       <c r="B1380" s="9"/>
-      <c r="C1380" s="33"/>
+      <c r="C1380" s="36"/>
     </row>
     <row r="1381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1381" s="8">
@@ -16000,10 +17307,10 @@
     </row>
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="4"/>
-      <c r="B1477" s="31" t="s">
+      <c r="B1477" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="C1477" s="32"/>
+      <c r="C1477" s="35"/>
     </row>
     <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1478" s="13" t="s">
@@ -16140,7 +17447,7 @@
       <c r="A1493" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1493" s="36" t="s">
+      <c r="B1493" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1493" s="24" t="s">
@@ -16149,7 +17456,7 @@
     </row>
     <row r="1494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1494" s="25"/>
-      <c r="B1494" s="36"/>
+      <c r="B1494" s="33"/>
       <c r="C1494" s="24"/>
     </row>
     <row r="1495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16157,14 +17464,14 @@
         <v>6.1</v>
       </c>
       <c r="B1495" s="9"/>
-      <c r="C1495" s="33" t="s">
+      <c r="C1495" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1496" s="8"/>
       <c r="B1496" s="9"/>
-      <c r="C1496" s="33"/>
+      <c r="C1496" s="36"/>
     </row>
     <row r="1497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1497" s="8">
@@ -16249,14 +17556,14 @@
         <v>2.1</v>
       </c>
       <c r="B1541" s="9"/>
-      <c r="C1541" s="33" t="s">
+      <c r="C1541" s="36" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1542" s="8"/>
       <c r="B1542" s="9"/>
-      <c r="C1542" s="33"/>
+      <c r="C1542" s="36"/>
     </row>
     <row r="1543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1543" s="8">
@@ -16376,10 +17683,10 @@
     </row>
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="4"/>
-      <c r="B1654" s="31" t="s">
+      <c r="B1654" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C1654" s="32"/>
+      <c r="C1654" s="35"/>
     </row>
     <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1655" s="13" t="s">
@@ -16486,14 +17793,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1665" s="9"/>
-      <c r="C1665" s="33" t="s">
+      <c r="C1665" s="36" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="1666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1666" s="8"/>
       <c r="B1666" s="9"/>
-      <c r="C1666" s="33"/>
+      <c r="C1666" s="36"/>
     </row>
     <row r="1667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1667" s="8">
@@ -16718,7 +18025,7 @@
       <c r="A1729" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1729" s="36" t="s">
+      <c r="B1729" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1729" s="24" t="s">
@@ -16727,7 +18034,7 @@
     </row>
     <row r="1730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1730" s="25"/>
-      <c r="B1730" s="36"/>
+      <c r="B1730" s="33"/>
       <c r="C1730" s="24"/>
     </row>
     <row r="1731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16735,14 +18042,14 @@
         <v>6.1</v>
       </c>
       <c r="B1731" s="9"/>
-      <c r="C1731" s="33" t="s">
+      <c r="C1731" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1732" s="8"/>
       <c r="B1732" s="9"/>
-      <c r="C1732" s="33"/>
+      <c r="C1732" s="36"/>
     </row>
     <row r="1733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1733" s="8">
@@ -16775,10 +18082,10 @@
     </row>
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="4"/>
-      <c r="B1772" s="31" t="s">
+      <c r="B1772" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="C1772" s="32"/>
+      <c r="C1772" s="35"/>
     </row>
     <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1773" s="13" t="s">
@@ -16908,7 +18215,7 @@
       <c r="A1787" s="16">
         <v>5.2</v>
       </c>
-      <c r="B1787" s="36" t="s">
+      <c r="B1787" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1787" s="24" t="s">
@@ -16917,7 +18224,7 @@
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="16"/>
-      <c r="B1788" s="36"/>
+      <c r="B1788" s="33"/>
       <c r="C1788" s="24"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16925,19 +18232,19 @@
         <v>6.1</v>
       </c>
       <c r="B1789" s="9"/>
-      <c r="C1789" s="33" t="s">
+      <c r="C1789" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="1790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1790" s="8"/>
       <c r="B1790" s="9"/>
-      <c r="C1790" s="33"/>
+      <c r="C1790" s="36"/>
     </row>
     <row r="1791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1791" s="8"/>
       <c r="B1791" s="9"/>
-      <c r="C1791" s="33"/>
+      <c r="C1791" s="36"/>
     </row>
     <row r="1792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1792" s="8">
@@ -16959,7 +18266,7 @@
       <c r="A1794" s="16">
         <v>7.2</v>
       </c>
-      <c r="B1794" s="36" t="s">
+      <c r="B1794" s="33" t="s">
         <v>352</v>
       </c>
       <c r="C1794" s="24" t="s">
@@ -16968,7 +18275,7 @@
     </row>
     <row r="1795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1795" s="16"/>
-      <c r="B1795" s="36"/>
+      <c r="B1795" s="33"/>
       <c r="C1795" s="24"/>
     </row>
     <row r="1796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17166,7 +18473,7 @@
       <c r="A1846" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1846" s="36" t="s">
+      <c r="B1846" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C1846" s="24" t="s">
@@ -17175,7 +18482,7 @@
     </row>
     <row r="1847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1847" s="25"/>
-      <c r="B1847" s="36"/>
+      <c r="B1847" s="33"/>
       <c r="C1847" s="24"/>
     </row>
     <row r="1848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17183,14 +18490,14 @@
         <v>6.1</v>
       </c>
       <c r="B1848" s="9"/>
-      <c r="C1848" s="33" t="s">
+      <c r="C1848" s="36" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="1849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1849" s="8"/>
       <c r="B1849" s="9"/>
-      <c r="C1849" s="33"/>
+      <c r="C1849" s="36"/>
     </row>
     <row r="1850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1850" s="8">
@@ -17388,10 +18695,10 @@
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1949" s="4"/>
-      <c r="B1949" s="31" t="s">
+      <c r="B1949" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C1949" s="32"/>
+      <c r="C1949" s="35"/>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1950" s="13" t="s">
@@ -17546,14 +18853,14 @@
         <v>8.1</v>
       </c>
       <c r="B1966" s="9"/>
-      <c r="C1966" s="33" t="s">
+      <c r="C1966" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="1967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1967" s="8"/>
       <c r="B1967" s="9"/>
-      <c r="C1967" s="33"/>
+      <c r="C1967" s="36"/>
     </row>
     <row r="1968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1968" s="8">
@@ -17586,10 +18893,10 @@
     </row>
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="4"/>
-      <c r="B2008" s="31" t="s">
+      <c r="B2008" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="C2008" s="32"/>
+      <c r="C2008" s="35"/>
     </row>
     <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2009" s="13" t="s">
@@ -17889,14 +19196,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2078" s="9"/>
-      <c r="C2078" s="33" t="s">
+      <c r="C2078" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2079" s="8"/>
       <c r="B2079" s="9"/>
-      <c r="C2079" s="33"/>
+      <c r="C2079" s="36"/>
     </row>
     <row r="2080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2080" s="8">
@@ -18035,19 +19342,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2137" s="9"/>
-      <c r="C2137" s="33" t="s">
+      <c r="C2137" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="2138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2138" s="8"/>
       <c r="B2138" s="9"/>
-      <c r="C2138" s="33"/>
+      <c r="C2138" s="36"/>
     </row>
     <row r="2139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2139" s="8"/>
       <c r="B2139" s="9"/>
-      <c r="C2139" s="33"/>
+      <c r="C2139" s="36"/>
     </row>
     <row r="2140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2140" s="8">
@@ -18186,14 +19493,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2196" s="9"/>
-      <c r="C2196" s="33" t="s">
+      <c r="C2196" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2197" s="8"/>
       <c r="B2197" s="9"/>
-      <c r="C2197" s="33"/>
+      <c r="C2197" s="36"/>
     </row>
     <row r="2198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2198" s="8">
@@ -18226,10 +19533,10 @@
     </row>
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="4"/>
-      <c r="B2244" s="31" t="s">
+      <c r="B2244" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C2244" s="32"/>
+      <c r="C2244" s="35"/>
     </row>
     <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2245" s="13" t="s">
@@ -18332,19 +19639,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="9"/>
-      <c r="C2255" s="33" t="s">
+      <c r="C2255" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="8"/>
       <c r="B2256" s="9"/>
-      <c r="C2256" s="33"/>
+      <c r="C2256" s="36"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="8"/>
       <c r="B2257" s="9"/>
-      <c r="C2257" s="33"/>
+      <c r="C2257" s="36"/>
     </row>
     <row r="2258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2258" s="8">
@@ -18429,10 +19736,10 @@
     </row>
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="4"/>
-      <c r="B2303" s="31" t="s">
+      <c r="B2303" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="C2303" s="32"/>
+      <c r="C2303" s="35"/>
     </row>
     <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2304" s="13" t="s">
@@ -18577,7 +19884,7 @@
       <c r="A2319" s="25">
         <v>7.2</v>
       </c>
-      <c r="B2319" s="36" t="s">
+      <c r="B2319" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C2319" s="18" t="s">
@@ -18586,7 +19893,7 @@
     </row>
     <row r="2320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2320" s="25"/>
-      <c r="B2320" s="36"/>
+      <c r="B2320" s="33"/>
       <c r="C2320" s="18"/>
     </row>
     <row r="2321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18594,14 +19901,14 @@
         <v>8.1</v>
       </c>
       <c r="B2321" s="9"/>
-      <c r="C2321" s="33" t="s">
+      <c r="C2321" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2322" s="8"/>
       <c r="B2322" s="9"/>
-      <c r="C2322" s="33"/>
+      <c r="C2322" s="36"/>
     </row>
     <row r="2323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2323" s="8">
@@ -18823,14 +20130,14 @@
         <v>3.1</v>
       </c>
       <c r="B2428" s="9"/>
-      <c r="C2428" s="33" t="s">
+      <c r="C2428" s="36" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="2429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2429" s="8"/>
       <c r="B2429" s="9"/>
-      <c r="C2429" s="33"/>
+      <c r="C2429" s="36"/>
     </row>
     <row r="2430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2430" s="8">
@@ -18915,19 +20222,19 @@
         <v>2.1</v>
       </c>
       <c r="B2485" s="9"/>
-      <c r="C2485" s="33" t="s">
+      <c r="C2485" s="36" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2486" s="8"/>
       <c r="B2486" s="9"/>
-      <c r="C2486" s="33"/>
+      <c r="C2486" s="36"/>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2487" s="8"/>
       <c r="B2487" s="9"/>
-      <c r="C2487" s="33"/>
+      <c r="C2487" s="36"/>
     </row>
     <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2488" s="8">
@@ -18960,10 +20267,10 @@
     </row>
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="4"/>
-      <c r="B2539" s="31" t="s">
+      <c r="B2539" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2539" s="32"/>
+      <c r="C2539" s="35"/>
     </row>
     <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2540" s="13" t="s">
@@ -19203,19 +20510,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2609" s="9"/>
-      <c r="C2609" s="33" t="s">
+      <c r="C2609" s="36" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2610" s="8"/>
       <c r="B2610" s="9"/>
-      <c r="C2610" s="33"/>
+      <c r="C2610" s="36"/>
     </row>
     <row r="2611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2611" s="8"/>
       <c r="B2611" s="9"/>
-      <c r="C2611" s="33"/>
+      <c r="C2611" s="36"/>
     </row>
     <row r="2612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2612" s="8">
@@ -19358,14 +20665,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2668" s="9"/>
-      <c r="C2668" s="33" t="s">
+      <c r="C2668" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2669" s="8"/>
       <c r="B2669" s="9"/>
-      <c r="C2669" s="33"/>
+      <c r="C2669" s="36"/>
     </row>
     <row r="2670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2670" s="8">
@@ -19398,10 +20705,10 @@
     </row>
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="4"/>
-      <c r="B2716" s="31" t="s">
+      <c r="B2716" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C2716" s="32"/>
+      <c r="C2716" s="35"/>
     </row>
     <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2717" s="13" t="s">
@@ -19508,19 +20815,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2727" s="9"/>
-      <c r="C2727" s="33" t="s">
+      <c r="C2727" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2728" s="8"/>
       <c r="B2728" s="9"/>
-      <c r="C2728" s="33"/>
+      <c r="C2728" s="36"/>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="8"/>
       <c r="B2729" s="9"/>
-      <c r="C2729" s="33"/>
+      <c r="C2729" s="36"/>
     </row>
     <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2730" s="8">
@@ -19605,10 +20912,10 @@
     </row>
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="4"/>
-      <c r="B2775" s="31" t="s">
+      <c r="B2775" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C2775" s="32"/>
+      <c r="C2775" s="35"/>
     </row>
     <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2776" s="13" t="s">
@@ -19723,7 +21030,7 @@
       <c r="A2787" s="25">
         <v>5.2</v>
       </c>
-      <c r="B2787" s="36" t="s">
+      <c r="B2787" s="33" t="s">
         <v>351</v>
       </c>
       <c r="C2787" s="24" t="s">
@@ -19732,7 +21039,7 @@
     </row>
     <row r="2788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2788" s="25"/>
-      <c r="B2788" s="36"/>
+      <c r="B2788" s="33"/>
       <c r="C2788" s="24"/>
     </row>
     <row r="2789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19740,14 +21047,14 @@
         <v>6.1</v>
       </c>
       <c r="B2789" s="9"/>
-      <c r="C2789" s="33" t="s">
+      <c r="C2789" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2790" s="8"/>
       <c r="B2790" s="9"/>
-      <c r="C2790" s="33"/>
+      <c r="C2790" s="36"/>
     </row>
     <row r="2791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2791" s="8">
@@ -19885,10 +21192,10 @@
     </row>
     <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2893" s="4"/>
-      <c r="B2893" s="31" t="s">
+      <c r="B2893" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C2893" s="32"/>
+      <c r="C2893" s="35"/>
     </row>
     <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2894" s="13" t="s">
@@ -20059,7 +21366,7 @@
       <c r="A2913" s="25">
         <v>7.2</v>
       </c>
-      <c r="B2913" s="36" t="s">
+      <c r="B2913" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C2913" s="24" t="s">
@@ -20068,7 +21375,7 @@
     </row>
     <row r="2914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2914" s="25"/>
-      <c r="B2914" s="36"/>
+      <c r="B2914" s="33"/>
       <c r="C2914" s="24"/>
     </row>
     <row r="2915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20076,14 +21383,14 @@
         <v>8.1</v>
       </c>
       <c r="B2915" s="9"/>
-      <c r="C2915" s="33" t="s">
+      <c r="C2915" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2916" s="8"/>
       <c r="B2916" s="9"/>
-      <c r="C2916" s="33"/>
+      <c r="C2916" s="36"/>
     </row>
     <row r="2917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2917" s="8">
@@ -20116,10 +21423,10 @@
     </row>
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="4"/>
-      <c r="B2952" s="31" t="s">
+      <c r="B2952" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="C2952" s="32"/>
+      <c r="C2952" s="35"/>
     </row>
     <row r="2953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2953" s="13" t="s">
@@ -20258,14 +21565,14 @@
         <v>7.1</v>
       </c>
       <c r="B2967" s="9"/>
-      <c r="C2967" s="33" t="s">
+      <c r="C2967" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2968" s="8"/>
       <c r="B2968" s="9"/>
-      <c r="C2968" s="33"/>
+      <c r="C2968" s="36"/>
     </row>
     <row r="2969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2969" s="8">
@@ -20298,10 +21605,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="4"/>
-      <c r="B3011" s="31" t="s">
+      <c r="B3011" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C3011" s="32"/>
+      <c r="C3011" s="35"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="13" t="s">
@@ -20456,7 +21763,7 @@
       <c r="A3029" s="25">
         <v>7.2</v>
       </c>
-      <c r="B3029" s="36" t="s">
+      <c r="B3029" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3029" s="24" t="s">
@@ -20465,7 +21772,7 @@
     </row>
     <row r="3030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3030" s="25"/>
-      <c r="B3030" s="36"/>
+      <c r="B3030" s="33"/>
       <c r="C3030" s="24"/>
     </row>
     <row r="3031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20473,14 +21780,14 @@
         <v>8.1</v>
       </c>
       <c r="B3031" s="9"/>
-      <c r="C3031" s="33" t="s">
+      <c r="C3031" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3032" s="8"/>
       <c r="B3032" s="9"/>
-      <c r="C3032" s="33"/>
+      <c r="C3032" s="36"/>
     </row>
     <row r="3033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3033" s="8">
@@ -20633,19 +21940,19 @@
         <v>6.1</v>
       </c>
       <c r="B3083" s="9"/>
-      <c r="C3083" s="33" t="s">
+      <c r="C3083" s="36" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="3084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3084" s="8"/>
       <c r="B3084" s="9"/>
-      <c r="C3084" s="33"/>
+      <c r="C3084" s="36"/>
     </row>
     <row r="3085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3085" s="8"/>
       <c r="B3085" s="9"/>
-      <c r="C3085" s="33"/>
+      <c r="C3085" s="36"/>
     </row>
     <row r="3086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3086" s="8">
@@ -20798,14 +22105,14 @@
         <v>6.1</v>
       </c>
       <c r="B3142" s="9"/>
-      <c r="C3142" s="33" t="s">
+      <c r="C3142" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3143" s="8"/>
       <c r="B3143" s="9"/>
-      <c r="C3143" s="33"/>
+      <c r="C3143" s="36"/>
     </row>
     <row r="3144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3144" s="8">
@@ -20838,10 +22145,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="4"/>
-      <c r="B3188" s="31" t="s">
+      <c r="B3188" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="C3188" s="32"/>
+      <c r="C3188" s="35"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="13" t="s">
@@ -20958,19 +22265,19 @@
         <v>6.1</v>
       </c>
       <c r="B3201" s="9"/>
-      <c r="C3201" s="33" t="s">
+      <c r="C3201" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3202" s="8"/>
       <c r="B3202" s="9"/>
-      <c r="C3202" s="33"/>
+      <c r="C3202" s="36"/>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="8"/>
       <c r="B3203" s="9"/>
-      <c r="C3203" s="33"/>
+      <c r="C3203" s="36"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="8">
@@ -21055,10 +22362,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="4"/>
-      <c r="B3247" s="31" t="s">
+      <c r="B3247" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C3247" s="32"/>
+      <c r="C3247" s="35"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="13" t="s">
@@ -21219,7 +22526,7 @@
       <c r="A3265" s="25">
         <v>7.2</v>
       </c>
-      <c r="B3265" s="36" t="s">
+      <c r="B3265" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3265" s="24" t="s">
@@ -21228,7 +22535,7 @@
     </row>
     <row r="3266" spans="1:3" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3266" s="25"/>
-      <c r="B3266" s="36"/>
+      <c r="B3266" s="33"/>
       <c r="C3266" s="24"/>
     </row>
     <row r="3267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21236,14 +22543,14 @@
         <v>8.1</v>
       </c>
       <c r="B3267" s="9"/>
-      <c r="C3267" s="33" t="s">
+      <c r="C3267" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3268" s="8"/>
       <c r="B3268" s="9"/>
-      <c r="C3268" s="33"/>
+      <c r="C3268" s="36"/>
     </row>
     <row r="3269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3269" s="8">
@@ -21363,10 +22670,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="4"/>
-      <c r="B3365" s="31" t="s">
+      <c r="B3365" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="C3365" s="32"/>
+      <c r="C3365" s="35"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="13" t="s">
@@ -21503,7 +22810,7 @@
       <c r="A3381" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3381" s="36" t="s">
+      <c r="B3381" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3381" s="18" t="s">
@@ -21512,7 +22819,7 @@
     </row>
     <row r="3382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3382" s="25"/>
-      <c r="B3382" s="36"/>
+      <c r="B3382" s="33"/>
       <c r="C3382" s="18"/>
     </row>
     <row r="3383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21520,14 +22827,14 @@
         <v>6.1</v>
       </c>
       <c r="B3383" s="9"/>
-      <c r="C3383" s="33" t="s">
+      <c r="C3383" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3384" s="8"/>
       <c r="B3384" s="9"/>
-      <c r="C3384" s="33"/>
+      <c r="C3384" s="36"/>
     </row>
     <row r="3385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3385" s="8">
@@ -21612,14 +22919,14 @@
         <v>2.1</v>
       </c>
       <c r="B3429" s="9"/>
-      <c r="C3429" s="33" t="s">
+      <c r="C3429" s="36" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3430" s="8"/>
       <c r="B3430" s="9"/>
-      <c r="C3430" s="33"/>
+      <c r="C3430" s="36"/>
     </row>
     <row r="3431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3431" s="8">
@@ -21879,7 +23186,7 @@
       <c r="A3558" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3558" s="36" t="s">
+      <c r="B3558" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3558" s="24" t="s">
@@ -21888,7 +23195,7 @@
     </row>
     <row r="3559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3559" s="25"/>
-      <c r="B3559" s="36"/>
+      <c r="B3559" s="33"/>
       <c r="C3559" s="24"/>
     </row>
     <row r="3560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21896,19 +23203,19 @@
         <v>6.1</v>
       </c>
       <c r="B3560" s="9"/>
-      <c r="C3560" s="33" t="s">
+      <c r="C3560" s="36" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="3561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3561" s="8"/>
       <c r="B3561" s="9"/>
-      <c r="C3561" s="33"/>
+      <c r="C3561" s="36"/>
     </row>
     <row r="3562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3562" s="8"/>
       <c r="B3562" s="9"/>
-      <c r="C3562" s="33"/>
+      <c r="C3562" s="36"/>
     </row>
     <row r="3563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3563" s="8">
@@ -22074,7 +23381,7 @@
       <c r="A3616" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3616" s="36" t="s">
+      <c r="B3616" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3616" s="24" t="s">
@@ -22083,7 +23390,7 @@
     </row>
     <row r="3617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3617" s="25"/>
-      <c r="B3617" s="36"/>
+      <c r="B3617" s="33"/>
       <c r="C3617" s="24"/>
     </row>
     <row r="3618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22091,14 +23398,14 @@
         <v>6.1</v>
       </c>
       <c r="B3618" s="9"/>
-      <c r="C3618" s="33" t="s">
+      <c r="C3618" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3619" s="8"/>
       <c r="B3619" s="9"/>
-      <c r="C3619" s="33"/>
+      <c r="C3619" s="36"/>
     </row>
     <row r="3620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3620" s="8">
@@ -22131,10 +23438,10 @@
     </row>
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="4"/>
-      <c r="B3660" s="31" t="s">
+      <c r="B3660" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="C3660" s="32"/>
+      <c r="C3660" s="35"/>
     </row>
     <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3661" s="13" t="s">
@@ -22257,7 +23564,7 @@
       <c r="A3674" s="16">
         <v>5.2</v>
       </c>
-      <c r="B3674" s="36" t="s">
+      <c r="B3674" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3674" s="24" t="s">
@@ -22266,7 +23573,7 @@
     </row>
     <row r="3675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3675" s="16"/>
-      <c r="B3675" s="36"/>
+      <c r="B3675" s="33"/>
       <c r="C3675" s="24"/>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22274,19 +23581,19 @@
         <v>6.1</v>
       </c>
       <c r="B3676" s="9"/>
-      <c r="C3676" s="33" t="s">
+      <c r="C3676" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="8"/>
       <c r="B3677" s="9"/>
-      <c r="C3677" s="33"/>
+      <c r="C3677" s="36"/>
     </row>
     <row r="3678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3678" s="8"/>
       <c r="B3678" s="9"/>
-      <c r="C3678" s="33"/>
+      <c r="C3678" s="36"/>
     </row>
     <row r="3679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3679" s="8">
@@ -22308,7 +23615,7 @@
       <c r="A3681" s="16">
         <v>7.2</v>
       </c>
-      <c r="B3681" s="36" t="s">
+      <c r="B3681" s="33" t="s">
         <v>352</v>
       </c>
       <c r="C3681" s="24" t="s">
@@ -22317,7 +23624,7 @@
     </row>
     <row r="3682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3682" s="16"/>
-      <c r="B3682" s="36"/>
+      <c r="B3682" s="33"/>
       <c r="C3682" s="24"/>
     </row>
     <row r="3683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22376,10 +23683,10 @@
     </row>
     <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3719" s="4"/>
-      <c r="B3719" s="31" t="s">
+      <c r="B3719" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="C3719" s="32"/>
+      <c r="C3719" s="35"/>
     </row>
     <row r="3720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3720" s="13" t="s">
@@ -22508,7 +23815,7 @@
       <c r="A3733" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3733" s="36" t="s">
+      <c r="B3733" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C3733" s="18" t="s">
@@ -22517,7 +23824,7 @@
     </row>
     <row r="3734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3734" s="25"/>
-      <c r="B3734" s="36"/>
+      <c r="B3734" s="33"/>
       <c r="C3734" s="18"/>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22525,14 +23832,14 @@
         <v>6.1</v>
       </c>
       <c r="B3735" s="9"/>
-      <c r="C3735" s="33" t="s">
+      <c r="C3735" s="36" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3736" s="8"/>
       <c r="B3736" s="9"/>
-      <c r="C3736" s="33"/>
+      <c r="C3736" s="36"/>
     </row>
     <row r="3737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3737" s="8">
@@ -22738,10 +24045,10 @@
     </row>
     <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3837" s="4"/>
-      <c r="B3837" s="31" t="s">
+      <c r="B3837" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C3837" s="32"/>
+      <c r="C3837" s="35"/>
     </row>
     <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3838" s="13" t="s">
@@ -22896,14 +24203,14 @@
         <v>8.1</v>
       </c>
       <c r="B3854" s="9"/>
-      <c r="C3854" s="33" t="s">
+      <c r="C3854" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="3855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3855" s="8"/>
       <c r="B3855" s="9"/>
-      <c r="C3855" s="33"/>
+      <c r="C3855" s="36"/>
     </row>
     <row r="3856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3856" s="8">
@@ -23023,10 +24330,10 @@
     </row>
     <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3955" s="4"/>
-      <c r="B3955" s="31" t="s">
+      <c r="B3955" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C3955" s="32"/>
+      <c r="C3955" s="35"/>
     </row>
     <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3956" s="13" t="s">
@@ -23127,14 +24434,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B3966" s="9"/>
-      <c r="C3966" s="33" t="s">
+      <c r="C3966" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3967" s="8"/>
       <c r="B3967" s="9"/>
-      <c r="C3967" s="33"/>
+      <c r="C3967" s="36"/>
     </row>
     <row r="3968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3968" s="8">
@@ -23167,10 +24474,10 @@
     </row>
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="4"/>
-      <c r="B4014" s="31" t="s">
+      <c r="B4014" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="C4014" s="32"/>
+      <c r="C4014" s="35"/>
     </row>
     <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4015" s="13" t="s">
@@ -23277,14 +24584,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="9"/>
-      <c r="C4025" s="33" t="s">
+      <c r="C4025" s="36" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="8"/>
       <c r="B4026" s="9"/>
-      <c r="C4026" s="33"/>
+      <c r="C4026" s="36"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="8">
@@ -23345,10 +24652,10 @@
     </row>
     <row r="4073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4073" s="4"/>
-      <c r="B4073" s="31" t="s">
+      <c r="B4073" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="C4073" s="32"/>
+      <c r="C4073" s="35"/>
     </row>
     <row r="4074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4074" s="13" t="s">
@@ -23451,14 +24758,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4084" s="9"/>
-      <c r="C4084" s="33" t="s">
+      <c r="C4084" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4085" s="8"/>
       <c r="B4085" s="9"/>
-      <c r="C4085" s="33"/>
+      <c r="C4085" s="36"/>
     </row>
     <row r="4086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4086" s="8">
@@ -23491,10 +24798,10 @@
     </row>
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="4"/>
-      <c r="B4132" s="31" t="s">
+      <c r="B4132" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C4132" s="32"/>
+      <c r="C4132" s="35"/>
     </row>
     <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4133" s="13" t="s">
@@ -23597,19 +24904,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="9"/>
-      <c r="C4143" s="33" t="s">
+      <c r="C4143" s="36" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="8"/>
       <c r="B4144" s="9"/>
-      <c r="C4144" s="33"/>
+      <c r="C4144" s="36"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="8"/>
       <c r="B4145" s="9"/>
-      <c r="C4145" s="33"/>
+      <c r="C4145" s="36"/>
     </row>
     <row r="4146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4146" s="8">
@@ -23694,10 +25001,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="4"/>
-      <c r="B4191" s="31" t="s">
+      <c r="B4191" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="C4191" s="32"/>
+      <c r="C4191" s="35"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="13" t="s">
@@ -23842,7 +25149,7 @@
       <c r="A4207" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4207" s="36" t="s">
+      <c r="B4207" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C4207" s="24" t="s">
@@ -23851,7 +25158,7 @@
     </row>
     <row r="4208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4208" s="25"/>
-      <c r="B4208" s="36"/>
+      <c r="B4208" s="33"/>
       <c r="C4208" s="24"/>
     </row>
     <row r="4209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23859,14 +25166,14 @@
         <v>8.1</v>
       </c>
       <c r="B4209" s="9"/>
-      <c r="C4209" s="33" t="s">
+      <c r="C4209" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4210" s="8"/>
       <c r="B4210" s="9"/>
-      <c r="C4210" s="33"/>
+      <c r="C4210" s="36"/>
     </row>
     <row r="4211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4211" s="8">
@@ -24094,14 +25401,14 @@
         <v>3.1</v>
       </c>
       <c r="B4316" s="9"/>
-      <c r="C4316" s="33" t="s">
-        <v>379</v>
+      <c r="C4316" s="36" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="4317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4317" s="8"/>
       <c r="B4317" s="9"/>
-      <c r="C4317" s="33"/>
+      <c r="C4317" s="36"/>
     </row>
     <row r="4318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4318" s="8">
@@ -24186,14 +25493,14 @@
         <v>2.1</v>
       </c>
       <c r="B4373" s="9"/>
-      <c r="C4373" s="33" t="s">
+      <c r="C4373" s="36" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4374" s="8"/>
       <c r="B4374" s="9"/>
-      <c r="C4374" s="33"/>
+      <c r="C4374" s="36"/>
     </row>
     <row r="4375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4375" s="8">
@@ -24544,14 +25851,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4556" s="9"/>
-      <c r="C4556" s="33" t="s">
+      <c r="C4556" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4557" s="8"/>
       <c r="B4557" s="9"/>
-      <c r="C4557" s="33"/>
+      <c r="C4557" s="36"/>
     </row>
     <row r="4558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4558" s="8">
@@ -24584,10 +25891,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="4"/>
-      <c r="B4604" s="31" t="s">
+      <c r="B4604" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C4604" s="32"/>
+      <c r="C4604" s="35"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="13" t="s">
@@ -24694,19 +26001,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4615" s="9"/>
-      <c r="C4615" s="33" t="s">
+      <c r="C4615" s="36" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4616" s="8"/>
       <c r="B4616" s="9"/>
-      <c r="C4616" s="33"/>
+      <c r="C4616" s="36"/>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="8"/>
       <c r="B4617" s="9"/>
-      <c r="C4617" s="33"/>
+      <c r="C4617" s="36"/>
     </row>
     <row r="4618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4618" s="8">
@@ -24791,10 +26098,10 @@
     </row>
     <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4663" s="4"/>
-      <c r="B4663" s="31" t="s">
+      <c r="B4663" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C4663" s="32"/>
+      <c r="C4663" s="35"/>
     </row>
     <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4664" s="13" t="s">
@@ -24909,7 +26216,7 @@
       <c r="A4675" s="25">
         <v>5.2</v>
       </c>
-      <c r="B4675" s="36" t="s">
+      <c r="B4675" s="33" t="s">
         <v>351</v>
       </c>
       <c r="C4675" s="24" t="s">
@@ -24918,7 +26225,7 @@
     </row>
     <row r="4676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4676" s="25"/>
-      <c r="B4676" s="36"/>
+      <c r="B4676" s="33"/>
       <c r="C4676" s="24"/>
     </row>
     <row r="4677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24926,14 +26233,14 @@
         <v>6.1</v>
       </c>
       <c r="B4677" s="9"/>
-      <c r="C4677" s="33" t="s">
+      <c r="C4677" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4678" s="8"/>
       <c r="B4678" s="9"/>
-      <c r="C4678" s="33"/>
+      <c r="C4678" s="36"/>
     </row>
     <row r="4679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4679" s="8">
@@ -25071,10 +26378,10 @@
     </row>
     <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4781" s="4"/>
-      <c r="B4781" s="31" t="s">
+      <c r="B4781" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C4781" s="32"/>
+      <c r="C4781" s="35"/>
     </row>
     <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4782" s="13" t="s">
@@ -25245,7 +26552,7 @@
       <c r="A4801" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4801" s="36" t="s">
+      <c r="B4801" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C4801" s="24" t="s">
@@ -25254,7 +26561,7 @@
     </row>
     <row r="4802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4802" s="25"/>
-      <c r="B4802" s="36"/>
+      <c r="B4802" s="33"/>
       <c r="C4802" s="24"/>
     </row>
     <row r="4803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25262,14 +26569,14 @@
         <v>8.1</v>
       </c>
       <c r="B4803" s="9"/>
-      <c r="C4803" s="33" t="s">
+      <c r="C4803" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4804" s="8"/>
       <c r="B4804" s="9"/>
-      <c r="C4804" s="33"/>
+      <c r="C4804" s="36"/>
     </row>
     <row r="4805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4805" s="8">
@@ -25444,14 +26751,14 @@
         <v>7.1</v>
       </c>
       <c r="B4855" s="9"/>
-      <c r="C4855" s="33" t="s">
+      <c r="C4855" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4856" s="8"/>
       <c r="B4856" s="9"/>
-      <c r="C4856" s="33"/>
+      <c r="C4856" s="36"/>
     </row>
     <row r="4857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4857" s="8">
@@ -25484,10 +26791,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="4"/>
-      <c r="B4899" s="31" t="s">
+      <c r="B4899" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C4899" s="32"/>
+      <c r="C4899" s="35"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="13" t="s">
@@ -25642,7 +26949,7 @@
       <c r="A4917" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4917" s="36" t="s">
+      <c r="B4917" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C4917" s="24" t="s">
@@ -25651,7 +26958,7 @@
     </row>
     <row r="4918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4918" s="25"/>
-      <c r="B4918" s="36"/>
+      <c r="B4918" s="33"/>
       <c r="C4918" s="24"/>
     </row>
     <row r="4919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25659,14 +26966,14 @@
         <v>8.1</v>
       </c>
       <c r="B4919" s="9"/>
-      <c r="C4919" s="33" t="s">
+      <c r="C4919" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4920" s="8"/>
       <c r="B4920" s="9"/>
-      <c r="C4920" s="33"/>
+      <c r="C4920" s="36"/>
     </row>
     <row r="4921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4921" s="8">
@@ -25699,10 +27006,10 @@
     </row>
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="4"/>
-      <c r="B4958" s="31" t="s">
+      <c r="B4958" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="C4958" s="32"/>
+      <c r="C4958" s="35"/>
     </row>
     <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4959" s="13" t="s">
@@ -25809,14 +27116,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="9"/>
-      <c r="C4969" s="33" t="s">
+      <c r="C4969" s="36" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="8"/>
       <c r="B4970" s="9"/>
-      <c r="C4970" s="33"/>
+      <c r="C4970" s="36"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="8">
@@ -25997,14 +27304,14 @@
         <v>6.1</v>
       </c>
       <c r="B5030" s="9"/>
-      <c r="C5030" s="33" t="s">
+      <c r="C5030" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="5031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5031" s="8"/>
       <c r="B5031" s="9"/>
-      <c r="C5031" s="33"/>
+      <c r="C5031" s="36"/>
     </row>
     <row r="5032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5032" s="8">
@@ -26037,10 +27344,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="4"/>
-      <c r="B5076" s="31" t="s">
+      <c r="B5076" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="C5076" s="32"/>
+      <c r="C5076" s="35"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="13" t="s">
@@ -26157,19 +27464,19 @@
         <v>6.1</v>
       </c>
       <c r="B5089" s="9"/>
-      <c r="C5089" s="33" t="s">
+      <c r="C5089" s="36" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="5090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5090" s="8"/>
       <c r="B5090" s="9"/>
-      <c r="C5090" s="33"/>
+      <c r="C5090" s="36"/>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="8"/>
       <c r="B5091" s="9"/>
-      <c r="C5091" s="33"/>
+      <c r="C5091" s="36"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="8">
@@ -26418,7 +27725,7 @@
       <c r="A5153" s="25">
         <v>7.2</v>
       </c>
-      <c r="B5153" s="36" t="s">
+      <c r="B5153" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C5153" s="24" t="s">
@@ -26427,7 +27734,7 @@
     </row>
     <row r="5154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5154" s="25"/>
-      <c r="B5154" s="36"/>
+      <c r="B5154" s="33"/>
       <c r="C5154" s="24"/>
     </row>
     <row r="5155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26435,14 +27742,14 @@
         <v>8.1</v>
       </c>
       <c r="B5155" s="9"/>
-      <c r="C5155" s="33" t="s">
+      <c r="C5155" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="5156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5156" s="8"/>
       <c r="B5156" s="9"/>
-      <c r="C5156" s="33"/>
+      <c r="C5156" s="36"/>
     </row>
     <row r="5157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5157" s="8">
@@ -26702,7 +28009,7 @@
       <c r="A5266" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5266" s="36" t="s">
+      <c r="B5266" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C5266" s="24" t="s">
@@ -26711,7 +28018,7 @@
     </row>
     <row r="5267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5267" s="25"/>
-      <c r="B5267" s="36"/>
+      <c r="B5267" s="33"/>
       <c r="C5267" s="24"/>
     </row>
     <row r="5268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26719,14 +28026,14 @@
         <v>6.1</v>
       </c>
       <c r="B5268" s="9"/>
-      <c r="C5268" s="33" t="s">
+      <c r="C5268" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="5269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5269" s="8"/>
       <c r="B5269" s="9"/>
-      <c r="C5269" s="33"/>
+      <c r="C5269" s="36"/>
     </row>
     <row r="5270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5270" s="8">
@@ -26969,10 +28276,10 @@
     </row>
     <row r="5427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5427" s="4"/>
-      <c r="B5427" s="31" t="s">
+      <c r="B5427" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="C5427" s="32"/>
+      <c r="C5427" s="35"/>
     </row>
     <row r="5428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5428" s="13" t="s">
@@ -27236,7 +28543,7 @@
       <c r="A5502" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5502" s="36" t="s">
+      <c r="B5502" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C5502" s="24" t="s">
@@ -27245,7 +28552,7 @@
     </row>
     <row r="5503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5503" s="25"/>
-      <c r="B5503" s="36"/>
+      <c r="B5503" s="33"/>
       <c r="C5503" s="24"/>
     </row>
     <row r="5504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27253,14 +28560,14 @@
         <v>6.1</v>
       </c>
       <c r="B5504" s="9"/>
-      <c r="C5504" s="33" t="s">
+      <c r="C5504" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="5505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5505" s="8"/>
       <c r="B5505" s="9"/>
-      <c r="C5505" s="33"/>
+      <c r="C5505" s="36"/>
     </row>
     <row r="5506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5506" s="8">
@@ -27293,10 +28600,10 @@
     </row>
     <row r="5545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5545" s="4"/>
-      <c r="B5545" s="31" t="s">
+      <c r="B5545" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="C5545" s="32"/>
+      <c r="C5545" s="35"/>
     </row>
     <row r="5546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5546" s="13" t="s">
@@ -27419,7 +28726,7 @@
       <c r="A5559" s="16">
         <v>5.2</v>
       </c>
-      <c r="B5559" s="36" t="s">
+      <c r="B5559" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C5559" s="24" t="s">
@@ -27428,7 +28735,7 @@
     </row>
     <row r="5560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5560" s="16"/>
-      <c r="B5560" s="36"/>
+      <c r="B5560" s="33"/>
       <c r="C5560" s="24"/>
     </row>
     <row r="5561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27436,19 +28743,19 @@
         <v>6.1</v>
       </c>
       <c r="B5561" s="9"/>
-      <c r="C5561" s="33" t="s">
+      <c r="C5561" s="36" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="5562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5562" s="8"/>
       <c r="B5562" s="9"/>
-      <c r="C5562" s="33"/>
+      <c r="C5562" s="36"/>
     </row>
     <row r="5563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5563" s="8"/>
       <c r="B5563" s="9"/>
-      <c r="C5563" s="33"/>
+      <c r="C5563" s="36"/>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="8">
@@ -27470,7 +28777,7 @@
       <c r="A5566" s="16">
         <v>7.2</v>
       </c>
-      <c r="B5566" s="36" t="s">
+      <c r="B5566" s="33" t="s">
         <v>352</v>
       </c>
       <c r="C5566" s="24" t="s">
@@ -27479,7 +28786,7 @@
     </row>
     <row r="5567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5567" s="16"/>
-      <c r="B5567" s="36"/>
+      <c r="B5567" s="33"/>
       <c r="C5567" s="24"/>
     </row>
     <row r="5568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27538,10 +28845,10 @@
     </row>
     <row r="5604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5604" s="4"/>
-      <c r="B5604" s="31" t="s">
+      <c r="B5604" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="C5604" s="32"/>
+      <c r="C5604" s="35"/>
     </row>
     <row r="5605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5605" s="13" t="s">
@@ -27670,7 +28977,7 @@
       <c r="A5618" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5618" s="36" t="s">
+      <c r="B5618" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C5618" s="24" t="s">
@@ -27679,7 +28986,7 @@
     </row>
     <row r="5619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5619" s="25"/>
-      <c r="B5619" s="36"/>
+      <c r="B5619" s="33"/>
       <c r="C5619" s="24"/>
     </row>
     <row r="5620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27687,14 +28994,14 @@
         <v>6.1</v>
       </c>
       <c r="B5620" s="9"/>
-      <c r="C5620" s="33" t="s">
+      <c r="C5620" s="36" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="5621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5621" s="8"/>
       <c r="B5621" s="9"/>
-      <c r="C5621" s="33"/>
+      <c r="C5621" s="36"/>
     </row>
     <row r="5622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5622" s="8">
@@ -27727,10 +29034,10 @@
     </row>
     <row r="5663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5663" s="4"/>
-      <c r="B5663" s="31" t="s">
+      <c r="B5663" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C5663" s="32"/>
+      <c r="C5663" s="35"/>
     </row>
     <row r="5664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5664" s="13" t="s">
@@ -27876,10 +29183,10 @@
     </row>
     <row r="5722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5722" s="4"/>
-      <c r="B5722" s="31" t="s">
+      <c r="B5722" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C5722" s="32"/>
+      <c r="C5722" s="35"/>
     </row>
     <row r="5723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5723" s="13" t="s">
@@ -28286,10 +29593,10 @@
     </row>
     <row r="5781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5781" s="4"/>
-      <c r="B5781" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5781" s="27"/>
+      <c r="B5781" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5781" s="35"/>
     </row>
     <row r="5782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5782" s="13" t="s">
@@ -29404,19 +30711,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6028" s="9"/>
-      <c r="C6028" s="33" t="s">
+      <c r="C6028" s="36" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="6029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6029" s="8"/>
       <c r="B6029" s="9"/>
-      <c r="C6029" s="33"/>
+      <c r="C6029" s="36"/>
     </row>
     <row r="6030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6030" s="8"/>
       <c r="B6030" s="9"/>
-      <c r="C6030" s="33"/>
+      <c r="C6030" s="36"/>
     </row>
     <row r="6031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6031" s="8">
@@ -29501,10 +30808,10 @@
     </row>
     <row r="6076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6076" s="4"/>
-      <c r="B6076" s="31" t="s">
+      <c r="B6076" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="C6076" s="32"/>
+      <c r="C6076" s="35"/>
     </row>
     <row r="6077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6077" s="13" t="s">
@@ -29649,7 +30956,7 @@
       <c r="A6092" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6092" s="36" t="s">
+      <c r="B6092" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C6092" s="24" t="s">
@@ -29658,7 +30965,7 @@
     </row>
     <row r="6093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6093" s="25"/>
-      <c r="B6093" s="36"/>
+      <c r="B6093" s="33"/>
       <c r="C6093" s="24"/>
     </row>
     <row r="6094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30018,14 +31325,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6146" s="9"/>
-      <c r="C6146" s="33" t="s">
+      <c r="C6146" s="36" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="6147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6147" s="8"/>
       <c r="B6147" s="9"/>
-      <c r="C6147" s="33"/>
+      <c r="C6147" s="36"/>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6148" s="8">
@@ -30434,19 +31741,19 @@
         <v>2.1</v>
       </c>
       <c r="B6258" s="9"/>
-      <c r="C6258" s="33" t="s">
+      <c r="C6258" s="36" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="6259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6259" s="8"/>
       <c r="B6259" s="9"/>
-      <c r="C6259" s="33"/>
+      <c r="C6259" s="36"/>
     </row>
     <row r="6260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6260" s="8"/>
       <c r="B6260" s="9"/>
-      <c r="C6260" s="33"/>
+      <c r="C6260" s="36"/>
     </row>
     <row r="6261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6261" s="8">
@@ -30630,10 +31937,10 @@
     </row>
     <row r="6371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6371" s="4"/>
-      <c r="B6371" s="31" t="s">
+      <c r="B6371" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="C6371" s="32"/>
+      <c r="C6371" s="35"/>
     </row>
     <row r="6372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6372" s="13" t="s">
@@ -31137,10 +32444,10 @@
     </row>
     <row r="6489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6489" s="4"/>
-      <c r="B6489" s="31" t="s">
+      <c r="B6489" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C6489" s="32"/>
+      <c r="C6489" s="35"/>
     </row>
     <row r="6490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6490" s="13" t="s">
@@ -31247,19 +32554,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6500" s="9"/>
-      <c r="C6500" s="33" t="s">
+      <c r="C6500" s="36" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="6501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6501" s="8"/>
       <c r="B6501" s="9"/>
-      <c r="C6501" s="33"/>
+      <c r="C6501" s="36"/>
     </row>
     <row r="6502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6502" s="8"/>
       <c r="B6502" s="9"/>
-      <c r="C6502" s="33"/>
+      <c r="C6502" s="36"/>
     </row>
     <row r="6503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6503" s="8">
@@ -31344,10 +32651,10 @@
     </row>
     <row r="6548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6548" s="4"/>
-      <c r="B6548" s="31" t="s">
+      <c r="B6548" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C6548" s="32"/>
+      <c r="C6548" s="35"/>
     </row>
     <row r="6549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6549" s="13" t="s">
@@ -31462,7 +32769,7 @@
       <c r="A6560" s="25">
         <v>5.2</v>
       </c>
-      <c r="B6560" s="36" t="s">
+      <c r="B6560" s="33" t="s">
         <v>351</v>
       </c>
       <c r="C6560" s="24" t="s">
@@ -31471,7 +32778,7 @@
     </row>
     <row r="6561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6561" s="25"/>
-      <c r="B6561" s="36"/>
+      <c r="B6561" s="33"/>
       <c r="C6561" s="24"/>
     </row>
     <row r="6562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31836,10 +33143,10 @@
     </row>
     <row r="6666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6666" s="4"/>
-      <c r="B6666" s="31" t="s">
+      <c r="B6666" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C6666" s="32"/>
+      <c r="C6666" s="35"/>
     </row>
     <row r="6667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6667" s="13" t="s">
@@ -31978,14 +33285,14 @@
       <c r="A6682" s="16">
         <v>5.2</v>
       </c>
-      <c r="B6682" s="37"/>
+      <c r="B6682" s="31"/>
       <c r="C6682" s="24"/>
     </row>
     <row r="6683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6683" s="16">
         <v>6.1</v>
       </c>
-      <c r="B6683" s="37"/>
+      <c r="B6683" s="31"/>
       <c r="C6683" s="24"/>
     </row>
     <row r="6684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32010,7 +33317,7 @@
       <c r="A6686" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6686" s="36" t="s">
+      <c r="B6686" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C6686" s="18" t="s">
@@ -32019,7 +33326,7 @@
     </row>
     <row r="6687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6687" s="25"/>
-      <c r="B6687" s="36"/>
+      <c r="B6687" s="33"/>
       <c r="C6687" s="18"/>
     </row>
     <row r="6688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32673,10 +33980,10 @@
     </row>
     <row r="6784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6784" s="4"/>
-      <c r="B6784" s="31" t="s">
+      <c r="B6784" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C6784" s="32"/>
+      <c r="C6784" s="35"/>
     </row>
     <row r="6785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6785" s="13" t="s">
@@ -32831,7 +34138,7 @@
       <c r="A6802" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6802" s="36" t="s">
+      <c r="B6802" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C6802" s="24" t="s">
@@ -32840,7 +34147,7 @@
     </row>
     <row r="6803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6803" s="25"/>
-      <c r="B6803" s="36"/>
+      <c r="B6803" s="33"/>
       <c r="C6803" s="24"/>
     </row>
     <row r="6804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33625,10 +34932,10 @@
     </row>
     <row r="6961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6961" s="4"/>
-      <c r="B6961" s="31" t="s">
+      <c r="B6961" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="C6961" s="32"/>
+      <c r="C6961" s="35"/>
     </row>
     <row r="6962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6962" s="13" t="s">
@@ -33745,19 +35052,19 @@
         <v>6.1</v>
       </c>
       <c r="B6974" s="9"/>
-      <c r="C6974" s="33" t="s">
+      <c r="C6974" s="36" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="6975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6975" s="8"/>
       <c r="B6975" s="9"/>
-      <c r="C6975" s="33"/>
+      <c r="C6975" s="36"/>
     </row>
     <row r="6976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6976" s="8"/>
       <c r="B6976" s="9"/>
-      <c r="C6976" s="33"/>
+      <c r="C6976" s="36"/>
     </row>
     <row r="6977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6977" s="8">
@@ -33842,10 +35149,10 @@
     </row>
     <row r="7020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7020" s="4"/>
-      <c r="B7020" s="31" t="s">
+      <c r="B7020" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C7020" s="32"/>
+      <c r="C7020" s="35"/>
     </row>
     <row r="7021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7021" s="13" t="s">
@@ -34006,7 +35313,7 @@
       <c r="A7038" s="25">
         <v>7.2</v>
       </c>
-      <c r="B7038" s="36" t="s">
+      <c r="B7038" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C7038" s="24" t="s">
@@ -34015,7 +35322,7 @@
     </row>
     <row r="7039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7039" s="25"/>
-      <c r="B7039" s="36"/>
+      <c r="B7039" s="33"/>
       <c r="C7039" s="24"/>
     </row>
     <row r="7040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34264,7 +35571,7 @@
     </row>
     <row r="7078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7078" s="1" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B7078" s="2" t="s">
         <v>22</v>
@@ -34328,7 +35635,7 @@
       </c>
       <c r="B7084" s="9"/>
       <c r="C7084" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34351,7 +35658,7 @@
     </row>
     <row r="7137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7137" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B7137" s="2" t="s">
         <v>24</v>
@@ -34502,7 +35809,7 @@
       <c r="A7154" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7154" s="36" t="s">
+      <c r="B7154" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C7154" s="24" t="s">
@@ -34511,7 +35818,7 @@
     </row>
     <row r="7155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7155" s="25"/>
-      <c r="B7155" s="36"/>
+      <c r="B7155" s="33"/>
       <c r="C7155" s="24"/>
     </row>
     <row r="7156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34760,7 +36067,7 @@
     </row>
     <row r="7196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7196" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B7196" s="2" t="s">
         <v>24</v>
@@ -34845,7 +36152,7 @@
         <v>173</v>
       </c>
       <c r="C7205" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34871,14 +36178,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B7208" s="9"/>
-      <c r="C7208" s="33" t="s">
-        <v>368</v>
+      <c r="C7208" s="36" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="7209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7209" s="8"/>
       <c r="B7209" s="9"/>
-      <c r="C7209" s="33"/>
+      <c r="C7209" s="36"/>
     </row>
     <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7210" s="8">
@@ -34900,7 +36207,7 @@
     </row>
     <row r="7255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7255" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B7255" s="2" t="s">
         <v>22</v>
@@ -34964,7 +36271,7 @@
       </c>
       <c r="B7261" s="9"/>
       <c r="C7261" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34987,7 +36294,7 @@
     </row>
     <row r="7314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7314" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B7314" s="2" t="s">
         <v>6</v>
@@ -34998,10 +36305,10 @@
     </row>
     <row r="7315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7315" s="4"/>
-      <c r="B7315" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="C7315" s="32"/>
+      <c r="B7315" s="34" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7315" s="35"/>
     </row>
     <row r="7316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7316" s="13" t="s">
@@ -35071,7 +36378,7 @@
       </c>
       <c r="B7322" s="9"/>
       <c r="C7322" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35146,7 +36453,7 @@
     </row>
     <row r="7373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7373" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B7373" s="2" t="s">
         <v>24</v>
@@ -35297,7 +36604,7 @@
       <c r="A7390" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7390" s="36" t="s">
+      <c r="B7390" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C7390" s="24" t="s">
@@ -35306,7 +36613,7 @@
     </row>
     <row r="7391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7391" s="25"/>
-      <c r="B7391" s="36"/>
+      <c r="B7391" s="33"/>
       <c r="C7391" s="24"/>
     </row>
     <row r="7392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35555,7 +36862,7 @@
     </row>
     <row r="7432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7432" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7432" s="2" t="s">
         <v>129</v>
@@ -35566,10 +36873,10 @@
     </row>
     <row r="7433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7433" s="4"/>
-      <c r="B7433" s="31" t="s">
+      <c r="B7433" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="C7433" s="32"/>
+      <c r="C7433" s="35"/>
     </row>
     <row r="7434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7434" s="13" t="s">
@@ -35692,7 +36999,7 @@
       <c r="A7447" s="16">
         <v>5.2</v>
       </c>
-      <c r="B7447" s="36" t="s">
+      <c r="B7447" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C7447" s="24" t="s">
@@ -35701,7 +37008,7 @@
     </row>
     <row r="7448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7448" s="16"/>
-      <c r="B7448" s="36"/>
+      <c r="B7448" s="33"/>
       <c r="C7448" s="24"/>
     </row>
     <row r="7449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35709,19 +37016,19 @@
         <v>6.1</v>
       </c>
       <c r="B7449" s="9"/>
-      <c r="C7449" s="33" t="s">
+      <c r="C7449" s="36" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="7450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7450" s="8"/>
       <c r="B7450" s="9"/>
-      <c r="C7450" s="33"/>
+      <c r="C7450" s="36"/>
     </row>
     <row r="7451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7451" s="8"/>
       <c r="B7451" s="9"/>
-      <c r="C7451" s="33"/>
+      <c r="C7451" s="36"/>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7452" s="8">
@@ -35743,7 +37050,7 @@
       <c r="A7454" s="16">
         <v>7.2</v>
       </c>
-      <c r="B7454" s="36" t="s">
+      <c r="B7454" s="33" t="s">
         <v>352</v>
       </c>
       <c r="C7454" s="24" t="s">
@@ -35752,14 +37059,14 @@
     </row>
     <row r="7455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7455" s="16"/>
-      <c r="B7455" s="36"/>
+      <c r="B7455" s="33"/>
       <c r="C7455" s="24"/>
     </row>
     <row r="7456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7456" s="8">
         <v>8.1</v>
       </c>
-      <c r="B7456" s="38"/>
+      <c r="B7456" s="32"/>
       <c r="C7456" s="10"/>
     </row>
     <row r="7457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35800,7 +37107,7 @@
     </row>
     <row r="7491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7491" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B7491" s="2" t="s">
         <v>19</v>
@@ -35943,7 +37250,7 @@
       <c r="A7506" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7506" s="36" t="s">
+      <c r="B7506" s="33" t="s">
         <v>350</v>
       </c>
       <c r="C7506" s="24" t="s">
@@ -35952,7 +37259,7 @@
     </row>
     <row r="7507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7507" s="25"/>
-      <c r="B7507" s="36"/>
+      <c r="B7507" s="33"/>
       <c r="C7507" s="24"/>
     </row>
     <row r="7508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36201,7 +37508,7 @@
     </row>
     <row r="7550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7550" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B7550" s="2" t="s">
         <v>15</v>
@@ -36245,7 +37552,7 @@
       </c>
       <c r="B7554" s="9"/>
       <c r="C7554" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36304,120 +37611,2098 @@
       <c r="B7560" s="21"/>
       <c r="C7560" s="22"/>
     </row>
+    <row r="7609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7609" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7609" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7609" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7610" s="4"/>
+      <c r="B7610" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7610" s="35"/>
+    </row>
+    <row r="7611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7611" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7611" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7611" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7612" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7612" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7612" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7613" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7613" s="9"/>
+      <c r="C7613" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7614" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7614" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7614" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7615" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7615" s="9"/>
+      <c r="C7615" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="7616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7616" s="8"/>
+      <c r="B7616" s="9"/>
+      <c r="C7616" s="10" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7617" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7617" s="9"/>
+      <c r="C7617" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7618" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="B7618" s="17"/>
+      <c r="C7618" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7619" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B7619" s="17"/>
+      <c r="C7619" s="24"/>
+    </row>
+    <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7620" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7620" s="9"/>
+      <c r="C7620" s="10"/>
+    </row>
+    <row r="7621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7621" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7621" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7621" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7622" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7622" s="9"/>
+      <c r="C7622" s="10"/>
+    </row>
+    <row r="7623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7623" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7623" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7623" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7624" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7624" s="32"/>
+      <c r="C7624" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7625" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B7625" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7625" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7626" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B7626" s="17"/>
+      <c r="C7626" s="24"/>
+    </row>
+    <row r="7627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7627" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B7627" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C7627" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7628" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B7628" s="9"/>
+      <c r="C7628" s="15"/>
+    </row>
+    <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7629" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B7629" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7629" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7630" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7630" s="21"/>
+      <c r="C7630" s="22"/>
+    </row>
+    <row r="7668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7668" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7668" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7668" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7669" s="4"/>
+      <c r="B7669" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7669" s="35"/>
+    </row>
+    <row r="7670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7670" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7670" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7670" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7671" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7671" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7671" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7672" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7672" s="9"/>
+      <c r="C7672" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7673" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7673" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7673" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7674" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7674" s="9"/>
+      <c r="C7674" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7675" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7675" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7675" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7676" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7676" s="9"/>
+      <c r="C7676" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7677" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B7677" s="9"/>
+      <c r="C7677" s="10"/>
+    </row>
+    <row r="7678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7678" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7678" s="9"/>
+      <c r="C7678" s="10" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7679" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7679" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7679" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7680" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7680" s="21"/>
+      <c r="C7680" s="22"/>
+    </row>
+    <row r="7727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7727" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B7727" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7727" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7728" s="4"/>
+      <c r="B7728" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7728" s="27"/>
+    </row>
+    <row r="7729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7729" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7729" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7729" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7730" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7730" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7730" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7731" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7731" s="9"/>
+      <c r="C7731" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7732" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7732" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7732" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7733" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7733" s="9"/>
+      <c r="C7733" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7734" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7734" s="9"/>
+      <c r="C7734" s="10"/>
+    </row>
+    <row r="7735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7735" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7735" s="9"/>
+      <c r="C7735" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7736" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B7736" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7736" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7737" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7737" s="17"/>
+      <c r="C7737" s="24"/>
+    </row>
+    <row r="7738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7738" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B7738" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7738" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7739" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7739" s="9"/>
+      <c r="C7739" s="10"/>
+    </row>
+    <row r="7740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7740" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7740" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7740" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7741" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7741" s="21"/>
+      <c r="C7741" s="22"/>
+    </row>
+    <row r="7786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7786" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7786" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7786" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7787" s="4"/>
+      <c r="B7787" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7787" s="27"/>
+    </row>
+    <row r="7788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7788" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7788" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7788" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7789" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7789" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7789" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7790" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7790" s="9"/>
+      <c r="C7790" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7791" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7791" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7791" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7792" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B7792" s="17"/>
+      <c r="C7792" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7793" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7793" s="17"/>
+      <c r="C7793" s="24"/>
+    </row>
+    <row r="7794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7794" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7794" s="9"/>
+      <c r="C7794" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7795" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B7795" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7795" s="10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7796" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7796" s="17"/>
+      <c r="C7796" s="24"/>
+    </row>
+    <row r="7797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7797" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B7797" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7797" s="24" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="7798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7798" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7798" s="9"/>
+      <c r="C7798" s="10"/>
+    </row>
+    <row r="7799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7799" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7799" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7799" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7800" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7800" s="21"/>
+      <c r="C7800" s="22"/>
+    </row>
+    <row r="7845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7845" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7845" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7845" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7846" s="4"/>
+      <c r="B7846" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7846" s="27"/>
+    </row>
+    <row r="7847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7847" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7847" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7847" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7848" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7848" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7848" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7849" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7849" s="9"/>
+      <c r="C7849" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7850" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7850" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7850" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7851" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B7851" s="17"/>
+      <c r="C7851" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7852" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7852" s="17"/>
+      <c r="C7852" s="24"/>
+    </row>
+    <row r="7853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7853" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7853" s="9"/>
+      <c r="C7853" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7854" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B7854" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7854" s="10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7855" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7855" s="17"/>
+      <c r="C7855" s="24"/>
+    </row>
+    <row r="7856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7856" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B7856" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7856" s="24" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7857" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7857" s="9"/>
+      <c r="C7857" s="10"/>
+    </row>
+    <row r="7858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7858" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7858" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7858" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7859" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7859" s="21"/>
+      <c r="C7859" s="22"/>
+    </row>
+    <row r="7904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7904" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B7904" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7904" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7905" s="4"/>
+      <c r="B7905" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7905" s="27"/>
+    </row>
+    <row r="7906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7906" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7906" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7906" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7907" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7907" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7907" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7908" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7908" s="9"/>
+      <c r="C7908" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7909" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7909" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7909" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7910" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B7910" s="17"/>
+      <c r="C7910" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7911" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7911" s="17"/>
+      <c r="C7911" s="24"/>
+    </row>
+    <row r="7912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7912" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7912" s="9"/>
+      <c r="C7912" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7913" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B7913" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7913" s="10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="7914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7914" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7914" s="17"/>
+      <c r="C7914" s="24"/>
+    </row>
+    <row r="7915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7915" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B7915" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7915" s="24" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7916" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7916" s="9"/>
+      <c r="C7916" s="10"/>
+    </row>
+    <row r="7917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7917" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7917" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7917" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7918" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7918" s="21"/>
+      <c r="C7918" s="22"/>
+    </row>
+    <row r="7963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7963" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B7963" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7963" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7964" s="4"/>
+      <c r="B7964" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7964" s="27"/>
+    </row>
+    <row r="7965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7965" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7965" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7965" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7966" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7966" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7966" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7967" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7967" s="9"/>
+      <c r="C7967" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7968" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7968" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7968" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7969" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B7969" s="17"/>
+      <c r="C7969" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7970" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7970" s="17"/>
+      <c r="C7970" s="24"/>
+    </row>
+    <row r="7971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7971" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7971" s="9"/>
+      <c r="C7971" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7972" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7972" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7972" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7973" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7973" s="9"/>
+      <c r="C7973" s="10"/>
+    </row>
+    <row r="7974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7974" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7974" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7974" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7975" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7975" s="9"/>
+      <c r="C7975" s="10"/>
+    </row>
+    <row r="7976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7976" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7976" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7976" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7977" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7977" s="9"/>
+      <c r="C7977" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7978" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B7978" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7978" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7979" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B7979" s="17"/>
+      <c r="C7979" s="24"/>
+    </row>
+    <row r="7980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7980" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B7980" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7980" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7981" s="25"/>
+      <c r="B7981" s="33"/>
+      <c r="C7981" s="24"/>
+    </row>
+    <row r="7982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7982" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B7982" s="9"/>
+      <c r="C7982" s="10"/>
+    </row>
+    <row r="7983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7983" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B7983" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7983" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7984" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7984" s="21"/>
+      <c r="C7984" s="22"/>
+    </row>
+    <row r="8022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8022" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B8022" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8022" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8023" s="4"/>
+      <c r="B8023" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8023" s="27"/>
+    </row>
+    <row r="8024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8024" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8024" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8024" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8025" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8025" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8025" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8026" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8026" s="9"/>
+      <c r="C8026" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8027" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B8027" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8027" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8028" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8028" s="9"/>
+      <c r="C8028" s="36" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8029" s="8"/>
+      <c r="B8029" s="9"/>
+      <c r="C8029" s="36"/>
+    </row>
+    <row r="8030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8030" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8030" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8030" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8031" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8031" s="21"/>
+      <c r="C8031" s="22"/>
+    </row>
+    <row r="8081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8081" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B8081" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8081" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8082" s="4"/>
+      <c r="B8082" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8082" s="27"/>
+    </row>
+    <row r="8083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8083" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8083" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8083" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8084" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8084" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8084" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8085" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8085" s="9"/>
+      <c r="C8085" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8086" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B8086" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8086" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8087" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B8087" s="17"/>
+      <c r="C8087" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8088" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8088" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8088" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8089" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8089" s="9"/>
+      <c r="C8089" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8090" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8090" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8090" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8091" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8091" s="21"/>
+      <c r="C8091" s="22"/>
+    </row>
+    <row r="8140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8140" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B8140" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8140" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8141" s="4"/>
+      <c r="B8141" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8141" s="27"/>
+    </row>
+    <row r="8142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8142" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8142" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8142" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8143" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8143" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8143" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8144" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8144" s="9"/>
+      <c r="C8144" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8145" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B8145" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8145" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8146" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8146" s="9"/>
+      <c r="C8146" s="36" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="8147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8147" s="8"/>
+      <c r="B8147" s="9"/>
+      <c r="C8147" s="36"/>
+    </row>
+    <row r="8148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8148" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8148" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8148" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8149" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8149" s="21"/>
+      <c r="C8149" s="22"/>
+    </row>
+    <row r="8199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8199" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8199" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8200" s="4"/>
+      <c r="B8200" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8200" s="27"/>
+    </row>
+    <row r="8201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8201" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8201" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8201" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8202" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8202" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8202" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8203" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8203" s="9"/>
+      <c r="C8203" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8204" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B8204" s="9"/>
+      <c r="C8204" s="10"/>
+    </row>
+    <row r="8205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8205" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B8205" s="17"/>
+      <c r="C8205" s="24"/>
+    </row>
+    <row r="8206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8206" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8206" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8206" s="24" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8207" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8207" s="9"/>
+      <c r="C8207" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8208" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8208" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8208" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8209" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8209" s="21"/>
+      <c r="C8209" s="22"/>
+    </row>
+    <row r="8258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8258" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8258" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8258" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8259" s="4"/>
+      <c r="B8259" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8259" s="27"/>
+    </row>
+    <row r="8260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8260" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8260" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8260" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8261" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8261" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8261" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8262" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8262" s="9"/>
+      <c r="C8262" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8263" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8263" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8263" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8264" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8264" s="9"/>
+      <c r="C8264" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8265" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8265" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8265" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8266" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8266" s="9"/>
+      <c r="C8266" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8267" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B8267" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8267" s="10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8268" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8268" s="17"/>
+      <c r="C8268" s="24"/>
+    </row>
+    <row r="8269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8269" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B8269" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8269" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8270" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8270" s="9"/>
+      <c r="C8270" s="10"/>
+    </row>
+    <row r="8271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8271" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8271" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8271" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8272" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8272" s="21"/>
+      <c r="C8272" s="22"/>
+    </row>
+    <row r="8317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8317" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B8317" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8317" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8318" s="4"/>
+      <c r="B8318" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8318" s="27"/>
+    </row>
+    <row r="8319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8319" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8319" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8319" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8320" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8320" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8320" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8321" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8321" s="9"/>
+      <c r="C8321" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8322" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8322" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8322" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8323" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8323" s="9"/>
+      <c r="C8323" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8324" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8324" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8324" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8325" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8325" s="9"/>
+      <c r="C8325" s="10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8326" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B8326" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8326" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="8327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8327" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8327" s="17"/>
+      <c r="C8327" s="24"/>
+    </row>
+    <row r="8328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8328" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B8328" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8328" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8329" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8329" s="9"/>
+      <c r="C8329" s="10"/>
+    </row>
+    <row r="8330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8330" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8330" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8330" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8331" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8331" s="21"/>
+      <c r="C8331" s="22"/>
+    </row>
+    <row r="8376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8376" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B8376" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8376" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8377" s="4"/>
+      <c r="B8377" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8377" s="27"/>
+    </row>
+    <row r="8378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8378" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8378" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8378" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8379" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8379" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8379" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8380" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8380" s="9"/>
+      <c r="C8380" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8381" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8381" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8381" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8382" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8382" s="9"/>
+      <c r="C8382" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8383" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8383" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8383" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8384" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8384" s="9"/>
+      <c r="C8384" s="10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8385" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B8385" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8385" s="10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8386" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8386" s="17"/>
+      <c r="C8386" s="24"/>
+    </row>
+    <row r="8387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8387" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B8387" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8387" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8388" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8388" s="9"/>
+      <c r="C8388" s="10"/>
+    </row>
+    <row r="8389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8389" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8389" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8389" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8390" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8390" s="21"/>
+      <c r="C8390" s="22"/>
+    </row>
+    <row r="8435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8435" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B8435" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8435" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8436" s="4"/>
+      <c r="B8436" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8436" s="27"/>
+    </row>
+    <row r="8437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8437" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8437" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8437" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8438" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8438" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8438" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8439" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8439" s="9"/>
+      <c r="C8439" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8440" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8440" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8440" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8441" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8441" s="9"/>
+      <c r="C8441" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8442" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8442" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8442" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8443" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8443" s="9"/>
+      <c r="C8443" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8444" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8444" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8444" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8445" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8445" s="9"/>
+      <c r="C8445" s="10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8446" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B8446" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8446" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="8447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8447" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8447" s="17"/>
+      <c r="C8447" s="24"/>
+    </row>
+    <row r="8448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8448" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B8448" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8448" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8449" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B8449" s="9"/>
+      <c r="C8449" s="10"/>
+    </row>
+    <row r="8450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8450" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B8450" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8450" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8451" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8451" s="21"/>
+      <c r="C8451" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="175">
-    <mergeCell ref="B7454:B7455"/>
-    <mergeCell ref="B7506:B7507"/>
-    <mergeCell ref="B7315:C7315"/>
-    <mergeCell ref="B7390:B7391"/>
-    <mergeCell ref="B7433:C7433"/>
-    <mergeCell ref="C7449:C7451"/>
-    <mergeCell ref="B7447:B7448"/>
-    <mergeCell ref="B7038:B7039"/>
-    <mergeCell ref="C7208:C7209"/>
-    <mergeCell ref="B7154:B7155"/>
-    <mergeCell ref="B6961:C6961"/>
-    <mergeCell ref="C6974:C6976"/>
-    <mergeCell ref="B7020:C7020"/>
-    <mergeCell ref="B6784:C6784"/>
-    <mergeCell ref="B6802:B6803"/>
-    <mergeCell ref="B6666:C6666"/>
-    <mergeCell ref="B6686:B6687"/>
-    <mergeCell ref="B6560:B6561"/>
-    <mergeCell ref="B1846:B1847"/>
-    <mergeCell ref="B3733:B3734"/>
-    <mergeCell ref="B5618:B5619"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="B3558:B3559"/>
-    <mergeCell ref="B3616:B3617"/>
-    <mergeCell ref="B5502:B5503"/>
-    <mergeCell ref="B1794:B1795"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B3681:B3682"/>
-    <mergeCell ref="B3674:B3675"/>
-    <mergeCell ref="B5559:B5560"/>
-    <mergeCell ref="B5566:B5567"/>
-    <mergeCell ref="B3381:B3382"/>
-    <mergeCell ref="B5266:B5267"/>
-    <mergeCell ref="B431:B432"/>
-    <mergeCell ref="B2319:B2320"/>
-    <mergeCell ref="B4207:B4208"/>
-    <mergeCell ref="B6092:B6093"/>
-    <mergeCell ref="B1025:B1026"/>
-    <mergeCell ref="B2913:B2914"/>
-    <mergeCell ref="B4801:B4802"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B3265:B3266"/>
-    <mergeCell ref="B5153:B5154"/>
-    <mergeCell ref="B899:B900"/>
-    <mergeCell ref="B2787:B2788"/>
-    <mergeCell ref="B4675:B4676"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="C6500:C6502"/>
-    <mergeCell ref="B6548:C6548"/>
-    <mergeCell ref="B1142:B1143"/>
-    <mergeCell ref="B3029:B3030"/>
-    <mergeCell ref="B4917:B4918"/>
-    <mergeCell ref="C6258:C6260"/>
-    <mergeCell ref="B6371:C6371"/>
-    <mergeCell ref="B6489:C6489"/>
-    <mergeCell ref="C6028:C6030"/>
-    <mergeCell ref="B6076:C6076"/>
-    <mergeCell ref="C6146:C6147"/>
-    <mergeCell ref="B5722:C5722"/>
-    <mergeCell ref="C5561:C5563"/>
-    <mergeCell ref="B5604:C5604"/>
-    <mergeCell ref="C5620:C5621"/>
-    <mergeCell ref="B5663:C5663"/>
-    <mergeCell ref="B5427:C5427"/>
-    <mergeCell ref="C5504:C5505"/>
-    <mergeCell ref="B5545:C5545"/>
-    <mergeCell ref="C5155:C5156"/>
-    <mergeCell ref="C5268:C5269"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5089:C5091"/>
-    <mergeCell ref="B4958:C4958"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="C5030:C5031"/>
-    <mergeCell ref="C4855:C4856"/>
-    <mergeCell ref="C4919:C4920"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4677:C4678"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="C4803:C4804"/>
-    <mergeCell ref="C4556:C4557"/>
-    <mergeCell ref="C4615:C4617"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4316:C4317"/>
-    <mergeCell ref="C4373:C4374"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="C4209:C4210"/>
-    <mergeCell ref="C4084:C4085"/>
-    <mergeCell ref="B4073:C4073"/>
-    <mergeCell ref="B4132:C4132"/>
-    <mergeCell ref="C4143:C4145"/>
-    <mergeCell ref="B4014:C4014"/>
-    <mergeCell ref="C4025:C4026"/>
-    <mergeCell ref="C2321:C2322"/>
-    <mergeCell ref="C2255:C2257"/>
-    <mergeCell ref="C2137:C2139"/>
-    <mergeCell ref="C2196:C2197"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B2303:C2303"/>
-    <mergeCell ref="C1966:C1967"/>
-    <mergeCell ref="B2008:C2008"/>
-    <mergeCell ref="C2078:C2079"/>
-    <mergeCell ref="C1848:C1849"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="C1731:C1732"/>
-    <mergeCell ref="C1789:C1791"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="C1541:C1542"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="C1665:C1666"/>
-    <mergeCell ref="C839:C841"/>
-    <mergeCell ref="C901:C902"/>
+  <mergeCells count="181">
+    <mergeCell ref="C8146:C8147"/>
+    <mergeCell ref="B5781:C5781"/>
+    <mergeCell ref="B7610:C7610"/>
+    <mergeCell ref="B7669:C7669"/>
+    <mergeCell ref="B7980:B7981"/>
+    <mergeCell ref="C8028:C8029"/>
+    <mergeCell ref="C3618:C3619"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="C3676:C3678"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3383:C3384"/>
+    <mergeCell ref="C3429:C3430"/>
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="C3966:C3967"/>
+    <mergeCell ref="C3854:C3855"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3719:C3719"/>
+    <mergeCell ref="C3735:C3736"/>
+    <mergeCell ref="C2915:C2916"/>
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="C2967:C2968"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="C3267:C3268"/>
+    <mergeCell ref="C3142:C3143"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3201:C3203"/>
+    <mergeCell ref="C3560:C3562"/>
     <mergeCell ref="C780:C781"/>
     <mergeCell ref="B1477:C1477"/>
     <mergeCell ref="C1495:C1496"/>
@@ -36433,9 +39718,7 @@
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="C190:C191"/>
     <mergeCell ref="B61:C61"/>
-    <mergeCell ref="C2428:C2429"/>
     <mergeCell ref="C597:C598"/>
-    <mergeCell ref="C2485:C2487"/>
     <mergeCell ref="C308:C309"/>
     <mergeCell ref="C367:C369"/>
     <mergeCell ref="C433:C434"/>
@@ -36444,11 +39727,34 @@
     <mergeCell ref="C1254:C1255"/>
     <mergeCell ref="C1144:C1145"/>
     <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="C1848:C1849"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="C1731:C1732"/>
+    <mergeCell ref="C1789:C1791"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="C1541:C1542"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="C1665:C1666"/>
+    <mergeCell ref="C839:C841"/>
+    <mergeCell ref="C901:C902"/>
     <mergeCell ref="C1193:C1194"/>
     <mergeCell ref="B1182:C1182"/>
     <mergeCell ref="C1027:C1028"/>
     <mergeCell ref="B1005:C1005"/>
     <mergeCell ref="C1079:C1080"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="C2321:C2322"/>
+    <mergeCell ref="C2255:C2257"/>
+    <mergeCell ref="C2137:C2139"/>
+    <mergeCell ref="C2196:C2197"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B2303:C2303"/>
+    <mergeCell ref="C1966:C1967"/>
+    <mergeCell ref="B2008:C2008"/>
+    <mergeCell ref="C2078:C2079"/>
+    <mergeCell ref="C2428:C2429"/>
+    <mergeCell ref="C2485:C2487"/>
     <mergeCell ref="B2716:C2716"/>
     <mergeCell ref="C2727:C2729"/>
     <mergeCell ref="B2775:C2775"/>
@@ -36460,27 +39766,97 @@
     <mergeCell ref="C3031:C3032"/>
     <mergeCell ref="C3083:C3085"/>
     <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="C2915:C2916"/>
-    <mergeCell ref="B2952:C2952"/>
-    <mergeCell ref="C2967:C2968"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="C3267:C3268"/>
-    <mergeCell ref="C3142:C3143"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3201:C3203"/>
-    <mergeCell ref="C3560:C3562"/>
-    <mergeCell ref="C3618:C3619"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="C3676:C3678"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3383:C3384"/>
-    <mergeCell ref="C3429:C3430"/>
-    <mergeCell ref="B3955:C3955"/>
-    <mergeCell ref="C3966:C3967"/>
-    <mergeCell ref="C3854:C3855"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3719:C3719"/>
-    <mergeCell ref="C3735:C3736"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4316:C4317"/>
+    <mergeCell ref="C4373:C4374"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="C4209:C4210"/>
+    <mergeCell ref="C4084:C4085"/>
+    <mergeCell ref="B4073:C4073"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="C4143:C4145"/>
+    <mergeCell ref="B431:B432"/>
+    <mergeCell ref="B2319:B2320"/>
+    <mergeCell ref="B4207:B4208"/>
+    <mergeCell ref="B6092:B6093"/>
+    <mergeCell ref="B1025:B1026"/>
+    <mergeCell ref="B2913:B2914"/>
+    <mergeCell ref="B4801:B4802"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B3265:B3266"/>
+    <mergeCell ref="B5153:B5154"/>
+    <mergeCell ref="B899:B900"/>
+    <mergeCell ref="B2787:B2788"/>
+    <mergeCell ref="B4675:B4676"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1142:B1143"/>
+    <mergeCell ref="B3029:B3030"/>
+    <mergeCell ref="B4917:B4918"/>
+    <mergeCell ref="B6076:C6076"/>
+    <mergeCell ref="B5722:C5722"/>
+    <mergeCell ref="C5561:C5563"/>
+    <mergeCell ref="B5604:C5604"/>
+    <mergeCell ref="C5620:C5621"/>
+    <mergeCell ref="B5663:C5663"/>
+    <mergeCell ref="B5427:C5427"/>
+    <mergeCell ref="B1729:B1730"/>
+    <mergeCell ref="B3558:B3559"/>
+    <mergeCell ref="B3616:B3617"/>
+    <mergeCell ref="B5502:B5503"/>
+    <mergeCell ref="B1794:B1795"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B3681:B3682"/>
+    <mergeCell ref="B3674:B3675"/>
+    <mergeCell ref="B5559:B5560"/>
+    <mergeCell ref="B3381:B3382"/>
+    <mergeCell ref="B5266:B5267"/>
+    <mergeCell ref="B5545:C5545"/>
+    <mergeCell ref="C5155:C5156"/>
+    <mergeCell ref="C5268:C5269"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5089:C5091"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="C5030:C5031"/>
+    <mergeCell ref="C4855:C4856"/>
+    <mergeCell ref="C4919:C4920"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4677:C4678"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="B6961:C6961"/>
+    <mergeCell ref="C6974:C6976"/>
+    <mergeCell ref="B7020:C7020"/>
+    <mergeCell ref="B6784:C6784"/>
+    <mergeCell ref="B6802:B6803"/>
+    <mergeCell ref="B6666:C6666"/>
+    <mergeCell ref="B6686:B6687"/>
+    <mergeCell ref="B6560:B6561"/>
+    <mergeCell ref="B1846:B1847"/>
+    <mergeCell ref="B3733:B3734"/>
+    <mergeCell ref="B5618:B5619"/>
+    <mergeCell ref="B5566:B5567"/>
+    <mergeCell ref="C6500:C6502"/>
+    <mergeCell ref="B6548:C6548"/>
+    <mergeCell ref="C6258:C6260"/>
+    <mergeCell ref="B6371:C6371"/>
+    <mergeCell ref="B6489:C6489"/>
+    <mergeCell ref="C6028:C6030"/>
+    <mergeCell ref="C6146:C6147"/>
+    <mergeCell ref="C5504:C5505"/>
+    <mergeCell ref="C4803:C4804"/>
+    <mergeCell ref="C4556:C4557"/>
+    <mergeCell ref="C4615:C4617"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B7454:B7455"/>
+    <mergeCell ref="B7506:B7507"/>
+    <mergeCell ref="B7315:C7315"/>
+    <mergeCell ref="B7390:B7391"/>
+    <mergeCell ref="B7433:C7433"/>
+    <mergeCell ref="C7449:C7451"/>
+    <mergeCell ref="B7447:B7448"/>
+    <mergeCell ref="B7038:B7039"/>
+    <mergeCell ref="C7208:C7209"/>
+    <mergeCell ref="B7154:B7155"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30663A2D-5CF5-4410-BF9B-CE176A0D7EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DB2B1A-1CD9-4765-8CEA-188692191B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$9437</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$10381</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4436" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4800" uniqueCount="481">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -13158,6 +13158,2225 @@
   </si>
   <si>
     <t>Absolute Long, X (Write)</t>
+  </si>
+  <si>
+    <t>LDY (A0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as Operand. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, skip the next cycle.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A1)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDX (A2)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A3)</t>
+  </si>
+  <si>
+    <t>LDY (A4)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A5)</t>
+  </si>
+  <si>
+    <t>LDX (A6)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A7)</t>
+  </si>
+  <si>
+    <t>TAY (A8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A9)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>TAX (AA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>PLB (AB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDY (AC)</t>
+  </si>
+  <si>
+    <t>LDA (AD)</t>
+  </si>
+  <si>
+    <t>LDX (AE)</t>
+  </si>
+  <si>
+    <t>LDA (AF)</t>
   </si>
 </sst>
 </file>
@@ -13771,7 +15990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C9398"/>
+  <dimension ref="A1:C10341"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -43044,12 +45263,2284 @@
       <c r="B9398" s="21"/>
       <c r="C9398" s="22"/>
     </row>
+    <row r="9438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9438" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9438" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9438" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9439" s="4"/>
+      <c r="B9439" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9439" s="27"/>
+    </row>
+    <row r="9440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9440" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9440" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9440" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9441" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9441" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9441" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9442" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9442" s="9"/>
+      <c r="C9442" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9443" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B9443" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9443" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9444" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9444" s="17"/>
+      <c r="C9444" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9445" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9445" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9445" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9446" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9446" s="9"/>
+      <c r="C9446" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="9447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9447" s="8"/>
+      <c r="B9447" s="9"/>
+      <c r="C9447" s="36"/>
+    </row>
+    <row r="9448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9448" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9448" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9448" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9449" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9449" s="21"/>
+      <c r="C9449" s="22"/>
+    </row>
+    <row r="9497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9497" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B9497" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9497" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9498" s="4"/>
+      <c r="B9498" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9498" s="35"/>
+    </row>
+    <row r="9499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9499" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9499" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9499" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9500" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9500" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9500" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9501" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9501" s="9"/>
+      <c r="C9501" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9502" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9502" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9502" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9503" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9503" s="9"/>
+      <c r="C9503" s="10" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="9504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9504" s="8"/>
+      <c r="B9504" s="9"/>
+      <c r="C9504" s="10" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9505" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9505" s="9"/>
+      <c r="C9505" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9506" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="B9506" s="17"/>
+      <c r="C9506" s="24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9507" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B9507" s="17"/>
+      <c r="C9507" s="24"/>
+    </row>
+    <row r="9508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9508" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9508" s="9"/>
+      <c r="C9508" s="10"/>
+    </row>
+    <row r="9509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9509" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9509" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9509" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9510" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9510" s="9"/>
+      <c r="C9510" s="10"/>
+    </row>
+    <row r="9511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9511" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9511" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9511" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9512" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B9512" s="9"/>
+      <c r="C9512" s="10"/>
+    </row>
+    <row r="9513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9513" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B9513" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9513" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9514" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B9514" s="17"/>
+      <c r="C9514" s="24"/>
+    </row>
+    <row r="9515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9515" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B9515" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9515" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9516" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B9516" s="32"/>
+      <c r="C9516" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9517" s="8"/>
+      <c r="B9517" s="32"/>
+      <c r="C9517" s="36"/>
+    </row>
+    <row r="9518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9518" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B9518" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9518" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9519" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9519" s="21"/>
+      <c r="C9519" s="22"/>
+    </row>
+    <row r="9556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9556" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B9556" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9556" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9557" s="4"/>
+      <c r="B9557" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9557" s="27"/>
+    </row>
+    <row r="9558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9558" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9558" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9558" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9559" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9559" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9559" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9560" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9560" s="9"/>
+      <c r="C9560" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9561" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B9561" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9561" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9562" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9562" s="17"/>
+      <c r="C9562" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9563" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9563" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9563" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9564" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9564" s="9"/>
+      <c r="C9564" s="36" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="9565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9565" s="8"/>
+      <c r="B9565" s="9"/>
+      <c r="C9565" s="36"/>
+    </row>
+    <row r="9566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9566" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9566" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9566" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9567" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9567" s="21"/>
+      <c r="C9567" s="22"/>
+    </row>
+    <row r="9615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9615" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9615" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9616" s="4"/>
+      <c r="B9616" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9616" s="27"/>
+    </row>
+    <row r="9617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9617" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9617" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9617" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9618" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9618" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9618" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9619" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9619" s="9"/>
+      <c r="C9619" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9620" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9620" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9620" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9621" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9621" s="9"/>
+      <c r="C9621" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9622" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9622" s="9"/>
+      <c r="C9622" s="10"/>
+    </row>
+    <row r="9623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9623" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9623" s="32"/>
+      <c r="C9623" s="10"/>
+    </row>
+    <row r="9624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9624" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B9624" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9624" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9625" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9625" s="31"/>
+      <c r="C9625" s="24"/>
+    </row>
+    <row r="9626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9626" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B9626" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9626" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9627" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9627" s="9"/>
+      <c r="C9627" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9628" s="8"/>
+      <c r="B9628" s="9"/>
+      <c r="C9628" s="36"/>
+    </row>
+    <row r="9629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9629" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9629" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9629" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9630" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9630" s="21"/>
+      <c r="C9630" s="22"/>
+    </row>
+    <row r="9674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9674" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B9674" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9674" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9675" s="4"/>
+      <c r="B9675" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9675" s="27"/>
+    </row>
+    <row r="9676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9676" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9676" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9676" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9677" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9677" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9677" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9678" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9678" s="9"/>
+      <c r="C9678" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9679" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9679" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9679" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9680" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9680" s="17"/>
+      <c r="C9680" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9681" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9681" s="17"/>
+      <c r="C9681" s="24"/>
+    </row>
+    <row r="9682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9682" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9682" s="32"/>
+      <c r="C9682" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9683" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B9683" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9683" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9684" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9684" s="31"/>
+      <c r="C9684" s="24"/>
+    </row>
+    <row r="9685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9685" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B9685" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9685" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9686" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9686" s="9"/>
+      <c r="C9686" s="36" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="9687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9687" s="8"/>
+      <c r="B9687" s="9"/>
+      <c r="C9687" s="36"/>
+    </row>
+    <row r="9688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9688" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9688" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9688" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9689" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9689" s="21"/>
+      <c r="C9689" s="22"/>
+    </row>
+    <row r="9733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9733" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9733" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9733" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9734" s="4"/>
+      <c r="B9734" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9734" s="27"/>
+    </row>
+    <row r="9735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9735" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9735" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9735" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9736" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9736" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9736" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9737" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9737" s="9"/>
+      <c r="C9737" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9738" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9738" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9738" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9739" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9739" s="17"/>
+      <c r="C9739" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9740" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9740" s="17"/>
+      <c r="C9740" s="24"/>
+    </row>
+    <row r="9741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9741" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9741" s="32"/>
+      <c r="C9741" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9742" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B9742" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9742" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9743" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9743" s="31"/>
+      <c r="C9743" s="24"/>
+    </row>
+    <row r="9744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9744" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B9744" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9744" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9745" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9745" s="9"/>
+      <c r="C9745" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9746" s="8"/>
+      <c r="B9746" s="9"/>
+      <c r="C9746" s="36"/>
+    </row>
+    <row r="9747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9747" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9747" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9747" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9748" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9748" s="21"/>
+      <c r="C9748" s="22"/>
+    </row>
+    <row r="9792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9792" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B9792" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9792" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9793" s="4"/>
+      <c r="B9793" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9793" s="27"/>
+    </row>
+    <row r="9794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9794" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9794" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9794" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9795" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9795" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9795" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9796" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9796" s="9"/>
+      <c r="C9796" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9797" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9797" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9797" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9798" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9798" s="17"/>
+      <c r="C9798" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9799" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9799" s="17"/>
+      <c r="C9799" s="24"/>
+    </row>
+    <row r="9800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9800" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9800" s="32"/>
+      <c r="C9800" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9801" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B9801" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9801" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9802" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9802" s="31"/>
+      <c r="C9802" s="24"/>
+    </row>
+    <row r="9803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9803" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B9803" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9803" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9804" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9804" s="9"/>
+      <c r="C9804" s="36" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="9805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9805" s="8"/>
+      <c r="B9805" s="9"/>
+      <c r="C9805" s="36"/>
+    </row>
+    <row r="9806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9806" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9806" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9806" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9807" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9807" s="21"/>
+      <c r="C9807" s="22"/>
+    </row>
+    <row r="9851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9851" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B9851" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9851" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9852" s="4"/>
+      <c r="B9852" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9852" s="27"/>
+    </row>
+    <row r="9853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9853" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9853" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9853" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9854" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9854" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9854" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9855" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9855" s="9"/>
+      <c r="C9855" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9856" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9856" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9856" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9857" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9857" s="17"/>
+      <c r="C9857" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9858" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9858" s="17"/>
+      <c r="C9858" s="24"/>
+    </row>
+    <row r="9859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9859" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9859" s="32"/>
+      <c r="C9859" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9860" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9860" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9860" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9861" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9861" s="32"/>
+      <c r="C9861" s="10"/>
+    </row>
+    <row r="9862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9862" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9862" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9862" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9863" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9863" s="32"/>
+      <c r="C9863" s="10"/>
+    </row>
+    <row r="9864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9864" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9864" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9864" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9865" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B9865" s="32"/>
+      <c r="C9865" s="10"/>
+    </row>
+    <row r="9866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9866" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B9866" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9866" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9867" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B9867" s="31"/>
+      <c r="C9867" s="24"/>
+    </row>
+    <row r="9868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9868" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B9868" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C9868" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9869" s="25"/>
+      <c r="B9869" s="33"/>
+      <c r="C9869" s="24"/>
+    </row>
+    <row r="9870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9870" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B9870" s="9"/>
+      <c r="C9870" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9871" s="8"/>
+      <c r="B9871" s="9"/>
+      <c r="C9871" s="36"/>
+    </row>
+    <row r="9872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9872" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B9872" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9872" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9873" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9873" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9873" s="21"/>
+      <c r="C9873" s="22"/>
+    </row>
+    <row r="9910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9910" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B9910" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9910" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9911" s="4"/>
+      <c r="B9911" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9911" s="27"/>
+    </row>
+    <row r="9912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9912" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9912" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9912" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9913" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9913" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9913" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9914" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9914" s="9"/>
+      <c r="C9914" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9915" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B9915" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9915" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9916" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9916" s="9"/>
+      <c r="C9916" s="36" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="9917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9917" s="8"/>
+      <c r="B9917" s="9"/>
+      <c r="C9917" s="36"/>
+    </row>
+    <row r="9918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9918" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9918" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9918" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9919" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9919" s="21"/>
+      <c r="C9919" s="22"/>
+    </row>
+    <row r="9969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9969" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B9969" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9969" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9970" s="4"/>
+      <c r="B9970" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9970" s="27"/>
+    </row>
+    <row r="9971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9971" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9971" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9971" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9972" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9972" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9972" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9973" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9973" s="9"/>
+      <c r="C9973" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9974" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B9974" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9974" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9975" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B9975" s="17"/>
+      <c r="C9975" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9976" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9976" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9976" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9977" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9977" s="9"/>
+      <c r="C9977" s="36" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9978" s="8"/>
+      <c r="B9978" s="9"/>
+      <c r="C9978" s="36"/>
+    </row>
+    <row r="9979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9979" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9979" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9979" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9980" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9980" s="21"/>
+      <c r="C9980" s="22"/>
+    </row>
+    <row r="10028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10028" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B10028" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10028" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10029" s="4"/>
+      <c r="B10029" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10029" s="27"/>
+    </row>
+    <row r="10030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10030" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10030" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10030" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10031" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10031" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10031" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10032" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10032" s="9"/>
+      <c r="C10032" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10033" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B10033" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10033" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10034" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10034" s="9"/>
+      <c r="C10034" s="36" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10035" s="8"/>
+      <c r="B10035" s="9"/>
+      <c r="C10035" s="36"/>
+    </row>
+    <row r="10036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10036" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10036" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10036" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10037" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10037" s="21"/>
+      <c r="C10037" s="22"/>
+    </row>
+    <row r="10087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10087" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10087" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10087" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10088" s="4"/>
+      <c r="B10088" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10088" s="27"/>
+    </row>
+    <row r="10089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10089" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10089" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10089" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10090" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10090" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10090" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10091" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10091" s="9"/>
+      <c r="C10091" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10092" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10092" s="32"/>
+      <c r="C10092" s="10"/>
+    </row>
+    <row r="10093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10093" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10093" s="9"/>
+      <c r="C10093" s="10"/>
+    </row>
+    <row r="10094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10094" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10094" s="9"/>
+      <c r="C10094" s="10"/>
+    </row>
+    <row r="10095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10095" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10095" s="9"/>
+      <c r="C10095" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10096" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B10096" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10096" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10097" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10097" s="9"/>
+      <c r="C10097" s="10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="10098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10098" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10098" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10098" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10099" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10099" s="21"/>
+      <c r="C10099" s="22"/>
+    </row>
+    <row r="10146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10146" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B10146" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10146" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10147" s="4"/>
+      <c r="B10147" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10147" s="27"/>
+    </row>
+    <row r="10148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10148" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10148" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10148" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10149" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10149" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10149" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10150" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10150" s="9"/>
+      <c r="C10150" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10151" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10151" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10151" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10152" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10152" s="9"/>
+      <c r="C10152" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10153" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10153" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10153" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10154" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10154" s="9"/>
+      <c r="C10154" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10155" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B10155" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10155" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="10156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10156" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10156" s="17"/>
+      <c r="C10156" s="24"/>
+    </row>
+    <row r="10157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10157" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B10157" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10157" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10158" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10158" s="9"/>
+      <c r="C10158" s="36" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="10159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10159" s="8"/>
+      <c r="B10159" s="9"/>
+      <c r="C10159" s="36"/>
+    </row>
+    <row r="10160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10160" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10160" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10160" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10161" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10161" s="21"/>
+      <c r="C10161" s="22"/>
+    </row>
+    <row r="10205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10205" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B10205" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10205" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10206" s="4"/>
+      <c r="B10206" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10206" s="27"/>
+    </row>
+    <row r="10207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10207" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10207" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10207" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10208" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10208" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10208" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10209" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10209" s="9"/>
+      <c r="C10209" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10210" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10210" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10210" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10211" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10211" s="9"/>
+      <c r="C10211" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10212" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10212" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10212" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10213" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10213" s="9"/>
+      <c r="C10213" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10214" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B10214" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10214" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10215" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10215" s="17"/>
+      <c r="C10215" s="24"/>
+    </row>
+    <row r="10216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10216" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B10216" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10216" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10217" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10217" s="9"/>
+      <c r="C10217" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10218" s="8"/>
+      <c r="B10218" s="9"/>
+      <c r="C10218" s="36"/>
+    </row>
+    <row r="10219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10219" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10219" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10219" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10220" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10220" s="21"/>
+      <c r="C10220" s="22"/>
+    </row>
+    <row r="10264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10264" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B10264" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10264" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10265" s="4"/>
+      <c r="B10265" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10265" s="27"/>
+    </row>
+    <row r="10266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10266" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10266" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10266" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10267" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10267" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10267" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10268" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10268" s="9"/>
+      <c r="C10268" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10269" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10269" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10269" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10270" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10270" s="9"/>
+      <c r="C10270" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10271" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10271" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10271" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10272" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10272" s="9"/>
+      <c r="C10272" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10273" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="B10273" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10273" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="10274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10274" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10274" s="17"/>
+      <c r="C10274" s="24"/>
+    </row>
+    <row r="10275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10275" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="B10275" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10275" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10276" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10276" s="9"/>
+      <c r="C10276" s="36" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="10277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10277" s="8"/>
+      <c r="B10277" s="9"/>
+      <c r="C10277" s="36"/>
+    </row>
+    <row r="10278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10278" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10278" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10278" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10279" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10279" s="21"/>
+      <c r="C10279" s="22"/>
+    </row>
+    <row r="10323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10323" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B10323" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10323" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10324" s="4"/>
+      <c r="B10324" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10324" s="27"/>
+    </row>
+    <row r="10325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10325" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10325" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10325" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10326" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10326" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10326" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10327" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10327" s="9"/>
+      <c r="C10327" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10328" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10328" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10328" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10329" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10329" s="32"/>
+      <c r="C10329" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10330" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10330" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10330" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10331" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10331" s="9"/>
+      <c r="C10331" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10332" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10332" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10332" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10333" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10333" s="9"/>
+      <c r="C10333" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10334" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B10334" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10334" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10335" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10335" s="17"/>
+      <c r="C10335" s="24"/>
+    </row>
+    <row r="10336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10336" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B10336" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="C10336" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10337" s="25"/>
+      <c r="B10337" s="33"/>
+      <c r="C10337" s="24"/>
+    </row>
+    <row r="10338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10338" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10338" s="9"/>
+      <c r="C10338" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10339" s="8"/>
+      <c r="B10339" s="9"/>
+      <c r="C10339" s="36"/>
+    </row>
+    <row r="10340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10340" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B10340" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10340" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10341" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10341" s="21"/>
+      <c r="C10341" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="193">
+  <mergeCells count="211">
+    <mergeCell ref="C10158:C10159"/>
+    <mergeCell ref="C10217:C10218"/>
+    <mergeCell ref="B10336:B10337"/>
+    <mergeCell ref="C10338:C10339"/>
+    <mergeCell ref="C9916:C9917"/>
+    <mergeCell ref="C10276:C10277"/>
+    <mergeCell ref="C9870:C9871"/>
+    <mergeCell ref="B9868:B9869"/>
+    <mergeCell ref="C9977:C9978"/>
+    <mergeCell ref="C10034:C10035"/>
+    <mergeCell ref="C9564:C9565"/>
+    <mergeCell ref="C9627:C9628"/>
+    <mergeCell ref="C9686:C9687"/>
+    <mergeCell ref="C9745:C9746"/>
+    <mergeCell ref="C9804:C9805"/>
     <mergeCell ref="C9149:C9150"/>
     <mergeCell ref="B9276:B9277"/>
     <mergeCell ref="B9335:B9336"/>
     <mergeCell ref="B9394:B9395"/>
+    <mergeCell ref="C9446:C9447"/>
+    <mergeCell ref="B9498:C9498"/>
+    <mergeCell ref="C9516:C9517"/>
     <mergeCell ref="B8926:B8927"/>
     <mergeCell ref="B8908:C8908"/>
     <mergeCell ref="C8972:C8973"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DB2B1A-1CD9-4765-8CEA-188692191B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EB1F10-CC1C-4A21-8764-122D08C3B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$10381</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$11325</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4800" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5205" uniqueCount="505">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -15377,6 +15377,907 @@
   </si>
   <si>
     <t>LDA (AF)</t>
+  </si>
+  <si>
+    <t>Direct, Y (Write)</t>
+  </si>
+  <si>
+    <t>BCS (B0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (B1)</t>
+  </si>
+  <si>
+    <t>LDA (B2)</t>
+  </si>
+  <si>
+    <t>LDA (B3)</t>
+  </si>
+  <si>
+    <t>LDY (B4)</t>
+  </si>
+  <si>
+    <t>LDA (B5)</t>
+  </si>
+  <si>
+    <t>LDX (B6)</t>
+  </si>
+  <si>
+    <t>Direct, Y (Read)</t>
+  </si>
+  <si>
+    <t>LDA (B7)</t>
+  </si>
+  <si>
+    <t>CLV (B8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (B9)</t>
+  </si>
+  <si>
+    <t>Inc. PC. Perform Orig = Pointer.</t>
+  </si>
+  <si>
+    <t>TSX (BA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>TYX (BB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDY (BC)</t>
+  </si>
+  <si>
+    <t>LDA (BD)</t>
+  </si>
+  <si>
+    <t>LDX (BE)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off X.L, otherwise set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (BF)</t>
   </si>
 </sst>
 </file>
@@ -15990,7 +16891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C10341"/>
+  <dimension ref="A1:C11287"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -43780,7 +44681,7 @@
     <row r="8849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8849" s="4"/>
       <c r="B8849" s="26" t="s">
-        <v>358</v>
+        <v>481</v>
       </c>
       <c r="C8849" s="27"/>
     </row>
@@ -47517,8 +48418,2715 @@
       <c r="B10341" s="21"/>
       <c r="C10341" s="22"/>
     </row>
+    <row r="10382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10382" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B10382" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10382" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10383" s="4"/>
+      <c r="B10383" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10383" s="6"/>
+    </row>
+    <row r="10384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10384" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10384" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10384" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10385" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10385" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10385" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10386" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10386" s="9"/>
+      <c r="C10386" s="10" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="10387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10387" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B10387" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10387" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10388" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10388" s="9"/>
+      <c r="C10388" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10389" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10389" s="9"/>
+      <c r="C10389" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10390" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10390" s="9"/>
+      <c r="C10390" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10391" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10391" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10391" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10392" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10392" s="21"/>
+      <c r="C10392" s="22"/>
+    </row>
+    <row r="10441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10441" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B10441" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10441" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10442" s="4"/>
+      <c r="B10442" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10442" s="35"/>
+    </row>
+    <row r="10443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10443" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10443" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10443" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10444" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10444" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10444" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10445" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10445" s="9"/>
+      <c r="C10445" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10446" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10446" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10446" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10447" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B10447" s="17"/>
+      <c r="C10447" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10448" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10448" s="17"/>
+      <c r="C10448" s="24"/>
+    </row>
+    <row r="10449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10449" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10449" s="9"/>
+      <c r="C10449" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10450" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10450" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10450" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10451" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10451" s="9"/>
+      <c r="C10451" s="10"/>
+    </row>
+    <row r="10452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10452" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10452" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10452" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10453" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10453" s="9"/>
+      <c r="C10453" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10454" s="8"/>
+      <c r="B10454" s="9"/>
+      <c r="C10454" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10455" s="8"/>
+      <c r="B10455" s="9"/>
+      <c r="C10455" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10456" s="8"/>
+      <c r="B10456" s="9"/>
+      <c r="C10456" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10457" s="8"/>
+      <c r="B10457" s="9"/>
+      <c r="C10457" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10458" s="16">
+        <v>5.2</v>
+      </c>
+      <c r="B10458" s="17"/>
+      <c r="C10458" s="24"/>
+    </row>
+    <row r="10459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10459" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B10459" s="17"/>
+      <c r="C10459" s="24"/>
+    </row>
+    <row r="10460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10460" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B10460" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10460" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10461" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B10461" s="17"/>
+      <c r="C10461" s="24"/>
+    </row>
+    <row r="10462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10462" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B10462" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10462" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10463" s="25"/>
+      <c r="B10463" s="33"/>
+      <c r="C10463" s="24"/>
+    </row>
+    <row r="10464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10464" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B10464" s="9"/>
+      <c r="C10464" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10465" s="8"/>
+      <c r="B10465" s="9"/>
+      <c r="C10465" s="36"/>
+    </row>
+    <row r="10466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10466" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B10466" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10466" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10467" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10467" s="21"/>
+      <c r="C10467" s="22"/>
+    </row>
+    <row r="10500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10500" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B10500" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10500" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10501" s="4"/>
+      <c r="B10501" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10501" s="27"/>
+    </row>
+    <row r="10502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10502" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10502" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10502" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10503" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10503" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10503" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10504" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10504" s="9"/>
+      <c r="C10504" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10505" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10505" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10505" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10506" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B10506" s="17"/>
+      <c r="C10506" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10507" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10507" s="17"/>
+      <c r="C10507" s="24"/>
+    </row>
+    <row r="10508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10508" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10508" s="9"/>
+      <c r="C10508" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10509" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10509" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10509" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10510" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10510" s="9"/>
+      <c r="C10510" s="10"/>
+    </row>
+    <row r="10511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10511" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10511" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10511" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10512" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10512" s="9"/>
+      <c r="C10512" s="10"/>
+    </row>
+    <row r="10513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10513" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="B10513" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10513" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10514" s="16">
+        <v>6.1</v>
+      </c>
+      <c r="B10514" s="17"/>
+      <c r="C10514" s="24"/>
+    </row>
+    <row r="10515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10515" s="25">
+        <v>6.2</v>
+      </c>
+      <c r="B10515" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10515" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10516" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B10516" s="9"/>
+      <c r="C10516" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10517" s="8"/>
+      <c r="B10517" s="9"/>
+      <c r="C10517" s="36"/>
+    </row>
+    <row r="10518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10518" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B10518" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10518" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10519" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10519" s="21"/>
+      <c r="C10519" s="22"/>
+    </row>
+    <row r="10559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10559" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10559" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10559" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10560" s="4"/>
+      <c r="B10560" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10560" s="35"/>
+    </row>
+    <row r="10561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10561" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10561" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10561" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10562" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10562" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10562" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10563" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10563" s="9"/>
+      <c r="C10563" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10564" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10564" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10564" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10565" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10565" s="9"/>
+      <c r="C10565" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10566" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10566" s="9"/>
+      <c r="C10566" s="10"/>
+    </row>
+    <row r="10567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10567" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10567" s="9"/>
+      <c r="C10567" s="10"/>
+    </row>
+    <row r="10568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10568" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10568" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10568" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10569" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10569" s="9"/>
+      <c r="C10569" s="10"/>
+    </row>
+    <row r="10570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10570" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10570" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10570" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10571" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10571" s="9"/>
+      <c r="C10571" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10572" s="8"/>
+      <c r="B10572" s="9"/>
+      <c r="C10572" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10573" s="8"/>
+      <c r="B10573" s="9"/>
+      <c r="C10573" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10574" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10574" s="9"/>
+      <c r="C10574" s="10"/>
+    </row>
+    <row r="10575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10575" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10575" s="9"/>
+      <c r="C10575" s="10"/>
+    </row>
+    <row r="10576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10576" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B10576" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10576" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10577" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B10577" s="17"/>
+      <c r="C10577" s="24"/>
+    </row>
+    <row r="10578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10578" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B10578" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10578" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10579" s="25"/>
+      <c r="B10579" s="33"/>
+      <c r="C10579" s="24"/>
+    </row>
+    <row r="10580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10580" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B10580" s="9"/>
+      <c r="C10580" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10581" s="8"/>
+      <c r="B10581" s="9"/>
+      <c r="C10581" s="36"/>
+    </row>
+    <row r="10582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10582" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B10582" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10582" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10583" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10583" s="21"/>
+      <c r="C10583" s="22"/>
+    </row>
+    <row r="10618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10618" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B10618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10618" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10619" s="4"/>
+      <c r="B10619" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10619" s="27"/>
+    </row>
+    <row r="10620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10620" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10620" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10620" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10621" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10621" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10621" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10622" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10622" s="9"/>
+      <c r="C10622" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10623" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10623" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10623" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10624" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10624" s="9"/>
+      <c r="C10624" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10625" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10625" s="9"/>
+      <c r="C10625" s="10"/>
+    </row>
+    <row r="10626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10626" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10626" s="9"/>
+      <c r="C10626" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10627" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10627" s="9"/>
+      <c r="C10627" s="10"/>
+    </row>
+    <row r="10628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10628" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10628" s="9"/>
+      <c r="C10628" s="10"/>
+    </row>
+    <row r="10629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10629" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B10629" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10629" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="10630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10630" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10630" s="17"/>
+      <c r="C10630" s="24"/>
+    </row>
+    <row r="10631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10631" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B10631" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10631" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10632" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10632" s="9"/>
+      <c r="C10632" s="36" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="10633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10633" s="8"/>
+      <c r="B10633" s="9"/>
+      <c r="C10633" s="36"/>
+    </row>
+    <row r="10634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10634" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B10634" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10634" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10635" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10635" s="21"/>
+      <c r="C10635" s="22"/>
+    </row>
+    <row r="10677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10677" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B10677" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10677" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10678" s="4"/>
+      <c r="B10678" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10678" s="27"/>
+    </row>
+    <row r="10679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10679" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10679" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10679" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10680" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10680" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10680" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10681" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10681" s="9"/>
+      <c r="C10681" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10682" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10682" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10682" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10683" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10683" s="9"/>
+      <c r="C10683" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10684" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10684" s="9"/>
+      <c r="C10684" s="10"/>
+    </row>
+    <row r="10685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10685" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10685" s="9"/>
+      <c r="C10685" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10686" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10686" s="9"/>
+      <c r="C10686" s="10"/>
+    </row>
+    <row r="10687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10687" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10687" s="9"/>
+      <c r="C10687" s="10"/>
+    </row>
+    <row r="10688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10688" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B10688" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10688" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10689" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10689" s="17"/>
+      <c r="C10689" s="24"/>
+    </row>
+    <row r="10690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10690" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B10690" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10690" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10691" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10691" s="9"/>
+      <c r="C10691" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10692" s="8"/>
+      <c r="B10692" s="9"/>
+      <c r="C10692" s="36"/>
+    </row>
+    <row r="10693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10693" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B10693" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10693" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10694" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10694" s="21"/>
+      <c r="C10694" s="22"/>
+    </row>
+    <row r="10736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10736" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B10736" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10736" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10737" s="4"/>
+      <c r="B10737" s="26" t="s">
+        <v>490</v>
+      </c>
+      <c r="C10737" s="27"/>
+    </row>
+    <row r="10738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10738" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10738" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10738" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10739" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10739" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10739" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10740" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10740" s="9"/>
+      <c r="C10740" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10741" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10741" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10741" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10742" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10742" s="9"/>
+      <c r="C10742" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10743" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10743" s="9"/>
+      <c r="C10743" s="10"/>
+    </row>
+    <row r="10744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10744" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10744" s="9"/>
+      <c r="C10744" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10745" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10745" s="9"/>
+      <c r="C10745" s="10"/>
+    </row>
+    <row r="10746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10746" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10746" s="9"/>
+      <c r="C10746" s="10"/>
+    </row>
+    <row r="10747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10747" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B10747" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10747" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="10748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10748" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10748" s="17"/>
+      <c r="C10748" s="24"/>
+    </row>
+    <row r="10749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10749" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B10749" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10749" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10750" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10750" s="9"/>
+      <c r="C10750" s="36" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="10751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10751" s="8"/>
+      <c r="B10751" s="9"/>
+      <c r="C10751" s="36"/>
+    </row>
+    <row r="10752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10752" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B10752" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10752" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10753" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10753" s="21"/>
+      <c r="C10753" s="22"/>
+    </row>
+    <row r="10795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10795" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10795" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10795" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10796" s="4"/>
+      <c r="B10796" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10796" s="35"/>
+    </row>
+    <row r="10797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10797" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10797" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10797" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10798" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10798" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10798" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10799" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10799" s="9"/>
+      <c r="C10799" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10800" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10800" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10800" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10801" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B10801" s="17"/>
+      <c r="C10801" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10802" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10802" s="17"/>
+      <c r="C10802" s="24"/>
+    </row>
+    <row r="10803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10803" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10803" s="9"/>
+      <c r="C10803" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10804" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10804" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10804" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10805" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10805" s="9"/>
+      <c r="C10805" s="10"/>
+    </row>
+    <row r="10806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10806" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10806" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10806" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10807" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10807" s="9"/>
+      <c r="C10807" s="10"/>
+    </row>
+    <row r="10808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10808" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10808" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10808" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10809" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10809" s="9"/>
+      <c r="C10809" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10810" s="8"/>
+      <c r="B10810" s="9"/>
+      <c r="C10810" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10811" s="8"/>
+      <c r="B10811" s="9"/>
+      <c r="C10811" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10812" s="19">
+        <v>6.2</v>
+      </c>
+      <c r="B10812" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10812" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10813" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="B10813" s="17"/>
+      <c r="C10813" s="24"/>
+    </row>
+    <row r="10814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10814" s="25">
+        <v>7.2</v>
+      </c>
+      <c r="B10814" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10814" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10815" s="25"/>
+      <c r="B10815" s="33"/>
+      <c r="C10815" s="18"/>
+    </row>
+    <row r="10816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10816" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B10816" s="9"/>
+      <c r="C10816" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10817" s="8"/>
+      <c r="B10817" s="9"/>
+      <c r="C10817" s="36"/>
+    </row>
+    <row r="10818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10818" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B10818" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10818" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10819" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10819" s="21"/>
+      <c r="C10819" s="22"/>
+    </row>
+    <row r="10854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10854" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B10854" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10854" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10855" s="4"/>
+      <c r="B10855" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10855" s="27"/>
+    </row>
+    <row r="10856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10856" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10856" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10856" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10857" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10857" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10857" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10858" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10858" s="9"/>
+      <c r="C10858" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10859" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B10859" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10859" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10860" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10860" s="9"/>
+      <c r="C10860" s="10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="10861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10861" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10861" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10861" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10862" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10862" s="21"/>
+      <c r="C10862" s="22"/>
+    </row>
+    <row r="10913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10913" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B10913" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10913" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10914" s="4"/>
+      <c r="B10914" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10914" s="27"/>
+    </row>
+    <row r="10915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10915" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10915" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10915" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10916" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10916" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10916" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10917" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10917" s="9"/>
+      <c r="C10917" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10918" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10918" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10918" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10919" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10919" s="9"/>
+      <c r="C10919" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10920" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10920" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10920" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10921" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10921" s="9"/>
+      <c r="C10921" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10922" s="8"/>
+      <c r="B10922" s="9"/>
+      <c r="C10922" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10923" s="8"/>
+      <c r="B10923" s="9"/>
+      <c r="C10923" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10924" s="8"/>
+      <c r="B10924" s="9"/>
+      <c r="C10924" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10925" s="8"/>
+      <c r="B10925" s="9"/>
+      <c r="C10925" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10926" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B10926" s="17"/>
+      <c r="C10926" s="24"/>
+    </row>
+    <row r="10927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10927" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10927" s="17"/>
+      <c r="C10927" s="24"/>
+    </row>
+    <row r="10928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10928" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B10928" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10928" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10929" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10929" s="17"/>
+      <c r="C10929" s="24"/>
+    </row>
+    <row r="10930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10930" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B10930" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10930" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10931" s="25"/>
+      <c r="B10931" s="33"/>
+      <c r="C10931" s="24"/>
+    </row>
+    <row r="10932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10932" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10932" s="9"/>
+      <c r="C10932" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10933" s="8"/>
+      <c r="B10933" s="9"/>
+      <c r="C10933" s="36"/>
+    </row>
+    <row r="10934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10934" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B10934" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10934" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10935" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10935" s="21"/>
+      <c r="C10935" s="22"/>
+    </row>
+    <row r="10972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10972" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B10972" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10972" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10973" s="4"/>
+      <c r="B10973" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10973" s="27"/>
+    </row>
+    <row r="10974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10974" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10974" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10974" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10975" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10975" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10975" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10976" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10976" s="9"/>
+      <c r="C10976" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10977" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B10977" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10977" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10978" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10978" s="9"/>
+      <c r="C10978" s="36" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="10979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10979" s="8"/>
+      <c r="B10979" s="9"/>
+      <c r="C10979" s="36"/>
+    </row>
+    <row r="10980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10980" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10980" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10980" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10981" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10981" s="21"/>
+      <c r="C10981" s="22"/>
+    </row>
+    <row r="11031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11031" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B11031" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11031" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11032" s="4"/>
+      <c r="B11032" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11032" s="27"/>
+    </row>
+    <row r="11033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11033" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11033" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11033" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11034" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11034" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11034" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11035" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11035" s="9"/>
+      <c r="C11035" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11036" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="B11036" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11036" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11037" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11037" s="9"/>
+      <c r="C11037" s="36" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="11038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11038" s="8"/>
+      <c r="B11038" s="9"/>
+      <c r="C11038" s="36"/>
+    </row>
+    <row r="11039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11039" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11039" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11039" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11040" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11040" s="21"/>
+      <c r="C11040" s="22"/>
+    </row>
+    <row r="11090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11090" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11090" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11090" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11091" s="4"/>
+      <c r="B11091" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11091" s="27"/>
+    </row>
+    <row r="11092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11092" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11092" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11092" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11093" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11093" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11093" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11094" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11094" s="9"/>
+      <c r="C11094" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11095" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11095" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11095" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11096" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11096" s="9"/>
+      <c r="C11096" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11097" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11097" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11097" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11098" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11098" s="9"/>
+      <c r="C11098" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11099" s="8"/>
+      <c r="B11099" s="9"/>
+      <c r="C11099" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11100" s="8"/>
+      <c r="B11100" s="9"/>
+      <c r="C11100" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11101" s="8"/>
+      <c r="B11101" s="9"/>
+      <c r="C11101" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11102" s="8"/>
+      <c r="B11102" s="9"/>
+      <c r="C11102" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11103" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B11103" s="17"/>
+      <c r="C11103" s="24"/>
+    </row>
+    <row r="11104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11104" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11104" s="17"/>
+      <c r="C11104" s="24"/>
+    </row>
+    <row r="11105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11105" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B11105" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11105" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11106" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11106" s="17"/>
+      <c r="C11106" s="24"/>
+    </row>
+    <row r="11107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11107" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B11107" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11107" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11108" s="25"/>
+      <c r="B11108" s="33"/>
+      <c r="C11108" s="24"/>
+    </row>
+    <row r="11109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11109" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B11109" s="32"/>
+      <c r="C11109" s="36" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="11110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11110" s="8"/>
+      <c r="B11110" s="32"/>
+      <c r="C11110" s="36"/>
+    </row>
+    <row r="11111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11111" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B11111" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11111" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11112" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11112" s="21"/>
+      <c r="C11112" s="22"/>
+    </row>
+    <row r="11149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11149" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B11149" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11149" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11150" s="4"/>
+      <c r="B11150" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11150" s="27"/>
+    </row>
+    <row r="11151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11151" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11151" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11151" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11152" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11152" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11152" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11153" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11153" s="9"/>
+      <c r="C11153" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11154" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11154" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11154" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11155" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11155" s="9"/>
+      <c r="C11155" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11156" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11156" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11156" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11157" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11157" s="9"/>
+      <c r="C11157" s="10" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="11158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11158" s="8"/>
+      <c r="B11158" s="9"/>
+      <c r="C11158" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11159" s="8"/>
+      <c r="B11159" s="9"/>
+      <c r="C11159" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11160" s="8"/>
+      <c r="B11160" s="9"/>
+      <c r="C11160" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11161" s="8"/>
+      <c r="B11161" s="9"/>
+      <c r="C11161" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11162" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B11162" s="17"/>
+      <c r="C11162" s="24"/>
+    </row>
+    <row r="11163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11163" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11163" s="17"/>
+      <c r="C11163" s="24"/>
+    </row>
+    <row r="11164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11164" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B11164" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11164" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11165" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11165" s="17"/>
+      <c r="C11165" s="24"/>
+    </row>
+    <row r="11166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11166" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B11166" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11166" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11167" s="25"/>
+      <c r="B11167" s="33"/>
+      <c r="C11167" s="24"/>
+    </row>
+    <row r="11168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11168" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B11168" s="32"/>
+      <c r="C11168" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="11169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11169" s="8"/>
+      <c r="B11169" s="32"/>
+      <c r="C11169" s="36"/>
+    </row>
+    <row r="11170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11170" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B11170" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11170" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11171" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11171" s="21"/>
+      <c r="C11171" s="22"/>
+    </row>
+    <row r="11208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11208" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B11208" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11208" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11209" s="4"/>
+      <c r="B11209" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11209" s="27"/>
+    </row>
+    <row r="11210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11210" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11210" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11210" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11211" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11211" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11211" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11212" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11212" s="9"/>
+      <c r="C11212" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11213" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11213" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11213" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11214" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11214" s="9"/>
+      <c r="C11214" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11215" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11215" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11215" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11216" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11216" s="9"/>
+      <c r="C11216" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11217" s="8"/>
+      <c r="B11217" s="9"/>
+      <c r="C11217" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11218" s="8"/>
+      <c r="B11218" s="9"/>
+      <c r="C11218" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11219" s="8"/>
+      <c r="B11219" s="9"/>
+      <c r="C11219" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11220" s="8"/>
+      <c r="B11220" s="9"/>
+      <c r="C11220" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11221" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B11221" s="17"/>
+      <c r="C11221" s="24"/>
+    </row>
+    <row r="11222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11222" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11222" s="17"/>
+      <c r="C11222" s="24"/>
+    </row>
+    <row r="11223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11223" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B11223" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11223" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11224" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11224" s="17"/>
+      <c r="C11224" s="24"/>
+    </row>
+    <row r="11225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11225" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B11225" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11225" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11226" s="25"/>
+      <c r="B11226" s="33"/>
+      <c r="C11226" s="24"/>
+    </row>
+    <row r="11227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11227" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B11227" s="32"/>
+      <c r="C11227" s="36" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="11228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11228" s="8"/>
+      <c r="B11228" s="32"/>
+      <c r="C11228" s="36"/>
+    </row>
+    <row r="11229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11229" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B11229" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11229" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11230" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11230" s="21"/>
+      <c r="C11230" s="22"/>
+    </row>
+    <row r="11267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11267" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B11267" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11267" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11268" s="4"/>
+      <c r="B11268" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11268" s="27"/>
+    </row>
+    <row r="11269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11269" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11269" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11269" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11270" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11270" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11270" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11271" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11271" s="9"/>
+      <c r="C11271" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11272" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11272" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11272" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11273" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11273" s="9"/>
+      <c r="C11273" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11274" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11274" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11274" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11275" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11275" s="9"/>
+      <c r="C11275" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11276" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B11276" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11276" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11277" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11277" s="9"/>
+      <c r="C11277" s="10" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11278" s="8"/>
+      <c r="B11278" s="9"/>
+      <c r="C11278" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11279" s="8"/>
+      <c r="B11279" s="9"/>
+      <c r="C11279" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11280" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="B11280" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11280" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11281" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11281" s="17"/>
+      <c r="C11281" s="24"/>
+    </row>
+    <row r="11282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11282" s="25">
+        <v>5.2</v>
+      </c>
+      <c r="B11282" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11282" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11283" s="25"/>
+      <c r="B11283" s="33"/>
+      <c r="C11283" s="24"/>
+    </row>
+    <row r="11284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11284" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B11284" s="9"/>
+      <c r="C11284" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="11285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11285" s="8"/>
+      <c r="B11285" s="9"/>
+      <c r="C11285" s="36"/>
+    </row>
+    <row r="11286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11286" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B11286" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11286" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11287" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11287" s="21"/>
+      <c r="C11287" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="211">
+  <mergeCells count="236">
+    <mergeCell ref="B11166:B11167"/>
+    <mergeCell ref="C11168:C11169"/>
+    <mergeCell ref="B11225:B11226"/>
+    <mergeCell ref="C11227:C11228"/>
+    <mergeCell ref="B11282:B11283"/>
+    <mergeCell ref="C11284:C11285"/>
+    <mergeCell ref="B10930:B10931"/>
+    <mergeCell ref="C10932:C10933"/>
+    <mergeCell ref="C10978:C10979"/>
+    <mergeCell ref="C11037:C11038"/>
+    <mergeCell ref="B11107:B11108"/>
+    <mergeCell ref="C11109:C11110"/>
+    <mergeCell ref="C10816:C10817"/>
+    <mergeCell ref="B10814:B10815"/>
+    <mergeCell ref="B10796:C10796"/>
+    <mergeCell ref="B10578:B10579"/>
+    <mergeCell ref="C10580:C10581"/>
+    <mergeCell ref="C10632:C10633"/>
+    <mergeCell ref="C10691:C10692"/>
+    <mergeCell ref="C10750:C10751"/>
+    <mergeCell ref="B10462:B10463"/>
+    <mergeCell ref="C10464:C10465"/>
+    <mergeCell ref="B10442:C10442"/>
+    <mergeCell ref="C10516:C10517"/>
+    <mergeCell ref="B10560:C10560"/>
     <mergeCell ref="C10158:C10159"/>
     <mergeCell ref="C10217:C10218"/>
     <mergeCell ref="B10336:B10337"/>

--- a/Research/Instructions/Instructions Native SNES.xlsx
+++ b/Research/Instructions/Instructions Native SNES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EC012B-DFF5-4D0C-8F89-3040028FB1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF22C7E-9550-439B-97A1-54546A29E133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1455" windowWidth="16575" windowHeight="14745" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19611,92 +19611,6 @@
     <t>SEP (E2)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> |= Operand.L, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 0 if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag is set.</t>
-    </r>
-  </si>
-  <si>
     <t>SBC (E3)</t>
   </si>
   <si>
@@ -21173,6 +21087,95 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> based off Operand.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 0 if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set.</t>
     </r>
   </si>
 </sst>
@@ -21450,6 +21453,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -21457,9 +21463,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -22092,10 +22095,10 @@
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="33"/>
+      <c r="C61" s="34"/>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
@@ -22250,14 +22253,14 @@
         <v>8.1</v>
       </c>
       <c r="B78" s="7"/>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="7"/>
-      <c r="C79" s="35"/>
+      <c r="C79" s="32"/>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
@@ -22634,14 +22637,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B190" s="7"/>
-      <c r="C190" s="35" t="s">
+      <c r="C190" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="B191" s="7"/>
-      <c r="C191" s="35"/>
+      <c r="C191" s="32"/>
     </row>
     <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
@@ -22780,14 +22783,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B249" s="7"/>
-      <c r="C249" s="35" t="s">
+      <c r="C249" s="32" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3"/>
       <c r="B250" s="7"/>
-      <c r="C250" s="35"/>
+      <c r="C250" s="32"/>
     </row>
     <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
@@ -22978,14 +22981,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B308" s="7"/>
-      <c r="C308" s="35" t="s">
+      <c r="C308" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3"/>
       <c r="B309" s="7"/>
-      <c r="C309" s="35"/>
+      <c r="C309" s="32"/>
     </row>
     <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
@@ -23124,19 +23127,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="7"/>
-      <c r="C367" s="35" t="s">
+      <c r="C367" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="7"/>
-      <c r="C368" s="35"/>
+      <c r="C368" s="32"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="7"/>
-      <c r="C369" s="35"/>
+      <c r="C369" s="32"/>
     </row>
     <row r="370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
@@ -23369,7 +23372,7 @@
       <c r="A431" s="25">
         <v>7.2</v>
       </c>
-      <c r="B431" s="34" t="s">
+      <c r="B431" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C431" s="8" t="s">
@@ -23378,7 +23381,7 @@
     </row>
     <row r="432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="25"/>
-      <c r="B432" s="34"/>
+      <c r="B432" s="35"/>
       <c r="C432" s="8"/>
     </row>
     <row r="433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23386,14 +23389,14 @@
         <v>8.1</v>
       </c>
       <c r="B433" s="7"/>
-      <c r="C433" s="35" t="s">
+      <c r="C433" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="B434" s="7"/>
-      <c r="C434" s="35"/>
+      <c r="C434" s="32"/>
     </row>
     <row r="435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="3">
@@ -23601,14 +23604,14 @@
         <v>3.1</v>
       </c>
       <c r="B540" s="7"/>
-      <c r="C540" s="35" t="s">
+      <c r="C540" s="32" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
       <c r="B541" s="7"/>
-      <c r="C541" s="35"/>
+      <c r="C541" s="32"/>
     </row>
     <row r="542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3">
@@ -23693,14 +23696,14 @@
         <v>2.1</v>
       </c>
       <c r="B597" s="7"/>
-      <c r="C597" s="35" t="s">
+      <c r="C597" s="32" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="3"/>
       <c r="B598" s="7"/>
-      <c r="C598" s="35"/>
+      <c r="C598" s="32"/>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="3">
@@ -23948,7 +23951,7 @@
       <c r="A720" s="23">
         <v>4.2</v>
       </c>
-      <c r="B720" s="34" t="s">
+      <c r="B720" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C720" s="8" t="s">
@@ -23957,7 +23960,7 @@
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="23"/>
-      <c r="B721" s="34"/>
+      <c r="B721" s="35"/>
       <c r="C721" s="8"/>
     </row>
     <row r="722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23989,7 +23992,7 @@
       <c r="A725" s="25">
         <v>6.2</v>
       </c>
-      <c r="B725" s="34" t="s">
+      <c r="B725" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C725" s="8" t="s">
@@ -23998,7 +24001,7 @@
     </row>
     <row r="726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="25"/>
-      <c r="B726" s="34"/>
+      <c r="B726" s="35"/>
       <c r="C726" s="8"/>
     </row>
     <row r="727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24155,7 +24158,7 @@
       <c r="A779" s="25">
         <v>4.2</v>
       </c>
-      <c r="B779" s="34" t="s">
+      <c r="B779" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C779" s="8" t="s">
@@ -24164,7 +24167,7 @@
     </row>
     <row r="780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="25"/>
-      <c r="B780" s="34"/>
+      <c r="B780" s="35"/>
       <c r="C780" s="8"/>
     </row>
     <row r="781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24172,14 +24175,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B781" s="7"/>
-      <c r="C781" s="35" t="s">
+      <c r="C781" s="32" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="3"/>
       <c r="B782" s="7"/>
-      <c r="C782" s="35"/>
+      <c r="C782" s="32"/>
     </row>
     <row r="783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="3">
@@ -24310,7 +24313,7 @@
       <c r="A838" s="23">
         <v>4.2</v>
       </c>
-      <c r="B838" s="34" t="s">
+      <c r="B838" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C838" s="8" t="s">
@@ -24319,7 +24322,7 @@
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="23"/>
-      <c r="B839" s="34"/>
+      <c r="B839" s="35"/>
       <c r="C839" s="8"/>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24327,19 +24330,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B840" s="7"/>
-      <c r="C840" s="35" t="s">
+      <c r="C840" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="3"/>
       <c r="B841" s="7"/>
-      <c r="C841" s="35"/>
+      <c r="C841" s="32"/>
     </row>
     <row r="842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="3"/>
       <c r="B842" s="7"/>
-      <c r="C842" s="35"/>
+      <c r="C842" s="32"/>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="3">
@@ -24361,7 +24364,7 @@
       <c r="A845" s="25">
         <v>6.2</v>
       </c>
-      <c r="B845" s="34" t="s">
+      <c r="B845" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C845" s="8" t="s">
@@ -24370,7 +24373,7 @@
     </row>
     <row r="846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="25"/>
-      <c r="B846" s="34"/>
+      <c r="B846" s="35"/>
       <c r="C846" s="8"/>
     </row>
     <row r="847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24547,7 +24550,7 @@
       <c r="A899" s="25">
         <v>5.2</v>
       </c>
-      <c r="B899" s="34" t="s">
+      <c r="B899" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C899" s="8" t="s">
@@ -24556,7 +24559,7 @@
     </row>
     <row r="900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="25"/>
-      <c r="B900" s="34"/>
+      <c r="B900" s="35"/>
       <c r="C900" s="8"/>
     </row>
     <row r="901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24564,14 +24567,14 @@
         <v>6.1</v>
       </c>
       <c r="B901" s="7"/>
-      <c r="C901" s="35" t="s">
+      <c r="C901" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="3"/>
       <c r="B902" s="7"/>
-      <c r="C902" s="35"/>
+      <c r="C902" s="32"/>
     </row>
     <row r="903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="3">
@@ -24709,10 +24712,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="17"/>
-      <c r="B1005" s="32" t="s">
+      <c r="B1005" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C1005" s="33"/>
+      <c r="C1005" s="34"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="5" t="s">
@@ -24883,7 +24886,7 @@
       <c r="A1025" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1025" s="34" t="s">
+      <c r="B1025" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1025" s="8" t="s">
@@ -24892,7 +24895,7 @@
     </row>
     <row r="1026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="25"/>
-      <c r="B1026" s="34"/>
+      <c r="B1026" s="35"/>
       <c r="C1026" s="8"/>
     </row>
     <row r="1027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24900,14 +24903,14 @@
         <v>8.1</v>
       </c>
       <c r="B1027" s="7"/>
-      <c r="C1027" s="35" t="s">
+      <c r="C1027" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="3"/>
       <c r="B1028" s="7"/>
-      <c r="C1028" s="35"/>
+      <c r="C1028" s="32"/>
     </row>
     <row r="1029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="3">
@@ -25082,14 +25085,14 @@
         <v>7.1</v>
       </c>
       <c r="B1079" s="7"/>
-      <c r="C1079" s="35" t="s">
+      <c r="C1079" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="3"/>
       <c r="B1080" s="7"/>
-      <c r="C1080" s="35"/>
+      <c r="C1080" s="32"/>
     </row>
     <row r="1081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="3">
@@ -25122,10 +25125,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="17"/>
-      <c r="B1123" s="32" t="s">
+      <c r="B1123" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C1123" s="33"/>
+      <c r="C1123" s="34"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="5" t="s">
@@ -25287,7 +25290,7 @@
       <c r="A1142" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1142" s="34" t="s">
+      <c r="B1142" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1142" s="11" t="s">
@@ -25296,7 +25299,7 @@
     </row>
     <row r="1143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1143" s="25"/>
-      <c r="B1143" s="34"/>
+      <c r="B1143" s="35"/>
       <c r="C1143" s="11"/>
     </row>
     <row r="1144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25304,14 +25307,14 @@
         <v>8.1</v>
       </c>
       <c r="B1144" s="7"/>
-      <c r="C1144" s="35" t="s">
+      <c r="C1144" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="3"/>
       <c r="B1145" s="7"/>
-      <c r="C1145" s="35"/>
+      <c r="C1145" s="32"/>
     </row>
     <row r="1146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1146" s="3">
@@ -25344,10 +25347,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="17"/>
-      <c r="B1182" s="32" t="s">
+      <c r="B1182" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C1182" s="33"/>
+      <c r="C1182" s="34"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="5" t="s">
@@ -25450,14 +25453,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1193" s="7"/>
-      <c r="C1193" s="35" t="s">
+      <c r="C1193" s="32" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="1194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1194" s="3"/>
       <c r="B1194" s="7"/>
-      <c r="C1194" s="35"/>
+      <c r="C1194" s="32"/>
     </row>
     <row r="1195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1195" s="3">
@@ -25662,14 +25665,14 @@
         <v>6.1</v>
       </c>
       <c r="B1254" s="7"/>
-      <c r="C1254" s="35" t="s">
+      <c r="C1254" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1255" s="3"/>
       <c r="B1255" s="7"/>
-      <c r="C1255" s="35"/>
+      <c r="C1255" s="32"/>
     </row>
     <row r="1256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1256" s="3">
@@ -25702,10 +25705,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="17"/>
-      <c r="B1300" s="32" t="s">
+      <c r="B1300" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C1300" s="33"/>
+      <c r="C1300" s="34"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="5" t="s">
@@ -25822,19 +25825,19 @@
         <v>6.1</v>
       </c>
       <c r="B1313" s="7"/>
-      <c r="C1313" s="35" t="s">
+      <c r="C1313" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="1314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="3"/>
       <c r="B1314" s="7"/>
-      <c r="C1314" s="35"/>
+      <c r="C1314" s="32"/>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="3"/>
       <c r="B1315" s="7"/>
-      <c r="C1315" s="35"/>
+      <c r="C1315" s="32"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="3">
@@ -25919,10 +25922,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="17"/>
-      <c r="B1359" s="32" t="s">
+      <c r="B1359" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C1359" s="33"/>
+      <c r="C1359" s="34"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="5" t="s">
@@ -26083,7 +26086,7 @@
       <c r="A1377" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1377" s="34" t="s">
+      <c r="B1377" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1377" s="8" t="s">
@@ -26092,7 +26095,7 @@
     </row>
     <row r="1378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1378" s="25"/>
-      <c r="B1378" s="34"/>
+      <c r="B1378" s="35"/>
       <c r="C1378" s="8"/>
     </row>
     <row r="1379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26100,14 +26103,14 @@
         <v>8.1</v>
       </c>
       <c r="B1379" s="7"/>
-      <c r="C1379" s="35" t="s">
+      <c r="C1379" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="3"/>
       <c r="B1380" s="7"/>
-      <c r="C1380" s="35"/>
+      <c r="C1380" s="32"/>
     </row>
     <row r="1381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1381" s="3">
@@ -26227,10 +26230,10 @@
     </row>
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="17"/>
-      <c r="B1477" s="32" t="s">
+      <c r="B1477" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C1477" s="33"/>
+      <c r="C1477" s="34"/>
     </row>
     <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1478" s="5" t="s">
@@ -26367,7 +26370,7 @@
       <c r="A1493" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1493" s="34" t="s">
+      <c r="B1493" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1493" s="11" t="s">
@@ -26376,7 +26379,7 @@
     </row>
     <row r="1494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1494" s="25"/>
-      <c r="B1494" s="34"/>
+      <c r="B1494" s="35"/>
       <c r="C1494" s="11"/>
     </row>
     <row r="1495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26384,14 +26387,14 @@
         <v>6.1</v>
       </c>
       <c r="B1495" s="7"/>
-      <c r="C1495" s="35" t="s">
+      <c r="C1495" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1496" s="3"/>
       <c r="B1496" s="7"/>
-      <c r="C1496" s="35"/>
+      <c r="C1496" s="32"/>
     </row>
     <row r="1497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1497" s="3">
@@ -26476,14 +26479,14 @@
         <v>2.1</v>
       </c>
       <c r="B1541" s="7"/>
-      <c r="C1541" s="35" t="s">
+      <c r="C1541" s="32" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1542" s="3"/>
       <c r="B1542" s="7"/>
-      <c r="C1542" s="35"/>
+      <c r="C1542" s="32"/>
     </row>
     <row r="1543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1543" s="3">
@@ -26603,10 +26606,10 @@
     </row>
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="17"/>
-      <c r="B1654" s="32" t="s">
+      <c r="B1654" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C1654" s="33"/>
+      <c r="C1654" s="34"/>
     </row>
     <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1655" s="5" t="s">
@@ -26701,7 +26704,7 @@
       <c r="A1664" s="23">
         <v>4.2</v>
       </c>
-      <c r="B1664" s="34" t="s">
+      <c r="B1664" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C1664" s="11" t="s">
@@ -26710,7 +26713,7 @@
     </row>
     <row r="1665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1665" s="23"/>
-      <c r="B1665" s="34"/>
+      <c r="B1665" s="35"/>
       <c r="C1665" s="11"/>
     </row>
     <row r="1666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26718,14 +26721,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1666" s="7"/>
-      <c r="C1666" s="35" t="s">
+      <c r="C1666" s="32" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="1667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1667" s="3"/>
       <c r="B1667" s="7"/>
-      <c r="C1667" s="35"/>
+      <c r="C1667" s="32"/>
     </row>
     <row r="1668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1668" s="3">
@@ -26747,7 +26750,7 @@
       <c r="A1670" s="23">
         <v>6.2</v>
       </c>
-      <c r="B1670" s="34" t="s">
+      <c r="B1670" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C1670" s="8" t="s">
@@ -26756,7 +26759,7 @@
     </row>
     <row r="1671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1671" s="23"/>
-      <c r="B1671" s="34"/>
+      <c r="B1671" s="35"/>
       <c r="C1671" s="8"/>
     </row>
     <row r="1672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26955,7 +26958,7 @@
       <c r="A1729" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1729" s="34" t="s">
+      <c r="B1729" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1729" s="11" t="s">
@@ -26964,7 +26967,7 @@
     </row>
     <row r="1730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1730" s="25"/>
-      <c r="B1730" s="34"/>
+      <c r="B1730" s="35"/>
       <c r="C1730" s="11"/>
     </row>
     <row r="1731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26972,14 +26975,14 @@
         <v>6.1</v>
       </c>
       <c r="B1731" s="7"/>
-      <c r="C1731" s="35" t="s">
+      <c r="C1731" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1732" s="3"/>
       <c r="B1732" s="7"/>
-      <c r="C1732" s="35"/>
+      <c r="C1732" s="32"/>
     </row>
     <row r="1733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1733" s="3">
@@ -27012,10 +27015,10 @@
     </row>
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="17"/>
-      <c r="B1772" s="32" t="s">
+      <c r="B1772" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C1772" s="33"/>
+      <c r="C1772" s="34"/>
     </row>
     <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1773" s="5" t="s">
@@ -27145,7 +27148,7 @@
       <c r="A1787" s="23">
         <v>5.2</v>
       </c>
-      <c r="B1787" s="34" t="s">
+      <c r="B1787" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1787" s="11" t="s">
@@ -27154,7 +27157,7 @@
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="23"/>
-      <c r="B1788" s="34"/>
+      <c r="B1788" s="35"/>
       <c r="C1788" s="11"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27162,19 +27165,19 @@
         <v>6.1</v>
       </c>
       <c r="B1789" s="7"/>
-      <c r="C1789" s="35" t="s">
+      <c r="C1789" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="1790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1790" s="3"/>
       <c r="B1790" s="7"/>
-      <c r="C1790" s="35"/>
+      <c r="C1790" s="32"/>
     </row>
     <row r="1791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1791" s="3"/>
       <c r="B1791" s="7"/>
-      <c r="C1791" s="35"/>
+      <c r="C1791" s="32"/>
     </row>
     <row r="1792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1792" s="3">
@@ -27196,7 +27199,7 @@
       <c r="A1794" s="23">
         <v>7.2</v>
       </c>
-      <c r="B1794" s="34" t="s">
+      <c r="B1794" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C1794" s="11" t="s">
@@ -27205,7 +27208,7 @@
     </row>
     <row r="1795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1795" s="23"/>
-      <c r="B1795" s="34"/>
+      <c r="B1795" s="35"/>
       <c r="C1795" s="11"/>
     </row>
     <row r="1796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27403,7 +27406,7 @@
       <c r="A1846" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1846" s="34" t="s">
+      <c r="B1846" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C1846" s="11" t="s">
@@ -27412,7 +27415,7 @@
     </row>
     <row r="1847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1847" s="25"/>
-      <c r="B1847" s="34"/>
+      <c r="B1847" s="35"/>
       <c r="C1847" s="11"/>
     </row>
     <row r="1848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27420,14 +27423,14 @@
         <v>6.1</v>
       </c>
       <c r="B1848" s="7"/>
-      <c r="C1848" s="35" t="s">
+      <c r="C1848" s="32" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1849" s="3"/>
       <c r="B1849" s="7"/>
-      <c r="C1849" s="35"/>
+      <c r="C1849" s="32"/>
     </row>
     <row r="1850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1850" s="3">
@@ -27625,10 +27628,10 @@
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1949" s="17"/>
-      <c r="B1949" s="32" t="s">
+      <c r="B1949" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C1949" s="33"/>
+      <c r="C1949" s="34"/>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1950" s="5" t="s">
@@ -27783,14 +27786,14 @@
         <v>8.1</v>
       </c>
       <c r="B1966" s="7"/>
-      <c r="C1966" s="35" t="s">
+      <c r="C1966" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="1967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1967" s="3"/>
       <c r="B1967" s="7"/>
-      <c r="C1967" s="35"/>
+      <c r="C1967" s="32"/>
     </row>
     <row r="1968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1968" s="3">
@@ -27823,10 +27826,10 @@
     </row>
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="17"/>
-      <c r="B2008" s="32" t="s">
+      <c r="B2008" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C2008" s="33"/>
+      <c r="C2008" s="34"/>
     </row>
     <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2009" s="5" t="s">
@@ -28126,14 +28129,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2078" s="7"/>
-      <c r="C2078" s="35" t="s">
+      <c r="C2078" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2079" s="3"/>
       <c r="B2079" s="7"/>
-      <c r="C2079" s="35"/>
+      <c r="C2079" s="32"/>
     </row>
     <row r="2080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2080" s="3">
@@ -28272,19 +28275,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2137" s="7"/>
-      <c r="C2137" s="35" t="s">
+      <c r="C2137" s="32" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="2138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2138" s="3"/>
       <c r="B2138" s="7"/>
-      <c r="C2138" s="35"/>
+      <c r="C2138" s="32"/>
     </row>
     <row r="2139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2139" s="3"/>
       <c r="B2139" s="7"/>
-      <c r="C2139" s="35"/>
+      <c r="C2139" s="32"/>
     </row>
     <row r="2140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2140" s="3">
@@ -28423,14 +28426,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2196" s="7"/>
-      <c r="C2196" s="35" t="s">
+      <c r="C2196" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2197" s="3"/>
       <c r="B2197" s="7"/>
-      <c r="C2197" s="35"/>
+      <c r="C2197" s="32"/>
     </row>
     <row r="2198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2198" s="3">
@@ -28463,10 +28466,10 @@
     </row>
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="17"/>
-      <c r="B2244" s="32" t="s">
+      <c r="B2244" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C2244" s="33"/>
+      <c r="C2244" s="34"/>
     </row>
     <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2245" s="5" t="s">
@@ -28569,19 +28572,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="7"/>
-      <c r="C2255" s="35" t="s">
+      <c r="C2255" s="32" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="3"/>
       <c r="B2256" s="7"/>
-      <c r="C2256" s="35"/>
+      <c r="C2256" s="32"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="3"/>
       <c r="B2257" s="7"/>
-      <c r="C2257" s="35"/>
+      <c r="C2257" s="32"/>
     </row>
     <row r="2258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2258" s="3">
@@ -28666,10 +28669,10 @@
     </row>
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="17"/>
-      <c r="B2303" s="32" t="s">
+      <c r="B2303" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C2303" s="33"/>
+      <c r="C2303" s="34"/>
     </row>
     <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2304" s="5" t="s">
@@ -28814,7 +28817,7 @@
       <c r="A2319" s="25">
         <v>7.2</v>
       </c>
-      <c r="B2319" s="34" t="s">
+      <c r="B2319" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C2319" s="8" t="s">
@@ -28823,7 +28826,7 @@
     </row>
     <row r="2320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2320" s="25"/>
-      <c r="B2320" s="34"/>
+      <c r="B2320" s="35"/>
       <c r="C2320" s="8"/>
     </row>
     <row r="2321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28831,14 +28834,14 @@
         <v>8.1</v>
       </c>
       <c r="B2321" s="7"/>
-      <c r="C2321" s="35" t="s">
+      <c r="C2321" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2322" s="3"/>
       <c r="B2322" s="7"/>
-      <c r="C2322" s="35"/>
+      <c r="C2322" s="32"/>
     </row>
     <row r="2323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2323" s="3">
@@ -29060,14 +29063,14 @@
         <v>3.1</v>
       </c>
       <c r="B2428" s="7"/>
-      <c r="C2428" s="35" t="s">
+      <c r="C2428" s="32" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="2429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2429" s="3"/>
       <c r="B2429" s="7"/>
-      <c r="C2429" s="35"/>
+      <c r="C2429" s="32"/>
     </row>
     <row r="2430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2430" s="3">
@@ -29152,19 +29155,19 @@
         <v>2.1</v>
       </c>
       <c r="B2485" s="7"/>
-      <c r="C2485" s="35" t="s">
+      <c r="C2485" s="32" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2486" s="3"/>
       <c r="B2486" s="7"/>
-      <c r="C2486" s="35"/>
+      <c r="C2486" s="32"/>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2487" s="3"/>
       <c r="B2487" s="7"/>
-      <c r="C2487" s="35"/>
+      <c r="C2487" s="32"/>
     </row>
     <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2488" s="3">
@@ -29197,10 +29200,10 @@
     </row>
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="17"/>
-      <c r="B2539" s="32" t="s">
+      <c r="B2539" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C2539" s="33"/>
+      <c r="C2539" s="34"/>
     </row>
     <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2540" s="5" t="s">
@@ -29428,7 +29431,7 @@
       <c r="A2608" s="25">
         <v>4.2</v>
       </c>
-      <c r="B2608" s="34" t="s">
+      <c r="B2608" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C2608" s="11" t="s">
@@ -29437,7 +29440,7 @@
     </row>
     <row r="2609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2609" s="25"/>
-      <c r="B2609" s="34"/>
+      <c r="B2609" s="35"/>
       <c r="C2609" s="11"/>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29445,19 +29448,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2610" s="7"/>
-      <c r="C2610" s="35" t="s">
+      <c r="C2610" s="32" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="2611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2611" s="3"/>
       <c r="B2611" s="7"/>
-      <c r="C2611" s="35"/>
+      <c r="C2611" s="32"/>
     </row>
     <row r="2612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2612" s="3"/>
       <c r="B2612" s="7"/>
-      <c r="C2612" s="35"/>
+      <c r="C2612" s="32"/>
     </row>
     <row r="2613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2613" s="3">
@@ -29588,7 +29591,7 @@
       <c r="A2667" s="25">
         <v>4.2</v>
       </c>
-      <c r="B2667" s="34" t="s">
+      <c r="B2667" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C2667" s="11" t="s">
@@ -29597,7 +29600,7 @@
     </row>
     <row r="2668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2668" s="25"/>
-      <c r="B2668" s="34"/>
+      <c r="B2668" s="35"/>
       <c r="C2668" s="11"/>
     </row>
     <row r="2669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29605,14 +29608,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2669" s="7"/>
-      <c r="C2669" s="35" t="s">
+      <c r="C2669" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2670" s="3"/>
       <c r="B2670" s="7"/>
-      <c r="C2670" s="35"/>
+      <c r="C2670" s="32"/>
     </row>
     <row r="2671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2671" s="3">
@@ -29645,10 +29648,10 @@
     </row>
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="17"/>
-      <c r="B2716" s="32" t="s">
+      <c r="B2716" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C2716" s="33"/>
+      <c r="C2716" s="34"/>
     </row>
     <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2717" s="5" t="s">
@@ -29743,7 +29746,7 @@
       <c r="A2726" s="23">
         <v>4.2</v>
       </c>
-      <c r="B2726" s="34" t="s">
+      <c r="B2726" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C2726" s="8" t="s">
@@ -29752,7 +29755,7 @@
     </row>
     <row r="2727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2727" s="23"/>
-      <c r="B2727" s="34"/>
+      <c r="B2727" s="35"/>
       <c r="C2727" s="8"/>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29760,19 +29763,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2728" s="7"/>
-      <c r="C2728" s="35" t="s">
+      <c r="C2728" s="32" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="3"/>
       <c r="B2729" s="7"/>
-      <c r="C2729" s="35"/>
+      <c r="C2729" s="32"/>
     </row>
     <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2730" s="3"/>
       <c r="B2730" s="7"/>
-      <c r="C2730" s="35"/>
+      <c r="C2730" s="32"/>
     </row>
     <row r="2731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2731" s="3">
@@ -29794,7 +29797,7 @@
       <c r="A2733" s="23">
         <v>6.2</v>
       </c>
-      <c r="B2733" s="34" t="s">
+      <c r="B2733" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C2733" s="8" t="s">
@@ -29803,7 +29806,7 @@
     </row>
     <row r="2734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2734" s="23"/>
-      <c r="B2734" s="34"/>
+      <c r="B2734" s="35"/>
       <c r="C2734" s="8"/>
     </row>
     <row r="2735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29862,10 +29865,10 @@
     </row>
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="17"/>
-      <c r="B2775" s="32" t="s">
+      <c r="B2775" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C2775" s="33"/>
+      <c r="C2775" s="34"/>
     </row>
     <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2776" s="5" t="s">
@@ -29980,7 +29983,7 @@
       <c r="A2787" s="25">
         <v>5.2</v>
       </c>
-      <c r="B2787" s="34" t="s">
+      <c r="B2787" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C2787" s="11" t="s">
@@ -29989,7 +29992,7 @@
     </row>
     <row r="2788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2788" s="25"/>
-      <c r="B2788" s="34"/>
+      <c r="B2788" s="35"/>
       <c r="C2788" s="11"/>
     </row>
     <row r="2789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29997,14 +30000,14 @@
         <v>6.1</v>
       </c>
       <c r="B2789" s="7"/>
-      <c r="C2789" s="35" t="s">
+      <c r="C2789" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2790" s="3"/>
       <c r="B2790" s="7"/>
-      <c r="C2790" s="35"/>
+      <c r="C2790" s="32"/>
     </row>
     <row r="2791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2791" s="3">
@@ -30142,10 +30145,10 @@
     </row>
     <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2893" s="17"/>
-      <c r="B2893" s="32" t="s">
+      <c r="B2893" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C2893" s="33"/>
+      <c r="C2893" s="34"/>
     </row>
     <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2894" s="5" t="s">
@@ -30316,7 +30319,7 @@
       <c r="A2913" s="25">
         <v>7.2</v>
       </c>
-      <c r="B2913" s="34" t="s">
+      <c r="B2913" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C2913" s="11" t="s">
@@ -30325,7 +30328,7 @@
     </row>
     <row r="2914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2914" s="25"/>
-      <c r="B2914" s="34"/>
+      <c r="B2914" s="35"/>
       <c r="C2914" s="11"/>
     </row>
     <row r="2915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30333,14 +30336,14 @@
         <v>8.1</v>
       </c>
       <c r="B2915" s="7"/>
-      <c r="C2915" s="35" t="s">
+      <c r="C2915" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2916" s="3"/>
       <c r="B2916" s="7"/>
-      <c r="C2916" s="35"/>
+      <c r="C2916" s="32"/>
     </row>
     <row r="2917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2917" s="3">
@@ -30373,10 +30376,10 @@
     </row>
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="17"/>
-      <c r="B2952" s="32" t="s">
+      <c r="B2952" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="C2952" s="33"/>
+      <c r="C2952" s="34"/>
     </row>
     <row r="2953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2953" s="5" t="s">
@@ -30515,14 +30518,14 @@
         <v>7.1</v>
       </c>
       <c r="B2967" s="7"/>
-      <c r="C2967" s="35" t="s">
+      <c r="C2967" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2968" s="3"/>
       <c r="B2968" s="7"/>
-      <c r="C2968" s="35"/>
+      <c r="C2968" s="32"/>
     </row>
     <row r="2969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2969" s="3">
@@ -30555,10 +30558,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="17"/>
-      <c r="B3011" s="32" t="s">
+      <c r="B3011" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C3011" s="33"/>
+      <c r="C3011" s="34"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="5" t="s">
@@ -30713,7 +30716,7 @@
       <c r="A3029" s="25">
         <v>7.2</v>
       </c>
-      <c r="B3029" s="34" t="s">
+      <c r="B3029" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3029" s="11" t="s">
@@ -30722,7 +30725,7 @@
     </row>
     <row r="3030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3030" s="25"/>
-      <c r="B3030" s="34"/>
+      <c r="B3030" s="35"/>
       <c r="C3030" s="11"/>
     </row>
     <row r="3031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30730,14 +30733,14 @@
         <v>8.1</v>
       </c>
       <c r="B3031" s="7"/>
-      <c r="C3031" s="35" t="s">
+      <c r="C3031" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3032" s="3"/>
       <c r="B3032" s="7"/>
-      <c r="C3032" s="35"/>
+      <c r="C3032" s="32"/>
     </row>
     <row r="3033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3033" s="3">
@@ -30890,19 +30893,19 @@
         <v>6.1</v>
       </c>
       <c r="B3083" s="7"/>
-      <c r="C3083" s="35" t="s">
+      <c r="C3083" s="32" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3084" s="3"/>
       <c r="B3084" s="7"/>
-      <c r="C3084" s="35"/>
+      <c r="C3084" s="32"/>
     </row>
     <row r="3085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3085" s="3"/>
       <c r="B3085" s="7"/>
-      <c r="C3085" s="35"/>
+      <c r="C3085" s="32"/>
     </row>
     <row r="3086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3086" s="3">
@@ -31055,14 +31058,14 @@
         <v>6.1</v>
       </c>
       <c r="B3142" s="7"/>
-      <c r="C3142" s="35" t="s">
+      <c r="C3142" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3143" s="3"/>
       <c r="B3143" s="7"/>
-      <c r="C3143" s="35"/>
+      <c r="C3143" s="32"/>
     </row>
     <row r="3144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3144" s="3">
@@ -31095,10 +31098,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="17"/>
-      <c r="B3188" s="32" t="s">
+      <c r="B3188" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C3188" s="33"/>
+      <c r="C3188" s="34"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="5" t="s">
@@ -31215,19 +31218,19 @@
         <v>6.1</v>
       </c>
       <c r="B3201" s="7"/>
-      <c r="C3201" s="35" t="s">
+      <c r="C3201" s="32" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3202" s="3"/>
       <c r="B3202" s="7"/>
-      <c r="C3202" s="35"/>
+      <c r="C3202" s="32"/>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="3"/>
       <c r="B3203" s="7"/>
-      <c r="C3203" s="35"/>
+      <c r="C3203" s="32"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="3">
@@ -31312,10 +31315,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="17"/>
-      <c r="B3247" s="32" t="s">
+      <c r="B3247" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C3247" s="33"/>
+      <c r="C3247" s="34"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="5" t="s">
@@ -31476,7 +31479,7 @@
       <c r="A3265" s="25">
         <v>7.2</v>
       </c>
-      <c r="B3265" s="34" t="s">
+      <c r="B3265" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3265" s="11" t="s">
@@ -31485,7 +31488,7 @@
     </row>
     <row r="3266" spans="1:3" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3266" s="25"/>
-      <c r="B3266" s="34"/>
+      <c r="B3266" s="35"/>
       <c r="C3266" s="11"/>
     </row>
     <row r="3267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31493,14 +31496,14 @@
         <v>8.1</v>
       </c>
       <c r="B3267" s="7"/>
-      <c r="C3267" s="35" t="s">
+      <c r="C3267" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3268" s="3"/>
       <c r="B3268" s="7"/>
-      <c r="C3268" s="35"/>
+      <c r="C3268" s="32"/>
     </row>
     <row r="3269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3269" s="3">
@@ -31620,10 +31623,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="17"/>
-      <c r="B3365" s="32" t="s">
+      <c r="B3365" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C3365" s="33"/>
+      <c r="C3365" s="34"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="5" t="s">
@@ -31760,7 +31763,7 @@
       <c r="A3381" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3381" s="34" t="s">
+      <c r="B3381" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3381" s="8" t="s">
@@ -31769,7 +31772,7 @@
     </row>
     <row r="3382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3382" s="25"/>
-      <c r="B3382" s="34"/>
+      <c r="B3382" s="35"/>
       <c r="C3382" s="8"/>
     </row>
     <row r="3383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31777,14 +31780,14 @@
         <v>6.1</v>
       </c>
       <c r="B3383" s="7"/>
-      <c r="C3383" s="35" t="s">
+      <c r="C3383" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3384" s="3"/>
       <c r="B3384" s="7"/>
-      <c r="C3384" s="35"/>
+      <c r="C3384" s="32"/>
     </row>
     <row r="3385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3385" s="3">
@@ -31869,14 +31872,14 @@
         <v>2.1</v>
       </c>
       <c r="B3429" s="7"/>
-      <c r="C3429" s="35" t="s">
+      <c r="C3429" s="32" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3430" s="3"/>
       <c r="B3430" s="7"/>
-      <c r="C3430" s="35"/>
+      <c r="C3430" s="32"/>
     </row>
     <row r="3431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3431" s="3">
@@ -32136,7 +32139,7 @@
       <c r="A3558" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3558" s="34" t="s">
+      <c r="B3558" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3558" s="11" t="s">
@@ -32145,7 +32148,7 @@
     </row>
     <row r="3559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3559" s="25"/>
-      <c r="B3559" s="34"/>
+      <c r="B3559" s="35"/>
       <c r="C3559" s="11"/>
     </row>
     <row r="3560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32153,19 +32156,19 @@
         <v>6.1</v>
       </c>
       <c r="B3560" s="7"/>
-      <c r="C3560" s="35" t="s">
+      <c r="C3560" s="32" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3561" s="3"/>
       <c r="B3561" s="7"/>
-      <c r="C3561" s="35"/>
+      <c r="C3561" s="32"/>
     </row>
     <row r="3562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3562" s="3"/>
       <c r="B3562" s="7"/>
-      <c r="C3562" s="35"/>
+      <c r="C3562" s="32"/>
     </row>
     <row r="3563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3563" s="3">
@@ -32331,7 +32334,7 @@
       <c r="A3616" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3616" s="34" t="s">
+      <c r="B3616" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3616" s="11" t="s">
@@ -32340,7 +32343,7 @@
     </row>
     <row r="3617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3617" s="25"/>
-      <c r="B3617" s="34"/>
+      <c r="B3617" s="35"/>
       <c r="C3617" s="11"/>
     </row>
     <row r="3618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32348,14 +32351,14 @@
         <v>6.1</v>
       </c>
       <c r="B3618" s="7"/>
-      <c r="C3618" s="35" t="s">
+      <c r="C3618" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3619" s="3"/>
       <c r="B3619" s="7"/>
-      <c r="C3619" s="35"/>
+      <c r="C3619" s="32"/>
     </row>
     <row r="3620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3620" s="3">
@@ -32388,10 +32391,10 @@
     </row>
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="17"/>
-      <c r="B3660" s="32" t="s">
+      <c r="B3660" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C3660" s="33"/>
+      <c r="C3660" s="34"/>
     </row>
     <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3661" s="5" t="s">
@@ -32514,7 +32517,7 @@
       <c r="A3674" s="23">
         <v>5.2</v>
       </c>
-      <c r="B3674" s="34" t="s">
+      <c r="B3674" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3674" s="11" t="s">
@@ -32523,7 +32526,7 @@
     </row>
     <row r="3675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3675" s="23"/>
-      <c r="B3675" s="34"/>
+      <c r="B3675" s="35"/>
       <c r="C3675" s="11"/>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32531,19 +32534,19 @@
         <v>6.1</v>
       </c>
       <c r="B3676" s="7"/>
-      <c r="C3676" s="35" t="s">
+      <c r="C3676" s="32" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="3"/>
       <c r="B3677" s="7"/>
-      <c r="C3677" s="35"/>
+      <c r="C3677" s="32"/>
     </row>
     <row r="3678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3678" s="3"/>
       <c r="B3678" s="7"/>
-      <c r="C3678" s="35"/>
+      <c r="C3678" s="32"/>
     </row>
     <row r="3679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3679" s="3">
@@ -32565,7 +32568,7 @@
       <c r="A3681" s="23">
         <v>7.2</v>
       </c>
-      <c r="B3681" s="34" t="s">
+      <c r="B3681" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C3681" s="11" t="s">
@@ -32574,7 +32577,7 @@
     </row>
     <row r="3682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3682" s="23"/>
-      <c r="B3682" s="34"/>
+      <c r="B3682" s="35"/>
       <c r="C3682" s="11"/>
     </row>
     <row r="3683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32633,10 +32636,10 @@
     </row>
     <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3719" s="17"/>
-      <c r="B3719" s="32" t="s">
+      <c r="B3719" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C3719" s="33"/>
+      <c r="C3719" s="34"/>
     </row>
     <row r="3720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3720" s="5" t="s">
@@ -32765,7 +32768,7 @@
       <c r="A3733" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3733" s="34" t="s">
+      <c r="B3733" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C3733" s="8" t="s">
@@ -32774,7 +32777,7 @@
     </row>
     <row r="3734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3734" s="25"/>
-      <c r="B3734" s="34"/>
+      <c r="B3734" s="35"/>
       <c r="C3734" s="8"/>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32782,14 +32785,14 @@
         <v>6.1</v>
       </c>
       <c r="B3735" s="7"/>
-      <c r="C3735" s="35" t="s">
+      <c r="C3735" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3736" s="3"/>
       <c r="B3736" s="7"/>
-      <c r="C3736" s="35"/>
+      <c r="C3736" s="32"/>
     </row>
     <row r="3737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3737" s="3">
@@ -32995,10 +32998,10 @@
     </row>
     <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3837" s="17"/>
-      <c r="B3837" s="32" t="s">
+      <c r="B3837" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C3837" s="33"/>
+      <c r="C3837" s="34"/>
     </row>
     <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3838" s="5" t="s">
@@ -33153,14 +33156,14 @@
         <v>8.1</v>
       </c>
       <c r="B3854" s="7"/>
-      <c r="C3854" s="35" t="s">
+      <c r="C3854" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="3855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3855" s="3"/>
       <c r="B3855" s="7"/>
-      <c r="C3855" s="35"/>
+      <c r="C3855" s="32"/>
     </row>
     <row r="3856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3856" s="3">
@@ -33280,10 +33283,10 @@
     </row>
     <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3955" s="17"/>
-      <c r="B3955" s="32" t="s">
+      <c r="B3955" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C3955" s="33"/>
+      <c r="C3955" s="34"/>
     </row>
     <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3956" s="5" t="s">
@@ -33384,14 +33387,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B3966" s="7"/>
-      <c r="C3966" s="35" t="s">
+      <c r="C3966" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3967" s="3"/>
       <c r="B3967" s="7"/>
-      <c r="C3967" s="35"/>
+      <c r="C3967" s="32"/>
     </row>
     <row r="3968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3968" s="3">
@@ -33424,10 +33427,10 @@
     </row>
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="17"/>
-      <c r="B4014" s="32" t="s">
+      <c r="B4014" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="C4014" s="33"/>
+      <c r="C4014" s="34"/>
     </row>
     <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4015" s="5" t="s">
@@ -33534,14 +33537,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="7"/>
-      <c r="C4025" s="35" t="s">
+      <c r="C4025" s="32" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="3"/>
       <c r="B4026" s="7"/>
-      <c r="C4026" s="35"/>
+      <c r="C4026" s="32"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="3">
@@ -33602,10 +33605,10 @@
     </row>
     <row r="4073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4073" s="17"/>
-      <c r="B4073" s="32" t="s">
+      <c r="B4073" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="C4073" s="33"/>
+      <c r="C4073" s="34"/>
     </row>
     <row r="4074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4074" s="5" t="s">
@@ -33708,14 +33711,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4084" s="7"/>
-      <c r="C4084" s="35" t="s">
+      <c r="C4084" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4085" s="3"/>
       <c r="B4085" s="7"/>
-      <c r="C4085" s="35"/>
+      <c r="C4085" s="32"/>
     </row>
     <row r="4086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4086" s="3">
@@ -33748,10 +33751,10 @@
     </row>
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="17"/>
-      <c r="B4132" s="32" t="s">
+      <c r="B4132" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C4132" s="33"/>
+      <c r="C4132" s="34"/>
     </row>
     <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4133" s="5" t="s">
@@ -33854,19 +33857,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="7"/>
-      <c r="C4143" s="35" t="s">
+      <c r="C4143" s="32" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="3"/>
       <c r="B4144" s="7"/>
-      <c r="C4144" s="35"/>
+      <c r="C4144" s="32"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="3"/>
       <c r="B4145" s="7"/>
-      <c r="C4145" s="35"/>
+      <c r="C4145" s="32"/>
     </row>
     <row r="4146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4146" s="3">
@@ -33951,10 +33954,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="17"/>
-      <c r="B4191" s="32" t="s">
+      <c r="B4191" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C4191" s="33"/>
+      <c r="C4191" s="34"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="5" t="s">
@@ -34099,7 +34102,7 @@
       <c r="A4207" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4207" s="34" t="s">
+      <c r="B4207" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C4207" s="11" t="s">
@@ -34108,7 +34111,7 @@
     </row>
     <row r="4208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4208" s="25"/>
-      <c r="B4208" s="34"/>
+      <c r="B4208" s="35"/>
       <c r="C4208" s="11"/>
     </row>
     <row r="4209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34116,14 +34119,14 @@
         <v>8.1</v>
       </c>
       <c r="B4209" s="7"/>
-      <c r="C4209" s="35" t="s">
+      <c r="C4209" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4210" s="3"/>
       <c r="B4210" s="7"/>
-      <c r="C4210" s="35"/>
+      <c r="C4210" s="32"/>
     </row>
     <row r="4211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4211" s="3">
@@ -34351,14 +34354,14 @@
         <v>3.1</v>
       </c>
       <c r="B4316" s="7"/>
-      <c r="C4316" s="35" t="s">
+      <c r="C4316" s="32" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="4317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4317" s="3"/>
       <c r="B4317" s="7"/>
-      <c r="C4317" s="35"/>
+      <c r="C4317" s="32"/>
     </row>
     <row r="4318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4318" s="3">
@@ -34443,14 +34446,14 @@
         <v>2.1</v>
       </c>
       <c r="B4373" s="7"/>
-      <c r="C4373" s="35" t="s">
+      <c r="C4373" s="32" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4374" s="3"/>
       <c r="B4374" s="7"/>
-      <c r="C4374" s="35"/>
+      <c r="C4374" s="32"/>
     </row>
     <row r="4375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4375" s="3">
@@ -34789,7 +34792,7 @@
       <c r="A4555" s="25">
         <v>4.2</v>
       </c>
-      <c r="B4555" s="34" t="s">
+      <c r="B4555" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C4555" s="11" t="s">
@@ -34798,7 +34801,7 @@
     </row>
     <row r="4556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4556" s="25"/>
-      <c r="B4556" s="34"/>
+      <c r="B4556" s="35"/>
       <c r="C4556" s="11"/>
     </row>
     <row r="4557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34806,14 +34809,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4557" s="7"/>
-      <c r="C4557" s="35" t="s">
+      <c r="C4557" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4558" s="3"/>
       <c r="B4558" s="7"/>
-      <c r="C4558" s="35"/>
+      <c r="C4558" s="32"/>
     </row>
     <row r="4559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4559" s="3">
@@ -34846,10 +34849,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="17"/>
-      <c r="B4604" s="32" t="s">
+      <c r="B4604" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C4604" s="33"/>
+      <c r="C4604" s="34"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="5" t="s">
@@ -34944,7 +34947,7 @@
       <c r="A4614" s="23">
         <v>4.2</v>
       </c>
-      <c r="B4614" s="34" t="s">
+      <c r="B4614" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C4614" s="11" t="s">
@@ -34953,7 +34956,7 @@
     </row>
     <row r="4615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4615" s="23"/>
-      <c r="B4615" s="34"/>
+      <c r="B4615" s="35"/>
       <c r="C4615" s="11"/>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34961,19 +34964,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4616" s="7"/>
-      <c r="C4616" s="35" t="s">
+      <c r="C4616" s="32" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="3"/>
       <c r="B4617" s="7"/>
-      <c r="C4617" s="35"/>
+      <c r="C4617" s="32"/>
     </row>
     <row r="4618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4618" s="3"/>
       <c r="B4618" s="7"/>
-      <c r="C4618" s="35"/>
+      <c r="C4618" s="32"/>
     </row>
     <row r="4619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4619" s="3">
@@ -34995,7 +34998,7 @@
       <c r="A4621" s="23">
         <v>6.2</v>
       </c>
-      <c r="B4621" s="34" t="s">
+      <c r="B4621" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C4621" s="11" t="s">
@@ -35004,7 +35007,7 @@
     </row>
     <row r="4622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4622" s="23"/>
-      <c r="B4622" s="34"/>
+      <c r="B4622" s="35"/>
       <c r="C4622" s="11"/>
     </row>
     <row r="4623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35063,10 +35066,10 @@
     </row>
     <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4663" s="17"/>
-      <c r="B4663" s="32" t="s">
+      <c r="B4663" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C4663" s="33"/>
+      <c r="C4663" s="34"/>
     </row>
     <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4664" s="5" t="s">
@@ -35181,7 +35184,7 @@
       <c r="A4675" s="25">
         <v>5.2</v>
       </c>
-      <c r="B4675" s="34" t="s">
+      <c r="B4675" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C4675" s="11" t="s">
@@ -35190,7 +35193,7 @@
     </row>
     <row r="4676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4676" s="25"/>
-      <c r="B4676" s="34"/>
+      <c r="B4676" s="35"/>
       <c r="C4676" s="11"/>
     </row>
     <row r="4677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35198,14 +35201,14 @@
         <v>6.1</v>
       </c>
       <c r="B4677" s="7"/>
-      <c r="C4677" s="35" t="s">
+      <c r="C4677" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4678" s="3"/>
       <c r="B4678" s="7"/>
-      <c r="C4678" s="35"/>
+      <c r="C4678" s="32"/>
     </row>
     <row r="4679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4679" s="3">
@@ -35343,10 +35346,10 @@
     </row>
     <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4781" s="17"/>
-      <c r="B4781" s="32" t="s">
+      <c r="B4781" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C4781" s="33"/>
+      <c r="C4781" s="34"/>
     </row>
     <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4782" s="5" t="s">
@@ -35517,7 +35520,7 @@
       <c r="A4801" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4801" s="34" t="s">
+      <c r="B4801" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C4801" s="11" t="s">
@@ -35526,7 +35529,7 @@
     </row>
     <row r="4802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4802" s="25"/>
-      <c r="B4802" s="34"/>
+      <c r="B4802" s="35"/>
       <c r="C4802" s="11"/>
     </row>
     <row r="4803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35534,14 +35537,14 @@
         <v>8.1</v>
       </c>
       <c r="B4803" s="7"/>
-      <c r="C4803" s="35" t="s">
+      <c r="C4803" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4804" s="3"/>
       <c r="B4804" s="7"/>
-      <c r="C4804" s="35"/>
+      <c r="C4804" s="32"/>
     </row>
     <row r="4805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4805" s="3">
@@ -35716,14 +35719,14 @@
         <v>7.1</v>
       </c>
       <c r="B4855" s="7"/>
-      <c r="C4855" s="35" t="s">
+      <c r="C4855" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4856" s="3"/>
       <c r="B4856" s="7"/>
-      <c r="C4856" s="35"/>
+      <c r="C4856" s="32"/>
     </row>
     <row r="4857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4857" s="3">
@@ -35756,10 +35759,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="17"/>
-      <c r="B4899" s="32" t="s">
+      <c r="B4899" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C4899" s="33"/>
+      <c r="C4899" s="34"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="5" t="s">
@@ -35914,7 +35917,7 @@
       <c r="A4917" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4917" s="34" t="s">
+      <c r="B4917" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C4917" s="11" t="s">
@@ -35923,7 +35926,7 @@
     </row>
     <row r="4918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4918" s="25"/>
-      <c r="B4918" s="34"/>
+      <c r="B4918" s="35"/>
       <c r="C4918" s="11"/>
     </row>
     <row r="4919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35931,14 +35934,14 @@
         <v>8.1</v>
       </c>
       <c r="B4919" s="7"/>
-      <c r="C4919" s="35" t="s">
+      <c r="C4919" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4920" s="3"/>
       <c r="B4920" s="7"/>
-      <c r="C4920" s="35"/>
+      <c r="C4920" s="32"/>
     </row>
     <row r="4921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4921" s="3">
@@ -35971,10 +35974,10 @@
     </row>
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="17"/>
-      <c r="B4958" s="32" t="s">
+      <c r="B4958" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="C4958" s="33"/>
+      <c r="C4958" s="34"/>
     </row>
     <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4959" s="5" t="s">
@@ -36081,14 +36084,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="7"/>
-      <c r="C4969" s="35" t="s">
+      <c r="C4969" s="32" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="3"/>
       <c r="B4970" s="7"/>
-      <c r="C4970" s="35"/>
+      <c r="C4970" s="32"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="3">
@@ -36269,14 +36272,14 @@
         <v>6.1</v>
       </c>
       <c r="B5030" s="7"/>
-      <c r="C5030" s="35" t="s">
+      <c r="C5030" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5031" s="3"/>
       <c r="B5031" s="7"/>
-      <c r="C5031" s="35"/>
+      <c r="C5031" s="32"/>
     </row>
     <row r="5032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5032" s="3">
@@ -36309,10 +36312,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="17"/>
-      <c r="B5076" s="32" t="s">
+      <c r="B5076" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C5076" s="33"/>
+      <c r="C5076" s="34"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="5" t="s">
@@ -36429,19 +36432,19 @@
         <v>6.1</v>
       </c>
       <c r="B5089" s="7"/>
-      <c r="C5089" s="35" t="s">
+      <c r="C5089" s="32" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5090" s="3"/>
       <c r="B5090" s="7"/>
-      <c r="C5090" s="35"/>
+      <c r="C5090" s="32"/>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="3"/>
       <c r="B5091" s="7"/>
-      <c r="C5091" s="35"/>
+      <c r="C5091" s="32"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="3">
@@ -36690,7 +36693,7 @@
       <c r="A5153" s="25">
         <v>7.2</v>
       </c>
-      <c r="B5153" s="34" t="s">
+      <c r="B5153" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C5153" s="11" t="s">
@@ -36699,7 +36702,7 @@
     </row>
     <row r="5154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5154" s="25"/>
-      <c r="B5154" s="34"/>
+      <c r="B5154" s="35"/>
       <c r="C5154" s="11"/>
     </row>
     <row r="5155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36707,14 +36710,14 @@
         <v>8.1</v>
       </c>
       <c r="B5155" s="7"/>
-      <c r="C5155" s="35" t="s">
+      <c r="C5155" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5156" s="3"/>
       <c r="B5156" s="7"/>
-      <c r="C5156" s="35"/>
+      <c r="C5156" s="32"/>
     </row>
     <row r="5157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5157" s="3">
@@ -36974,7 +36977,7 @@
       <c r="A5266" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5266" s="34" t="s">
+      <c r="B5266" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C5266" s="11" t="s">
@@ -36983,7 +36986,7 @@
     </row>
     <row r="5267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5267" s="25"/>
-      <c r="B5267" s="34"/>
+      <c r="B5267" s="35"/>
       <c r="C5267" s="11"/>
     </row>
     <row r="5268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36991,14 +36994,14 @@
         <v>6.1</v>
       </c>
       <c r="B5268" s="7"/>
-      <c r="C5268" s="35" t="s">
+      <c r="C5268" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5269" s="3"/>
       <c r="B5269" s="7"/>
-      <c r="C5269" s="35"/>
+      <c r="C5269" s="32"/>
     </row>
     <row r="5270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5270" s="3">
@@ -37241,10 +37244,10 @@
     </row>
     <row r="5427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5427" s="17"/>
-      <c r="B5427" s="32" t="s">
+      <c r="B5427" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C5427" s="33"/>
+      <c r="C5427" s="34"/>
     </row>
     <row r="5428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5428" s="5" t="s">
@@ -37508,7 +37511,7 @@
       <c r="A5502" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5502" s="34" t="s">
+      <c r="B5502" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C5502" s="11" t="s">
@@ -37517,7 +37520,7 @@
     </row>
     <row r="5503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5503" s="25"/>
-      <c r="B5503" s="34"/>
+      <c r="B5503" s="35"/>
       <c r="C5503" s="11"/>
     </row>
     <row r="5504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37525,14 +37528,14 @@
         <v>6.1</v>
       </c>
       <c r="B5504" s="7"/>
-      <c r="C5504" s="35" t="s">
+      <c r="C5504" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5505" s="3"/>
       <c r="B5505" s="7"/>
-      <c r="C5505" s="35"/>
+      <c r="C5505" s="32"/>
     </row>
     <row r="5506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5506" s="3">
@@ -37565,10 +37568,10 @@
     </row>
     <row r="5545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5545" s="17"/>
-      <c r="B5545" s="32" t="s">
+      <c r="B5545" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C5545" s="33"/>
+      <c r="C5545" s="34"/>
     </row>
     <row r="5546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5546" s="5" t="s">
@@ -37691,7 +37694,7 @@
       <c r="A5559" s="23">
         <v>5.2</v>
       </c>
-      <c r="B5559" s="34" t="s">
+      <c r="B5559" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C5559" s="11" t="s">
@@ -37700,7 +37703,7 @@
     </row>
     <row r="5560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5560" s="23"/>
-      <c r="B5560" s="34"/>
+      <c r="B5560" s="35"/>
       <c r="C5560" s="11"/>
     </row>
     <row r="5561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37708,19 +37711,19 @@
         <v>6.1</v>
       </c>
       <c r="B5561" s="7"/>
-      <c r="C5561" s="35" t="s">
+      <c r="C5561" s="32" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5562" s="3"/>
       <c r="B5562" s="7"/>
-      <c r="C5562" s="35"/>
+      <c r="C5562" s="32"/>
     </row>
     <row r="5563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5563" s="3"/>
       <c r="B5563" s="7"/>
-      <c r="C5563" s="35"/>
+      <c r="C5563" s="32"/>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="3">
@@ -37742,7 +37745,7 @@
       <c r="A5566" s="23">
         <v>7.2</v>
       </c>
-      <c r="B5566" s="34" t="s">
+      <c r="B5566" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C5566" s="11" t="s">
@@ -37751,7 +37754,7 @@
     </row>
     <row r="5567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5567" s="23"/>
-      <c r="B5567" s="34"/>
+      <c r="B5567" s="35"/>
       <c r="C5567" s="11"/>
     </row>
     <row r="5568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37810,10 +37813,10 @@
     </row>
     <row r="5604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5604" s="17"/>
-      <c r="B5604" s="32" t="s">
+      <c r="B5604" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C5604" s="33"/>
+      <c r="C5604" s="34"/>
     </row>
     <row r="5605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5605" s="5" t="s">
@@ -37942,7 +37945,7 @@
       <c r="A5618" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5618" s="34" t="s">
+      <c r="B5618" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C5618" s="11" t="s">
@@ -37951,7 +37954,7 @@
     </row>
     <row r="5619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5619" s="25"/>
-      <c r="B5619" s="34"/>
+      <c r="B5619" s="35"/>
       <c r="C5619" s="11"/>
     </row>
     <row r="5620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37959,14 +37962,14 @@
         <v>6.1</v>
       </c>
       <c r="B5620" s="7"/>
-      <c r="C5620" s="35" t="s">
+      <c r="C5620" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5621" s="3"/>
       <c r="B5621" s="7"/>
-      <c r="C5621" s="35"/>
+      <c r="C5621" s="32"/>
     </row>
     <row r="5622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5622" s="3">
@@ -37999,10 +38002,10 @@
     </row>
     <row r="5663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5663" s="17"/>
-      <c r="B5663" s="32" t="s">
+      <c r="B5663" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C5663" s="33"/>
+      <c r="C5663" s="34"/>
     </row>
     <row r="5664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5664" s="5" t="s">
@@ -38148,10 +38151,10 @@
     </row>
     <row r="5722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5722" s="17"/>
-      <c r="B5722" s="32" t="s">
+      <c r="B5722" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C5722" s="33"/>
+      <c r="C5722" s="34"/>
     </row>
     <row r="5723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5723" s="5" t="s">
@@ -38558,10 +38561,10 @@
     </row>
     <row r="5781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5781" s="17"/>
-      <c r="B5781" s="32" t="s">
+      <c r="B5781" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="C5781" s="33"/>
+      <c r="C5781" s="34"/>
     </row>
     <row r="5782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5782" s="5" t="s">
@@ -39676,19 +39679,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6028" s="7"/>
-      <c r="C6028" s="35" t="s">
+      <c r="C6028" s="32" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6029" s="3"/>
       <c r="B6029" s="7"/>
-      <c r="C6029" s="35"/>
+      <c r="C6029" s="32"/>
     </row>
     <row r="6030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6030" s="3"/>
       <c r="B6030" s="7"/>
-      <c r="C6030" s="35"/>
+      <c r="C6030" s="32"/>
     </row>
     <row r="6031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6031" s="3">
@@ -39773,10 +39776,10 @@
     </row>
     <row r="6076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6076" s="17"/>
-      <c r="B6076" s="32" t="s">
+      <c r="B6076" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C6076" s="33"/>
+      <c r="C6076" s="34"/>
     </row>
     <row r="6077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6077" s="5" t="s">
@@ -39921,7 +39924,7 @@
       <c r="A6092" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6092" s="34" t="s">
+      <c r="B6092" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C6092" s="11" t="s">
@@ -39930,7 +39933,7 @@
     </row>
     <row r="6093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6093" s="25"/>
-      <c r="B6093" s="34"/>
+      <c r="B6093" s="35"/>
       <c r="C6093" s="11"/>
     </row>
     <row r="6094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40290,14 +40293,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6146" s="7"/>
-      <c r="C6146" s="35" t="s">
+      <c r="C6146" s="32" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="6147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6147" s="3"/>
       <c r="B6147" s="7"/>
-      <c r="C6147" s="35"/>
+      <c r="C6147" s="32"/>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6148" s="3">
@@ -40706,19 +40709,19 @@
         <v>2.1</v>
       </c>
       <c r="B6258" s="7"/>
-      <c r="C6258" s="35" t="s">
+      <c r="C6258" s="32" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="6259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6259" s="3"/>
       <c r="B6259" s="7"/>
-      <c r="C6259" s="35"/>
+      <c r="C6259" s="32"/>
     </row>
     <row r="6260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6260" s="3"/>
       <c r="B6260" s="7"/>
-      <c r="C6260" s="35"/>
+      <c r="C6260" s="32"/>
     </row>
     <row r="6261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6261" s="3">
@@ -40902,10 +40905,10 @@
     </row>
     <row r="6371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6371" s="17"/>
-      <c r="B6371" s="32" t="s">
+      <c r="B6371" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="C6371" s="33"/>
+      <c r="C6371" s="34"/>
     </row>
     <row r="6372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6372" s="5" t="s">
@@ -41145,7 +41148,7 @@
       <c r="A6440" s="25">
         <v>4.2</v>
       </c>
-      <c r="B6440" s="34" t="s">
+      <c r="B6440" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C6440" s="11" t="s">
@@ -41154,7 +41157,7 @@
     </row>
     <row r="6441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6441" s="25"/>
-      <c r="B6441" s="34"/>
+      <c r="B6441" s="35"/>
       <c r="C6441" s="11"/>
     </row>
     <row r="6442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41414,10 +41417,10 @@
     </row>
     <row r="6489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6489" s="17"/>
-      <c r="B6489" s="32" t="s">
+      <c r="B6489" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C6489" s="33"/>
+      <c r="C6489" s="34"/>
     </row>
     <row r="6490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6490" s="5" t="s">
@@ -41512,7 +41515,7 @@
       <c r="A6499" s="23">
         <v>4.2</v>
       </c>
-      <c r="B6499" s="34" t="s">
+      <c r="B6499" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C6499" s="11" t="s">
@@ -41521,7 +41524,7 @@
     </row>
     <row r="6500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6500" s="23"/>
-      <c r="B6500" s="34"/>
+      <c r="B6500" s="35"/>
       <c r="C6500" s="11"/>
     </row>
     <row r="6501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41529,19 +41532,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6501" s="7"/>
-      <c r="C6501" s="35" t="s">
+      <c r="C6501" s="32" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6502" s="3"/>
       <c r="B6502" s="7"/>
-      <c r="C6502" s="35"/>
+      <c r="C6502" s="32"/>
     </row>
     <row r="6503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6503" s="3"/>
       <c r="B6503" s="7"/>
-      <c r="C6503" s="35"/>
+      <c r="C6503" s="32"/>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="3">
@@ -41563,7 +41566,7 @@
       <c r="A6506" s="23">
         <v>6.2</v>
       </c>
-      <c r="B6506" s="34" t="s">
+      <c r="B6506" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C6506" s="8" t="s">
@@ -41572,7 +41575,7 @@
     </row>
     <row r="6507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6507" s="23"/>
-      <c r="B6507" s="34"/>
+      <c r="B6507" s="35"/>
       <c r="C6507" s="8"/>
     </row>
     <row r="6508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41631,10 +41634,10 @@
     </row>
     <row r="6548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6548" s="17"/>
-      <c r="B6548" s="32" t="s">
+      <c r="B6548" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C6548" s="33"/>
+      <c r="C6548" s="34"/>
     </row>
     <row r="6549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6549" s="5" t="s">
@@ -41749,7 +41752,7 @@
       <c r="A6560" s="25">
         <v>5.2</v>
       </c>
-      <c r="B6560" s="34" t="s">
+      <c r="B6560" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C6560" s="11" t="s">
@@ -41758,7 +41761,7 @@
     </row>
     <row r="6561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6561" s="25"/>
-      <c r="B6561" s="34"/>
+      <c r="B6561" s="35"/>
       <c r="C6561" s="11"/>
     </row>
     <row r="6562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42123,10 +42126,10 @@
     </row>
     <row r="6666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6666" s="17"/>
-      <c r="B6666" s="32" t="s">
+      <c r="B6666" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C6666" s="33"/>
+      <c r="C6666" s="34"/>
     </row>
     <row r="6667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6667" s="5" t="s">
@@ -42297,7 +42300,7 @@
       <c r="A6686" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6686" s="34" t="s">
+      <c r="B6686" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C6686" s="8" t="s">
@@ -42306,7 +42309,7 @@
     </row>
     <row r="6687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6687" s="25"/>
-      <c r="B6687" s="34"/>
+      <c r="B6687" s="35"/>
       <c r="C6687" s="8"/>
     </row>
     <row r="6688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42960,10 +42963,10 @@
     </row>
     <row r="6784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6784" s="17"/>
-      <c r="B6784" s="32" t="s">
+      <c r="B6784" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C6784" s="33"/>
+      <c r="C6784" s="34"/>
     </row>
     <row r="6785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6785" s="5" t="s">
@@ -43118,7 +43121,7 @@
       <c r="A6802" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6802" s="34" t="s">
+      <c r="B6802" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C6802" s="11" t="s">
@@ -43127,7 +43130,7 @@
     </row>
     <row r="6803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6803" s="25"/>
-      <c r="B6803" s="34"/>
+      <c r="B6803" s="35"/>
       <c r="C6803" s="11"/>
     </row>
     <row r="6804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43912,10 +43915,10 @@
     </row>
     <row r="6961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6961" s="17"/>
-      <c r="B6961" s="32" t="s">
+      <c r="B6961" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C6961" s="33"/>
+      <c r="C6961" s="34"/>
     </row>
     <row r="6962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6962" s="5" t="s">
@@ -44032,19 +44035,19 @@
         <v>6.1</v>
       </c>
       <c r="B6974" s="7"/>
-      <c r="C6974" s="35" t="s">
+      <c r="C6974" s="32" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6975" s="3"/>
       <c r="B6975" s="7"/>
-      <c r="C6975" s="35"/>
+      <c r="C6975" s="32"/>
     </row>
     <row r="6976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6976" s="3"/>
       <c r="B6976" s="7"/>
-      <c r="C6976" s="35"/>
+      <c r="C6976" s="32"/>
     </row>
     <row r="6977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6977" s="3">
@@ -44129,10 +44132,10 @@
     </row>
     <row r="7020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7020" s="17"/>
-      <c r="B7020" s="32" t="s">
+      <c r="B7020" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C7020" s="33"/>
+      <c r="C7020" s="34"/>
     </row>
     <row r="7021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7021" s="5" t="s">
@@ -44293,7 +44296,7 @@
       <c r="A7038" s="25">
         <v>7.2</v>
       </c>
-      <c r="B7038" s="34" t="s">
+      <c r="B7038" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C7038" s="11" t="s">
@@ -44302,7 +44305,7 @@
     </row>
     <row r="7039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7039" s="25"/>
-      <c r="B7039" s="34"/>
+      <c r="B7039" s="35"/>
       <c r="C7039" s="11"/>
     </row>
     <row r="7040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44789,7 +44792,7 @@
       <c r="A7154" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7154" s="34" t="s">
+      <c r="B7154" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C7154" s="11" t="s">
@@ -44798,7 +44801,7 @@
     </row>
     <row r="7155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7155" s="25"/>
-      <c r="B7155" s="34"/>
+      <c r="B7155" s="35"/>
       <c r="C7155" s="11"/>
     </row>
     <row r="7156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45158,14 +45161,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B7208" s="7"/>
-      <c r="C7208" s="35" t="s">
+      <c r="C7208" s="32" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="7209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7209" s="3"/>
       <c r="B7209" s="7"/>
-      <c r="C7209" s="35"/>
+      <c r="C7209" s="32"/>
     </row>
     <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7210" s="3">
@@ -45285,10 +45288,10 @@
     </row>
     <row r="7315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7315" s="17"/>
-      <c r="B7315" s="32" t="s">
-        <v>621</v>
-      </c>
-      <c r="C7315" s="33"/>
+      <c r="B7315" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="C7315" s="34"/>
     </row>
     <row r="7316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7316" s="5" t="s">
@@ -45584,7 +45587,7 @@
       <c r="A7390" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7390" s="34" t="s">
+      <c r="B7390" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C7390" s="11" t="s">
@@ -45593,7 +45596,7 @@
     </row>
     <row r="7391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7391" s="25"/>
-      <c r="B7391" s="34"/>
+      <c r="B7391" s="35"/>
       <c r="C7391" s="11"/>
     </row>
     <row r="7392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45853,10 +45856,10 @@
     </row>
     <row r="7433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7433" s="17"/>
-      <c r="B7433" s="32" t="s">
+      <c r="B7433" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C7433" s="33"/>
+      <c r="C7433" s="34"/>
     </row>
     <row r="7434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7434" s="5" t="s">
@@ -45979,7 +45982,7 @@
       <c r="A7447" s="23">
         <v>5.2</v>
       </c>
-      <c r="B7447" s="34" t="s">
+      <c r="B7447" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C7447" s="11" t="s">
@@ -45988,7 +45991,7 @@
     </row>
     <row r="7448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7448" s="23"/>
-      <c r="B7448" s="34"/>
+      <c r="B7448" s="35"/>
       <c r="C7448" s="11"/>
     </row>
     <row r="7449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45996,19 +45999,19 @@
         <v>6.1</v>
       </c>
       <c r="B7449" s="7"/>
-      <c r="C7449" s="35" t="s">
+      <c r="C7449" s="32" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="7450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7450" s="3"/>
       <c r="B7450" s="7"/>
-      <c r="C7450" s="35"/>
+      <c r="C7450" s="32"/>
     </row>
     <row r="7451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7451" s="3"/>
       <c r="B7451" s="7"/>
-      <c r="C7451" s="35"/>
+      <c r="C7451" s="32"/>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7452" s="3">
@@ -46030,7 +46033,7 @@
       <c r="A7454" s="23">
         <v>7.2</v>
       </c>
-      <c r="B7454" s="34" t="s">
+      <c r="B7454" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C7454" s="11" t="s">
@@ -46039,7 +46042,7 @@
     </row>
     <row r="7455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7455" s="23"/>
-      <c r="B7455" s="34"/>
+      <c r="B7455" s="35"/>
       <c r="C7455" s="11"/>
     </row>
     <row r="7456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46230,7 +46233,7 @@
       <c r="A7506" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7506" s="34" t="s">
+      <c r="B7506" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C7506" s="11" t="s">
@@ -46239,7 +46242,7 @@
     </row>
     <row r="7507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7507" s="25"/>
-      <c r="B7507" s="34"/>
+      <c r="B7507" s="35"/>
       <c r="C7507" s="11"/>
     </row>
     <row r="7508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46604,10 +46607,10 @@
     </row>
     <row r="7610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7610" s="17"/>
-      <c r="B7610" s="32" t="s">
+      <c r="B7610" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="C7610" s="33"/>
+      <c r="C7610" s="34"/>
     </row>
     <row r="7611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7611" s="5" t="s">
@@ -46804,10 +46807,10 @@
     </row>
     <row r="7669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7669" s="17"/>
-      <c r="B7669" s="32" t="s">
+      <c r="B7669" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="C7669" s="33"/>
+      <c r="C7669" s="34"/>
     </row>
     <row r="7670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7670" s="5" t="s">
@@ -47633,7 +47636,7 @@
       <c r="A7980" s="25">
         <v>7.2</v>
       </c>
-      <c r="B7980" s="34" t="s">
+      <c r="B7980" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C7980" s="11" t="s">
@@ -47642,7 +47645,7 @@
     </row>
     <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7981" s="25"/>
-      <c r="B7981" s="34"/>
+      <c r="B7981" s="35"/>
       <c r="C7981" s="11"/>
     </row>
     <row r="7982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47735,14 +47738,14 @@
         <v>2.1</v>
       </c>
       <c r="B8028" s="7"/>
-      <c r="C8028" s="35" t="s">
+      <c r="C8028" s="32" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="8029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8029" s="3"/>
       <c r="B8029" s="7"/>
-      <c r="C8029" s="35"/>
+      <c r="C8029" s="32"/>
     </row>
     <row r="8030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8030" s="3">
@@ -47934,14 +47937,14 @@
         <v>2.1</v>
       </c>
       <c r="B8146" s="7"/>
-      <c r="C8146" s="35" t="s">
+      <c r="C8146" s="32" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="8147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8147" s="3"/>
       <c r="B8147" s="7"/>
-      <c r="C8147" s="35"/>
+      <c r="C8147" s="32"/>
     </row>
     <row r="8148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8148" s="3">
@@ -48173,7 +48176,7 @@
       <c r="A8269" s="25">
         <v>4.2</v>
       </c>
-      <c r="B8269" s="34" t="s">
+      <c r="B8269" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C8269" s="11" t="s">
@@ -48182,7 +48185,7 @@
     </row>
     <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8270" s="25"/>
-      <c r="B8270" s="34"/>
+      <c r="B8270" s="35"/>
       <c r="C8270" s="11"/>
     </row>
     <row r="8271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48321,7 +48324,7 @@
       <c r="A8328" s="25">
         <v>4.2</v>
       </c>
-      <c r="B8328" s="34" t="s">
+      <c r="B8328" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C8328" s="11" t="s">
@@ -48330,7 +48333,7 @@
     </row>
     <row r="8329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8329" s="25"/>
-      <c r="B8329" s="34"/>
+      <c r="B8329" s="35"/>
       <c r="C8329" s="11"/>
     </row>
     <row r="8330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48469,7 +48472,7 @@
       <c r="A8387" s="25">
         <v>4.2</v>
       </c>
-      <c r="B8387" s="34" t="s">
+      <c r="B8387" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C8387" s="11" t="s">
@@ -48478,7 +48481,7 @@
     </row>
     <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8388" s="25"/>
-      <c r="B8388" s="34"/>
+      <c r="B8388" s="35"/>
       <c r="C8388" s="11"/>
     </row>
     <row r="8389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48787,10 +48790,10 @@
     </row>
     <row r="8554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8554" s="17"/>
-      <c r="B8554" s="32" t="s">
+      <c r="B8554" s="33" t="s">
         <v>414</v>
       </c>
-      <c r="C8554" s="33"/>
+      <c r="C8554" s="34"/>
     </row>
     <row r="8555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8555" s="5" t="s">
@@ -48949,7 +48952,7 @@
       <c r="A8572" s="25">
         <v>7.2</v>
       </c>
-      <c r="B8572" s="34" t="s">
+      <c r="B8572" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C8572" s="11" t="s">
@@ -48958,7 +48961,7 @@
     </row>
     <row r="8573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8573" s="25"/>
-      <c r="B8573" s="34"/>
+      <c r="B8573" s="35"/>
       <c r="C8573" s="11"/>
     </row>
     <row r="8574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49176,10 +49179,10 @@
     </row>
     <row r="8672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8672" s="17"/>
-      <c r="B8672" s="32" t="s">
+      <c r="B8672" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="C8672" s="33"/>
+      <c r="C8672" s="34"/>
     </row>
     <row r="8673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8673" s="5" t="s">
@@ -49336,7 +49339,7 @@
       <c r="A8690" s="25">
         <v>7.2</v>
       </c>
-      <c r="B8690" s="34" t="s">
+      <c r="B8690" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C8690" s="11" t="s">
@@ -49345,7 +49348,7 @@
     </row>
     <row r="8691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8691" s="25"/>
-      <c r="B8691" s="34"/>
+      <c r="B8691" s="35"/>
       <c r="C8691" s="11"/>
     </row>
     <row r="8692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49845,10 +49848,10 @@
     </row>
     <row r="8908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8908" s="17"/>
-      <c r="B8908" s="32" t="s">
+      <c r="B8908" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="C8908" s="33"/>
+      <c r="C8908" s="34"/>
     </row>
     <row r="8909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8909" s="5" t="s">
@@ -50009,7 +50012,7 @@
       <c r="A8926" s="25">
         <v>7.2</v>
       </c>
-      <c r="B8926" s="34" t="s">
+      <c r="B8926" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C8926" s="11" t="s">
@@ -50018,7 +50021,7 @@
     </row>
     <row r="8927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8927" s="25"/>
-      <c r="B8927" s="34"/>
+      <c r="B8927" s="35"/>
       <c r="C8927" s="11"/>
     </row>
     <row r="8928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50111,14 +50114,14 @@
         <v>2.1</v>
       </c>
       <c r="B8972" s="7"/>
-      <c r="C8972" s="35" t="s">
+      <c r="C8972" s="32" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="8973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8973" s="3"/>
       <c r="B8973" s="7"/>
-      <c r="C8973" s="35"/>
+      <c r="C8973" s="32"/>
     </row>
     <row r="8974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8974" s="3">
@@ -50279,7 +50282,7 @@
       <c r="A9040" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9040" s="34" t="s">
+      <c r="B9040" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C9040" s="11" t="s">
@@ -50288,7 +50291,7 @@
     </row>
     <row r="9041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9041" s="25"/>
-      <c r="B9041" s="34"/>
+      <c r="B9041" s="35"/>
       <c r="C9041" s="11"/>
     </row>
     <row r="9042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50468,14 +50471,14 @@
         <v>2.1</v>
       </c>
       <c r="B9149" s="7"/>
-      <c r="C9149" s="35" t="s">
+      <c r="C9149" s="32" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="9150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9150" s="3"/>
       <c r="B9150" s="7"/>
-      <c r="C9150" s="35"/>
+      <c r="C9150" s="32"/>
     </row>
     <row r="9151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9151" s="3">
@@ -50606,7 +50609,7 @@
       <c r="A9213" s="25">
         <v>4.2</v>
       </c>
-      <c r="B9213" s="34" t="s">
+      <c r="B9213" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C9213" s="11" t="s">
@@ -50615,7 +50618,7 @@
     </row>
     <row r="9214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9214" s="25"/>
-      <c r="B9214" s="34"/>
+      <c r="B9214" s="35"/>
       <c r="C9214" s="11"/>
     </row>
     <row r="9215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50784,7 +50787,7 @@
       <c r="A9276" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9276" s="34" t="s">
+      <c r="B9276" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C9276" s="11" t="s">
@@ -50793,7 +50796,7 @@
     </row>
     <row r="9277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9277" s="25"/>
-      <c r="B9277" s="34"/>
+      <c r="B9277" s="35"/>
       <c r="C9277" s="11"/>
     </row>
     <row r="9278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50962,7 +50965,7 @@
       <c r="A9335" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9335" s="34" t="s">
+      <c r="B9335" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C9335" s="11" t="s">
@@ -50971,7 +50974,7 @@
     </row>
     <row r="9336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9336" s="25"/>
-      <c r="B9336" s="34"/>
+      <c r="B9336" s="35"/>
       <c r="C9336" s="11"/>
     </row>
     <row r="9337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51144,7 +51147,7 @@
       <c r="A9394" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9394" s="34" t="s">
+      <c r="B9394" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C9394" s="11" t="s">
@@ -51153,7 +51156,7 @@
     </row>
     <row r="9395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9395" s="25"/>
-      <c r="B9395" s="34"/>
+      <c r="B9395" s="35"/>
       <c r="C9395" s="11"/>
     </row>
     <row r="9396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51266,14 +51269,14 @@
         <v>3.1</v>
       </c>
       <c r="B9446" s="7"/>
-      <c r="C9446" s="35" t="s">
+      <c r="C9446" s="32" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="9447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9447" s="3"/>
       <c r="B9447" s="7"/>
-      <c r="C9447" s="35"/>
+      <c r="C9447" s="32"/>
     </row>
     <row r="9448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9448" s="3">
@@ -51306,10 +51309,10 @@
     </row>
     <row r="9498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9498" s="17"/>
-      <c r="B9498" s="32" t="s">
+      <c r="B9498" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C9498" s="33"/>
+      <c r="C9498" s="34"/>
     </row>
     <row r="9499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9499" s="5" t="s">
@@ -51471,14 +51474,14 @@
         <v>8.1</v>
       </c>
       <c r="B9516" s="2"/>
-      <c r="C9516" s="35" t="s">
+      <c r="C9516" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9517" s="3"/>
       <c r="B9517" s="2"/>
-      <c r="C9517" s="35"/>
+      <c r="C9517" s="32"/>
     </row>
     <row r="9518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9518" s="3">
@@ -51583,14 +51586,14 @@
         <v>3.1</v>
       </c>
       <c r="B9564" s="7"/>
-      <c r="C9564" s="35" t="s">
+      <c r="C9564" s="32" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="9565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9565" s="3"/>
       <c r="B9565" s="7"/>
-      <c r="C9565" s="35"/>
+      <c r="C9565" s="32"/>
     </row>
     <row r="9566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9566" s="3">
@@ -51727,14 +51730,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9627" s="7"/>
-      <c r="C9627" s="35" t="s">
+      <c r="C9627" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9628" s="3"/>
       <c r="B9628" s="7"/>
-      <c r="C9628" s="35"/>
+      <c r="C9628" s="32"/>
     </row>
     <row r="9629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9629" s="3">
@@ -51873,14 +51876,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9686" s="7"/>
-      <c r="C9686" s="35" t="s">
+      <c r="C9686" s="32" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="9687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9687" s="3"/>
       <c r="B9687" s="7"/>
-      <c r="C9687" s="35"/>
+      <c r="C9687" s="32"/>
     </row>
     <row r="9688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9688" s="3">
@@ -52019,14 +52022,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9745" s="7"/>
-      <c r="C9745" s="35" t="s">
+      <c r="C9745" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9746" s="3"/>
       <c r="B9746" s="7"/>
-      <c r="C9746" s="35"/>
+      <c r="C9746" s="32"/>
     </row>
     <row r="9747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9747" s="3">
@@ -52165,14 +52168,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9804" s="7"/>
-      <c r="C9804" s="35" t="s">
+      <c r="C9804" s="32" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="9805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9805" s="3"/>
       <c r="B9805" s="7"/>
-      <c r="C9805" s="35"/>
+      <c r="C9805" s="32"/>
     </row>
     <row r="9806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9806" s="3">
@@ -52353,7 +52356,7 @@
       <c r="A9868" s="25">
         <v>7.2</v>
       </c>
-      <c r="B9868" s="34" t="s">
+      <c r="B9868" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C9868" s="11" t="s">
@@ -52362,7 +52365,7 @@
     </row>
     <row r="9869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9869" s="25"/>
-      <c r="B9869" s="34"/>
+      <c r="B9869" s="35"/>
       <c r="C9869" s="11"/>
     </row>
     <row r="9870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52370,14 +52373,14 @@
         <v>8.1</v>
       </c>
       <c r="B9870" s="7"/>
-      <c r="C9870" s="35" t="s">
+      <c r="C9870" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9871" s="3"/>
       <c r="B9871" s="7"/>
-      <c r="C9871" s="35"/>
+      <c r="C9871" s="32"/>
     </row>
     <row r="9872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9872" s="3">
@@ -52462,14 +52465,14 @@
         <v>2.1</v>
       </c>
       <c r="B9916" s="7"/>
-      <c r="C9916" s="35" t="s">
+      <c r="C9916" s="32" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="9917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9917" s="3"/>
       <c r="B9917" s="7"/>
-      <c r="C9917" s="35"/>
+      <c r="C9917" s="32"/>
     </row>
     <row r="9918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9918" s="3">
@@ -52574,14 +52577,14 @@
         <v>3.1</v>
       </c>
       <c r="B9977" s="7"/>
-      <c r="C9977" s="35" t="s">
+      <c r="C9977" s="32" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="9978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9978" s="3"/>
       <c r="B9978" s="7"/>
-      <c r="C9978" s="35"/>
+      <c r="C9978" s="32"/>
     </row>
     <row r="9979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9979" s="3">
@@ -52666,14 +52669,14 @@
         <v>2.1</v>
       </c>
       <c r="B10034" s="7"/>
-      <c r="C10034" s="35" t="s">
+      <c r="C10034" s="32" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="10035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10035" s="3"/>
       <c r="B10035" s="7"/>
-      <c r="C10035" s="35"/>
+      <c r="C10035" s="32"/>
     </row>
     <row r="10036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10036" s="3">
@@ -52921,7 +52924,7 @@
       <c r="A10157" s="25">
         <v>4.2</v>
       </c>
-      <c r="B10157" s="34" t="s">
+      <c r="B10157" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C10157" s="11" t="s">
@@ -52930,7 +52933,7 @@
     </row>
     <row r="10158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10158" s="25"/>
-      <c r="B10158" s="34"/>
+      <c r="B10158" s="35"/>
       <c r="C10158" s="11"/>
     </row>
     <row r="10159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52938,14 +52941,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10159" s="7"/>
-      <c r="C10159" s="35" t="s">
+      <c r="C10159" s="32" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="10160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10160" s="3"/>
       <c r="B10160" s="7"/>
-      <c r="C10160" s="35"/>
+      <c r="C10160" s="32"/>
     </row>
     <row r="10161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10161" s="3">
@@ -53076,7 +53079,7 @@
       <c r="A10216" s="25">
         <v>4.2</v>
       </c>
-      <c r="B10216" s="34" t="s">
+      <c r="B10216" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C10216" s="11" t="s">
@@ -53085,7 +53088,7 @@
     </row>
     <row r="10217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10217" s="25"/>
-      <c r="B10217" s="34"/>
+      <c r="B10217" s="35"/>
       <c r="C10217" s="11"/>
     </row>
     <row r="10218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53093,14 +53096,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10218" s="7"/>
-      <c r="C10218" s="35" t="s">
+      <c r="C10218" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10219" s="3"/>
       <c r="B10219" s="7"/>
-      <c r="C10219" s="35"/>
+      <c r="C10219" s="32"/>
     </row>
     <row r="10220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10220" s="3">
@@ -53231,7 +53234,7 @@
       <c r="A10275" s="25">
         <v>4.2</v>
       </c>
-      <c r="B10275" s="34" t="s">
+      <c r="B10275" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C10275" s="11" t="s">
@@ -53240,7 +53243,7 @@
     </row>
     <row r="10276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10276" s="25"/>
-      <c r="B10276" s="34"/>
+      <c r="B10276" s="35"/>
       <c r="C10276" s="11"/>
     </row>
     <row r="10277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53248,14 +53251,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10277" s="7"/>
-      <c r="C10277" s="35" t="s">
+      <c r="C10277" s="32" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10278" s="3"/>
       <c r="B10278" s="7"/>
-      <c r="C10278" s="35"/>
+      <c r="C10278" s="32"/>
     </row>
     <row r="10279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10279" s="3">
@@ -53406,7 +53409,7 @@
       <c r="A10336" s="25">
         <v>5.2</v>
       </c>
-      <c r="B10336" s="34" t="s">
+      <c r="B10336" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C10336" s="11" t="s">
@@ -53415,7 +53418,7 @@
     </row>
     <row r="10337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10337" s="25"/>
-      <c r="B10337" s="34"/>
+      <c r="B10337" s="35"/>
       <c r="C10337" s="11"/>
     </row>
     <row r="10338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53423,14 +53426,14 @@
         <v>6.1</v>
       </c>
       <c r="B10338" s="7"/>
-      <c r="C10338" s="35" t="s">
+      <c r="C10338" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10339" s="3"/>
       <c r="B10339" s="7"/>
-      <c r="C10339" s="35"/>
+      <c r="C10339" s="32"/>
     </row>
     <row r="10340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10340" s="3">
@@ -53568,10 +53571,10 @@
     </row>
     <row r="10442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10442" s="17"/>
-      <c r="B10442" s="32" t="s">
+      <c r="B10442" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C10442" s="33"/>
+      <c r="C10442" s="34"/>
     </row>
     <row r="10443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10443" s="5" t="s">
@@ -53742,7 +53745,7 @@
       <c r="A10462" s="25">
         <v>7.2</v>
       </c>
-      <c r="B10462" s="34" t="s">
+      <c r="B10462" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C10462" s="11" t="s">
@@ -53751,7 +53754,7 @@
     </row>
     <row r="10463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10463" s="25"/>
-      <c r="B10463" s="34"/>
+      <c r="B10463" s="35"/>
       <c r="C10463" s="11"/>
     </row>
     <row r="10464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53759,14 +53762,14 @@
         <v>8.1</v>
       </c>
       <c r="B10464" s="7"/>
-      <c r="C10464" s="35" t="s">
+      <c r="C10464" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10465" s="3"/>
       <c r="B10465" s="7"/>
-      <c r="C10465" s="35"/>
+      <c r="C10465" s="32"/>
     </row>
     <row r="10466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10466" s="3">
@@ -53941,14 +53944,14 @@
         <v>7.1</v>
       </c>
       <c r="B10516" s="7"/>
-      <c r="C10516" s="35" t="s">
+      <c r="C10516" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10517" s="3"/>
       <c r="B10517" s="7"/>
-      <c r="C10517" s="35"/>
+      <c r="C10517" s="32"/>
     </row>
     <row r="10518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10518" s="3">
@@ -53981,10 +53984,10 @@
     </row>
     <row r="10560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10560" s="17"/>
-      <c r="B10560" s="32" t="s">
+      <c r="B10560" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C10560" s="33"/>
+      <c r="C10560" s="34"/>
     </row>
     <row r="10561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10561" s="5" t="s">
@@ -54139,7 +54142,7 @@
       <c r="A10578" s="25">
         <v>7.2</v>
       </c>
-      <c r="B10578" s="34" t="s">
+      <c r="B10578" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C10578" s="11" t="s">
@@ -54148,7 +54151,7 @@
     </row>
     <row r="10579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10579" s="25"/>
-      <c r="B10579" s="34"/>
+      <c r="B10579" s="35"/>
       <c r="C10579" s="11"/>
     </row>
     <row r="10580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54156,14 +54159,14 @@
         <v>8.1</v>
       </c>
       <c r="B10580" s="7"/>
-      <c r="C10580" s="35" t="s">
+      <c r="C10580" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10581" s="3"/>
       <c r="B10581" s="7"/>
-      <c r="C10581" s="35"/>
+      <c r="C10581" s="32"/>
     </row>
     <row r="10582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10582" s="3">
@@ -54316,14 +54319,14 @@
         <v>6.1</v>
       </c>
       <c r="B10632" s="7"/>
-      <c r="C10632" s="35" t="s">
+      <c r="C10632" s="32" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="10633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10633" s="3"/>
       <c r="B10633" s="7"/>
-      <c r="C10633" s="35"/>
+      <c r="C10633" s="32"/>
     </row>
     <row r="10634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10634" s="3">
@@ -54476,14 +54479,14 @@
         <v>6.1</v>
       </c>
       <c r="B10691" s="7"/>
-      <c r="C10691" s="35" t="s">
+      <c r="C10691" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10692" s="3"/>
       <c r="B10692" s="7"/>
-      <c r="C10692" s="35"/>
+      <c r="C10692" s="32"/>
     </row>
     <row r="10693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10693" s="3">
@@ -54636,14 +54639,14 @@
         <v>6.1</v>
       </c>
       <c r="B10750" s="7"/>
-      <c r="C10750" s="35" t="s">
+      <c r="C10750" s="32" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10751" s="3"/>
       <c r="B10751" s="7"/>
-      <c r="C10751" s="35"/>
+      <c r="C10751" s="32"/>
     </row>
     <row r="10752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10752" s="3">
@@ -54676,10 +54679,10 @@
     </row>
     <row r="10796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10796" s="17"/>
-      <c r="B10796" s="32" t="s">
+      <c r="B10796" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C10796" s="33"/>
+      <c r="C10796" s="34"/>
     </row>
     <row r="10797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10797" s="5" t="s">
@@ -54840,7 +54843,7 @@
       <c r="A10814" s="25">
         <v>7.2</v>
       </c>
-      <c r="B10814" s="34" t="s">
+      <c r="B10814" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C10814" s="8" t="s">
@@ -54849,7 +54852,7 @@
     </row>
     <row r="10815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10815" s="25"/>
-      <c r="B10815" s="34"/>
+      <c r="B10815" s="35"/>
       <c r="C10815" s="8"/>
     </row>
     <row r="10816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54857,14 +54860,14 @@
         <v>8.1</v>
       </c>
       <c r="B10816" s="7"/>
-      <c r="C10816" s="35" t="s">
+      <c r="C10816" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10817" s="3"/>
       <c r="B10817" s="7"/>
-      <c r="C10817" s="35"/>
+      <c r="C10817" s="32"/>
     </row>
     <row r="10818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10818" s="3">
@@ -55124,7 +55127,7 @@
       <c r="A10930" s="25">
         <v>5.2</v>
       </c>
-      <c r="B10930" s="34" t="s">
+      <c r="B10930" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C10930" s="11" t="s">
@@ -55133,7 +55136,7 @@
     </row>
     <row r="10931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10931" s="25"/>
-      <c r="B10931" s="34"/>
+      <c r="B10931" s="35"/>
       <c r="C10931" s="11"/>
     </row>
     <row r="10932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55141,14 +55144,14 @@
         <v>6.1</v>
       </c>
       <c r="B10932" s="7"/>
-      <c r="C10932" s="35" t="s">
+      <c r="C10932" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10933" s="3"/>
       <c r="B10933" s="7"/>
-      <c r="C10933" s="35"/>
+      <c r="C10933" s="32"/>
     </row>
     <row r="10934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10934" s="3">
@@ -55233,14 +55236,14 @@
         <v>2.1</v>
       </c>
       <c r="B10978" s="7"/>
-      <c r="C10978" s="35" t="s">
+      <c r="C10978" s="32" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="10979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10979" s="3"/>
       <c r="B10979" s="7"/>
-      <c r="C10979" s="35"/>
+      <c r="C10979" s="32"/>
     </row>
     <row r="10980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10980" s="3">
@@ -55325,14 +55328,14 @@
         <v>2.1</v>
       </c>
       <c r="B11037" s="7"/>
-      <c r="C11037" s="35" t="s">
+      <c r="C11037" s="32" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11038" s="3"/>
       <c r="B11038" s="7"/>
-      <c r="C11038" s="35"/>
+      <c r="C11038" s="32"/>
     </row>
     <row r="11039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11039" s="3">
@@ -55505,7 +55508,7 @@
       <c r="A11107" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11107" s="34" t="s">
+      <c r="B11107" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C11107" s="11" t="s">
@@ -55514,7 +55517,7 @@
     </row>
     <row r="11108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11108" s="25"/>
-      <c r="B11108" s="34"/>
+      <c r="B11108" s="35"/>
       <c r="C11108" s="11"/>
     </row>
     <row r="11109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55522,14 +55525,14 @@
         <v>6.1</v>
       </c>
       <c r="B11109" s="2"/>
-      <c r="C11109" s="35" t="s">
+      <c r="C11109" s="32" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="11110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11110" s="3"/>
       <c r="B11110" s="2"/>
-      <c r="C11110" s="35"/>
+      <c r="C11110" s="32"/>
     </row>
     <row r="11111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11111" s="3">
@@ -55702,7 +55705,7 @@
       <c r="A11166" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11166" s="34" t="s">
+      <c r="B11166" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C11166" s="11" t="s">
@@ -55711,7 +55714,7 @@
     </row>
     <row r="11167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11167" s="25"/>
-      <c r="B11167" s="34"/>
+      <c r="B11167" s="35"/>
       <c r="C11167" s="11"/>
     </row>
     <row r="11168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55719,14 +55722,14 @@
         <v>6.1</v>
       </c>
       <c r="B11168" s="2"/>
-      <c r="C11168" s="35" t="s">
+      <c r="C11168" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="11169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11169" s="3"/>
       <c r="B11169" s="2"/>
-      <c r="C11169" s="35"/>
+      <c r="C11169" s="32"/>
     </row>
     <row r="11170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11170" s="3">
@@ -55899,7 +55902,7 @@
       <c r="A11225" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11225" s="34" t="s">
+      <c r="B11225" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C11225" s="11" t="s">
@@ -55908,7 +55911,7 @@
     </row>
     <row r="11226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11226" s="25"/>
-      <c r="B11226" s="34"/>
+      <c r="B11226" s="35"/>
       <c r="C11226" s="11"/>
     </row>
     <row r="11227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55916,14 +55919,14 @@
         <v>6.1</v>
       </c>
       <c r="B11227" s="2"/>
-      <c r="C11227" s="35" t="s">
+      <c r="C11227" s="32" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="11228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11228" s="3"/>
       <c r="B11228" s="2"/>
-      <c r="C11228" s="35"/>
+      <c r="C11228" s="32"/>
     </row>
     <row r="11229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11229" s="3">
@@ -56088,7 +56091,7 @@
       <c r="A11282" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11282" s="34" t="s">
+      <c r="B11282" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C11282" s="11" t="s">
@@ -56097,7 +56100,7 @@
     </row>
     <row r="11283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11283" s="25"/>
-      <c r="B11283" s="34"/>
+      <c r="B11283" s="35"/>
       <c r="C11283" s="11"/>
     </row>
     <row r="11284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -56105,14 +56108,14 @@
         <v>6.1</v>
       </c>
       <c r="B11284" s="7"/>
-      <c r="C11284" s="35" t="s">
+      <c r="C11284" s="32" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="11285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11285" s="3"/>
       <c r="B11285" s="7"/>
-      <c r="C11285" s="35"/>
+      <c r="C11285" s="32"/>
     </row>
     <row r="11286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11286" s="3">
@@ -56217,19 +56220,19 @@
         <v>3.1</v>
       </c>
       <c r="B11334" s="7"/>
-      <c r="C11334" s="35" t="s">
+      <c r="C11334" s="32" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="11335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11335" s="3"/>
       <c r="B11335" s="7"/>
-      <c r="C11335" s="35"/>
+      <c r="C11335" s="32"/>
     </row>
     <row r="11336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11336" s="3"/>
       <c r="B11336" s="7"/>
-      <c r="C11336" s="35"/>
+      <c r="C11336" s="32"/>
     </row>
     <row r="11337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11337" s="3">
@@ -56262,10 +56265,10 @@
     </row>
     <row r="11386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11386" s="17"/>
-      <c r="B11386" s="32" t="s">
+      <c r="B11386" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C11386" s="33"/>
+      <c r="C11386" s="34"/>
     </row>
     <row r="11387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11387" s="5" t="s">
@@ -56427,19 +56430,19 @@
         <v>8.1</v>
       </c>
       <c r="B11404" s="7"/>
-      <c r="C11404" s="35" t="s">
+      <c r="C11404" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="11405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11405" s="3"/>
       <c r="B11405" s="7"/>
-      <c r="C11405" s="35"/>
+      <c r="C11405" s="32"/>
     </row>
     <row r="11406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11406" s="3"/>
       <c r="B11406" s="7"/>
-      <c r="C11406" s="35"/>
+      <c r="C11406" s="32"/>
     </row>
     <row r="11407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11407" s="3">
@@ -56679,19 +56682,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11515" s="7"/>
-      <c r="C11515" s="35" t="s">
+      <c r="C11515" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="11516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11516" s="3"/>
       <c r="B11516" s="7"/>
-      <c r="C11516" s="35"/>
+      <c r="C11516" s="32"/>
     </row>
     <row r="11517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11517" s="3"/>
       <c r="B11517" s="7"/>
-      <c r="C11517" s="35"/>
+      <c r="C11517" s="32"/>
     </row>
     <row r="11518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11518" s="3">
@@ -56830,19 +56833,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11574" s="7"/>
-      <c r="C11574" s="35" t="s">
+      <c r="C11574" s="32" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="11575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11575" s="3"/>
       <c r="B11575" s="7"/>
-      <c r="C11575" s="35"/>
+      <c r="C11575" s="32"/>
     </row>
     <row r="11576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11576" s="3"/>
       <c r="B11576" s="7"/>
-      <c r="C11576" s="35"/>
+      <c r="C11576" s="32"/>
     </row>
     <row r="11577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11577" s="3">
@@ -56981,19 +56984,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11633" s="7"/>
-      <c r="C11633" s="35" t="s">
+      <c r="C11633" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="11634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11634" s="3"/>
       <c r="B11634" s="7"/>
-      <c r="C11634" s="35"/>
+      <c r="C11634" s="32"/>
     </row>
     <row r="11635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11635" s="3"/>
       <c r="B11635" s="7"/>
-      <c r="C11635" s="35"/>
+      <c r="C11635" s="32"/>
     </row>
     <row r="11636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11636" s="3">
@@ -57026,10 +57029,10 @@
     </row>
     <row r="11681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11681" s="17"/>
-      <c r="B11681" s="32" t="s">
+      <c r="B11681" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C11681" s="33"/>
+      <c r="C11681" s="34"/>
     </row>
     <row r="11682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11682" s="5" t="s">
@@ -57132,14 +57135,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11692" s="7"/>
-      <c r="C11692" s="35" t="s">
-        <v>625</v>
+      <c r="C11692" s="32" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="11693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11693" s="3"/>
       <c r="B11693" s="7"/>
-      <c r="C11693" s="35"/>
+      <c r="C11693" s="32"/>
     </row>
     <row r="11694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11694" s="23">
@@ -57372,7 +57375,7 @@
       <c r="A11756" s="25">
         <v>7.2</v>
       </c>
-      <c r="B11756" s="34" t="s">
+      <c r="B11756" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C11756" s="8" t="s">
@@ -57381,7 +57384,7 @@
     </row>
     <row r="11757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11757" s="25"/>
-      <c r="B11757" s="34"/>
+      <c r="B11757" s="35"/>
       <c r="C11757" s="8"/>
     </row>
     <row r="11758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57389,19 +57392,19 @@
         <v>8.1</v>
       </c>
       <c r="B11758" s="7"/>
-      <c r="C11758" s="35" t="s">
+      <c r="C11758" s="32" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="11759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11759" s="3"/>
       <c r="B11759" s="7"/>
-      <c r="C11759" s="35"/>
+      <c r="C11759" s="32"/>
     </row>
     <row r="11760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11760" s="3"/>
       <c r="B11760" s="7"/>
-      <c r="C11760" s="35"/>
+      <c r="C11760" s="32"/>
     </row>
     <row r="11761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11761" s="3">
@@ -57486,14 +57489,14 @@
         <v>2.1</v>
       </c>
       <c r="B11804" s="7"/>
-      <c r="C11804" s="35" t="s">
+      <c r="C11804" s="32" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="11805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11805" s="3"/>
       <c r="B11805" s="7"/>
-      <c r="C11805" s="35"/>
+      <c r="C11805" s="32"/>
     </row>
     <row r="11806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11806" s="3">
@@ -57598,19 +57601,19 @@
         <v>3.1</v>
       </c>
       <c r="B11865" s="7"/>
-      <c r="C11865" s="35" t="s">
+      <c r="C11865" s="32" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="11866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11866" s="3"/>
       <c r="B11866" s="7"/>
-      <c r="C11866" s="35"/>
+      <c r="C11866" s="32"/>
     </row>
     <row r="11867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11867" s="3"/>
       <c r="B11867" s="7"/>
-      <c r="C11867" s="35"/>
+      <c r="C11867" s="32"/>
     </row>
     <row r="11868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11868" s="3">
@@ -57695,14 +57698,14 @@
         <v>2.1</v>
       </c>
       <c r="B11922" s="7"/>
-      <c r="C11922" s="35" t="s">
+      <c r="C11922" s="32" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="11923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11923" s="3"/>
       <c r="B11923" s="7"/>
-      <c r="C11923" s="35"/>
+      <c r="C11923" s="32"/>
     </row>
     <row r="11924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11924" s="3">
@@ -57923,7 +57926,7 @@
       <c r="A12045" s="25">
         <v>4.2</v>
       </c>
-      <c r="B12045" s="34" t="s">
+      <c r="B12045" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C12045" s="11" t="s">
@@ -57932,7 +57935,7 @@
     </row>
     <row r="12046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12046" s="25"/>
-      <c r="B12046" s="34"/>
+      <c r="B12046" s="35"/>
       <c r="C12046" s="11"/>
     </row>
     <row r="12047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57940,19 +57943,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12047" s="7"/>
-      <c r="C12047" s="35" t="s">
+      <c r="C12047" s="32" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="12048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12048" s="3"/>
       <c r="B12048" s="7"/>
-      <c r="C12048" s="35"/>
+      <c r="C12048" s="32"/>
     </row>
     <row r="12049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12049" s="3"/>
       <c r="B12049" s="7"/>
-      <c r="C12049" s="35"/>
+      <c r="C12049" s="32"/>
     </row>
     <row r="12050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12050" s="3">
@@ -58083,7 +58086,7 @@
       <c r="A12104" s="25">
         <v>4.2</v>
       </c>
-      <c r="B12104" s="34" t="s">
+      <c r="B12104" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C12104" s="11" t="s">
@@ -58092,7 +58095,7 @@
     </row>
     <row r="12105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12105" s="25"/>
-      <c r="B12105" s="34"/>
+      <c r="B12105" s="35"/>
       <c r="C12105" s="11"/>
     </row>
     <row r="12106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58100,19 +58103,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12106" s="7"/>
-      <c r="C12106" s="35" t="s">
+      <c r="C12106" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12107" s="3"/>
       <c r="B12107" s="7"/>
-      <c r="C12107" s="35"/>
+      <c r="C12107" s="32"/>
     </row>
     <row r="12108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12108" s="3"/>
       <c r="B12108" s="7"/>
-      <c r="C12108" s="35"/>
+      <c r="C12108" s="32"/>
     </row>
     <row r="12109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12109" s="3">
@@ -58145,10 +58148,10 @@
     </row>
     <row r="12153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12153" s="17"/>
-      <c r="B12153" s="32" t="s">
+      <c r="B12153" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C12153" s="33"/>
+      <c r="C12153" s="34"/>
     </row>
     <row r="12154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12154" s="5" t="s">
@@ -58243,7 +58246,7 @@
       <c r="A12163" s="23">
         <v>4.2</v>
       </c>
-      <c r="B12163" s="34" t="s">
+      <c r="B12163" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C12163" s="11" t="s">
@@ -58252,7 +58255,7 @@
     </row>
     <row r="12164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12164" s="23"/>
-      <c r="B12164" s="34"/>
+      <c r="B12164" s="35"/>
       <c r="C12164" s="11"/>
     </row>
     <row r="12165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58260,14 +58263,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12165" s="7"/>
-      <c r="C12165" s="35" t="s">
-        <v>625</v>
+      <c r="C12165" s="32" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="12166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12166" s="3"/>
       <c r="B12166" s="7"/>
-      <c r="C12166" s="35"/>
+      <c r="C12166" s="32"/>
     </row>
     <row r="12167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12167" s="3">
@@ -58289,7 +58292,7 @@
       <c r="A12169" s="23">
         <v>6.2</v>
       </c>
-      <c r="B12169" s="34" t="s">
+      <c r="B12169" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C12169" s="11" t="s">
@@ -58298,7 +58301,7 @@
     </row>
     <row r="12170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12170" s="23"/>
-      <c r="B12170" s="34"/>
+      <c r="B12170" s="35"/>
       <c r="C12170" s="11"/>
     </row>
     <row r="12171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58475,7 +58478,7 @@
       <c r="A12224" s="25">
         <v>5.2</v>
       </c>
-      <c r="B12224" s="34" t="s">
+      <c r="B12224" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C12224" s="8" t="s">
@@ -58484,7 +58487,7 @@
     </row>
     <row r="12225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12225" s="25"/>
-      <c r="B12225" s="34"/>
+      <c r="B12225" s="35"/>
       <c r="C12225" s="8"/>
     </row>
     <row r="12226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58492,19 +58495,19 @@
         <v>6.1</v>
       </c>
       <c r="B12226" s="7"/>
-      <c r="C12226" s="35" t="s">
+      <c r="C12226" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12227" s="3"/>
       <c r="B12227" s="7"/>
-      <c r="C12227" s="35"/>
+      <c r="C12227" s="32"/>
     </row>
     <row r="12228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12228" s="3"/>
       <c r="B12228" s="7"/>
-      <c r="C12228" s="35"/>
+      <c r="C12228" s="32"/>
     </row>
     <row r="12229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12229" s="3">
@@ -58642,10 +58645,10 @@
     </row>
     <row r="12330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12330" s="17"/>
-      <c r="B12330" s="32" t="s">
+      <c r="B12330" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C12330" s="33"/>
+      <c r="C12330" s="34"/>
     </row>
     <row r="12331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12331" s="5" t="s">
@@ -58816,7 +58819,7 @@
       <c r="A12350" s="25">
         <v>7.2</v>
       </c>
-      <c r="B12350" s="34" t="s">
+      <c r="B12350" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C12350" s="8" t="s">
@@ -58825,7 +58828,7 @@
     </row>
     <row r="12351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12351" s="25"/>
-      <c r="B12351" s="34"/>
+      <c r="B12351" s="35"/>
       <c r="C12351" s="8"/>
     </row>
     <row r="12352" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58833,19 +58836,19 @@
         <v>8.1</v>
       </c>
       <c r="B12352" s="7"/>
-      <c r="C12352" s="35" t="s">
+      <c r="C12352" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12353" s="3"/>
       <c r="B12353" s="7"/>
-      <c r="C12353" s="35"/>
+      <c r="C12353" s="32"/>
     </row>
     <row r="12354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12354" s="3"/>
       <c r="B12354" s="7"/>
-      <c r="C12354" s="35"/>
+      <c r="C12354" s="32"/>
     </row>
     <row r="12355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12355" s="3">
@@ -59020,19 +59023,19 @@
         <v>7.1</v>
       </c>
       <c r="B12404" s="7"/>
-      <c r="C12404" s="35" t="s">
+      <c r="C12404" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12405" s="3"/>
       <c r="B12405" s="7"/>
-      <c r="C12405" s="35"/>
+      <c r="C12405" s="32"/>
     </row>
     <row r="12406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12406" s="3"/>
       <c r="B12406" s="7"/>
-      <c r="C12406" s="35"/>
+      <c r="C12406" s="32"/>
     </row>
     <row r="12407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12407" s="3">
@@ -59065,10 +59068,10 @@
     </row>
     <row r="12448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12448" s="17"/>
-      <c r="B12448" s="32" t="s">
+      <c r="B12448" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C12448" s="33"/>
+      <c r="C12448" s="34"/>
     </row>
     <row r="12449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12449" s="5" t="s">
@@ -59223,7 +59226,7 @@
       <c r="A12466" s="25">
         <v>7.2</v>
       </c>
-      <c r="B12466" s="34" t="s">
+      <c r="B12466" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C12466" s="8" t="s">
@@ -59232,7 +59235,7 @@
     </row>
     <row r="12467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12467" s="25"/>
-      <c r="B12467" s="34"/>
+      <c r="B12467" s="35"/>
       <c r="C12467" s="8"/>
     </row>
     <row r="12468" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -59240,19 +59243,19 @@
         <v>8.1</v>
       </c>
       <c r="B12468" s="7"/>
-      <c r="C12468" s="35" t="s">
+      <c r="C12468" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12469" s="3"/>
       <c r="B12469" s="7"/>
-      <c r="C12469" s="35"/>
+      <c r="C12469" s="32"/>
     </row>
     <row r="12470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12470" s="3"/>
       <c r="B12470" s="7"/>
-      <c r="C12470" s="35"/>
+      <c r="C12470" s="32"/>
     </row>
     <row r="12471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12471" s="3">
@@ -59379,7 +59382,7 @@
       <c r="A12517" s="3">
         <v>4.2</v>
       </c>
-      <c r="B12517" s="35" t="s">
+      <c r="B12517" s="32" t="s">
         <v>537</v>
       </c>
       <c r="C12517" s="2" t="s">
@@ -59388,12 +59391,12 @@
     </row>
     <row r="12518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12518" s="3"/>
-      <c r="B12518" s="35"/>
+      <c r="B12518" s="32"/>
       <c r="C12518" s="2"/>
     </row>
     <row r="12519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12519" s="3"/>
-      <c r="B12519" s="35"/>
+      <c r="B12519" s="32"/>
       <c r="C12519" s="2"/>
     </row>
     <row r="12520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -59592,19 +59595,19 @@
         <v>6.1</v>
       </c>
       <c r="B12579" s="7"/>
-      <c r="C12579" s="35" t="s">
+      <c r="C12579" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12580" s="3"/>
       <c r="B12580" s="7"/>
-      <c r="C12580" s="35"/>
+      <c r="C12580" s="32"/>
     </row>
     <row r="12581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12581" s="3"/>
       <c r="B12581" s="7"/>
-      <c r="C12581" s="35"/>
+      <c r="C12581" s="32"/>
     </row>
     <row r="12582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12582" s="3">
@@ -59757,14 +59760,14 @@
         <v>6.1</v>
       </c>
       <c r="B12638" s="7"/>
-      <c r="C12638" s="35" t="s">
-        <v>587</v>
+      <c r="C12638" s="32" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="12639" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12639" s="3"/>
       <c r="B12639" s="7"/>
-      <c r="C12639" s="35"/>
+      <c r="C12639" s="32"/>
     </row>
     <row r="12640" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12640" s="3">
@@ -59849,10 +59852,10 @@
     </row>
     <row r="12684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12684" s="17"/>
-      <c r="B12684" s="32" t="s">
+      <c r="B12684" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C12684" s="33"/>
+      <c r="C12684" s="34"/>
     </row>
     <row r="12685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12685" s="5" t="s">
@@ -60013,7 +60016,7 @@
       <c r="A12702" s="25">
         <v>7.2</v>
       </c>
-      <c r="B12702" s="34" t="s">
+      <c r="B12702" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C12702" s="11" t="s">
@@ -60022,7 +60025,7 @@
     </row>
     <row r="12703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12703" s="25"/>
-      <c r="B12703" s="34"/>
+      <c r="B12703" s="35"/>
       <c r="C12703" s="11"/>
     </row>
     <row r="12704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60030,19 +60033,19 @@
         <v>8.1</v>
       </c>
       <c r="B12704" s="2"/>
-      <c r="C12704" s="35" t="s">
+      <c r="C12704" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12705" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12705" s="3"/>
       <c r="B12705" s="2"/>
-      <c r="C12705" s="35"/>
+      <c r="C12705" s="32"/>
     </row>
     <row r="12706" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12706" s="3"/>
       <c r="B12706" s="2"/>
-      <c r="C12706" s="35"/>
+      <c r="C12706" s="32"/>
     </row>
     <row r="12707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12707" s="3">
@@ -60302,7 +60305,7 @@
       <c r="A12818" s="25">
         <v>5.2</v>
       </c>
-      <c r="B12818" s="34" t="s">
+      <c r="B12818" s="35" t="s">
         <v>544</v>
       </c>
       <c r="C12818" s="11" t="s">
@@ -60311,7 +60314,7 @@
     </row>
     <row r="12819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12819" s="25"/>
-      <c r="B12819" s="34"/>
+      <c r="B12819" s="35"/>
       <c r="C12819" s="11"/>
     </row>
     <row r="12820" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60319,19 +60322,19 @@
         <v>6.1</v>
       </c>
       <c r="B12820" s="7"/>
-      <c r="C12820" s="35" t="s">
+      <c r="C12820" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12821" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12821" s="3"/>
       <c r="B12821" s="7"/>
-      <c r="C12821" s="35"/>
+      <c r="C12821" s="32"/>
     </row>
     <row r="12822" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12822" s="3"/>
       <c r="B12822" s="7"/>
-      <c r="C12822" s="35"/>
+      <c r="C12822" s="32"/>
     </row>
     <row r="12823" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12823" s="3">
@@ -60696,7 +60699,7 @@
       <c r="A12991" s="24">
         <v>5.2</v>
       </c>
-      <c r="B12991" s="35" t="s">
+      <c r="B12991" s="32" t="s">
         <v>552</v>
       </c>
       <c r="C12991" s="2" t="s">
@@ -60705,12 +60708,12 @@
     </row>
     <row r="12992" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12992" s="24"/>
-      <c r="B12992" s="35"/>
+      <c r="B12992" s="32"/>
       <c r="C12992" s="2"/>
     </row>
     <row r="12993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12993" s="24"/>
-      <c r="B12993" s="35"/>
+      <c r="B12993" s="32"/>
       <c r="C12993" s="2"/>
     </row>
     <row r="12994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60893,7 +60896,7 @@
       <c r="A13054" s="25">
         <v>5.2</v>
       </c>
-      <c r="B13054" s="34" t="s">
+      <c r="B13054" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C13054" s="11" t="s">
@@ -60902,7 +60905,7 @@
     </row>
     <row r="13055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13055" s="25"/>
-      <c r="B13055" s="34"/>
+      <c r="B13055" s="35"/>
       <c r="C13055" s="11"/>
     </row>
     <row r="13056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60910,19 +60913,19 @@
         <v>6.1</v>
       </c>
       <c r="B13056" s="2"/>
-      <c r="C13056" s="35" t="s">
+      <c r="C13056" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="13057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13057" s="3"/>
       <c r="B13057" s="2"/>
-      <c r="C13057" s="35"/>
+      <c r="C13057" s="32"/>
     </row>
     <row r="13058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13058" s="3"/>
       <c r="B13058" s="2"/>
-      <c r="C13058" s="35"/>
+      <c r="C13058" s="32"/>
     </row>
     <row r="13059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13059" s="3">
@@ -60955,10 +60958,10 @@
     </row>
     <row r="13097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13097" s="17"/>
-      <c r="B13097" s="32" t="s">
+      <c r="B13097" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C13097" s="33"/>
+      <c r="C13097" s="34"/>
     </row>
     <row r="13098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13098" s="5" t="s">
@@ -61081,7 +61084,7 @@
       <c r="A13111" s="23">
         <v>5.2</v>
       </c>
-      <c r="B13111" s="34" t="s">
+      <c r="B13111" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C13111" s="11" t="s">
@@ -61090,7 +61093,7 @@
     </row>
     <row r="13112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13112" s="23"/>
-      <c r="B13112" s="34"/>
+      <c r="B13112" s="35"/>
       <c r="C13112" s="11"/>
     </row>
     <row r="13113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -61098,14 +61101,14 @@
         <v>6.1</v>
       </c>
       <c r="B13113" s="7"/>
-      <c r="C13113" s="35" t="s">
-        <v>625</v>
+      <c r="C13113" s="32" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="13114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13114" s="3"/>
       <c r="B13114" s="7"/>
-      <c r="C13114" s="35"/>
+      <c r="C13114" s="32"/>
     </row>
     <row r="13115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13115" s="3">
@@ -61127,7 +61130,7 @@
       <c r="A13117" s="23">
         <v>7.2</v>
       </c>
-      <c r="B13117" s="34" t="s">
+      <c r="B13117" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C13117" s="11" t="s">
@@ -61136,7 +61139,7 @@
     </row>
     <row r="13118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13118" s="23"/>
-      <c r="B13118" s="34"/>
+      <c r="B13118" s="35"/>
       <c r="C13118" s="11"/>
     </row>
     <row r="13119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -61327,7 +61330,7 @@
       <c r="A13170" s="25">
         <v>5.2</v>
       </c>
-      <c r="B13170" s="34" t="s">
+      <c r="B13170" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C13170" s="11" t="s">
@@ -61336,7 +61339,7 @@
     </row>
     <row r="13171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13171" s="25"/>
-      <c r="B13171" s="34"/>
+      <c r="B13171" s="35"/>
       <c r="C13171" s="11"/>
     </row>
     <row r="13172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -61344,19 +61347,19 @@
         <v>6.1</v>
       </c>
       <c r="B13172" s="2"/>
-      <c r="C13172" s="35" t="s">
+      <c r="C13172" s="32" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="13173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13173" s="3"/>
       <c r="B13173" s="2"/>
-      <c r="C13173" s="35"/>
+      <c r="C13173" s="32"/>
     </row>
     <row r="13174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13174" s="3"/>
       <c r="B13174" s="2"/>
-      <c r="C13174" s="35"/>
+      <c r="C13174" s="32"/>
     </row>
     <row r="13175" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13175" s="3">
@@ -61461,19 +61464,19 @@
         <v>3.1</v>
       </c>
       <c r="B13222" s="7"/>
-      <c r="C13222" s="35" t="s">
+      <c r="C13222" s="32" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="13223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13223" s="3"/>
       <c r="B13223" s="7"/>
-      <c r="C13223" s="35"/>
+      <c r="C13223" s="32"/>
     </row>
     <row r="13224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13224" s="3"/>
       <c r="B13224" s="7"/>
-      <c r="C13224" s="35"/>
+      <c r="C13224" s="32"/>
     </row>
     <row r="13225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13225" s="3">
@@ -61506,10 +61509,10 @@
     </row>
     <row r="13274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13274" s="17"/>
-      <c r="B13274" s="32" t="s">
+      <c r="B13274" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C13274" s="33"/>
+      <c r="C13274" s="34"/>
     </row>
     <row r="13275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13275" s="5" t="s">
@@ -61990,7 +61993,7 @@
       </c>
       <c r="B13340" s="7"/>
       <c r="C13340" s="2" t="s">
-        <v>581</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -62013,7 +62016,7 @@
     </row>
     <row r="13391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13391" s="14" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B13391" s="15" t="s">
         <v>24</v>
@@ -62369,7 +62372,7 @@
     </row>
     <row r="13450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13450" s="14" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B13450" s="15" t="s">
         <v>15</v>
@@ -62486,19 +62489,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13462" s="7"/>
-      <c r="C13462" s="35" t="s">
-        <v>584</v>
+      <c r="C13462" s="32" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="13463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13463" s="3"/>
       <c r="B13463" s="7"/>
-      <c r="C13463" s="35"/>
+      <c r="C13463" s="32"/>
     </row>
     <row r="13464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13464" s="3"/>
       <c r="B13464" s="7"/>
-      <c r="C13464" s="35"/>
+      <c r="C13464" s="32"/>
     </row>
     <row r="13465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13465" s="3">
@@ -62520,7 +62523,7 @@
     </row>
     <row r="13509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13509" s="14" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B13509" s="15" t="s">
         <v>15</v>
@@ -62878,7 +62881,7 @@
     </row>
     <row r="13568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13568" s="14" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B13568" s="15" t="s">
         <v>19</v>
@@ -62995,14 +62998,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13580" s="7"/>
-      <c r="C13580" s="35" t="s">
-        <v>587</v>
+      <c r="C13580" s="32" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="13581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13581" s="3"/>
       <c r="B13581" s="7"/>
-      <c r="C13581" s="35"/>
+      <c r="C13581" s="32"/>
     </row>
     <row r="13582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13582" s="3">
@@ -63076,7 +63079,7 @@
     </row>
     <row r="13627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13627" s="14" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B13627" s="15" t="s">
         <v>6</v>
@@ -63235,7 +63238,7 @@
       <c r="A13644" s="25">
         <v>7.2</v>
       </c>
-      <c r="B13644" s="34" t="s">
+      <c r="B13644" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C13644" s="11" t="s">
@@ -63244,7 +63247,7 @@
     </row>
     <row r="13645" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13645" s="25"/>
-      <c r="B13645" s="34"/>
+      <c r="B13645" s="35"/>
       <c r="C13645" s="11"/>
     </row>
     <row r="13646" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63493,7 +63496,7 @@
     </row>
     <row r="13686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13686" s="14" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B13686" s="15" t="s">
         <v>22</v>
@@ -63556,14 +63559,14 @@
         <v>2.1</v>
       </c>
       <c r="B13692" s="7"/>
-      <c r="C13692" s="35" t="s">
-        <v>590</v>
+      <c r="C13692" s="32" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="13693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13693" s="3"/>
       <c r="B13693" s="7"/>
-      <c r="C13693" s="35"/>
+      <c r="C13693" s="32"/>
     </row>
     <row r="13694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13694" s="3">
@@ -63585,7 +63588,7 @@
     </row>
     <row r="13745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13745" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B13745" s="15" t="s">
         <v>22</v>
@@ -63909,7 +63912,7 @@
     </row>
     <row r="13804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13804" s="14" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B13804" s="15" t="s">
         <v>22</v>
@@ -63994,7 +63997,7 @@
     </row>
     <row r="13863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13863" s="14" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B13863" s="15" t="s">
         <v>15</v>
@@ -64068,7 +64071,7 @@
       </c>
       <c r="B13871" s="2"/>
       <c r="C13871" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64091,7 +64094,7 @@
     </row>
     <row r="13922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13922" s="14" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B13922" s="15" t="s">
         <v>24</v>
@@ -64200,7 +64203,7 @@
       <c r="A13933" s="25">
         <v>4.2</v>
       </c>
-      <c r="B13933" s="34" t="s">
+      <c r="B13933" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C13933" s="11" t="s">
@@ -64209,7 +64212,7 @@
     </row>
     <row r="13934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13934" s="25"/>
-      <c r="B13934" s="34"/>
+      <c r="B13934" s="35"/>
       <c r="C13934" s="11"/>
     </row>
     <row r="13935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64217,19 +64220,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13935" s="2"/>
-      <c r="C13935" s="35" t="s">
-        <v>584</v>
+      <c r="C13935" s="32" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="13936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13936" s="3"/>
       <c r="B13936" s="2"/>
-      <c r="C13936" s="35"/>
+      <c r="C13936" s="32"/>
     </row>
     <row r="13937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13937" s="3"/>
       <c r="B13937" s="2"/>
-      <c r="C13937" s="35"/>
+      <c r="C13937" s="32"/>
     </row>
     <row r="13938" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13938" s="3">
@@ -64251,7 +64254,7 @@
     </row>
     <row r="13981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13981" s="14" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B13981" s="15" t="s">
         <v>24</v>
@@ -64360,7 +64363,7 @@
       <c r="A13992" s="25">
         <v>4.2</v>
       </c>
-      <c r="B13992" s="34" t="s">
+      <c r="B13992" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C13992" s="11" t="s">
@@ -64369,7 +64372,7 @@
     </row>
     <row r="13993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13993" s="25"/>
-      <c r="B13993" s="34"/>
+      <c r="B13993" s="35"/>
       <c r="C13993" s="11"/>
     </row>
     <row r="13994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64618,7 +64621,7 @@
     </row>
     <row r="14040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14040" s="14" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B14040" s="15" t="s">
         <v>6</v>
@@ -64629,10 +64632,10 @@
     </row>
     <row r="14041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14041" s="17"/>
-      <c r="B14041" s="32" t="s">
+      <c r="B14041" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C14041" s="33"/>
+      <c r="C14041" s="34"/>
     </row>
     <row r="14042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14042" s="5" t="s">
@@ -64727,7 +64730,7 @@
       <c r="A14051" s="23">
         <v>4.2</v>
       </c>
-      <c r="B14051" s="34" t="s">
+      <c r="B14051" s="35" t="s">
         <v>514</v>
       </c>
       <c r="C14051" s="11" t="s">
@@ -64736,7 +64739,7 @@
     </row>
     <row r="14052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14052" s="23"/>
-      <c r="B14052" s="34"/>
+      <c r="B14052" s="35"/>
       <c r="C14052" s="11"/>
     </row>
     <row r="14053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64744,14 +64747,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B14053" s="7"/>
-      <c r="C14053" s="35" t="s">
-        <v>587</v>
+      <c r="C14053" s="32" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="14054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14054" s="3"/>
       <c r="B14054" s="7"/>
-      <c r="C14054" s="35"/>
+      <c r="C14054" s="32"/>
     </row>
     <row r="14055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14055" s="3">
@@ -64773,7 +64776,7 @@
       <c r="A14057" s="23">
         <v>6.2</v>
       </c>
-      <c r="B14057" s="34" t="s">
+      <c r="B14057" s="35" t="s">
         <v>515</v>
       </c>
       <c r="C14057" s="11" t="s">
@@ -64782,7 +64785,7 @@
     </row>
     <row r="14058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14058" s="23"/>
-      <c r="B14058" s="34"/>
+      <c r="B14058" s="35"/>
       <c r="C14058" s="11"/>
     </row>
     <row r="14059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64830,7 +64833,7 @@
     </row>
     <row r="14099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14099" s="14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B14099" s="15" t="s">
         <v>19</v>
@@ -64959,7 +64962,7 @@
       <c r="A14112" s="25">
         <v>5.2</v>
       </c>
-      <c r="B14112" s="34" t="s">
+      <c r="B14112" s="35" t="s">
         <v>343</v>
       </c>
       <c r="C14112" s="11" t="s">
@@ -64968,7 +64971,7 @@
     </row>
     <row r="14113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14113" s="25"/>
-      <c r="B14113" s="34"/>
+      <c r="B14113" s="35"/>
       <c r="C14113" s="11"/>
     </row>
     <row r="14114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65217,7 +65220,7 @@
     </row>
     <row r="14158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14158" s="14" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B14158" s="15" t="s">
         <v>22</v>
@@ -65261,7 +65264,7 @@
       </c>
       <c r="B14162" s="7"/>
       <c r="C14162" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65322,7 +65325,7 @@
     </row>
     <row r="14217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14217" s="14" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B14217" s="15" t="s">
         <v>19</v>
@@ -65333,10 +65336,10 @@
     </row>
     <row r="14218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14218" s="17"/>
-      <c r="B14218" s="32" t="s">
+      <c r="B14218" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C14218" s="33"/>
+      <c r="C14218" s="34"/>
     </row>
     <row r="14219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14219" s="5" t="s">
@@ -65507,7 +65510,7 @@
       <c r="A14238" s="25">
         <v>7.2</v>
       </c>
-      <c r="B14238" s="34" t="s">
+      <c r="B14238" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C14238" s="11" t="s">
@@ -65516,7 +65519,7 @@
     </row>
     <row r="14239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14239" s="25"/>
-      <c r="B14239" s="34"/>
+      <c r="B14239" s="35"/>
       <c r="C14239" s="11"/>
     </row>
     <row r="14240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65765,7 +65768,7 @@
     </row>
     <row r="14276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14276" s="14" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B14276" s="15" t="s">
         <v>19</v>
@@ -66159,7 +66162,7 @@
     </row>
     <row r="14335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14335" s="14" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B14335" s="15" t="s">
         <v>126</v>
@@ -66170,10 +66173,10 @@
     </row>
     <row r="14336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14336" s="17"/>
-      <c r="B14336" s="32" t="s">
+      <c r="B14336" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C14336" s="33"/>
+      <c r="C14336" s="34"/>
     </row>
     <row r="14337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14337" s="5" t="s">
@@ -66328,7 +66331,7 @@
       <c r="A14354" s="25">
         <v>7.2</v>
       </c>
-      <c r="B14354" s="34" t="s">
+      <c r="B14354" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C14354" s="11" t="s">
@@ -66337,7 +66340,7 @@
     </row>
     <row r="14355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14355" s="25"/>
-      <c r="B14355" s="34"/>
+      <c r="B14355" s="35"/>
       <c r="C14355" s="11"/>
     </row>
     <row r="14356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66586,7 +66589,7 @@
     </row>
     <row r="14394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14394" s="14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B14394" s="15" t="s">
         <v>19</v>
@@ -66598,7 +66601,7 @@
     <row r="14395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14395" s="17"/>
       <c r="B14395" s="18" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C14395" s="19"/>
     </row>
@@ -66731,7 +66734,7 @@
     </row>
     <row r="14453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14453" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B14453" s="15" t="s">
         <v>24</v>
@@ -67103,7 +67106,7 @@
     </row>
     <row r="14512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14512" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B14512" s="15" t="s">
         <v>6</v>
@@ -67114,10 +67117,10 @@
     </row>
     <row r="14513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14513" s="17"/>
-      <c r="B14513" s="32" t="s">
+      <c r="B14513" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C14513" s="33"/>
+      <c r="C14513" s="34"/>
     </row>
     <row r="14514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14514" s="5" t="s">
@@ -67234,14 +67237,14 @@
         <v>6.1</v>
       </c>
       <c r="B14526" s="7"/>
-      <c r="C14526" s="35" t="s">
-        <v>587</v>
+      <c r="C14526" s="32" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="14527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14527" s="3"/>
       <c r="B14527" s="7"/>
-      <c r="C14527" s="35"/>
+      <c r="C14527" s="32"/>
     </row>
     <row r="14528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14528" s="3">
@@ -67315,7 +67318,7 @@
     </row>
     <row r="14571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14571" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B14571" s="15" t="s">
         <v>6</v>
@@ -67326,10 +67329,10 @@
     </row>
     <row r="14572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14572" s="17"/>
-      <c r="B14572" s="32" t="s">
+      <c r="B14572" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C14572" s="33"/>
+      <c r="C14572" s="34"/>
     </row>
     <row r="14573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14573" s="5" t="s">
@@ -67743,7 +67746,7 @@
     </row>
     <row r="14630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14630" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B14630" s="15" t="s">
         <v>22</v>
@@ -67807,7 +67810,7 @@
       </c>
       <c r="B14636" s="7"/>
       <c r="C14636" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="14637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67830,7 +67833,7 @@
     </row>
     <row r="14689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14689" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B14689" s="15" t="s">
         <v>24</v>
@@ -67981,7 +67984,7 @@
       <c r="A14706" s="23">
         <v>5.2</v>
       </c>
-      <c r="B14706" s="34" t="s">
+      <c r="B14706" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C14706" s="11" t="s">
@@ -67990,7 +67993,7 @@
     </row>
     <row r="14707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14707" s="23"/>
-      <c r="B14707" s="34"/>
+      <c r="B14707" s="35"/>
       <c r="C14707" s="11"/>
     </row>
     <row r="14708" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68239,7 +68242,7 @@
     </row>
     <row r="14748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14748" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B14748" s="15" t="s">
         <v>24</v>
@@ -68350,14 +68353,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B14760" s="7"/>
-      <c r="C14760" s="35" t="s">
-        <v>613</v>
+      <c r="C14760" s="32" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="14761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14761" s="3"/>
       <c r="B14761" s="7"/>
-      <c r="C14761" s="35"/>
+      <c r="C14761" s="32"/>
     </row>
     <row r="14762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14762" s="3">
@@ -68379,7 +68382,7 @@
     </row>
     <row r="14807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14807" s="14" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B14807" s="15" t="s">
         <v>22</v>
@@ -68442,14 +68445,14 @@
         <v>2.1</v>
       </c>
       <c r="B14813" s="7"/>
-      <c r="C14813" s="35" t="s">
-        <v>615</v>
+      <c r="C14813" s="32" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="14814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14814" s="3"/>
       <c r="B14814" s="7"/>
-      <c r="C14814" s="35"/>
+      <c r="C14814" s="32"/>
     </row>
     <row r="14815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14815" s="3">
@@ -68471,7 +68474,7 @@
     </row>
     <row r="14866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14866" s="14" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B14866" s="15" t="s">
         <v>14</v>
@@ -68482,10 +68485,10 @@
     </row>
     <row r="14867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14867" s="17"/>
-      <c r="B14867" s="32" t="s">
-        <v>620</v>
-      </c>
-      <c r="C14867" s="33"/>
+      <c r="B14867" s="33" t="s">
+        <v>619</v>
+      </c>
+      <c r="C14867" s="34"/>
     </row>
     <row r="14868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14868" s="5" t="s">
@@ -68573,7 +68576,7 @@
       </c>
       <c r="B14876" s="7"/>
       <c r="C14876" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14877" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68593,14 +68596,14 @@
       </c>
       <c r="B14878" s="7"/>
       <c r="C14878" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14879" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14879" s="3"/>
       <c r="B14879" s="7"/>
       <c r="C14879" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14880" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68675,7 +68678,7 @@
     </row>
     <row r="14925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14925" s="14" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B14925" s="15" t="s">
         <v>24</v>
@@ -68826,7 +68829,7 @@
       <c r="A14942" s="25">
         <v>5.2</v>
       </c>
-      <c r="B14942" s="34" t="s">
+      <c r="B14942" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C14942" s="11" t="s">
@@ -68835,7 +68838,7 @@
     </row>
     <row r="14943" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14943" s="25"/>
-      <c r="B14943" s="34"/>
+      <c r="B14943" s="35"/>
       <c r="C14943" s="11"/>
     </row>
     <row r="14944" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69084,7 +69087,7 @@
     </row>
     <row r="14984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14984" s="14" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B14984" s="15" t="s">
         <v>126</v>
@@ -69095,10 +69098,10 @@
     </row>
     <row r="14985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14985" s="17"/>
-      <c r="B14985" s="32" t="s">
+      <c r="B14985" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C14985" s="33"/>
+      <c r="C14985" s="34"/>
     </row>
     <row r="14986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14986" s="5" t="s">
@@ -69221,7 +69224,7 @@
       <c r="A14999" s="23">
         <v>5.2</v>
       </c>
-      <c r="B14999" s="34" t="s">
+      <c r="B14999" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C14999" s="11" t="s">
@@ -69230,7 +69233,7 @@
     </row>
     <row r="15000" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15000" s="23"/>
-      <c r="B15000" s="34"/>
+      <c r="B15000" s="35"/>
       <c r="C15000" s="11"/>
     </row>
     <row r="15001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69238,14 +69241,14 @@
         <v>6.1</v>
       </c>
       <c r="B15001" s="7"/>
-      <c r="C15001" s="35" t="s">
-        <v>587</v>
+      <c r="C15001" s="32" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="15002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15002" s="3"/>
       <c r="B15002" s="7"/>
-      <c r="C15002" s="35"/>
+      <c r="C15002" s="32"/>
     </row>
     <row r="15003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15003" s="3">
@@ -69267,7 +69270,7 @@
       <c r="A15005" s="23">
         <v>7.2</v>
       </c>
-      <c r="B15005" s="34" t="s">
+      <c r="B15005" s="35" t="s">
         <v>344</v>
       </c>
       <c r="C15005" s="11" t="s">
@@ -69276,7 +69279,7 @@
     </row>
     <row r="15006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15006" s="23"/>
-      <c r="B15006" s="34"/>
+      <c r="B15006" s="35"/>
       <c r="C15006" s="11"/>
     </row>
     <row r="15007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69324,7 +69327,7 @@
     </row>
     <row r="15043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15043" s="14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B15043" s="15" t="s">
         <v>19</v>
@@ -69467,7 +69470,7 @@
       <c r="A15058" s="25">
         <v>5.2</v>
       </c>
-      <c r="B15058" s="34" t="s">
+      <c r="B15058" s="35" t="s">
         <v>342</v>
       </c>
       <c r="C15058" s="11" t="s">
@@ -69476,7 +69479,7 @@
     </row>
     <row r="15059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15059" s="25"/>
-      <c r="B15059" s="34"/>
+      <c r="B15059" s="35"/>
       <c r="C15059" s="11"/>
     </row>
     <row r="15060" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69725,6 +69728,320 @@
     </row>
   </sheetData>
   <mergeCells count="338">
+    <mergeCell ref="B14867:C14867"/>
+    <mergeCell ref="B14942:B14943"/>
+    <mergeCell ref="B14985:C14985"/>
+    <mergeCell ref="C15001:C15002"/>
+    <mergeCell ref="B14999:B15000"/>
+    <mergeCell ref="B15005:B15006"/>
+    <mergeCell ref="B15058:B15059"/>
+    <mergeCell ref="B14513:C14513"/>
+    <mergeCell ref="C14526:C14527"/>
+    <mergeCell ref="B14572:C14572"/>
+    <mergeCell ref="B14706:B14707"/>
+    <mergeCell ref="C14760:C14761"/>
+    <mergeCell ref="C14813:C14814"/>
+    <mergeCell ref="B14112:B14113"/>
+    <mergeCell ref="B14218:C14218"/>
+    <mergeCell ref="B14238:B14239"/>
+    <mergeCell ref="B14354:B14355"/>
+    <mergeCell ref="B14336:C14336"/>
+    <mergeCell ref="C13935:C13937"/>
+    <mergeCell ref="B13933:B13934"/>
+    <mergeCell ref="B13992:B13993"/>
+    <mergeCell ref="B14051:B14052"/>
+    <mergeCell ref="B14057:B14058"/>
+    <mergeCell ref="C14053:C14054"/>
+    <mergeCell ref="B14041:C14041"/>
+    <mergeCell ref="B13274:C13274"/>
+    <mergeCell ref="C13462:C13464"/>
+    <mergeCell ref="C13580:C13581"/>
+    <mergeCell ref="B13644:B13645"/>
+    <mergeCell ref="C13692:C13693"/>
+    <mergeCell ref="B13117:B13118"/>
+    <mergeCell ref="B13170:B13171"/>
+    <mergeCell ref="C13172:C13174"/>
+    <mergeCell ref="C13222:C13224"/>
+    <mergeCell ref="B12991:B12993"/>
+    <mergeCell ref="B13054:B13055"/>
+    <mergeCell ref="C13056:C13058"/>
+    <mergeCell ref="B13097:C13097"/>
+    <mergeCell ref="C13113:C13114"/>
+    <mergeCell ref="B13111:B13112"/>
+    <mergeCell ref="C12820:C12822"/>
+    <mergeCell ref="B12818:B12819"/>
+    <mergeCell ref="C12579:C12581"/>
+    <mergeCell ref="C12638:C12639"/>
+    <mergeCell ref="B12684:C12684"/>
+    <mergeCell ref="B12702:B12703"/>
+    <mergeCell ref="C12704:C12706"/>
+    <mergeCell ref="B12448:C12448"/>
+    <mergeCell ref="B12466:B12467"/>
+    <mergeCell ref="C12468:C12470"/>
+    <mergeCell ref="B12517:B12519"/>
+    <mergeCell ref="B12330:C12330"/>
+    <mergeCell ref="B12350:B12351"/>
+    <mergeCell ref="C12352:C12354"/>
+    <mergeCell ref="C12404:C12406"/>
+    <mergeCell ref="B725:B726"/>
+    <mergeCell ref="B4555:B4556"/>
+    <mergeCell ref="B6440:B6441"/>
+    <mergeCell ref="B10157:B10158"/>
+    <mergeCell ref="B10216:B10217"/>
+    <mergeCell ref="B10275:B10276"/>
+    <mergeCell ref="B4614:B4615"/>
+    <mergeCell ref="B4621:B4622"/>
+    <mergeCell ref="B6506:B6507"/>
+    <mergeCell ref="B6499:B6500"/>
+    <mergeCell ref="B8269:B8270"/>
+    <mergeCell ref="B8328:B8329"/>
+    <mergeCell ref="B8387:B8388"/>
+    <mergeCell ref="B9213:B9214"/>
+    <mergeCell ref="C12106:C12108"/>
+    <mergeCell ref="B12153:C12153"/>
+    <mergeCell ref="B720:B721"/>
+    <mergeCell ref="B838:B839"/>
+    <mergeCell ref="B845:B846"/>
+    <mergeCell ref="B1664:B1665"/>
+    <mergeCell ref="B1670:B1671"/>
+    <mergeCell ref="B2726:B2727"/>
+    <mergeCell ref="B2733:B2734"/>
+    <mergeCell ref="B2608:B2609"/>
+    <mergeCell ref="B2667:B2668"/>
+    <mergeCell ref="C12165:C12166"/>
+    <mergeCell ref="B12224:B12225"/>
+    <mergeCell ref="C12226:C12228"/>
+    <mergeCell ref="B779:B780"/>
+    <mergeCell ref="B12045:B12046"/>
+    <mergeCell ref="B12104:B12105"/>
+    <mergeCell ref="B12169:B12170"/>
+    <mergeCell ref="B12163:B12164"/>
+    <mergeCell ref="C11804:C11805"/>
+    <mergeCell ref="C11865:C11867"/>
+    <mergeCell ref="C11922:C11923"/>
+    <mergeCell ref="C12047:C12049"/>
+    <mergeCell ref="C11633:C11635"/>
+    <mergeCell ref="C11692:C11693"/>
+    <mergeCell ref="B11681:C11681"/>
+    <mergeCell ref="C11758:C11760"/>
+    <mergeCell ref="B11756:B11757"/>
+    <mergeCell ref="C11334:C11336"/>
+    <mergeCell ref="B11386:C11386"/>
+    <mergeCell ref="C11404:C11406"/>
+    <mergeCell ref="C11515:C11517"/>
+    <mergeCell ref="C11574:C11576"/>
+    <mergeCell ref="B11166:B11167"/>
+    <mergeCell ref="C11168:C11169"/>
+    <mergeCell ref="B11225:B11226"/>
+    <mergeCell ref="C11227:C11228"/>
+    <mergeCell ref="B11282:B11283"/>
+    <mergeCell ref="C11284:C11285"/>
+    <mergeCell ref="B10930:B10931"/>
+    <mergeCell ref="C10932:C10933"/>
+    <mergeCell ref="C10978:C10979"/>
+    <mergeCell ref="C11037:C11038"/>
+    <mergeCell ref="B11107:B11108"/>
+    <mergeCell ref="C11109:C11110"/>
+    <mergeCell ref="C10816:C10817"/>
+    <mergeCell ref="B10814:B10815"/>
+    <mergeCell ref="B10796:C10796"/>
+    <mergeCell ref="B10578:B10579"/>
+    <mergeCell ref="C10580:C10581"/>
+    <mergeCell ref="C10632:C10633"/>
+    <mergeCell ref="C10691:C10692"/>
+    <mergeCell ref="C10750:C10751"/>
+    <mergeCell ref="B10462:B10463"/>
+    <mergeCell ref="C10464:C10465"/>
+    <mergeCell ref="B10442:C10442"/>
+    <mergeCell ref="C10516:C10517"/>
+    <mergeCell ref="B10560:C10560"/>
+    <mergeCell ref="C10159:C10160"/>
+    <mergeCell ref="C10218:C10219"/>
+    <mergeCell ref="B10336:B10337"/>
+    <mergeCell ref="C10338:C10339"/>
+    <mergeCell ref="C9916:C9917"/>
+    <mergeCell ref="C10277:C10278"/>
+    <mergeCell ref="C9870:C9871"/>
+    <mergeCell ref="B9868:B9869"/>
+    <mergeCell ref="C9977:C9978"/>
+    <mergeCell ref="C10034:C10035"/>
+    <mergeCell ref="C9564:C9565"/>
+    <mergeCell ref="C9627:C9628"/>
+    <mergeCell ref="C9686:C9687"/>
+    <mergeCell ref="C9745:C9746"/>
+    <mergeCell ref="C9804:C9805"/>
+    <mergeCell ref="C9149:C9150"/>
+    <mergeCell ref="B9276:B9277"/>
+    <mergeCell ref="B9335:B9336"/>
+    <mergeCell ref="B9394:B9395"/>
+    <mergeCell ref="C9446:C9447"/>
+    <mergeCell ref="B9498:C9498"/>
+    <mergeCell ref="C9516:C9517"/>
+    <mergeCell ref="B8926:B8927"/>
+    <mergeCell ref="B8908:C8908"/>
+    <mergeCell ref="C8972:C8973"/>
+    <mergeCell ref="B9040:B9041"/>
+    <mergeCell ref="C8146:C8147"/>
+    <mergeCell ref="B8572:B8573"/>
+    <mergeCell ref="B8554:C8554"/>
+    <mergeCell ref="B8690:B8691"/>
+    <mergeCell ref="B8672:C8672"/>
+    <mergeCell ref="B5781:C5781"/>
+    <mergeCell ref="B7610:C7610"/>
+    <mergeCell ref="B7669:C7669"/>
+    <mergeCell ref="B7980:B7981"/>
+    <mergeCell ref="C8028:C8029"/>
+    <mergeCell ref="B6961:C6961"/>
+    <mergeCell ref="C6974:C6976"/>
+    <mergeCell ref="B7020:C7020"/>
+    <mergeCell ref="B6784:C6784"/>
+    <mergeCell ref="B6802:B6803"/>
+    <mergeCell ref="B6666:C6666"/>
+    <mergeCell ref="B6686:B6687"/>
+    <mergeCell ref="B6560:B6561"/>
+    <mergeCell ref="C3676:C3678"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3383:C3384"/>
+    <mergeCell ref="C3429:C3430"/>
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="C3966:C3967"/>
+    <mergeCell ref="C3854:C3855"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3719:C3719"/>
+    <mergeCell ref="C3735:C3736"/>
+    <mergeCell ref="B3616:B3617"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="C3267:C3268"/>
+    <mergeCell ref="C3142:C3143"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3201:C3203"/>
+    <mergeCell ref="C3560:C3562"/>
+    <mergeCell ref="B3558:B3559"/>
+    <mergeCell ref="C3618:C3619"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="B1729:B1730"/>
+    <mergeCell ref="C781:C782"/>
+    <mergeCell ref="B1477:C1477"/>
+    <mergeCell ref="C1495:C1496"/>
+    <mergeCell ref="C1313:C1315"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="C1379:C1380"/>
+    <mergeCell ref="A27:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C249:C250"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A141:C146"/>
+    <mergeCell ref="A147:C147"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="C597:C598"/>
+    <mergeCell ref="C308:C309"/>
+    <mergeCell ref="C367:C369"/>
+    <mergeCell ref="C433:C434"/>
+    <mergeCell ref="C540:C541"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="C1254:C1255"/>
+    <mergeCell ref="C1144:C1145"/>
+    <mergeCell ref="C1541:C1542"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="C1666:C1667"/>
+    <mergeCell ref="C840:C842"/>
+    <mergeCell ref="C901:C902"/>
+    <mergeCell ref="C1193:C1194"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="C1027:C1028"/>
+    <mergeCell ref="B1005:C1005"/>
+    <mergeCell ref="C1079:C1080"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="C3031:C3032"/>
+    <mergeCell ref="C3083:C3085"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="C1848:C1849"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="C1731:C1732"/>
+    <mergeCell ref="C1789:C1791"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="C2915:C2916"/>
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="C2967:C2968"/>
+    <mergeCell ref="C2428:C2429"/>
+    <mergeCell ref="C2485:C2487"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2728:C2730"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2789:C2790"/>
+    <mergeCell ref="B2539:C2539"/>
+    <mergeCell ref="C2610:C2612"/>
+    <mergeCell ref="C2669:C2670"/>
+    <mergeCell ref="C2321:C2322"/>
+    <mergeCell ref="C2255:C2257"/>
+    <mergeCell ref="C2137:C2139"/>
+    <mergeCell ref="C2196:C2197"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B2303:C2303"/>
+    <mergeCell ref="C1966:C1967"/>
+    <mergeCell ref="B2008:C2008"/>
+    <mergeCell ref="C2078:C2079"/>
+    <mergeCell ref="C4316:C4317"/>
+    <mergeCell ref="C4373:C4374"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="C4209:C4210"/>
+    <mergeCell ref="C4084:C4085"/>
+    <mergeCell ref="B4073:C4073"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="C4143:C4145"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="B431:B432"/>
+    <mergeCell ref="B2319:B2320"/>
+    <mergeCell ref="B4207:B4208"/>
+    <mergeCell ref="B6092:B6093"/>
+    <mergeCell ref="B1025:B1026"/>
+    <mergeCell ref="B2913:B2914"/>
+    <mergeCell ref="B4801:B4802"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B3265:B3266"/>
+    <mergeCell ref="B5153:B5154"/>
+    <mergeCell ref="B899:B900"/>
+    <mergeCell ref="B2787:B2788"/>
+    <mergeCell ref="B4675:B4676"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1142:B1143"/>
+    <mergeCell ref="B3029:B3030"/>
+    <mergeCell ref="B4917:B4918"/>
+    <mergeCell ref="B6076:C6076"/>
+    <mergeCell ref="B5722:C5722"/>
+    <mergeCell ref="C5561:C5563"/>
+    <mergeCell ref="B5604:C5604"/>
+    <mergeCell ref="C5620:C5621"/>
+    <mergeCell ref="B5663:C5663"/>
+    <mergeCell ref="B5427:C5427"/>
+    <mergeCell ref="B1794:B1795"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B3681:B3682"/>
+    <mergeCell ref="B3674:B3675"/>
+    <mergeCell ref="B5559:B5560"/>
+    <mergeCell ref="B3381:B3382"/>
+    <mergeCell ref="B5266:B5267"/>
+    <mergeCell ref="B5545:C5545"/>
+    <mergeCell ref="C5155:C5156"/>
+    <mergeCell ref="C5268:C5269"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5089:C5091"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="C5030:C5031"/>
+    <mergeCell ref="C4855:C4856"/>
+    <mergeCell ref="C4919:C4920"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4677:C4678"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="B1846:B1847"/>
+    <mergeCell ref="B3733:B3734"/>
+    <mergeCell ref="C5504:C5505"/>
+    <mergeCell ref="B4663:C4663"/>
     <mergeCell ref="C4803:C4804"/>
     <mergeCell ref="C4557:C4558"/>
     <mergeCell ref="C4616:C4618"/>
@@ -69749,320 +70066,6 @@
     <mergeCell ref="C6028:C6030"/>
     <mergeCell ref="C6146:C6147"/>
     <mergeCell ref="B5502:B5503"/>
-    <mergeCell ref="B1794:B1795"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B3681:B3682"/>
-    <mergeCell ref="B3674:B3675"/>
-    <mergeCell ref="B5559:B5560"/>
-    <mergeCell ref="B3381:B3382"/>
-    <mergeCell ref="B5266:B5267"/>
-    <mergeCell ref="B5545:C5545"/>
-    <mergeCell ref="C5155:C5156"/>
-    <mergeCell ref="C5268:C5269"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5089:C5091"/>
-    <mergeCell ref="B4958:C4958"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="C5030:C5031"/>
-    <mergeCell ref="C4855:C4856"/>
-    <mergeCell ref="C4919:C4920"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4677:C4678"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="B1846:B1847"/>
-    <mergeCell ref="B3733:B3734"/>
-    <mergeCell ref="C5504:C5505"/>
-    <mergeCell ref="B431:B432"/>
-    <mergeCell ref="B2319:B2320"/>
-    <mergeCell ref="B4207:B4208"/>
-    <mergeCell ref="B6092:B6093"/>
-    <mergeCell ref="B1025:B1026"/>
-    <mergeCell ref="B2913:B2914"/>
-    <mergeCell ref="B4801:B4802"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B3265:B3266"/>
-    <mergeCell ref="B5153:B5154"/>
-    <mergeCell ref="B899:B900"/>
-    <mergeCell ref="B2787:B2788"/>
-    <mergeCell ref="B4675:B4676"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="B1142:B1143"/>
-    <mergeCell ref="B3029:B3030"/>
-    <mergeCell ref="B4917:B4918"/>
-    <mergeCell ref="B6076:C6076"/>
-    <mergeCell ref="B5722:C5722"/>
-    <mergeCell ref="C5561:C5563"/>
-    <mergeCell ref="B5604:C5604"/>
-    <mergeCell ref="C5620:C5621"/>
-    <mergeCell ref="B5663:C5663"/>
-    <mergeCell ref="B5427:C5427"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4316:C4317"/>
-    <mergeCell ref="C4373:C4374"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="C4209:C4210"/>
-    <mergeCell ref="C4084:C4085"/>
-    <mergeCell ref="B4073:C4073"/>
-    <mergeCell ref="B4132:C4132"/>
-    <mergeCell ref="C4143:C4145"/>
-    <mergeCell ref="B4014:C4014"/>
-    <mergeCell ref="C4025:C4026"/>
-    <mergeCell ref="C2321:C2322"/>
-    <mergeCell ref="C2255:C2257"/>
-    <mergeCell ref="C2137:C2139"/>
-    <mergeCell ref="C2196:C2197"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B2303:C2303"/>
-    <mergeCell ref="C1966:C1967"/>
-    <mergeCell ref="B2008:C2008"/>
-    <mergeCell ref="C2078:C2079"/>
-    <mergeCell ref="C2428:C2429"/>
-    <mergeCell ref="C2485:C2487"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2728:C2730"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2789:C2790"/>
-    <mergeCell ref="B2539:C2539"/>
-    <mergeCell ref="C2610:C2612"/>
-    <mergeCell ref="C2669:C2670"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="C3031:C3032"/>
-    <mergeCell ref="C3083:C3085"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="C1848:C1849"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="C1731:C1732"/>
-    <mergeCell ref="C1789:C1791"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="C1541:C1542"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="C1666:C1667"/>
-    <mergeCell ref="C840:C842"/>
-    <mergeCell ref="C901:C902"/>
-    <mergeCell ref="C1193:C1194"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="C1027:C1028"/>
-    <mergeCell ref="B1005:C1005"/>
-    <mergeCell ref="C1079:C1080"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="C781:C782"/>
-    <mergeCell ref="B1477:C1477"/>
-    <mergeCell ref="C1495:C1496"/>
-    <mergeCell ref="C1313:C1315"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="C1379:C1380"/>
-    <mergeCell ref="A27:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="C249:C250"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A141:C146"/>
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="C597:C598"/>
-    <mergeCell ref="C308:C309"/>
-    <mergeCell ref="C367:C369"/>
-    <mergeCell ref="C433:C434"/>
-    <mergeCell ref="C540:C541"/>
-    <mergeCell ref="B1300:C1300"/>
-    <mergeCell ref="C1254:C1255"/>
-    <mergeCell ref="C1144:C1145"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="C2915:C2916"/>
-    <mergeCell ref="B2952:C2952"/>
-    <mergeCell ref="C2967:C2968"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="C3267:C3268"/>
-    <mergeCell ref="C3142:C3143"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3201:C3203"/>
-    <mergeCell ref="C3560:C3562"/>
-    <mergeCell ref="B3558:B3559"/>
-    <mergeCell ref="C3618:C3619"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="C3676:C3678"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3383:C3384"/>
-    <mergeCell ref="C3429:C3430"/>
-    <mergeCell ref="B3955:C3955"/>
-    <mergeCell ref="C3966:C3967"/>
-    <mergeCell ref="C3854:C3855"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3719:C3719"/>
-    <mergeCell ref="C3735:C3736"/>
-    <mergeCell ref="B3616:B3617"/>
-    <mergeCell ref="C8146:C8147"/>
-    <mergeCell ref="B8572:B8573"/>
-    <mergeCell ref="B8554:C8554"/>
-    <mergeCell ref="B8690:B8691"/>
-    <mergeCell ref="B8672:C8672"/>
-    <mergeCell ref="B5781:C5781"/>
-    <mergeCell ref="B7610:C7610"/>
-    <mergeCell ref="B7669:C7669"/>
-    <mergeCell ref="B7980:B7981"/>
-    <mergeCell ref="C8028:C8029"/>
-    <mergeCell ref="B6961:C6961"/>
-    <mergeCell ref="C6974:C6976"/>
-    <mergeCell ref="B7020:C7020"/>
-    <mergeCell ref="B6784:C6784"/>
-    <mergeCell ref="B6802:B6803"/>
-    <mergeCell ref="B6666:C6666"/>
-    <mergeCell ref="B6686:B6687"/>
-    <mergeCell ref="B6560:B6561"/>
-    <mergeCell ref="C9149:C9150"/>
-    <mergeCell ref="B9276:B9277"/>
-    <mergeCell ref="B9335:B9336"/>
-    <mergeCell ref="B9394:B9395"/>
-    <mergeCell ref="C9446:C9447"/>
-    <mergeCell ref="B9498:C9498"/>
-    <mergeCell ref="C9516:C9517"/>
-    <mergeCell ref="B8926:B8927"/>
-    <mergeCell ref="B8908:C8908"/>
-    <mergeCell ref="C8972:C8973"/>
-    <mergeCell ref="B9040:B9041"/>
-    <mergeCell ref="C9870:C9871"/>
-    <mergeCell ref="B9868:B9869"/>
-    <mergeCell ref="C9977:C9978"/>
-    <mergeCell ref="C10034:C10035"/>
-    <mergeCell ref="C9564:C9565"/>
-    <mergeCell ref="C9627:C9628"/>
-    <mergeCell ref="C9686:C9687"/>
-    <mergeCell ref="C9745:C9746"/>
-    <mergeCell ref="C9804:C9805"/>
-    <mergeCell ref="B10442:C10442"/>
-    <mergeCell ref="C10516:C10517"/>
-    <mergeCell ref="B10560:C10560"/>
-    <mergeCell ref="C10159:C10160"/>
-    <mergeCell ref="C10218:C10219"/>
-    <mergeCell ref="B10336:B10337"/>
-    <mergeCell ref="C10338:C10339"/>
-    <mergeCell ref="C9916:C9917"/>
-    <mergeCell ref="C10277:C10278"/>
-    <mergeCell ref="C10816:C10817"/>
-    <mergeCell ref="B10814:B10815"/>
-    <mergeCell ref="B10796:C10796"/>
-    <mergeCell ref="B10578:B10579"/>
-    <mergeCell ref="C10580:C10581"/>
-    <mergeCell ref="C10632:C10633"/>
-    <mergeCell ref="C10691:C10692"/>
-    <mergeCell ref="C10750:C10751"/>
-    <mergeCell ref="B10462:B10463"/>
-    <mergeCell ref="C10464:C10465"/>
-    <mergeCell ref="B11225:B11226"/>
-    <mergeCell ref="C11227:C11228"/>
-    <mergeCell ref="B11282:B11283"/>
-    <mergeCell ref="C11284:C11285"/>
-    <mergeCell ref="B10930:B10931"/>
-    <mergeCell ref="C10932:C10933"/>
-    <mergeCell ref="C10978:C10979"/>
-    <mergeCell ref="C11037:C11038"/>
-    <mergeCell ref="B11107:B11108"/>
-    <mergeCell ref="C11109:C11110"/>
-    <mergeCell ref="C12165:C12166"/>
-    <mergeCell ref="B12224:B12225"/>
-    <mergeCell ref="C12226:C12228"/>
-    <mergeCell ref="B779:B780"/>
-    <mergeCell ref="B12045:B12046"/>
-    <mergeCell ref="B12104:B12105"/>
-    <mergeCell ref="B12169:B12170"/>
-    <mergeCell ref="B12163:B12164"/>
-    <mergeCell ref="C11804:C11805"/>
-    <mergeCell ref="C11865:C11867"/>
-    <mergeCell ref="C11922:C11923"/>
-    <mergeCell ref="C12047:C12049"/>
-    <mergeCell ref="C11633:C11635"/>
-    <mergeCell ref="C11692:C11693"/>
-    <mergeCell ref="B11681:C11681"/>
-    <mergeCell ref="C11758:C11760"/>
-    <mergeCell ref="B11756:B11757"/>
-    <mergeCell ref="C11334:C11336"/>
-    <mergeCell ref="B11386:C11386"/>
-    <mergeCell ref="C11404:C11406"/>
-    <mergeCell ref="C11515:C11517"/>
-    <mergeCell ref="C11574:C11576"/>
-    <mergeCell ref="B11166:B11167"/>
-    <mergeCell ref="C11168:C11169"/>
-    <mergeCell ref="B720:B721"/>
-    <mergeCell ref="B838:B839"/>
-    <mergeCell ref="B845:B846"/>
-    <mergeCell ref="B1664:B1665"/>
-    <mergeCell ref="B1670:B1671"/>
-    <mergeCell ref="B2726:B2727"/>
-    <mergeCell ref="B2733:B2734"/>
-    <mergeCell ref="B2608:B2609"/>
-    <mergeCell ref="B2667:B2668"/>
-    <mergeCell ref="B12448:C12448"/>
-    <mergeCell ref="B12466:B12467"/>
-    <mergeCell ref="C12468:C12470"/>
-    <mergeCell ref="B12517:B12519"/>
-    <mergeCell ref="B12330:C12330"/>
-    <mergeCell ref="B12350:B12351"/>
-    <mergeCell ref="C12352:C12354"/>
-    <mergeCell ref="C12404:C12406"/>
-    <mergeCell ref="B725:B726"/>
-    <mergeCell ref="B4555:B4556"/>
-    <mergeCell ref="B6440:B6441"/>
-    <mergeCell ref="B10157:B10158"/>
-    <mergeCell ref="B10216:B10217"/>
-    <mergeCell ref="B10275:B10276"/>
-    <mergeCell ref="B4614:B4615"/>
-    <mergeCell ref="B4621:B4622"/>
-    <mergeCell ref="B6506:B6507"/>
-    <mergeCell ref="B6499:B6500"/>
-    <mergeCell ref="B8269:B8270"/>
-    <mergeCell ref="B8328:B8329"/>
-    <mergeCell ref="B8387:B8388"/>
-    <mergeCell ref="B9213:B9214"/>
-    <mergeCell ref="C12106:C12108"/>
-    <mergeCell ref="B12153:C12153"/>
-    <mergeCell ref="B12991:B12993"/>
-    <mergeCell ref="B13054:B13055"/>
-    <mergeCell ref="C13056:C13058"/>
-    <mergeCell ref="B13097:C13097"/>
-    <mergeCell ref="C13113:C13114"/>
-    <mergeCell ref="B13111:B13112"/>
-    <mergeCell ref="C12820:C12822"/>
-    <mergeCell ref="B12818:B12819"/>
-    <mergeCell ref="C12579:C12581"/>
-    <mergeCell ref="C12638:C12639"/>
-    <mergeCell ref="B12684:C12684"/>
-    <mergeCell ref="B12702:B12703"/>
-    <mergeCell ref="C12704:C12706"/>
-    <mergeCell ref="B13274:C13274"/>
-    <mergeCell ref="C13462:C13464"/>
-    <mergeCell ref="C13580:C13581"/>
-    <mergeCell ref="B13644:B13645"/>
-    <mergeCell ref="C13692:C13693"/>
-    <mergeCell ref="B13117:B13118"/>
-    <mergeCell ref="B13170:B13171"/>
-    <mergeCell ref="C13172:C13174"/>
-    <mergeCell ref="C13222:C13224"/>
-    <mergeCell ref="B14112:B14113"/>
-    <mergeCell ref="B14218:C14218"/>
-    <mergeCell ref="B14238:B14239"/>
-    <mergeCell ref="B14354:B14355"/>
-    <mergeCell ref="B14336:C14336"/>
-    <mergeCell ref="C13935:C13937"/>
-    <mergeCell ref="B13933:B13934"/>
-    <mergeCell ref="B13992:B13993"/>
-    <mergeCell ref="B14051:B14052"/>
-    <mergeCell ref="B14057:B14058"/>
-    <mergeCell ref="C14053:C14054"/>
-    <mergeCell ref="B14041:C14041"/>
-    <mergeCell ref="B14867:C14867"/>
-    <mergeCell ref="B14942:B14943"/>
-    <mergeCell ref="B14985:C14985"/>
-    <mergeCell ref="C15001:C15002"/>
-    <mergeCell ref="B14999:B15000"/>
-    <mergeCell ref="B15005:B15006"/>
-    <mergeCell ref="B15058:B15059"/>
-    <mergeCell ref="B14513:C14513"/>
-    <mergeCell ref="C14526:C14527"/>
-    <mergeCell ref="B14572:C14572"/>
-    <mergeCell ref="B14706:B14707"/>
-    <mergeCell ref="C14760:C14761"/>
-    <mergeCell ref="C14813:C14814"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
